--- a/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C965C1F-E0C3-4D76-AE0B-EC524367511F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD0EFE1-7790-4DF9-BE23-6865B8072516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6409,37 +6409,109 @@
     <t>co2_Anqing_CHN</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_Shaoguan_CHN_ge400mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104365-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115523_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Shaoguan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Tongling_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115454_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000105105_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107982_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103003_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Anqing_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101467_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Beichengqu_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Fuzhou_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Hangzhou_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111650_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115437_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115489_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Changzhou_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115373_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000109191_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115490_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103478_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104066_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107983_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115297_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Yangjiang_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Rizhao_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Wuan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_ultra-supercritical_G100000105137_ccs-rf</t>
   </si>
   <si>
+    <t>ep_coal_ultra-supercritical_G100000114266_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_c_coal_ultra-supercritical_G100000114532_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_ultra-supercritical_G100000114266_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_ultra-supercritical_Zouping_CHN_ge300mw-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_subcritical_Shaoguan_CHN_ge300mw-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_subcritical_Rizhao_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105105_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103003_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115454_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107982_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Wuan_CHN_ge300mw-CHP_ccs-rf</t>
+    <t>ep_coal_supercritical_Liuzhou_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_CHN45p9N129p3E_CHN_ge300mw-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_ultra-supercritical_G100000109190_ccs-rf</t>
@@ -6448,1813 +6520,1741 @@
     <t>ep_c_coal_ultra-supercritical_G100000115851_ccs-rf</t>
   </si>
   <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115811_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104105_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_CHN45p9N129p3E_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yingchuan_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109118_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102034-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Yicheng_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109859_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Luohe_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yakeshi_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yangzhou_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103166_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100001000191-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CCS_G100000103395_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106819_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101757_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106502_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109010-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Fuzhou_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103385_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Wulan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106459_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Ningde_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000100712_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102943_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Jingling_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Hejin_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109218_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000114302_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Anshun_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_CCS_Hangzhou_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Shahezhai_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yiyang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115477_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Nanjing_CHN_ge400mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115817_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115841_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Putian_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Tongling_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000103364_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103153_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000114365_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Hejin_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101368_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_CHN44p7N89p1E_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115390_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101367_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115348_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Tongshan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115448_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101789_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104520_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Nantong_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CCS_G100000107469_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115313_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104073-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110695_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Nanjing_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Xiaoyi_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111005_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110262-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104169_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Yuanquan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103784-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yingchuan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Linyi_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000108246_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_CCS_G100001000353-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101468_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000114703_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Wulan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Changzhou_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103293_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000109862_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109861_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Shijiazhuang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104418_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107477-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_CCS_G100001000354-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Wuhan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Yicheng_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CCS_G100000104640_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000111314_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000104144_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Tangshan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Xiaoyi_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102033-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Luohe_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Anshun_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Liaoyang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115716_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115844_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115391_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115559_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000102229_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Mianyang_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Fangchenggang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103151_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Shaoguan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103384_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yangjiang_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000112939_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Fuzhou_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Yangzhou_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115474_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Sizhan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103167_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Changzhou_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Tianjin_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Hangzhou_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110112-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Yiyang_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104503_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104076-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Xiaoxita_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Chongqing_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102813_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Jingling_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Wulan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Hohhot_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Tangshan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115372_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110694_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_ZhongdongShequ_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111817_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Liaoyang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115825-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_CHN44p7N89p1E_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115495_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115952_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Fangchenggang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115826-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000113225_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Beichengqu_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103882_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_CHN45p9N129p3E_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Yanggezhuang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Qabqa_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115813_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115476_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103394_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106354_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Beichengqu_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Wuan_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000114702_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Zouping_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115347_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115731_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101756_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111453_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Qabqa_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110114-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115450_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111006_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Rizhao_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104519_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115447_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111602-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Yangzhou_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100001000279_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Ningde_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_CCS_G100001000355-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Wuhan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Zouping_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103867_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000114710_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Xiaoyi_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000105096_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106309_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101768_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000114746_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Xiaoxita_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110134_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115400_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Yuanquan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Shanghai_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115880_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Yingchuan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Fangchenggang_CHN_ge400mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110113-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000109192_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Putian_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Tongshan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Rizhao_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115560_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115521_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Hohhot_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Changzhou_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104367-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103479_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Beichengqu_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Anshun_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_CHN44p7N89p1E_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yicheng_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109117_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Luohe_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CHN44p2N116p5E_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yanggezhuang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000108347_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111200_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000114202_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103152_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000104143_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115653_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111818_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000100234_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000103363_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111479_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109207_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103868_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Anshan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Chongqing_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101335_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109656-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000111313_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_ultra-supercritical_Jingling_CHN_ge300mw_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_ultra-supercritical_G100000101467_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Tangshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104365-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115523_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Shaoguan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Tongling_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104105_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115811_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CHN45p9N129p3E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115437_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115489_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Changzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Fuzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Hangzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Liuzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CHN45p9N129p3E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115373_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103478_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104066_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107983_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000109191_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115297_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115490_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shaoguan_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114702_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Tongling_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Zouping_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105096_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106309_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_CCS_G100001000355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Zouping_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111453_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Qabqa_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103867_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114710_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Xiaoyi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111006_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115450_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110114-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Xiaoyi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Xiaoxita_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115880_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115731_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115347_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101756_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110134_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115400_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Shanghai_CHN_ge300mw_ccs-rf</t>
+    <t>ep_coal_supercritical_Hohhot_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101919_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109208_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Sanhe_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104684_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100001004192_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000114200-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000100235_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100001000280_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115370-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Liuzhou_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Yingchuan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115850_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111569_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000108245_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Sizhan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Anqing_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000108892_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Shahezhai_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CHN44p2N116p5E_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111756-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104366-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Shanghai_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Nantong_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103459_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111142_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115382-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Yakeshi_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Hohhot_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Tongshan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Sanhe_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111201_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Yangzhou_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102942_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103449-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Sizhan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115452_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115845_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101729_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102872_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Shijiazhuang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yuanquan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104682_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shanghai_CHN_ge400mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Nantong_CHN_ge400mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Tianjin_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Luohe_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Xiaoyi_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115449_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_CHN44p2N116p5E_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CHN44p7N89p1E_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000113342_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115371-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Tongshan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yakeshi_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106501_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104622-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000114267_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000114364_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115654_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Shanghai_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106355_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111298_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Putian_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yiyang_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000105104_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111299_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104504_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106820_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Anshan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yangjiang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Tianjin_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Wuhan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102041_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111568_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115878_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_ZhongdongShequ_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104074-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Linyi_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Qabqa_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103450-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Chongqing_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115814_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110263_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110115-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yuanquan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Luohe_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Nantong_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111663_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Jingling_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Shijiazhuang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Hejin_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109027_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115953_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Anshun_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000114835_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Harbin_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104623_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_CHN44p4N121p8E_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000101734_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000100894_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Fangchenggang_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000112940_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_CCS_Hangzhou_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104486-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000108348_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115842-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103458_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Changzhou_CHN_ge400mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Luohe_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104104_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109189_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000114199-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115475_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000104235_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_CCS_G100001000352-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104368-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Fangchenggang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Yingchuan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100001000236_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115438_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_CCS_Hangzhou_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_CHN44p4N121p8E_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Ningde_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Sanhe_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115346-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Putian_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Yiyang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115453_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Anshun_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000114040_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000105138-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109205_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Yingchuan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Putian_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115494_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Wuan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104428-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106310_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109028_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Yangjiang_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Liuzhou_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_CHN44p7N89p1E_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Jinbi_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115312_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Hangzhou_CHN_ge400mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106460_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000100893_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115931_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Shanghai_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Manlin_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Nanjing_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000100711_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Shaoguan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CCS_G100000107468_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000105306_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000105160_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102102_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104065_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Putian_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000101769_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111465-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104064-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115334_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104621-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111664_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109009-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115496_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_CCS_Hangzhou_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000110133_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115815_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Fuzhou_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106643_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000105065_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100001000237_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_CHN44p2N116p5E_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Yangjiang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Nanjing_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115517_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000114747_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Harbin_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Hejin_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111649_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Sizhan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Hohhot_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106226_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115932_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115810_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111454_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Wulan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Kuqa_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Anshan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Mianyang_CHN_ge400mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Changzhou_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Zouping_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yangjiang_CHN_ge400mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Chongqing_CHN_ge400mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yiyang_CHN_ge400mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115524_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CHN44p4N121p8E_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Shanghai_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000113343_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103471_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100001000190-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115656_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000105064_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Rizhao_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103783-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000105159_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Yuanquan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115838_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Liaoyang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102929_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Shahezhai_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Ningde_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Luohe_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Kuqa_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000108893_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115451_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104417_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Xiaoxita_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Yiyang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Yanggezhuang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Shaoguan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Tianjin_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103150_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000105097_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103004_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106227_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yingchuan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Sanhe_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Jingling_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shanghai_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yangzhou_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103294_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Nanjing_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101790_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102944_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104429-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115345-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000114802_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000101735_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111994_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115493_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CCS_G100000104639_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102101_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Yangzhou_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CCS_G100000109029_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Tongling_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115816_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115879_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111466-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102871_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Xichang_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Sizhan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CCS_G100000109030_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103393_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102811_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115715_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103611_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Qabqa_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Tongshan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103612_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104716_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000105307_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Wuan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000106644_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102042_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102812_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Mianyang_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Manlin_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103392_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000114201_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Shaoguan_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yangjiang_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shaoguan_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shijiazhuang_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Tongshan_CHN_ge400mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Chongqing_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115296_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Chongqing_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Mianyang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115839_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102930_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Hejin_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103362_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111755-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100001000347_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Yangjiang_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Xiaoyi_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Chongqing_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115459_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104683_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109860_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000114533_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Rizhao_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115640_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109655-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Zouping_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Tongshan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000102228_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102157_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103881_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000114039_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101336_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115641_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104485-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Nantong_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104717_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115812_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102941_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000114834_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115458_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_CHN44p2N116p5E_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115532_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Changzhou_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Xiaoxita_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111995_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000114301_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111478_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Nantong_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Fangchenggang_CHN_ge400mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CHN44p7N89p1E_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Liuzhou_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Tongling_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115401_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104685_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115383-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111603-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115520_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109217_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104063-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115732_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102810_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103463_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115642_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Shanghai_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Tongling_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_Hohhot_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115639_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000111143_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102817-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104624_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115843-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_Fangchenggang_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Nanjing_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_CHN44p4N121p8E_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115655_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_ZhongdongShequ_CHN_ge300mw_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100001004194_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115840_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000101728_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000103414_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000102816-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000114709_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_Tangshan_CHN_ge300mw-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000109206_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000104075-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_ultra-supercritical_G100000115335_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000107476-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_ultra-supercritical_G100000115531_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_ultra-supercritical_Sizhan_CHN_ge300mw-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_coal_ultra-supercritical_Yuanquan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000279_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104519_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111602-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115447_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yangzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114746_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101768_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Ningde_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Wuan_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CHN44p7N89p1E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Liuzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001004194_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115840_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101728_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CHN44p4N121p8E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115655_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_ZhongdongShequ_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103414_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114709_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102816-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tangshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102810_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115732_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103463_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115642_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109206_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115335_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104075-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_coal_ultra-supercritical_G100000114803_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_ZhongdongShequ_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Hohhot_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tongling_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115383-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104685_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115520_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115401_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109217_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111603-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Chongqing_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107476-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115531_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115639_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Tongling_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111143_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104624_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102817-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115843-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Fangchenggang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Fangchenggang_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000109192_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110113-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Putian_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Rizhao_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Chongqing_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000104143_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103152_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Zouping_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Anshun_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CHN44p7N89p1E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000103363_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000100234_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111818_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111479_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109207_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103868_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Sanhe_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109656-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000111313_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Hohhot_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109117_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Luohe_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109208_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115560_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115521_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Changzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103479_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104367-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Beichengqu_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CHN44p2N116p5E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yanggezhuang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Hohhot_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101335_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000108347_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Fangchenggang_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yicheng_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109118_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000100712_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102943_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Jingling_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103385_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102034-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106459_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Ningde_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yicheng_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109218_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114302_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yangjiang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CCS_Hangzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Shahezhai_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yiyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115477_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yuanquan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000191-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103166_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000103395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Luohe_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yakeshi_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yangzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Hejin_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106819_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101757_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106502_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109010-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Fuzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yingchuan_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106460_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115931_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000100893_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Shanghai_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115517_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114747_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Harbin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Hejin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105065_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000237_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106643_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CHN44p2N116p5E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Anshun_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000107468_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105160_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102102_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104065_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105306_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Putian_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yangjiang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Nanjing_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106226_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000101769_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111465-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104064-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115334_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115932_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115810_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Anshun_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Anshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Manlin_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Nanjing_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000100711_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Shaoguan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111454_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Wulan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Kuqa_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111664_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115496_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109009-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CCS_Hangzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104621-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Sizhan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115815_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110133_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yangjiang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Fuzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Hangzhou_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115524_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Xiaoyi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CHN44p4N121p8E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000108893_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Anshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105064_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115656_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000190-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102929_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shahezhai_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Ningde_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Luohe_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yiyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yanggezhuang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Rizhao_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CHN44p7N89p1E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Shaoguan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Tianjin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105097_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103004_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106227_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yingchuan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Sanhe_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yingchuan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Jingling_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Shanghai_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103471_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000113343_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103150_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115838_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103783-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105159_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yuanquan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115451_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104417_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Xiaoxita_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Liaoyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Chongqing_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Changzhou_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yangjiang_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Zouping_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yiyang_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Mianyang_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Rizhao_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001004192_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104684_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114200-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111201_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yangzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111142_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103459_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115382-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yakeshi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Tongshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Hohhot_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115845_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115452_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115850_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111569_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000108245_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Sizhan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Anqing_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101729_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104682_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000280_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000100235_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115370-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Liuzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yangjiang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102872_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CHN44p2N116p5E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000108892_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shahezhai_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103449-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102942_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Sizhan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104366-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111756-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Shanghai_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Sanhe_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103293_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000102229_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115559_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Mianyang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Fangchenggang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115716_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tongshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_CCS_G100001000354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107477-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Wuhan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yicheng_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115844_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115391_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103384_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yangjiang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000104640_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000104144_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000111314_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000112939_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Fuzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yangzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103167_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Changzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tianjin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000109862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109861_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shijiazhuang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104418_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115474_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Anshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Sizhan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Liaoyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102033-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Luohe_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Anshun_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103151_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Shaoguan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115817_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115841_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Putian_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111005_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000107469_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115313_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104073-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110695_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Nanjing_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101368_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Anqing_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yingchuan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Xiaoyi_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103784-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yingchuan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Linyi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114703_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101468_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Wulan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Changzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103153_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000103364_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114365_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Hejin_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000108246_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_CCS_G100001000353-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shaoguan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Jinbi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115448_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115348_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101367_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115390_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shanghai_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Tongshan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110262-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104169_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yuanquan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101789_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104520_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Nantong_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Liaoyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Nanjing_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115296_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Chongqing_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Mianyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114039_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101336_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115641_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104485-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Nantong_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Wulan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115459_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102157_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103881_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000102228_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102941_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109860_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114533_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Rizhao_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115458_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114834_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CHN44p2N116p5E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111995_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114301_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111478_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Nantong_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115839_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102930_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Hejin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103362_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000347_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111755-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Xiaoyi_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115532_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Changzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Xiaoxita_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115640_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104717_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115812_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Hohhot_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109655-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yangjiang_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shijiazhuang_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Chongqing_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Tongshan_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shaoguan_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110112-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tongshan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115826-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000113225_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Beichengqu_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115825-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CHN44p7N89p1E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102813_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Wulan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115952_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115495_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Fangchenggang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115476_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103394_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115813_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Tangshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106354_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Beichengqu_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yiyang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104076-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104503_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Xiaoxita_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Chongqing_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Shijiazhuang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110694_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Hejin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_ZhongdongShequ_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103882_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yanggezhuang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CHN45p9N129p3E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Qabqa_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111817_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Nanjing_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shanghai_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Hangzhou_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103294_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Nanjing_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000109030_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103611_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102811_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115715_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103393_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Qabqa_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Tongshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000104639_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115493_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111994_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103612_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104716_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105307_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Wuan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Kuqa_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106644_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102042_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102101_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yangzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102812_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Manlin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Mianyang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102944_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101790_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104429-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115345-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114802_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000101735_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103392_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114201_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115816_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000109029_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tongling_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115879_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111466-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102871_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Xichang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Sizhan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yangzhou_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shanghai_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Luohe_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yiyang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106355_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111298_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115371-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000113342_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Tongshan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Jingling_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yakeshi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Putian_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102041_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111568_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115878_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115449_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CHN44p2N116p5E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CHN44p7N89p1E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106820_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yangjiang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tianjin_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Wuhan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104622-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114267_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114364_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106501_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104504_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105104_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111299_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Nantong_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Tianjin_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shanghai_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Nantong_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109189_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104104_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115475_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114199-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yingchuan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Putian_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115453_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Wuhan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_CCS_G100001000352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114040_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109205_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105138-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104428-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104368-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Beichengqu_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Hohhot_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Fangchenggang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yingchuan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109028_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106310_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115312_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000104235_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Liuzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CHN44p7N89p1E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115346-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Putian_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yiyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000236_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115438_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CCS_Hangzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Ningde_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CHN44p4N121p8E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Sanhe_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115494_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Wuan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Luohe_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Changzhou_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104074-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Linyi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110263_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115814_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110115-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Luohe_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yuanquan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114835_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Harbin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000100894_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000101734_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Fangchenggang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111663_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Jingling_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000112940_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CCS_Hangzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103458_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Qabqa_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103450-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Chongqing_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000108348_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104486-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Shijiazhuang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104623_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CHN44p4N121p8E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109027_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115953_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Anshun_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Nantong_CHN_ge400mw-CHP_ccs-rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -10585,7 +10585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{308D1DEA-6DCD-4926-A710-FB0C5C93CE14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1982A0FD-01A1-404E-8A17-7B542CBBFA37}">
   <dimension ref="B2:AG1714"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51938,7 +51938,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E66B976-725F-4E1A-85CA-2758DF04AB15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A068989-CF01-4D98-876F-C3FD232FEFF7}">
   <dimension ref="B9:L24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -64859,7 +64859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26B811EE-4031-4B5B-9A2B-014991992B0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A267F55-58AF-4472-96A7-3A26CC4BCC06}">
   <dimension ref="B2:Q855"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -69292,10 +69292,10 @@
         <v>2110</v>
       </c>
       <c r="P240" t="s">
-        <v>2081</v>
+        <v>2089</v>
       </c>
       <c r="Q240">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="241" spans="14:17" x14ac:dyDescent="0.45">
@@ -69306,7 +69306,7 @@
         <v>2111</v>
       </c>
       <c r="P241" t="s">
-        <v>2083</v>
+        <v>2076</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -69320,7 +69320,7 @@
         <v>2112</v>
       </c>
       <c r="P242" t="s">
-        <v>2060</v>
+        <v>2055</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -69334,7 +69334,7 @@
         <v>2113</v>
       </c>
       <c r="P243" t="s">
-        <v>2078</v>
+        <v>2089</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -69348,7 +69348,7 @@
         <v>2114</v>
       </c>
       <c r="P244" t="s">
-        <v>2089</v>
+        <v>2108</v>
       </c>
       <c r="Q244">
         <v>0.85</v>
@@ -69362,7 +69362,7 @@
         <v>2115</v>
       </c>
       <c r="P245" t="s">
-        <v>2094</v>
+        <v>2071</v>
       </c>
       <c r="Q245">
         <v>0.85</v>
@@ -69390,7 +69390,7 @@
         <v>2117</v>
       </c>
       <c r="P247" t="s">
-        <v>2088</v>
+        <v>2081</v>
       </c>
       <c r="Q247">
         <v>0.85</v>
@@ -69404,7 +69404,7 @@
         <v>2118</v>
       </c>
       <c r="P248" t="s">
-        <v>2071</v>
+        <v>2088</v>
       </c>
       <c r="Q248">
         <v>0.85</v>
@@ -69418,7 +69418,7 @@
         <v>2119</v>
       </c>
       <c r="P249" t="s">
-        <v>2081</v>
+        <v>2109</v>
       </c>
       <c r="Q249">
         <v>0.85</v>
@@ -69432,7 +69432,7 @@
         <v>2120</v>
       </c>
       <c r="P250" t="s">
-        <v>2107</v>
+        <v>2095</v>
       </c>
       <c r="Q250">
         <v>0.85</v>
@@ -69446,7 +69446,7 @@
         <v>2121</v>
       </c>
       <c r="P251" t="s">
-        <v>2065</v>
+        <v>2087</v>
       </c>
       <c r="Q251">
         <v>0.85</v>
@@ -69460,7 +69460,7 @@
         <v>2122</v>
       </c>
       <c r="P252" t="s">
-        <v>2094</v>
+        <v>2083</v>
       </c>
       <c r="Q252">
         <v>0.85</v>
@@ -69474,7 +69474,7 @@
         <v>2123</v>
       </c>
       <c r="P253" t="s">
-        <v>2080</v>
+        <v>2063</v>
       </c>
       <c r="Q253">
         <v>0.85</v>
@@ -69488,7 +69488,7 @@
         <v>2124</v>
       </c>
       <c r="P254" t="s">
-        <v>2095</v>
+        <v>2051</v>
       </c>
       <c r="Q254">
         <v>0.85</v>
@@ -69502,7 +69502,7 @@
         <v>2125</v>
       </c>
       <c r="P255" t="s">
-        <v>2100</v>
+        <v>2051</v>
       </c>
       <c r="Q255">
         <v>0.85</v>
@@ -69516,7 +69516,7 @@
         <v>2126</v>
       </c>
       <c r="P256" t="s">
-        <v>2076</v>
+        <v>2082</v>
       </c>
       <c r="Q256">
         <v>0.85</v>
@@ -69530,7 +69530,7 @@
         <v>2127</v>
       </c>
       <c r="P257" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="Q257">
         <v>0.85</v>
@@ -69544,7 +69544,7 @@
         <v>2128</v>
       </c>
       <c r="P258" t="s">
-        <v>2089</v>
+        <v>2103</v>
       </c>
       <c r="Q258">
         <v>0.85</v>
@@ -69558,7 +69558,7 @@
         <v>2129</v>
       </c>
       <c r="P259" t="s">
-        <v>2108</v>
+        <v>2065</v>
       </c>
       <c r="Q259">
         <v>0.85</v>
@@ -69572,7 +69572,7 @@
         <v>2130</v>
       </c>
       <c r="P260" t="s">
-        <v>2060</v>
+        <v>2082</v>
       </c>
       <c r="Q260">
         <v>0.85</v>
@@ -69586,7 +69586,7 @@
         <v>2131</v>
       </c>
       <c r="P261" t="s">
-        <v>2065</v>
+        <v>2103</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -69600,7 +69600,7 @@
         <v>2132</v>
       </c>
       <c r="P262" t="s">
-        <v>2079</v>
+        <v>2104</v>
       </c>
       <c r="Q262">
         <v>0.85</v>
@@ -69614,7 +69614,7 @@
         <v>2133</v>
       </c>
       <c r="P263" t="s">
-        <v>2051</v>
+        <v>2081</v>
       </c>
       <c r="Q263">
         <v>0.85</v>
@@ -69628,7 +69628,7 @@
         <v>2134</v>
       </c>
       <c r="P264" t="s">
-        <v>2051</v>
+        <v>2093</v>
       </c>
       <c r="Q264">
         <v>0.85</v>
@@ -69642,7 +69642,7 @@
         <v>2135</v>
       </c>
       <c r="P265" t="s">
-        <v>2082</v>
+        <v>2071</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -69656,7 +69656,7 @@
         <v>2136</v>
       </c>
       <c r="P266" t="s">
-        <v>2058</v>
+        <v>2094</v>
       </c>
       <c r="Q266">
         <v>0.85</v>
@@ -69670,7 +69670,7 @@
         <v>2137</v>
       </c>
       <c r="P267" t="s">
-        <v>2083</v>
+        <v>2107</v>
       </c>
       <c r="Q267">
         <v>0.85</v>
@@ -69684,7 +69684,7 @@
         <v>2138</v>
       </c>
       <c r="P268" t="s">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="Q268">
         <v>0.85</v>
@@ -69698,7 +69698,7 @@
         <v>2139</v>
       </c>
       <c r="P269" t="s">
-        <v>2073</v>
+        <v>2060</v>
       </c>
       <c r="Q269">
         <v>0.85</v>
@@ -69712,7 +69712,7 @@
         <v>2140</v>
       </c>
       <c r="P270" t="s">
-        <v>2079</v>
+        <v>2083</v>
       </c>
       <c r="Q270">
         <v>0.85</v>
@@ -69726,7 +69726,7 @@
         <v>2141</v>
       </c>
       <c r="P271" t="s">
-        <v>2103</v>
+        <v>2078</v>
       </c>
       <c r="Q271">
         <v>0.85</v>
@@ -69740,7 +69740,7 @@
         <v>2142</v>
       </c>
       <c r="P272" t="s">
-        <v>2103</v>
+        <v>2089</v>
       </c>
       <c r="Q272">
         <v>0.85</v>
@@ -69754,7 +69754,7 @@
         <v>2143</v>
       </c>
       <c r="P273" t="s">
-        <v>2104</v>
+        <v>2073</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -69768,7 +69768,7 @@
         <v>2144</v>
       </c>
       <c r="P274" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="Q274">
         <v>0.85</v>
@@ -69796,7 +69796,7 @@
         <v>2146</v>
       </c>
       <c r="P276" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Q276">
         <v>0.85</v>
@@ -69810,7 +69810,7 @@
         <v>2147</v>
       </c>
       <c r="P277" t="s">
-        <v>2082</v>
+        <v>2065</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -69824,10 +69824,10 @@
         <v>2148</v>
       </c>
       <c r="P278" t="s">
-        <v>2089</v>
+        <v>2060</v>
       </c>
       <c r="Q278">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="279" spans="14:17" x14ac:dyDescent="0.45">
@@ -69838,7 +69838,7 @@
         <v>2149</v>
       </c>
       <c r="P279" t="s">
-        <v>2106</v>
+        <v>2079</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -69852,10 +69852,10 @@
         <v>2150</v>
       </c>
       <c r="P280" t="s">
-        <v>2108</v>
+        <v>2081</v>
       </c>
       <c r="Q280">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="281" spans="14:17" x14ac:dyDescent="0.45">
@@ -69866,7 +69866,7 @@
         <v>2151</v>
       </c>
       <c r="P281" t="s">
-        <v>2078</v>
+        <v>2103</v>
       </c>
       <c r="Q281">
         <v>0.85</v>
@@ -69880,7 +69880,7 @@
         <v>2152</v>
       </c>
       <c r="P282" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
       <c r="Q282">
         <v>0.85</v>
@@ -69894,7 +69894,7 @@
         <v>2153</v>
       </c>
       <c r="P283" t="s">
-        <v>2069</v>
+        <v>2091</v>
       </c>
       <c r="Q283">
         <v>0.85</v>
@@ -69908,7 +69908,7 @@
         <v>2154</v>
       </c>
       <c r="P284" t="s">
-        <v>2086</v>
+        <v>2063</v>
       </c>
       <c r="Q284">
         <v>0.85</v>
@@ -69922,7 +69922,7 @@
         <v>2155</v>
       </c>
       <c r="P285" t="s">
-        <v>2078</v>
+        <v>2082</v>
       </c>
       <c r="Q285">
         <v>0.85</v>
@@ -69936,7 +69936,7 @@
         <v>2156</v>
       </c>
       <c r="P286" t="s">
-        <v>2103</v>
+        <v>2061</v>
       </c>
       <c r="Q286">
         <v>0.85</v>
@@ -69950,7 +69950,7 @@
         <v>2157</v>
       </c>
       <c r="P287" t="s">
-        <v>2088</v>
+        <v>2104</v>
       </c>
       <c r="Q287">
         <v>0.85</v>
@@ -69964,7 +69964,7 @@
         <v>2158</v>
       </c>
       <c r="P288" t="s">
-        <v>2089</v>
+        <v>2077</v>
       </c>
       <c r="Q288">
         <v>0.85</v>
@@ -69978,7 +69978,7 @@
         <v>2159</v>
       </c>
       <c r="P289" t="s">
-        <v>2089</v>
+        <v>2051</v>
       </c>
       <c r="Q289">
         <v>0.85</v>
@@ -69992,7 +69992,7 @@
         <v>2160</v>
       </c>
       <c r="P290" t="s">
-        <v>2092</v>
+        <v>2058</v>
       </c>
       <c r="Q290">
         <v>0.85</v>
@@ -70006,7 +70006,7 @@
         <v>2161</v>
       </c>
       <c r="P291" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="Q291">
         <v>0.85</v>
@@ -70020,7 +70020,7 @@
         <v>2162</v>
       </c>
       <c r="P292" t="s">
-        <v>2089</v>
+        <v>2106</v>
       </c>
       <c r="Q292">
         <v>0.85</v>
@@ -70034,7 +70034,7 @@
         <v>2163</v>
       </c>
       <c r="P293" t="s">
-        <v>2053</v>
+        <v>2093</v>
       </c>
       <c r="Q293">
         <v>0.85</v>
@@ -70048,7 +70048,7 @@
         <v>2164</v>
       </c>
       <c r="P294" t="s">
-        <v>2092</v>
+        <v>2051</v>
       </c>
       <c r="Q294">
         <v>0.85</v>
@@ -70062,7 +70062,7 @@
         <v>2165</v>
       </c>
       <c r="P295" t="s">
-        <v>2097</v>
+        <v>2083</v>
       </c>
       <c r="Q295">
         <v>0.85</v>
@@ -70076,7 +70076,7 @@
         <v>2166</v>
       </c>
       <c r="P296" t="s">
-        <v>2051</v>
+        <v>2103</v>
       </c>
       <c r="Q296">
         <v>0.85</v>
@@ -70090,7 +70090,7 @@
         <v>2167</v>
       </c>
       <c r="P297" t="s">
-        <v>2076</v>
+        <v>2069</v>
       </c>
       <c r="Q297">
         <v>0.85</v>
@@ -70104,7 +70104,7 @@
         <v>2168</v>
       </c>
       <c r="P298" t="s">
-        <v>2055</v>
+        <v>2089</v>
       </c>
       <c r="Q298">
         <v>0.85</v>
@@ -70118,7 +70118,7 @@
         <v>2169</v>
       </c>
       <c r="P299" t="s">
-        <v>2106</v>
+        <v>2093</v>
       </c>
       <c r="Q299">
         <v>0.85</v>
@@ -70132,7 +70132,7 @@
         <v>2170</v>
       </c>
       <c r="P300" t="s">
-        <v>2084</v>
+        <v>2051</v>
       </c>
       <c r="Q300">
         <v>0.85</v>
@@ -70146,7 +70146,7 @@
         <v>2171</v>
       </c>
       <c r="P301" t="s">
-        <v>2083</v>
+        <v>2096</v>
       </c>
       <c r="Q301">
         <v>0.85</v>
@@ -70160,7 +70160,7 @@
         <v>2172</v>
       </c>
       <c r="P302" t="s">
-        <v>2051</v>
+        <v>2080</v>
       </c>
       <c r="Q302">
         <v>0.85</v>
@@ -70174,7 +70174,7 @@
         <v>2173</v>
       </c>
       <c r="P303" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="Q303">
         <v>0.85</v>
@@ -70188,7 +70188,7 @@
         <v>2174</v>
       </c>
       <c r="P304" t="s">
-        <v>2096</v>
+        <v>2087</v>
       </c>
       <c r="Q304">
         <v>0.85</v>
@@ -70202,7 +70202,7 @@
         <v>2175</v>
       </c>
       <c r="P305" t="s">
-        <v>2088</v>
+        <v>2109</v>
       </c>
       <c r="Q305">
         <v>0.85</v>
@@ -70216,7 +70216,7 @@
         <v>2176</v>
       </c>
       <c r="P306" t="s">
-        <v>2103</v>
+        <v>2059</v>
       </c>
       <c r="Q306">
         <v>0.85</v>
@@ -70230,7 +70230,7 @@
         <v>2177</v>
       </c>
       <c r="P307" t="s">
-        <v>2107</v>
+        <v>2063</v>
       </c>
       <c r="Q307">
         <v>0.85</v>
@@ -70244,7 +70244,7 @@
         <v>2178</v>
       </c>
       <c r="P308" t="s">
-        <v>2076</v>
+        <v>2067</v>
       </c>
       <c r="Q308">
         <v>0.85</v>
@@ -70258,7 +70258,7 @@
         <v>2179</v>
       </c>
       <c r="P309" t="s">
-        <v>2104</v>
+        <v>2060</v>
       </c>
       <c r="Q309">
         <v>0.85</v>
@@ -70272,7 +70272,7 @@
         <v>2180</v>
       </c>
       <c r="P310" t="s">
-        <v>2076</v>
+        <v>2081</v>
       </c>
       <c r="Q310">
         <v>0.85</v>
@@ -70286,10 +70286,10 @@
         <v>2181</v>
       </c>
       <c r="P311" t="s">
-        <v>2083</v>
+        <v>2090</v>
       </c>
       <c r="Q311">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="312" spans="14:17" x14ac:dyDescent="0.45">
@@ -70300,7 +70300,7 @@
         <v>2182</v>
       </c>
       <c r="P312" t="s">
-        <v>2093</v>
+        <v>2076</v>
       </c>
       <c r="Q312">
         <v>0.85</v>
@@ -70314,10 +70314,10 @@
         <v>2183</v>
       </c>
       <c r="P313" t="s">
-        <v>2107</v>
+        <v>2103</v>
       </c>
       <c r="Q313">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="314" spans="14:17" x14ac:dyDescent="0.45">
@@ -70328,7 +70328,7 @@
         <v>2184</v>
       </c>
       <c r="P314" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="Q314">
         <v>0.85</v>
@@ -70342,7 +70342,7 @@
         <v>2185</v>
       </c>
       <c r="P315" t="s">
-        <v>2073</v>
+        <v>2108</v>
       </c>
       <c r="Q315">
         <v>0.85</v>
@@ -70356,7 +70356,7 @@
         <v>2186</v>
       </c>
       <c r="P316" t="s">
-        <v>2083</v>
+        <v>2060</v>
       </c>
       <c r="Q316">
         <v>0.85</v>
@@ -70370,7 +70370,7 @@
         <v>2187</v>
       </c>
       <c r="P317" t="s">
-        <v>2103</v>
+        <v>2089</v>
       </c>
       <c r="Q317">
         <v>0.85</v>
@@ -70384,7 +70384,7 @@
         <v>2188</v>
       </c>
       <c r="P318" t="s">
-        <v>2094</v>
+        <v>2083</v>
       </c>
       <c r="Q318">
         <v>0.85</v>
@@ -70398,7 +70398,7 @@
         <v>2189</v>
       </c>
       <c r="P319" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="Q319">
         <v>0.85</v>
@@ -70412,7 +70412,7 @@
         <v>2190</v>
       </c>
       <c r="P320" t="s">
-        <v>2104</v>
+        <v>2076</v>
       </c>
       <c r="Q320">
         <v>0.85</v>
@@ -70426,7 +70426,7 @@
         <v>2191</v>
       </c>
       <c r="P321" t="s">
-        <v>2094</v>
+        <v>2075</v>
       </c>
       <c r="Q321">
         <v>0.85</v>
@@ -70440,7 +70440,7 @@
         <v>2192</v>
       </c>
       <c r="P322" t="s">
-        <v>2070</v>
+        <v>2051</v>
       </c>
       <c r="Q322">
         <v>0.85</v>
@@ -70454,7 +70454,7 @@
         <v>2193</v>
       </c>
       <c r="P323" t="s">
-        <v>2102</v>
+        <v>2076</v>
       </c>
       <c r="Q323">
         <v>0.85</v>
@@ -70468,7 +70468,7 @@
         <v>2194</v>
       </c>
       <c r="P324" t="s">
-        <v>2089</v>
+        <v>2055</v>
       </c>
       <c r="Q324">
         <v>0.85</v>
@@ -70482,7 +70482,7 @@
         <v>2195</v>
       </c>
       <c r="P325" t="s">
-        <v>2076</v>
+        <v>2106</v>
       </c>
       <c r="Q325">
         <v>0.85</v>
@@ -70496,7 +70496,7 @@
         <v>2196</v>
       </c>
       <c r="P326" t="s">
-        <v>2100</v>
+        <v>2076</v>
       </c>
       <c r="Q326">
         <v>0.85</v>
@@ -70510,7 +70510,7 @@
         <v>2197</v>
       </c>
       <c r="P327" t="s">
-        <v>2086</v>
+        <v>2058</v>
       </c>
       <c r="Q327">
         <v>0.85</v>
@@ -70524,7 +70524,7 @@
         <v>2198</v>
       </c>
       <c r="P328" t="s">
-        <v>2076</v>
+        <v>2103</v>
       </c>
       <c r="Q328">
         <v>0.85</v>
@@ -70538,7 +70538,7 @@
         <v>2199</v>
       </c>
       <c r="P329" t="s">
-        <v>2106</v>
+        <v>2098</v>
       </c>
       <c r="Q329">
         <v>0.85</v>
@@ -70552,7 +70552,7 @@
         <v>2200</v>
       </c>
       <c r="P330" t="s">
-        <v>2051</v>
+        <v>2063</v>
       </c>
       <c r="Q330">
         <v>0.85</v>
@@ -70566,7 +70566,7 @@
         <v>2201</v>
       </c>
       <c r="P331" t="s">
-        <v>2060</v>
+        <v>2109</v>
       </c>
       <c r="Q331">
         <v>0.85</v>
@@ -70580,7 +70580,7 @@
         <v>2202</v>
       </c>
       <c r="P332" t="s">
-        <v>2089</v>
+        <v>2095</v>
       </c>
       <c r="Q332">
         <v>0.85</v>
@@ -70594,7 +70594,7 @@
         <v>2203</v>
       </c>
       <c r="P333" t="s">
-        <v>2095</v>
+        <v>2051</v>
       </c>
       <c r="Q333">
         <v>0.85</v>
@@ -70608,7 +70608,7 @@
         <v>2204</v>
       </c>
       <c r="P334" t="s">
-        <v>2097</v>
+        <v>2090</v>
       </c>
       <c r="Q334">
         <v>0.85</v>
@@ -70622,7 +70622,7 @@
         <v>2205</v>
       </c>
       <c r="P335" t="s">
-        <v>2070</v>
+        <v>2092</v>
       </c>
       <c r="Q335">
         <v>0.85</v>
@@ -70636,7 +70636,7 @@
         <v>2206</v>
       </c>
       <c r="P336" t="s">
-        <v>2086</v>
+        <v>2075</v>
       </c>
       <c r="Q336">
         <v>0.85</v>
@@ -70664,7 +70664,7 @@
         <v>2208</v>
       </c>
       <c r="P338" t="s">
-        <v>2087</v>
+        <v>2108</v>
       </c>
       <c r="Q338">
         <v>0.85</v>
@@ -70678,7 +70678,7 @@
         <v>2209</v>
       </c>
       <c r="P339" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="Q339">
         <v>0.85</v>
@@ -70692,7 +70692,7 @@
         <v>2210</v>
       </c>
       <c r="P340" t="s">
-        <v>2055</v>
+        <v>2081</v>
       </c>
       <c r="Q340">
         <v>0.85</v>
@@ -70706,7 +70706,7 @@
         <v>2211</v>
       </c>
       <c r="P341" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="Q341">
         <v>0.85</v>
@@ -70720,7 +70720,7 @@
         <v>2212</v>
       </c>
       <c r="P342" t="s">
-        <v>2087</v>
+        <v>2062</v>
       </c>
       <c r="Q342">
         <v>0.85</v>
@@ -70734,7 +70734,7 @@
         <v>2213</v>
       </c>
       <c r="P343" t="s">
-        <v>2107</v>
+        <v>2055</v>
       </c>
       <c r="Q343">
         <v>0.85</v>
@@ -70748,7 +70748,7 @@
         <v>2214</v>
       </c>
       <c r="P344" t="s">
-        <v>2065</v>
+        <v>2086</v>
       </c>
       <c r="Q344">
         <v>0.85</v>
@@ -70762,7 +70762,7 @@
         <v>2215</v>
       </c>
       <c r="P345" t="s">
-        <v>2103</v>
+        <v>2095</v>
       </c>
       <c r="Q345">
         <v>0.85</v>
@@ -70776,7 +70776,7 @@
         <v>2216</v>
       </c>
       <c r="P346" t="s">
-        <v>2051</v>
+        <v>2106</v>
       </c>
       <c r="Q346">
         <v>0.85</v>
@@ -70790,7 +70790,7 @@
         <v>2217</v>
       </c>
       <c r="P347" t="s">
-        <v>2058</v>
+        <v>2069</v>
       </c>
       <c r="Q347">
         <v>0.85</v>
@@ -70804,7 +70804,7 @@
         <v>2218</v>
       </c>
       <c r="P348" t="s">
-        <v>2108</v>
+        <v>2058</v>
       </c>
       <c r="Q348">
         <v>0.85</v>
@@ -70818,7 +70818,7 @@
         <v>2219</v>
       </c>
       <c r="P349" t="s">
-        <v>2094</v>
+        <v>2103</v>
       </c>
       <c r="Q349">
         <v>0.85</v>
@@ -70832,7 +70832,7 @@
         <v>2220</v>
       </c>
       <c r="P350" t="s">
-        <v>2093</v>
+        <v>2063</v>
       </c>
       <c r="Q350">
         <v>0.85</v>
@@ -70846,7 +70846,7 @@
         <v>2221</v>
       </c>
       <c r="P351" t="s">
-        <v>2076</v>
+        <v>2063</v>
       </c>
       <c r="Q351">
         <v>0.85</v>
@@ -70860,7 +70860,7 @@
         <v>2222</v>
       </c>
       <c r="P352" t="s">
-        <v>2086</v>
+        <v>2052</v>
       </c>
       <c r="Q352">
         <v>0.85</v>
@@ -70874,7 +70874,7 @@
         <v>2223</v>
       </c>
       <c r="P353" t="s">
-        <v>2077</v>
+        <v>2104</v>
       </c>
       <c r="Q353">
         <v>0.85</v>
@@ -70888,10 +70888,10 @@
         <v>2224</v>
       </c>
       <c r="P354" t="s">
-        <v>2077</v>
+        <v>2103</v>
       </c>
       <c r="Q354">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="355" spans="14:17" x14ac:dyDescent="0.45">
@@ -70902,7 +70902,7 @@
         <v>2225</v>
       </c>
       <c r="P355" t="s">
-        <v>2065</v>
+        <v>2086</v>
       </c>
       <c r="Q355">
         <v>0.85</v>
@@ -70916,7 +70916,7 @@
         <v>2226</v>
       </c>
       <c r="P356" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="Q356">
         <v>0.85</v>
@@ -70930,7 +70930,7 @@
         <v>2227</v>
       </c>
       <c r="P357" t="s">
-        <v>2076</v>
+        <v>2091</v>
       </c>
       <c r="Q357">
         <v>0.85</v>
@@ -70944,7 +70944,7 @@
         <v>2228</v>
       </c>
       <c r="P358" t="s">
-        <v>2094</v>
+        <v>2101</v>
       </c>
       <c r="Q358">
         <v>0.85</v>
@@ -70958,7 +70958,7 @@
         <v>2229</v>
       </c>
       <c r="P359" t="s">
-        <v>2065</v>
+        <v>2104</v>
       </c>
       <c r="Q359">
         <v>0.85</v>
@@ -70986,7 +70986,7 @@
         <v>2231</v>
       </c>
       <c r="P361" t="s">
-        <v>2089</v>
+        <v>2100</v>
       </c>
       <c r="Q361">
         <v>0.85</v>
@@ -71000,7 +71000,7 @@
         <v>2232</v>
       </c>
       <c r="P362" t="s">
-        <v>2101</v>
+        <v>2092</v>
       </c>
       <c r="Q362">
         <v>0.85</v>
@@ -71014,7 +71014,7 @@
         <v>2233</v>
       </c>
       <c r="P363" t="s">
-        <v>2078</v>
+        <v>2095</v>
       </c>
       <c r="Q363">
         <v>0.85</v>
@@ -71028,7 +71028,7 @@
         <v>2234</v>
       </c>
       <c r="P364" t="s">
-        <v>2059</v>
+        <v>2082</v>
       </c>
       <c r="Q364">
         <v>0.85</v>
@@ -71042,7 +71042,7 @@
         <v>2235</v>
       </c>
       <c r="P365" t="s">
-        <v>2075</v>
+        <v>2059</v>
       </c>
       <c r="Q365">
         <v>0.85</v>
@@ -71056,7 +71056,7 @@
         <v>2236</v>
       </c>
       <c r="P366" t="s">
-        <v>2060</v>
+        <v>2099</v>
       </c>
       <c r="Q366">
         <v>0.85</v>
@@ -71070,7 +71070,7 @@
         <v>2237</v>
       </c>
       <c r="P367" t="s">
-        <v>2109</v>
+        <v>2098</v>
       </c>
       <c r="Q367">
         <v>0.85</v>
@@ -71084,7 +71084,7 @@
         <v>2238</v>
       </c>
       <c r="P368" t="s">
-        <v>2098</v>
+        <v>2086</v>
       </c>
       <c r="Q368">
         <v>0.85</v>
@@ -71098,7 +71098,7 @@
         <v>2239</v>
       </c>
       <c r="P369" t="s">
-        <v>2106</v>
+        <v>2051</v>
       </c>
       <c r="Q369">
         <v>0.85</v>
@@ -71112,7 +71112,7 @@
         <v>2240</v>
       </c>
       <c r="P370" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="Q370">
         <v>0.85</v>
@@ -71126,7 +71126,7 @@
         <v>2241</v>
       </c>
       <c r="P371" t="s">
-        <v>2080</v>
+        <v>2106</v>
       </c>
       <c r="Q371">
         <v>0.85</v>
@@ -71140,7 +71140,7 @@
         <v>2242</v>
       </c>
       <c r="P372" t="s">
-        <v>2089</v>
+        <v>2084</v>
       </c>
       <c r="Q372">
         <v>0.85</v>
@@ -71154,7 +71154,7 @@
         <v>2243</v>
       </c>
       <c r="P373" t="s">
-        <v>2056</v>
+        <v>2077</v>
       </c>
       <c r="Q373">
         <v>0.85</v>
@@ -71168,7 +71168,7 @@
         <v>2244</v>
       </c>
       <c r="P374" t="s">
-        <v>2067</v>
+        <v>2076</v>
       </c>
       <c r="Q374">
         <v>0.85</v>
@@ -71182,7 +71182,7 @@
         <v>2245</v>
       </c>
       <c r="P375" t="s">
-        <v>2104</v>
+        <v>2089</v>
       </c>
       <c r="Q375">
         <v>0.85</v>
@@ -71196,7 +71196,7 @@
         <v>2246</v>
       </c>
       <c r="P376" t="s">
-        <v>2086</v>
+        <v>2103</v>
       </c>
       <c r="Q376">
         <v>0.85</v>
@@ -71210,7 +71210,7 @@
         <v>2247</v>
       </c>
       <c r="P377" t="s">
-        <v>2103</v>
+        <v>2071</v>
       </c>
       <c r="Q377">
         <v>0.85</v>
@@ -71224,7 +71224,7 @@
         <v>2248</v>
       </c>
       <c r="P378" t="s">
-        <v>2082</v>
+        <v>2095</v>
       </c>
       <c r="Q378">
         <v>0.85</v>
@@ -71238,7 +71238,7 @@
         <v>2249</v>
       </c>
       <c r="P379" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="Q379">
         <v>0.85</v>
@@ -71252,7 +71252,7 @@
         <v>2250</v>
       </c>
       <c r="P380" t="s">
-        <v>2080</v>
+        <v>2104</v>
       </c>
       <c r="Q380">
         <v>0.85</v>
@@ -71266,7 +71266,7 @@
         <v>2251</v>
       </c>
       <c r="P381" t="s">
-        <v>2101</v>
+        <v>2106</v>
       </c>
       <c r="Q381">
         <v>0.85</v>
@@ -71280,7 +71280,7 @@
         <v>2252</v>
       </c>
       <c r="P382" t="s">
-        <v>2055</v>
+        <v>2103</v>
       </c>
       <c r="Q382">
         <v>0.85</v>
@@ -71294,7 +71294,7 @@
         <v>2253</v>
       </c>
       <c r="P383" t="s">
-        <v>2058</v>
+        <v>2077</v>
       </c>
       <c r="Q383">
         <v>0.85</v>
@@ -71308,7 +71308,7 @@
         <v>2254</v>
       </c>
       <c r="P384" t="s">
-        <v>2103</v>
+        <v>2058</v>
       </c>
       <c r="Q384">
         <v>0.85</v>
@@ -71322,7 +71322,7 @@
         <v>2255</v>
       </c>
       <c r="P385" t="s">
-        <v>2076</v>
+        <v>2053</v>
       </c>
       <c r="Q385">
         <v>0.85</v>
@@ -71336,10 +71336,10 @@
         <v>2256</v>
       </c>
       <c r="P386" t="s">
-        <v>2087</v>
+        <v>2063</v>
       </c>
       <c r="Q386">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="387" spans="14:17" x14ac:dyDescent="0.45">
@@ -71350,7 +71350,7 @@
         <v>2257</v>
       </c>
       <c r="P387" t="s">
-        <v>2105</v>
+        <v>2053</v>
       </c>
       <c r="Q387">
         <v>0.85</v>
@@ -71364,7 +71364,7 @@
         <v>2258</v>
       </c>
       <c r="P388" t="s">
-        <v>2095</v>
+        <v>2060</v>
       </c>
       <c r="Q388">
         <v>0.85</v>
@@ -71378,7 +71378,7 @@
         <v>2259</v>
       </c>
       <c r="P389" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="Q389">
         <v>0.85</v>
@@ -71392,7 +71392,7 @@
         <v>2260</v>
       </c>
       <c r="P390" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
       <c r="Q390">
         <v>0.85</v>
@@ -71406,7 +71406,7 @@
         <v>2261</v>
       </c>
       <c r="P391" t="s">
-        <v>2083</v>
+        <v>2097</v>
       </c>
       <c r="Q391">
         <v>0.85</v>
@@ -71420,7 +71420,7 @@
         <v>2262</v>
       </c>
       <c r="P392" t="s">
-        <v>2089</v>
+        <v>2065</v>
       </c>
       <c r="Q392">
         <v>0.85</v>
@@ -71434,10 +71434,10 @@
         <v>2263</v>
       </c>
       <c r="P393" t="s">
-        <v>2077</v>
+        <v>2086</v>
       </c>
       <c r="Q393">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="394" spans="14:17" x14ac:dyDescent="0.45">
@@ -71448,10 +71448,10 @@
         <v>2264</v>
       </c>
       <c r="P394" t="s">
-        <v>2091</v>
+        <v>2080</v>
       </c>
       <c r="Q394">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="395" spans="14:17" x14ac:dyDescent="0.45">
@@ -71462,7 +71462,7 @@
         <v>2265</v>
       </c>
       <c r="P395" t="s">
-        <v>2103</v>
+        <v>2069</v>
       </c>
       <c r="Q395">
         <v>0.85</v>
@@ -71476,7 +71476,7 @@
         <v>2266</v>
       </c>
       <c r="P396" t="s">
-        <v>2051</v>
+        <v>2086</v>
       </c>
       <c r="Q396">
         <v>0.85</v>
@@ -71490,7 +71490,7 @@
         <v>2267</v>
       </c>
       <c r="P397" t="s">
-        <v>2096</v>
+        <v>2100</v>
       </c>
       <c r="Q397">
         <v>0.85</v>
@@ -71504,7 +71504,7 @@
         <v>2268</v>
       </c>
       <c r="P398" t="s">
-        <v>2080</v>
+        <v>2103</v>
       </c>
       <c r="Q398">
         <v>0.85</v>
@@ -71518,7 +71518,7 @@
         <v>2269</v>
       </c>
       <c r="P399" t="s">
-        <v>2103</v>
+        <v>2051</v>
       </c>
       <c r="Q399">
         <v>0.85</v>
@@ -71532,7 +71532,7 @@
         <v>2270</v>
       </c>
       <c r="P400" t="s">
-        <v>2095</v>
+        <v>2070</v>
       </c>
       <c r="Q400">
         <v>0.85</v>
@@ -71546,7 +71546,7 @@
         <v>2271</v>
       </c>
       <c r="P401" t="s">
-        <v>2089</v>
+        <v>2106</v>
       </c>
       <c r="Q401">
         <v>0.85</v>
@@ -71560,7 +71560,7 @@
         <v>2272</v>
       </c>
       <c r="P402" t="s">
-        <v>2093</v>
+        <v>2099</v>
       </c>
       <c r="Q402">
         <v>0.85</v>
@@ -71574,7 +71574,7 @@
         <v>2273</v>
       </c>
       <c r="P403" t="s">
-        <v>2091</v>
+        <v>2056</v>
       </c>
       <c r="Q403">
         <v>0.85</v>
@@ -71588,7 +71588,7 @@
         <v>2274</v>
       </c>
       <c r="P404" t="s">
-        <v>2087</v>
+        <v>2075</v>
       </c>
       <c r="Q404">
         <v>0.85</v>
@@ -71602,7 +71602,7 @@
         <v>2275</v>
       </c>
       <c r="P405" t="s">
-        <v>2109</v>
+        <v>2075</v>
       </c>
       <c r="Q405">
         <v>0.85</v>
@@ -71616,7 +71616,7 @@
         <v>2276</v>
       </c>
       <c r="P406" t="s">
-        <v>2071</v>
+        <v>2089</v>
       </c>
       <c r="Q406">
         <v>0.85</v>
@@ -71630,7 +71630,7 @@
         <v>2277</v>
       </c>
       <c r="P407" t="s">
-        <v>2063</v>
+        <v>2077</v>
       </c>
       <c r="Q407">
         <v>0.85</v>
@@ -71644,7 +71644,7 @@
         <v>2278</v>
       </c>
       <c r="P408" t="s">
-        <v>2067</v>
+        <v>2056</v>
       </c>
       <c r="Q408">
         <v>0.85</v>
@@ -71658,7 +71658,7 @@
         <v>2279</v>
       </c>
       <c r="P409" t="s">
-        <v>2060</v>
+        <v>2106</v>
       </c>
       <c r="Q409">
         <v>0.85</v>
@@ -71672,7 +71672,7 @@
         <v>2280</v>
       </c>
       <c r="P410" t="s">
-        <v>2081</v>
+        <v>2087</v>
       </c>
       <c r="Q410">
         <v>0.85</v>
@@ -71686,7 +71686,7 @@
         <v>2281</v>
       </c>
       <c r="P411" t="s">
-        <v>2096</v>
+        <v>2073</v>
       </c>
       <c r="Q411">
         <v>0.85</v>
@@ -71700,7 +71700,7 @@
         <v>2282</v>
       </c>
       <c r="P412" t="s">
-        <v>2051</v>
+        <v>2079</v>
       </c>
       <c r="Q412">
         <v>0.85</v>
@@ -71714,7 +71714,7 @@
         <v>2283</v>
       </c>
       <c r="P413" t="s">
-        <v>2077</v>
+        <v>2095</v>
       </c>
       <c r="Q413">
         <v>0.85</v>
@@ -71728,7 +71728,7 @@
         <v>2284</v>
       </c>
       <c r="P414" t="s">
-        <v>2058</v>
+        <v>2088</v>
       </c>
       <c r="Q414">
         <v>0.85</v>
@@ -71742,7 +71742,7 @@
         <v>2285</v>
       </c>
       <c r="P415" t="s">
-        <v>2063</v>
+        <v>2096</v>
       </c>
       <c r="Q415">
         <v>0.85</v>
@@ -71756,7 +71756,7 @@
         <v>2286</v>
       </c>
       <c r="P416" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="Q416">
         <v>0.85</v>
@@ -71770,7 +71770,7 @@
         <v>2287</v>
       </c>
       <c r="P417" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="Q417">
         <v>0.85</v>
@@ -71784,7 +71784,7 @@
         <v>2288</v>
       </c>
       <c r="P418" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="Q418">
         <v>0.85</v>
@@ -71798,7 +71798,7 @@
         <v>2289</v>
       </c>
       <c r="P419" t="s">
-        <v>2101</v>
+        <v>2087</v>
       </c>
       <c r="Q419">
         <v>0.85</v>
@@ -71812,10 +71812,10 @@
         <v>2290</v>
       </c>
       <c r="P420" t="s">
-        <v>2076</v>
+        <v>2107</v>
       </c>
       <c r="Q420">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="421" spans="14:17" x14ac:dyDescent="0.45">
@@ -71840,7 +71840,7 @@
         <v>2292</v>
       </c>
       <c r="P422" t="s">
-        <v>2093</v>
+        <v>2078</v>
       </c>
       <c r="Q422">
         <v>0.85</v>
@@ -71854,7 +71854,7 @@
         <v>2293</v>
       </c>
       <c r="P423" t="s">
-        <v>2051</v>
+        <v>2055</v>
       </c>
       <c r="Q423">
         <v>0.85</v>
@@ -71868,7 +71868,7 @@
         <v>2294</v>
       </c>
       <c r="P424" t="s">
-        <v>2083</v>
+        <v>2076</v>
       </c>
       <c r="Q424">
         <v>0.85</v>
@@ -71882,10 +71882,10 @@
         <v>2295</v>
       </c>
       <c r="P425" t="s">
-        <v>2081</v>
+        <v>2106</v>
       </c>
       <c r="Q425">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="426" spans="14:17" x14ac:dyDescent="0.45">
@@ -71896,7 +71896,7 @@
         <v>2296</v>
       </c>
       <c r="P426" t="s">
-        <v>2089</v>
+        <v>2103</v>
       </c>
       <c r="Q426">
         <v>0.85</v>
@@ -71910,7 +71910,7 @@
         <v>2297</v>
       </c>
       <c r="P427" t="s">
-        <v>2065</v>
+        <v>2088</v>
       </c>
       <c r="Q427">
         <v>0.85</v>
@@ -71924,7 +71924,7 @@
         <v>2298</v>
       </c>
       <c r="P428" t="s">
-        <v>2078</v>
+        <v>2053</v>
       </c>
       <c r="Q428">
         <v>0.85</v>
@@ -71938,7 +71938,7 @@
         <v>2299</v>
       </c>
       <c r="P429" t="s">
-        <v>2051</v>
+        <v>2089</v>
       </c>
       <c r="Q429">
         <v>0.85</v>
@@ -71952,7 +71952,7 @@
         <v>2300</v>
       </c>
       <c r="P430" t="s">
-        <v>2106</v>
+        <v>2075</v>
       </c>
       <c r="Q430">
         <v>0.85</v>
@@ -71966,7 +71966,7 @@
         <v>2301</v>
       </c>
       <c r="P431" t="s">
-        <v>2076</v>
+        <v>2094</v>
       </c>
       <c r="Q431">
         <v>0.85</v>
@@ -71980,7 +71980,7 @@
         <v>2302</v>
       </c>
       <c r="P432" t="s">
-        <v>2057</v>
+        <v>2103</v>
       </c>
       <c r="Q432">
         <v>0.85</v>
@@ -71994,7 +71994,7 @@
         <v>2303</v>
       </c>
       <c r="P433" t="s">
-        <v>2101</v>
+        <v>2076</v>
       </c>
       <c r="Q433">
         <v>0.85</v>
@@ -72008,7 +72008,7 @@
         <v>2304</v>
       </c>
       <c r="P434" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="Q434">
         <v>0.85</v>
@@ -72022,7 +72022,7 @@
         <v>2305</v>
       </c>
       <c r="P435" t="s">
-        <v>2060</v>
+        <v>2104</v>
       </c>
       <c r="Q435">
         <v>0.85</v>
@@ -72036,7 +72036,7 @@
         <v>2306</v>
       </c>
       <c r="P436" t="s">
-        <v>2071</v>
+        <v>2088</v>
       </c>
       <c r="Q436">
         <v>0.85</v>
@@ -72050,7 +72050,7 @@
         <v>2307</v>
       </c>
       <c r="P437" t="s">
-        <v>2105</v>
+        <v>2093</v>
       </c>
       <c r="Q437">
         <v>0.85</v>
@@ -72064,7 +72064,7 @@
         <v>2308</v>
       </c>
       <c r="P438" t="s">
-        <v>2059</v>
+        <v>2086</v>
       </c>
       <c r="Q438">
         <v>0.85</v>
@@ -72078,7 +72078,7 @@
         <v>2309</v>
       </c>
       <c r="P439" t="s">
-        <v>2063</v>
+        <v>2055</v>
       </c>
       <c r="Q439">
         <v>0.85</v>
@@ -72092,7 +72092,7 @@
         <v>2310</v>
       </c>
       <c r="P440" t="s">
-        <v>2051</v>
+        <v>2078</v>
       </c>
       <c r="Q440">
         <v>0.85</v>
@@ -72106,7 +72106,7 @@
         <v>2311</v>
       </c>
       <c r="P441" t="s">
-        <v>2077</v>
+        <v>2089</v>
       </c>
       <c r="Q441">
         <v>0.85</v>
@@ -72120,7 +72120,7 @@
         <v>2312</v>
       </c>
       <c r="P442" t="s">
-        <v>2104</v>
+        <v>2089</v>
       </c>
       <c r="Q442">
         <v>0.85</v>
@@ -72134,7 +72134,7 @@
         <v>2313</v>
       </c>
       <c r="P443" t="s">
-        <v>2109</v>
+        <v>2092</v>
       </c>
       <c r="Q443">
         <v>0.85</v>
@@ -72148,7 +72148,7 @@
         <v>2314</v>
       </c>
       <c r="P444" t="s">
-        <v>2076</v>
+        <v>2098</v>
       </c>
       <c r="Q444">
         <v>0.85</v>
@@ -72162,7 +72162,7 @@
         <v>2315</v>
       </c>
       <c r="P445" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="Q445">
         <v>0.85</v>
@@ -72176,7 +72176,7 @@
         <v>2316</v>
       </c>
       <c r="P446" t="s">
-        <v>2090</v>
+        <v>2083</v>
       </c>
       <c r="Q446">
         <v>0.85</v>
@@ -72190,7 +72190,7 @@
         <v>2317</v>
       </c>
       <c r="P447" t="s">
-        <v>2103</v>
+        <v>2076</v>
       </c>
       <c r="Q447">
         <v>0.85</v>
@@ -72204,7 +72204,7 @@
         <v>2318</v>
       </c>
       <c r="P448" t="s">
-        <v>2083</v>
+        <v>2097</v>
       </c>
       <c r="Q448">
         <v>0.85</v>
@@ -72218,7 +72218,7 @@
         <v>2319</v>
       </c>
       <c r="P449" t="s">
-        <v>2052</v>
+        <v>2084</v>
       </c>
       <c r="Q449">
         <v>0.85</v>
@@ -72232,7 +72232,7 @@
         <v>2320</v>
       </c>
       <c r="P450" t="s">
-        <v>2104</v>
+        <v>2083</v>
       </c>
       <c r="Q450">
         <v>0.85</v>
@@ -72246,7 +72246,7 @@
         <v>2321</v>
       </c>
       <c r="P451" t="s">
-        <v>2089</v>
+        <v>2096</v>
       </c>
       <c r="Q451">
         <v>0.85</v>
@@ -72260,7 +72260,7 @@
         <v>2322</v>
       </c>
       <c r="P452" t="s">
-        <v>2065</v>
+        <v>2051</v>
       </c>
       <c r="Q452">
         <v>0.85</v>
@@ -72274,7 +72274,7 @@
         <v>2323</v>
       </c>
       <c r="P453" t="s">
-        <v>2065</v>
+        <v>2051</v>
       </c>
       <c r="Q453">
         <v>0.85</v>
@@ -72288,7 +72288,7 @@
         <v>2324</v>
       </c>
       <c r="P454" t="s">
-        <v>2059</v>
+        <v>2081</v>
       </c>
       <c r="Q454">
         <v>0.85</v>
@@ -72302,10 +72302,10 @@
         <v>2325</v>
       </c>
       <c r="P455" t="s">
-        <v>2054</v>
+        <v>2077</v>
       </c>
       <c r="Q455">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="456" spans="14:17" x14ac:dyDescent="0.45">
@@ -72316,7 +72316,7 @@
         <v>2326</v>
       </c>
       <c r="P456" t="s">
-        <v>2064</v>
+        <v>2053</v>
       </c>
       <c r="Q456">
         <v>0.85</v>
@@ -72330,7 +72330,7 @@
         <v>2327</v>
       </c>
       <c r="P457" t="s">
-        <v>2090</v>
+        <v>2065</v>
       </c>
       <c r="Q457">
         <v>0.85</v>
@@ -72344,7 +72344,7 @@
         <v>2328</v>
       </c>
       <c r="P458" t="s">
-        <v>2051</v>
+        <v>2076</v>
       </c>
       <c r="Q458">
         <v>0.85</v>
@@ -72358,7 +72358,7 @@
         <v>2329</v>
       </c>
       <c r="P459" t="s">
-        <v>2089</v>
+        <v>2106</v>
       </c>
       <c r="Q459">
         <v>0.85</v>
@@ -72372,7 +72372,7 @@
         <v>2330</v>
       </c>
       <c r="P460" t="s">
-        <v>2103</v>
+        <v>2094</v>
       </c>
       <c r="Q460">
         <v>0.85</v>
@@ -72386,7 +72386,7 @@
         <v>2331</v>
       </c>
       <c r="P461" t="s">
-        <v>2069</v>
+        <v>2101</v>
       </c>
       <c r="Q461">
         <v>0.85</v>
@@ -72400,7 +72400,7 @@
         <v>2332</v>
       </c>
       <c r="P462" t="s">
-        <v>2068</v>
+        <v>2055</v>
       </c>
       <c r="Q462">
         <v>0.85</v>
@@ -72414,7 +72414,7 @@
         <v>2333</v>
       </c>
       <c r="P463" t="s">
-        <v>2093</v>
+        <v>2086</v>
       </c>
       <c r="Q463">
         <v>0.85</v>
@@ -72428,7 +72428,7 @@
         <v>2334</v>
       </c>
       <c r="P464" t="s">
-        <v>2075</v>
+        <v>2058</v>
       </c>
       <c r="Q464">
         <v>0.85</v>
@@ -72442,7 +72442,7 @@
         <v>2335</v>
       </c>
       <c r="P465" t="s">
-        <v>2051</v>
+        <v>2076</v>
       </c>
       <c r="Q465">
         <v>0.85</v>
@@ -72456,7 +72456,7 @@
         <v>2336</v>
       </c>
       <c r="P466" t="s">
-        <v>2063</v>
+        <v>2103</v>
       </c>
       <c r="Q466">
         <v>0.85</v>
@@ -72470,7 +72470,7 @@
         <v>2337</v>
       </c>
       <c r="P467" t="s">
-        <v>2093</v>
+        <v>2087</v>
       </c>
       <c r="Q467">
         <v>0.85</v>
@@ -72484,7 +72484,7 @@
         <v>2338</v>
       </c>
       <c r="P468" t="s">
-        <v>2051</v>
+        <v>2059</v>
       </c>
       <c r="Q468">
         <v>0.85</v>
@@ -72498,7 +72498,7 @@
         <v>2339</v>
       </c>
       <c r="P469" t="s">
-        <v>2103</v>
+        <v>2075</v>
       </c>
       <c r="Q469">
         <v>0.85</v>
@@ -72512,10 +72512,10 @@
         <v>2340</v>
       </c>
       <c r="P470" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="Q470">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="471" spans="14:17" x14ac:dyDescent="0.45">
@@ -72526,7 +72526,7 @@
         <v>2341</v>
       </c>
       <c r="P471" t="s">
-        <v>2084</v>
+        <v>2103</v>
       </c>
       <c r="Q471">
         <v>0.85</v>
@@ -72540,7 +72540,7 @@
         <v>2342</v>
       </c>
       <c r="P472" t="s">
-        <v>2071</v>
+        <v>2082</v>
       </c>
       <c r="Q472">
         <v>0.85</v>
@@ -72554,7 +72554,7 @@
         <v>2343</v>
       </c>
       <c r="P473" t="s">
-        <v>2083</v>
+        <v>2105</v>
       </c>
       <c r="Q473">
         <v>0.85</v>
@@ -72568,10 +72568,10 @@
         <v>2344</v>
       </c>
       <c r="P474" t="s">
-        <v>2063</v>
+        <v>2095</v>
       </c>
       <c r="Q474">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="475" spans="14:17" x14ac:dyDescent="0.45">
@@ -72582,7 +72582,7 @@
         <v>2345</v>
       </c>
       <c r="P475" t="s">
-        <v>2055</v>
+        <v>2089</v>
       </c>
       <c r="Q475">
         <v>0.85</v>
@@ -72596,7 +72596,7 @@
         <v>2346</v>
       </c>
       <c r="P476" t="s">
-        <v>2092</v>
+        <v>2083</v>
       </c>
       <c r="Q476">
         <v>0.85</v>
@@ -72610,7 +72610,7 @@
         <v>2347</v>
       </c>
       <c r="P477" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="Q477">
         <v>0.85</v>
@@ -72624,7 +72624,7 @@
         <v>2348</v>
       </c>
       <c r="P478" t="s">
-        <v>2081</v>
+        <v>2089</v>
       </c>
       <c r="Q478">
         <v>0.85</v>
@@ -72638,7 +72638,7 @@
         <v>2349</v>
       </c>
       <c r="P479" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
       <c r="Q479">
         <v>0.85</v>
@@ -72652,7 +72652,7 @@
         <v>2350</v>
       </c>
       <c r="P480" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
       <c r="Q480">
         <v>0.85</v>
@@ -72666,7 +72666,7 @@
         <v>2351</v>
       </c>
       <c r="P481" t="s">
-        <v>2094</v>
+        <v>2106</v>
       </c>
       <c r="Q481">
         <v>0.85</v>
@@ -72680,7 +72680,7 @@
         <v>2352</v>
       </c>
       <c r="P482" t="s">
-        <v>2051</v>
+        <v>2109</v>
       </c>
       <c r="Q482">
         <v>0.85</v>
@@ -72694,7 +72694,7 @@
         <v>2353</v>
       </c>
       <c r="P483" t="s">
-        <v>2083</v>
+        <v>2060</v>
       </c>
       <c r="Q483">
         <v>0.85</v>
@@ -72708,7 +72708,7 @@
         <v>2354</v>
       </c>
       <c r="P484" t="s">
-        <v>2067</v>
+        <v>2103</v>
       </c>
       <c r="Q484">
         <v>0.85</v>
@@ -72722,7 +72722,7 @@
         <v>2355</v>
       </c>
       <c r="P485" t="s">
-        <v>2093</v>
+        <v>2080</v>
       </c>
       <c r="Q485">
         <v>0.85</v>
@@ -72736,7 +72736,7 @@
         <v>2356</v>
       </c>
       <c r="P486" t="s">
-        <v>2082</v>
+        <v>2089</v>
       </c>
       <c r="Q486">
         <v>0.85</v>
@@ -72750,7 +72750,7 @@
         <v>2357</v>
       </c>
       <c r="P487" t="s">
-        <v>2060</v>
+        <v>2054</v>
       </c>
       <c r="Q487">
         <v>0.85</v>
@@ -72764,7 +72764,7 @@
         <v>2358</v>
       </c>
       <c r="P488" t="s">
-        <v>2095</v>
+        <v>2065</v>
       </c>
       <c r="Q488">
         <v>0.85</v>
@@ -72778,7 +72778,7 @@
         <v>2359</v>
       </c>
       <c r="P489" t="s">
-        <v>2094</v>
+        <v>2098</v>
       </c>
       <c r="Q489">
         <v>0.85</v>
@@ -72792,7 +72792,7 @@
         <v>2360</v>
       </c>
       <c r="P490" t="s">
-        <v>2075</v>
+        <v>2067</v>
       </c>
       <c r="Q490">
         <v>0.85</v>
@@ -72806,7 +72806,7 @@
         <v>2361</v>
       </c>
       <c r="P491" t="s">
-        <v>2089</v>
+        <v>2104</v>
       </c>
       <c r="Q491">
         <v>0.85</v>
@@ -72820,7 +72820,7 @@
         <v>2362</v>
       </c>
       <c r="P492" t="s">
-        <v>2053</v>
+        <v>2080</v>
       </c>
       <c r="Q492">
         <v>0.85</v>
@@ -72834,7 +72834,7 @@
         <v>2363</v>
       </c>
       <c r="P493" t="s">
-        <v>2098</v>
+        <v>2086</v>
       </c>
       <c r="Q493">
         <v>0.85</v>
@@ -72848,7 +72848,7 @@
         <v>2364</v>
       </c>
       <c r="P494" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="Q494">
         <v>0.85</v>
@@ -72862,7 +72862,7 @@
         <v>2365</v>
       </c>
       <c r="P495" t="s">
-        <v>2103</v>
+        <v>2080</v>
       </c>
       <c r="Q495">
         <v>0.85</v>
@@ -72876,10 +72876,10 @@
         <v>2366</v>
       </c>
       <c r="P496" t="s">
-        <v>2081</v>
+        <v>2056</v>
       </c>
       <c r="Q496">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="497" spans="14:17" x14ac:dyDescent="0.45">
@@ -72890,7 +72890,7 @@
         <v>2367</v>
       </c>
       <c r="P497" t="s">
-        <v>2056</v>
+        <v>2093</v>
       </c>
       <c r="Q497">
         <v>0.85</v>
@@ -72904,7 +72904,7 @@
         <v>2368</v>
       </c>
       <c r="P498" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="Q498">
         <v>0.85</v>
@@ -72918,7 +72918,7 @@
         <v>2369</v>
       </c>
       <c r="P499" t="s">
-        <v>2080</v>
+        <v>2060</v>
       </c>
       <c r="Q499">
         <v>0.85</v>
@@ -72932,7 +72932,7 @@
         <v>2370</v>
       </c>
       <c r="P500" t="s">
-        <v>2051</v>
+        <v>2109</v>
       </c>
       <c r="Q500">
         <v>0.85</v>
@@ -72946,7 +72946,7 @@
         <v>2371</v>
       </c>
       <c r="P501" t="s">
-        <v>2106</v>
+        <v>2088</v>
       </c>
       <c r="Q501">
         <v>0.85</v>
@@ -72960,7 +72960,7 @@
         <v>2372</v>
       </c>
       <c r="P502" t="s">
-        <v>2087</v>
+        <v>2069</v>
       </c>
       <c r="Q502">
         <v>0.85</v>
@@ -72974,7 +72974,7 @@
         <v>2373</v>
       </c>
       <c r="P503" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
       <c r="Q503">
         <v>0.85</v>
@@ -72988,7 +72988,7 @@
         <v>2374</v>
       </c>
       <c r="P504" t="s">
-        <v>2103</v>
+        <v>2081</v>
       </c>
       <c r="Q504">
         <v>0.85</v>
@@ -73002,7 +73002,7 @@
         <v>2375</v>
       </c>
       <c r="P505" t="s">
-        <v>2081</v>
+        <v>2094</v>
       </c>
       <c r="Q505">
         <v>0.85</v>
@@ -73016,7 +73016,7 @@
         <v>2376</v>
       </c>
       <c r="P506" t="s">
-        <v>2051</v>
+        <v>2098</v>
       </c>
       <c r="Q506">
         <v>0.85</v>
@@ -73030,7 +73030,7 @@
         <v>2377</v>
       </c>
       <c r="P507" t="s">
-        <v>2096</v>
+        <v>2055</v>
       </c>
       <c r="Q507">
         <v>0.85</v>
@@ -73044,7 +73044,7 @@
         <v>2378</v>
       </c>
       <c r="P508" t="s">
-        <v>2089</v>
+        <v>2103</v>
       </c>
       <c r="Q508">
         <v>0.85</v>
@@ -73058,7 +73058,7 @@
         <v>2379</v>
       </c>
       <c r="P509" t="s">
-        <v>2104</v>
+        <v>2109</v>
       </c>
       <c r="Q509">
         <v>0.85</v>
@@ -73072,7 +73072,7 @@
         <v>2380</v>
       </c>
       <c r="P510" t="s">
-        <v>2097</v>
+        <v>2081</v>
       </c>
       <c r="Q510">
         <v>0.85</v>
@@ -73086,7 +73086,7 @@
         <v>2381</v>
       </c>
       <c r="P511" t="s">
-        <v>2099</v>
+        <v>2067</v>
       </c>
       <c r="Q511">
         <v>0.85</v>
@@ -73100,10 +73100,10 @@
         <v>2382</v>
       </c>
       <c r="P512" t="s">
-        <v>2065</v>
+        <v>2105</v>
       </c>
       <c r="Q512">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="513" spans="14:17" x14ac:dyDescent="0.45">
@@ -73114,10 +73114,10 @@
         <v>2383</v>
       </c>
       <c r="P513" t="s">
-        <v>2058</v>
+        <v>2106</v>
       </c>
       <c r="Q513">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="514" spans="14:17" x14ac:dyDescent="0.45">
@@ -73128,10 +73128,10 @@
         <v>2384</v>
       </c>
       <c r="P514" t="s">
-        <v>2071</v>
+        <v>2076</v>
       </c>
       <c r="Q514">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="515" spans="14:17" x14ac:dyDescent="0.45">
@@ -73142,10 +73142,10 @@
         <v>2385</v>
       </c>
       <c r="P515" t="s">
-        <v>2078</v>
+        <v>2051</v>
       </c>
       <c r="Q515">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="516" spans="14:17" x14ac:dyDescent="0.45">
@@ -73156,10 +73156,10 @@
         <v>2386</v>
       </c>
       <c r="P516" t="s">
-        <v>2060</v>
+        <v>2098</v>
       </c>
       <c r="Q516">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="517" spans="14:17" x14ac:dyDescent="0.45">
@@ -73170,10 +73170,10 @@
         <v>2387</v>
       </c>
       <c r="P517" t="s">
-        <v>2084</v>
+        <v>2071</v>
       </c>
       <c r="Q517">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="518" spans="14:17" x14ac:dyDescent="0.45">
@@ -73187,7 +73187,7 @@
         <v>2094</v>
       </c>
       <c r="Q518">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="519" spans="14:17" x14ac:dyDescent="0.45">
@@ -73198,7 +73198,7 @@
         <v>2389</v>
       </c>
       <c r="P519" t="s">
-        <v>2083</v>
+        <v>2087</v>
       </c>
       <c r="Q519">
         <v>0.85</v>
@@ -73212,7 +73212,7 @@
         <v>2390</v>
       </c>
       <c r="P520" t="s">
-        <v>2093</v>
+        <v>2061</v>
       </c>
       <c r="Q520">
         <v>0.85</v>
@@ -73226,7 +73226,7 @@
         <v>2391</v>
       </c>
       <c r="P521" t="s">
-        <v>2060</v>
+        <v>2086</v>
       </c>
       <c r="Q521">
         <v>0.85</v>
@@ -73240,7 +73240,7 @@
         <v>2392</v>
       </c>
       <c r="P522" t="s">
-        <v>2083</v>
+        <v>2106</v>
       </c>
       <c r="Q522">
         <v>0.85</v>
@@ -73254,7 +73254,7 @@
         <v>2393</v>
       </c>
       <c r="P523" t="s">
-        <v>2104</v>
+        <v>2056</v>
       </c>
       <c r="Q523">
         <v>0.85</v>
@@ -73268,7 +73268,7 @@
         <v>2394</v>
       </c>
       <c r="P524" t="s">
-        <v>2094</v>
+        <v>2083</v>
       </c>
       <c r="Q524">
         <v>0.85</v>
@@ -73282,7 +73282,7 @@
         <v>2395</v>
       </c>
       <c r="P525" t="s">
-        <v>2071</v>
+        <v>2104</v>
       </c>
       <c r="Q525">
         <v>0.85</v>
@@ -73296,7 +73296,7 @@
         <v>2396</v>
       </c>
       <c r="P526" t="s">
-        <v>2087</v>
+        <v>2096</v>
       </c>
       <c r="Q526">
         <v>0.85</v>
@@ -73310,7 +73310,7 @@
         <v>2397</v>
       </c>
       <c r="P527" t="s">
-        <v>2061</v>
+        <v>2078</v>
       </c>
       <c r="Q527">
         <v>0.85</v>
@@ -73324,7 +73324,7 @@
         <v>2398</v>
       </c>
       <c r="P528" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="Q528">
         <v>0.85</v>
@@ -73338,7 +73338,7 @@
         <v>2399</v>
       </c>
       <c r="P529" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="Q529">
         <v>0.85</v>
@@ -73366,7 +73366,7 @@
         <v>2401</v>
       </c>
       <c r="P531" t="s">
-        <v>2089</v>
+        <v>2094</v>
       </c>
       <c r="Q531">
         <v>0.85</v>
@@ -73380,7 +73380,7 @@
         <v>2402</v>
       </c>
       <c r="P532" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="Q532">
         <v>0.85</v>
@@ -73394,7 +73394,7 @@
         <v>2403</v>
       </c>
       <c r="P533" t="s">
-        <v>2098</v>
+        <v>2052</v>
       </c>
       <c r="Q533">
         <v>0.85</v>
@@ -73408,7 +73408,7 @@
         <v>2404</v>
       </c>
       <c r="P534" t="s">
-        <v>2055</v>
+        <v>2096</v>
       </c>
       <c r="Q534">
         <v>0.85</v>
@@ -73422,7 +73422,7 @@
         <v>2405</v>
       </c>
       <c r="P535" t="s">
-        <v>2103</v>
+        <v>2093</v>
       </c>
       <c r="Q535">
         <v>0.85</v>
@@ -73436,10 +73436,10 @@
         <v>2406</v>
       </c>
       <c r="P536" t="s">
-        <v>2109</v>
+        <v>2051</v>
       </c>
       <c r="Q536">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="537" spans="14:17" x14ac:dyDescent="0.45">
@@ -73450,10 +73450,10 @@
         <v>2407</v>
       </c>
       <c r="P537" t="s">
-        <v>2094</v>
+        <v>2098</v>
       </c>
       <c r="Q537">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="538" spans="14:17" x14ac:dyDescent="0.45">
@@ -73464,10 +73464,10 @@
         <v>2408</v>
       </c>
       <c r="P538" t="s">
-        <v>2093</v>
+        <v>2053</v>
       </c>
       <c r="Q538">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="539" spans="14:17" x14ac:dyDescent="0.45">
@@ -73478,7 +73478,7 @@
         <v>2409</v>
       </c>
       <c r="P539" t="s">
-        <v>2088</v>
+        <v>2082</v>
       </c>
       <c r="Q539">
         <v>0.85</v>
@@ -73492,7 +73492,7 @@
         <v>2410</v>
       </c>
       <c r="P540" t="s">
-        <v>2109</v>
+        <v>2092</v>
       </c>
       <c r="Q540">
         <v>0.85</v>
@@ -73506,7 +73506,7 @@
         <v>2411</v>
       </c>
       <c r="P541" t="s">
-        <v>2069</v>
+        <v>2089</v>
       </c>
       <c r="Q541">
         <v>0.85</v>
@@ -73520,7 +73520,7 @@
         <v>2412</v>
       </c>
       <c r="P542" t="s">
-        <v>2073</v>
+        <v>2105</v>
       </c>
       <c r="Q542">
         <v>0.85</v>
@@ -73534,7 +73534,7 @@
         <v>2413</v>
       </c>
       <c r="P543" t="s">
-        <v>2071</v>
+        <v>2075</v>
       </c>
       <c r="Q543">
         <v>0.85</v>
@@ -73548,7 +73548,7 @@
         <v>2414</v>
       </c>
       <c r="P544" t="s">
-        <v>2093</v>
+        <v>2087</v>
       </c>
       <c r="Q544">
         <v>0.85</v>
@@ -73562,7 +73562,7 @@
         <v>2415</v>
       </c>
       <c r="P545" t="s">
-        <v>2105</v>
+        <v>2069</v>
       </c>
       <c r="Q545">
         <v>0.85</v>
@@ -73576,7 +73576,7 @@
         <v>2416</v>
       </c>
       <c r="P546" t="s">
-        <v>2081</v>
+        <v>2106</v>
       </c>
       <c r="Q546">
         <v>0.85</v>
@@ -73590,7 +73590,7 @@
         <v>2417</v>
       </c>
       <c r="P547" t="s">
-        <v>2067</v>
+        <v>2061</v>
       </c>
       <c r="Q547">
         <v>0.85</v>
@@ -73604,7 +73604,7 @@
         <v>2418</v>
       </c>
       <c r="P548" t="s">
-        <v>2078</v>
+        <v>2093</v>
       </c>
       <c r="Q548">
         <v>0.85</v>
@@ -73618,7 +73618,7 @@
         <v>2419</v>
       </c>
       <c r="P549" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
       <c r="Q549">
         <v>0.85</v>
@@ -73632,7 +73632,7 @@
         <v>2420</v>
       </c>
       <c r="P550" t="s">
-        <v>2103</v>
+        <v>2060</v>
       </c>
       <c r="Q550">
         <v>0.85</v>
@@ -73646,7 +73646,7 @@
         <v>2421</v>
       </c>
       <c r="P551" t="s">
-        <v>2076</v>
+        <v>2083</v>
       </c>
       <c r="Q551">
         <v>0.85</v>
@@ -73660,7 +73660,7 @@
         <v>2422</v>
       </c>
       <c r="P552" t="s">
-        <v>2106</v>
+        <v>2098</v>
       </c>
       <c r="Q552">
         <v>0.85</v>
@@ -73688,10 +73688,10 @@
         <v>2424</v>
       </c>
       <c r="P554" t="s">
-        <v>2056</v>
+        <v>2106</v>
       </c>
       <c r="Q554">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="555" spans="14:17" x14ac:dyDescent="0.45">
@@ -73702,7 +73702,7 @@
         <v>2425</v>
       </c>
       <c r="P555" t="s">
-        <v>2103</v>
+        <v>2071</v>
       </c>
       <c r="Q555">
         <v>0.85</v>
@@ -73716,7 +73716,7 @@
         <v>2426</v>
       </c>
       <c r="P556" t="s">
-        <v>2106</v>
+        <v>2076</v>
       </c>
       <c r="Q556">
         <v>0.85</v>
@@ -73730,7 +73730,7 @@
         <v>2427</v>
       </c>
       <c r="P557" t="s">
-        <v>2101</v>
+        <v>2060</v>
       </c>
       <c r="Q557">
         <v>0.85</v>
@@ -73744,7 +73744,7 @@
         <v>2428</v>
       </c>
       <c r="P558" t="s">
-        <v>2084</v>
+        <v>2098</v>
       </c>
       <c r="Q558">
         <v>0.85</v>
@@ -73758,7 +73758,7 @@
         <v>2429</v>
       </c>
       <c r="P559" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="Q559">
         <v>0.85</v>
@@ -73772,7 +73772,7 @@
         <v>2430</v>
       </c>
       <c r="P560" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
       <c r="Q560">
         <v>0.85</v>
@@ -73786,7 +73786,7 @@
         <v>2431</v>
       </c>
       <c r="P561" t="s">
-        <v>2106</v>
+        <v>2076</v>
       </c>
       <c r="Q561">
         <v>0.85</v>
@@ -73800,7 +73800,7 @@
         <v>2432</v>
       </c>
       <c r="P562" t="s">
-        <v>2086</v>
+        <v>2054</v>
       </c>
       <c r="Q562">
         <v>0.85</v>
@@ -73814,7 +73814,7 @@
         <v>2433</v>
       </c>
       <c r="P563" t="s">
-        <v>2103</v>
+        <v>2071</v>
       </c>
       <c r="Q563">
         <v>0.85</v>
@@ -73828,7 +73828,7 @@
         <v>2434</v>
       </c>
       <c r="P564" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="Q564">
         <v>0.85</v>
@@ -73842,7 +73842,7 @@
         <v>2435</v>
       </c>
       <c r="P565" t="s">
-        <v>2091</v>
+        <v>2055</v>
       </c>
       <c r="Q565">
         <v>0.85</v>
@@ -73856,7 +73856,7 @@
         <v>2436</v>
       </c>
       <c r="P566" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="Q566">
         <v>0.85</v>
@@ -73870,7 +73870,7 @@
         <v>2437</v>
       </c>
       <c r="P567" t="s">
-        <v>2051</v>
+        <v>2098</v>
       </c>
       <c r="Q567">
         <v>0.85</v>
@@ -73884,7 +73884,7 @@
         <v>2438</v>
       </c>
       <c r="P568" t="s">
-        <v>2103</v>
+        <v>2084</v>
       </c>
       <c r="Q568">
         <v>0.85</v>
@@ -73898,7 +73898,7 @@
         <v>2439</v>
       </c>
       <c r="P569" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="Q569">
         <v>0.85</v>
@@ -73912,7 +73912,7 @@
         <v>2440</v>
       </c>
       <c r="P570" t="s">
-        <v>2101</v>
+        <v>2095</v>
       </c>
       <c r="Q570">
         <v>0.85</v>
@@ -73926,7 +73926,7 @@
         <v>2441</v>
       </c>
       <c r="P571" t="s">
-        <v>2051</v>
+        <v>2062</v>
       </c>
       <c r="Q571">
         <v>0.85</v>
@@ -73940,7 +73940,7 @@
         <v>2442</v>
       </c>
       <c r="P572" t="s">
-        <v>2104</v>
+        <v>2088</v>
       </c>
       <c r="Q572">
         <v>0.85</v>
@@ -73954,7 +73954,7 @@
         <v>2443</v>
       </c>
       <c r="P573" t="s">
-        <v>2095</v>
+        <v>2078</v>
       </c>
       <c r="Q573">
         <v>0.85</v>
@@ -73968,7 +73968,7 @@
         <v>2444</v>
       </c>
       <c r="P574" t="s">
-        <v>2083</v>
+        <v>2065</v>
       </c>
       <c r="Q574">
         <v>0.85</v>
@@ -73982,7 +73982,7 @@
         <v>2445</v>
       </c>
       <c r="P575" t="s">
-        <v>2104</v>
+        <v>2088</v>
       </c>
       <c r="Q575">
         <v>0.85</v>
@@ -73996,7 +73996,7 @@
         <v>2446</v>
       </c>
       <c r="P576" t="s">
-        <v>2077</v>
+        <v>2108</v>
       </c>
       <c r="Q576">
         <v>0.85</v>
@@ -74010,7 +74010,7 @@
         <v>2447</v>
       </c>
       <c r="P577" t="s">
-        <v>2058</v>
+        <v>2053</v>
       </c>
       <c r="Q577">
         <v>0.85</v>
@@ -74024,7 +74024,7 @@
         <v>2448</v>
       </c>
       <c r="P578" t="s">
-        <v>2053</v>
+        <v>2096</v>
       </c>
       <c r="Q578">
         <v>0.85</v>
@@ -74038,7 +74038,7 @@
         <v>2449</v>
       </c>
       <c r="P579" t="s">
-        <v>2063</v>
+        <v>2082</v>
       </c>
       <c r="Q579">
         <v>0.85</v>
@@ -74052,10 +74052,10 @@
         <v>2450</v>
       </c>
       <c r="P580" t="s">
-        <v>2063</v>
+        <v>2098</v>
       </c>
       <c r="Q580">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="581" spans="14:17" x14ac:dyDescent="0.45">
@@ -74066,7 +74066,7 @@
         <v>2451</v>
       </c>
       <c r="P581" t="s">
-        <v>2052</v>
+        <v>2093</v>
       </c>
       <c r="Q581">
         <v>0.85</v>
@@ -74080,7 +74080,7 @@
         <v>2452</v>
       </c>
       <c r="P582" t="s">
-        <v>2104</v>
+        <v>2080</v>
       </c>
       <c r="Q582">
         <v>0.85</v>
@@ -74094,7 +74094,7 @@
         <v>2453</v>
       </c>
       <c r="P583" t="s">
-        <v>2106</v>
+        <v>2052</v>
       </c>
       <c r="Q583">
         <v>0.85</v>
@@ -74108,7 +74108,7 @@
         <v>2454</v>
       </c>
       <c r="P584" t="s">
-        <v>2054</v>
+        <v>2101</v>
       </c>
       <c r="Q584">
         <v>0.85</v>
@@ -74122,7 +74122,7 @@
         <v>2455</v>
       </c>
       <c r="P585" t="s">
-        <v>2103</v>
+        <v>2089</v>
       </c>
       <c r="Q585">
         <v>0.85</v>
@@ -74136,7 +74136,7 @@
         <v>2456</v>
       </c>
       <c r="P586" t="s">
-        <v>2099</v>
+        <v>2089</v>
       </c>
       <c r="Q586">
         <v>0.85</v>
@@ -74150,7 +74150,7 @@
         <v>2457</v>
       </c>
       <c r="P587" t="s">
-        <v>2095</v>
+        <v>2059</v>
       </c>
       <c r="Q587">
         <v>0.85</v>
@@ -74164,7 +74164,7 @@
         <v>2458</v>
       </c>
       <c r="P588" t="s">
-        <v>2082</v>
+        <v>2071</v>
       </c>
       <c r="Q588">
         <v>0.85</v>
@@ -74178,7 +74178,7 @@
         <v>2459</v>
       </c>
       <c r="P589" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="Q589">
         <v>0.85</v>
@@ -74192,7 +74192,7 @@
         <v>2460</v>
       </c>
       <c r="P590" t="s">
-        <v>2076</v>
+        <v>2093</v>
       </c>
       <c r="Q590">
         <v>0.85</v>
@@ -74206,7 +74206,7 @@
         <v>2461</v>
       </c>
       <c r="P591" t="s">
-        <v>2089</v>
+        <v>2102</v>
       </c>
       <c r="Q591">
         <v>0.85</v>
@@ -74234,7 +74234,7 @@
         <v>2463</v>
       </c>
       <c r="P593" t="s">
-        <v>2103</v>
+        <v>2078</v>
       </c>
       <c r="Q593">
         <v>0.85</v>
@@ -74248,7 +74248,7 @@
         <v>2464</v>
       </c>
       <c r="P594" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="Q594">
         <v>0.85</v>
@@ -74262,7 +74262,7 @@
         <v>2465</v>
       </c>
       <c r="P595" t="s">
-        <v>2075</v>
+        <v>2095</v>
       </c>
       <c r="Q595">
         <v>0.85</v>
@@ -74290,7 +74290,7 @@
         <v>2467</v>
       </c>
       <c r="P597" t="s">
-        <v>2109</v>
+        <v>2081</v>
       </c>
       <c r="Q597">
         <v>0.85</v>
@@ -74304,7 +74304,7 @@
         <v>2468</v>
       </c>
       <c r="P598" t="s">
-        <v>2095</v>
+        <v>2089</v>
       </c>
       <c r="Q598">
         <v>0.85</v>
@@ -74318,7 +74318,7 @@
         <v>2469</v>
       </c>
       <c r="P599" t="s">
-        <v>2051</v>
+        <v>2086</v>
       </c>
       <c r="Q599">
         <v>0.85</v>
@@ -74332,7 +74332,7 @@
         <v>2470</v>
       </c>
       <c r="P600" t="s">
-        <v>2090</v>
+        <v>2071</v>
       </c>
       <c r="Q600">
         <v>0.85</v>
@@ -74346,10 +74346,10 @@
         <v>2471</v>
       </c>
       <c r="P601" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="Q601">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="602" spans="14:17" x14ac:dyDescent="0.45">
@@ -74360,10 +74360,10 @@
         <v>2472</v>
       </c>
       <c r="P602" t="s">
-        <v>2109</v>
+        <v>2082</v>
       </c>
       <c r="Q602">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="603" spans="14:17" x14ac:dyDescent="0.45">
@@ -74374,7 +74374,7 @@
         <v>2473</v>
       </c>
       <c r="P603" t="s">
-        <v>2081</v>
+        <v>2060</v>
       </c>
       <c r="Q603">
         <v>0.85</v>
@@ -74388,7 +74388,7 @@
         <v>2474</v>
       </c>
       <c r="P604" t="s">
-        <v>2092</v>
+        <v>2065</v>
       </c>
       <c r="Q604">
         <v>0.85</v>
@@ -74402,7 +74402,7 @@
         <v>2475</v>
       </c>
       <c r="P605" t="s">
-        <v>2081</v>
+        <v>2060</v>
       </c>
       <c r="Q605">
         <v>0.85</v>
@@ -74416,7 +74416,7 @@
         <v>2476</v>
       </c>
       <c r="P606" t="s">
-        <v>2081</v>
+        <v>2106</v>
       </c>
       <c r="Q606">
         <v>0.85</v>
@@ -74430,7 +74430,7 @@
         <v>2477</v>
       </c>
       <c r="P607" t="s">
-        <v>2062</v>
+        <v>2106</v>
       </c>
       <c r="Q607">
         <v>0.85</v>
@@ -74444,7 +74444,7 @@
         <v>2478</v>
       </c>
       <c r="P608" t="s">
-        <v>2106</v>
+        <v>2086</v>
       </c>
       <c r="Q608">
         <v>0.85</v>
@@ -74458,7 +74458,7 @@
         <v>2479</v>
       </c>
       <c r="P609" t="s">
-        <v>2095</v>
+        <v>2076</v>
       </c>
       <c r="Q609">
         <v>0.85</v>
@@ -74472,7 +74472,7 @@
         <v>2480</v>
       </c>
       <c r="P610" t="s">
-        <v>2069</v>
+        <v>2077</v>
       </c>
       <c r="Q610">
         <v>0.85</v>
@@ -74486,7 +74486,7 @@
         <v>2481</v>
       </c>
       <c r="P611" t="s">
-        <v>2058</v>
+        <v>2081</v>
       </c>
       <c r="Q611">
         <v>0.85</v>
@@ -74500,7 +74500,7 @@
         <v>2482</v>
       </c>
       <c r="P612" t="s">
-        <v>2089</v>
+        <v>2060</v>
       </c>
       <c r="Q612">
         <v>0.85</v>
@@ -74514,7 +74514,7 @@
         <v>2483</v>
       </c>
       <c r="P613" t="s">
-        <v>2060</v>
+        <v>2051</v>
       </c>
       <c r="Q613">
         <v>0.85</v>
@@ -74528,7 +74528,7 @@
         <v>2484</v>
       </c>
       <c r="P614" t="s">
-        <v>2083</v>
+        <v>2063</v>
       </c>
       <c r="Q614">
         <v>0.85</v>
@@ -74542,7 +74542,7 @@
         <v>2485</v>
       </c>
       <c r="P615" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="Q615">
         <v>0.85</v>
@@ -74556,7 +74556,7 @@
         <v>2486</v>
       </c>
       <c r="P616" t="s">
-        <v>2055</v>
+        <v>2093</v>
       </c>
       <c r="Q616">
         <v>0.85</v>
@@ -74570,7 +74570,7 @@
         <v>2487</v>
       </c>
       <c r="P617" t="s">
-        <v>2086</v>
+        <v>2056</v>
       </c>
       <c r="Q617">
         <v>0.85</v>
@@ -74584,7 +74584,7 @@
         <v>2488</v>
       </c>
       <c r="P618" t="s">
-        <v>2089</v>
+        <v>2055</v>
       </c>
       <c r="Q618">
         <v>0.85</v>
@@ -74598,7 +74598,7 @@
         <v>2489</v>
       </c>
       <c r="P619" t="s">
-        <v>2072</v>
+        <v>2076</v>
       </c>
       <c r="Q619">
         <v>0.85</v>
@@ -74612,7 +74612,7 @@
         <v>2490</v>
       </c>
       <c r="P620" t="s">
-        <v>2076</v>
+        <v>2060</v>
       </c>
       <c r="Q620">
         <v>0.85</v>
@@ -74626,7 +74626,7 @@
         <v>2491</v>
       </c>
       <c r="P621" t="s">
-        <v>2055</v>
+        <v>2071</v>
       </c>
       <c r="Q621">
         <v>0.85</v>
@@ -74640,7 +74640,7 @@
         <v>2492</v>
       </c>
       <c r="P622" t="s">
-        <v>2076</v>
+        <v>2059</v>
       </c>
       <c r="Q622">
         <v>0.85</v>
@@ -74654,7 +74654,7 @@
         <v>2493</v>
       </c>
       <c r="P623" t="s">
-        <v>2051</v>
+        <v>2101</v>
       </c>
       <c r="Q623">
         <v>0.85</v>
@@ -74668,7 +74668,7 @@
         <v>2494</v>
       </c>
       <c r="P624" t="s">
-        <v>2051</v>
+        <v>2081</v>
       </c>
       <c r="Q624">
         <v>0.85</v>
@@ -74682,7 +74682,7 @@
         <v>2495</v>
       </c>
       <c r="P625" t="s">
-        <v>2106</v>
+        <v>2060</v>
       </c>
       <c r="Q625">
         <v>0.85</v>
@@ -74696,7 +74696,7 @@
         <v>2496</v>
       </c>
       <c r="P626" t="s">
-        <v>2108</v>
+        <v>2081</v>
       </c>
       <c r="Q626">
         <v>0.85</v>
@@ -74710,7 +74710,7 @@
         <v>2497</v>
       </c>
       <c r="P627" t="s">
-        <v>2108</v>
+        <v>2076</v>
       </c>
       <c r="Q627">
         <v>0.85</v>
@@ -74724,7 +74724,7 @@
         <v>2498</v>
       </c>
       <c r="P628" t="s">
-        <v>2096</v>
+        <v>2075</v>
       </c>
       <c r="Q628">
         <v>0.85</v>
@@ -74738,7 +74738,7 @@
         <v>2499</v>
       </c>
       <c r="P629" t="s">
-        <v>2058</v>
+        <v>2107</v>
       </c>
       <c r="Q629">
         <v>0.85</v>
@@ -74752,7 +74752,7 @@
         <v>2500</v>
       </c>
       <c r="P630" t="s">
-        <v>2103</v>
+        <v>2062</v>
       </c>
       <c r="Q630">
         <v>0.85</v>
@@ -74766,7 +74766,7 @@
         <v>2501</v>
       </c>
       <c r="P631" t="s">
-        <v>2098</v>
+        <v>2069</v>
       </c>
       <c r="Q631">
         <v>0.85</v>
@@ -74780,7 +74780,7 @@
         <v>2502</v>
       </c>
       <c r="P632" t="s">
-        <v>2099</v>
+        <v>2089</v>
       </c>
       <c r="Q632">
         <v>0.85</v>
@@ -74794,10 +74794,10 @@
         <v>2503</v>
       </c>
       <c r="P633" t="s">
-        <v>2090</v>
+        <v>2071</v>
       </c>
       <c r="Q633">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="634" spans="14:17" x14ac:dyDescent="0.45">
@@ -74808,7 +74808,7 @@
         <v>2504</v>
       </c>
       <c r="P634" t="s">
-        <v>2093</v>
+        <v>2073</v>
       </c>
       <c r="Q634">
         <v>0.85</v>
@@ -74822,7 +74822,7 @@
         <v>2505</v>
       </c>
       <c r="P635" t="s">
-        <v>2065</v>
+        <v>2075</v>
       </c>
       <c r="Q635">
         <v>0.85</v>
@@ -74836,7 +74836,7 @@
         <v>2506</v>
       </c>
       <c r="P636" t="s">
-        <v>2084</v>
+        <v>2072</v>
       </c>
       <c r="Q636">
         <v>0.85</v>
@@ -74850,7 +74850,7 @@
         <v>2507</v>
       </c>
       <c r="P637" t="s">
-        <v>2101</v>
+        <v>2109</v>
       </c>
       <c r="Q637">
         <v>0.85</v>
@@ -74864,10 +74864,10 @@
         <v>2508</v>
       </c>
       <c r="P638" t="s">
-        <v>2098</v>
+        <v>2063</v>
       </c>
       <c r="Q638">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="639" spans="14:17" x14ac:dyDescent="0.45">
@@ -74878,7 +74878,7 @@
         <v>2509</v>
       </c>
       <c r="P639" t="s">
-        <v>2051</v>
+        <v>2089</v>
       </c>
       <c r="Q639">
         <v>0.85</v>
@@ -74892,7 +74892,7 @@
         <v>2510</v>
       </c>
       <c r="P640" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="Q640">
         <v>0.85</v>
@@ -74906,7 +74906,7 @@
         <v>2511</v>
       </c>
       <c r="P641" t="s">
-        <v>2098</v>
+        <v>2065</v>
       </c>
       <c r="Q641">
         <v>0.85</v>
@@ -74920,7 +74920,7 @@
         <v>2512</v>
       </c>
       <c r="P642" t="s">
-        <v>2069</v>
+        <v>2051</v>
       </c>
       <c r="Q642">
         <v>0.85</v>
@@ -74934,7 +74934,7 @@
         <v>2513</v>
       </c>
       <c r="P643" t="s">
-        <v>2077</v>
+        <v>2064</v>
       </c>
       <c r="Q643">
         <v>0.85</v>
@@ -74948,7 +74948,7 @@
         <v>2514</v>
       </c>
       <c r="P644" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="Q644">
         <v>0.85</v>
@@ -74962,7 +74962,7 @@
         <v>2515</v>
       </c>
       <c r="P645" t="s">
-        <v>2101</v>
+        <v>2051</v>
       </c>
       <c r="Q645">
         <v>0.85</v>
@@ -74976,7 +74976,7 @@
         <v>2516</v>
       </c>
       <c r="P646" t="s">
-        <v>2073</v>
+        <v>2089</v>
       </c>
       <c r="Q646">
         <v>0.85</v>
@@ -74990,7 +74990,7 @@
         <v>2517</v>
       </c>
       <c r="P647" t="s">
-        <v>2106</v>
+        <v>2063</v>
       </c>
       <c r="Q647">
         <v>0.85</v>
@@ -75004,7 +75004,7 @@
         <v>2518</v>
       </c>
       <c r="P648" t="s">
-        <v>2096</v>
+        <v>2109</v>
       </c>
       <c r="Q648">
         <v>0.85</v>
@@ -75018,7 +75018,7 @@
         <v>2519</v>
       </c>
       <c r="P649" t="s">
-        <v>2063</v>
+        <v>2051</v>
       </c>
       <c r="Q649">
         <v>0.85</v>
@@ -75032,7 +75032,7 @@
         <v>2520</v>
       </c>
       <c r="P650" t="s">
-        <v>2083</v>
+        <v>2077</v>
       </c>
       <c r="Q650">
         <v>0.85</v>
@@ -75046,7 +75046,7 @@
         <v>2521</v>
       </c>
       <c r="P651" t="s">
-        <v>2094</v>
+        <v>2104</v>
       </c>
       <c r="Q651">
         <v>0.85</v>
@@ -75060,7 +75060,7 @@
         <v>2522</v>
       </c>
       <c r="P652" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="Q652">
         <v>0.85</v>
@@ -75074,7 +75074,7 @@
         <v>2523</v>
       </c>
       <c r="P653" t="s">
-        <v>2071</v>
+        <v>2083</v>
       </c>
       <c r="Q653">
         <v>0.85</v>
@@ -75088,7 +75088,7 @@
         <v>2524</v>
       </c>
       <c r="P654" t="s">
-        <v>2105</v>
+        <v>2052</v>
       </c>
       <c r="Q654">
         <v>0.85</v>
@@ -75102,7 +75102,7 @@
         <v>2525</v>
       </c>
       <c r="P655" t="s">
-        <v>2077</v>
+        <v>2104</v>
       </c>
       <c r="Q655">
         <v>0.85</v>
@@ -75116,7 +75116,7 @@
         <v>2526</v>
       </c>
       <c r="P656" t="s">
-        <v>2109</v>
+        <v>2089</v>
       </c>
       <c r="Q656">
         <v>0.85</v>
@@ -75130,7 +75130,7 @@
         <v>2527</v>
       </c>
       <c r="P657" t="s">
-        <v>2103</v>
+        <v>2093</v>
       </c>
       <c r="Q657">
         <v>0.85</v>
@@ -75144,7 +75144,7 @@
         <v>2528</v>
       </c>
       <c r="P658" t="s">
-        <v>2098</v>
+        <v>2093</v>
       </c>
       <c r="Q658">
         <v>0.85</v>
@@ -75158,7 +75158,7 @@
         <v>2529</v>
       </c>
       <c r="P659" t="s">
-        <v>2103</v>
+        <v>2051</v>
       </c>
       <c r="Q659">
         <v>0.85</v>
@@ -75172,7 +75172,7 @@
         <v>2530</v>
       </c>
       <c r="P660" t="s">
-        <v>2083</v>
+        <v>2075</v>
       </c>
       <c r="Q660">
         <v>0.85</v>
@@ -75186,7 +75186,7 @@
         <v>2531</v>
       </c>
       <c r="P661" t="s">
-        <v>2101</v>
+        <v>2063</v>
       </c>
       <c r="Q661">
         <v>0.85</v>
@@ -75200,7 +75200,7 @@
         <v>2532</v>
       </c>
       <c r="P662" t="s">
-        <v>2102</v>
+        <v>2084</v>
       </c>
       <c r="Q662">
         <v>0.85</v>
@@ -75214,7 +75214,7 @@
         <v>2533</v>
       </c>
       <c r="P663" t="s">
-        <v>2106</v>
+        <v>2088</v>
       </c>
       <c r="Q663">
         <v>0.85</v>
@@ -75228,7 +75228,7 @@
         <v>2534</v>
       </c>
       <c r="P664" t="s">
-        <v>2106</v>
+        <v>2083</v>
       </c>
       <c r="Q664">
         <v>0.85</v>
@@ -75242,7 +75242,7 @@
         <v>2535</v>
       </c>
       <c r="P665" t="s">
-        <v>2092</v>
+        <v>2071</v>
       </c>
       <c r="Q665">
         <v>0.85</v>
@@ -75256,7 +75256,7 @@
         <v>2536</v>
       </c>
       <c r="P666" t="s">
-        <v>2051</v>
+        <v>2104</v>
       </c>
       <c r="Q666">
         <v>0.85</v>
@@ -75270,7 +75270,7 @@
         <v>2537</v>
       </c>
       <c r="P667" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="Q667">
         <v>0.85</v>
@@ -75284,7 +75284,7 @@
         <v>2538</v>
       </c>
       <c r="P668" t="s">
-        <v>2097</v>
+        <v>2105</v>
       </c>
       <c r="Q668">
         <v>0.85</v>
@@ -75298,7 +75298,7 @@
         <v>2539</v>
       </c>
       <c r="P669" t="s">
-        <v>2058</v>
+        <v>2071</v>
       </c>
       <c r="Q669">
         <v>0.85</v>
@@ -75312,7 +75312,7 @@
         <v>2540</v>
       </c>
       <c r="P670" t="s">
-        <v>2055</v>
+        <v>2090</v>
       </c>
       <c r="Q670">
         <v>0.85</v>
@@ -75326,7 +75326,7 @@
         <v>2541</v>
       </c>
       <c r="P671" t="s">
-        <v>2096</v>
+        <v>2106</v>
       </c>
       <c r="Q671">
         <v>0.85</v>
@@ -75340,7 +75340,7 @@
         <v>2542</v>
       </c>
       <c r="P672" t="s">
-        <v>2086</v>
+        <v>2076</v>
       </c>
       <c r="Q672">
         <v>0.85</v>
@@ -75354,7 +75354,7 @@
         <v>2543</v>
       </c>
       <c r="P673" t="s">
-        <v>2067</v>
+        <v>2057</v>
       </c>
       <c r="Q673">
         <v>0.85</v>
@@ -75368,10 +75368,10 @@
         <v>2544</v>
       </c>
       <c r="P674" t="s">
-        <v>2071</v>
+        <v>2101</v>
       </c>
       <c r="Q674">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="675" spans="14:17" x14ac:dyDescent="0.45">
@@ -75382,10 +75382,10 @@
         <v>2545</v>
       </c>
       <c r="P675" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="Q675">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="676" spans="14:17" x14ac:dyDescent="0.45">
@@ -75396,10 +75396,10 @@
         <v>2546</v>
       </c>
       <c r="P676" t="s">
-        <v>2065</v>
+        <v>2103</v>
       </c>
       <c r="Q676">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="677" spans="14:17" x14ac:dyDescent="0.45">
@@ -75410,10 +75410,10 @@
         <v>2547</v>
       </c>
       <c r="P677" t="s">
-        <v>2106</v>
+        <v>2086</v>
       </c>
       <c r="Q677">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="678" spans="14:17" x14ac:dyDescent="0.45">
@@ -75424,10 +75424,10 @@
         <v>2548</v>
       </c>
       <c r="P678" t="s">
-        <v>2089</v>
+        <v>2103</v>
       </c>
       <c r="Q678">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="679" spans="14:17" x14ac:dyDescent="0.45">
@@ -75438,7 +75438,7 @@
         <v>2549</v>
       </c>
       <c r="P679" t="s">
-        <v>2053</v>
+        <v>2065</v>
       </c>
       <c r="Q679">
         <v>0.85</v>
@@ -75452,7 +75452,7 @@
         <v>2550</v>
       </c>
       <c r="P680" t="s">
-        <v>2106</v>
+        <v>2065</v>
       </c>
       <c r="Q680">
         <v>0.85</v>
@@ -75466,7 +75466,7 @@
         <v>2551</v>
       </c>
       <c r="P681" t="s">
-        <v>2056</v>
+        <v>2103</v>
       </c>
       <c r="Q681">
         <v>0.85</v>
@@ -75480,7 +75480,7 @@
         <v>2552</v>
       </c>
       <c r="P682" t="s">
-        <v>2106</v>
+        <v>2069</v>
       </c>
       <c r="Q682">
         <v>0.85</v>
@@ -75494,7 +75494,7 @@
         <v>2553</v>
       </c>
       <c r="P683" t="s">
-        <v>2087</v>
+        <v>2068</v>
       </c>
       <c r="Q683">
         <v>0.85</v>
@@ -75508,7 +75508,7 @@
         <v>2554</v>
       </c>
       <c r="P684" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="Q684">
         <v>0.85</v>
@@ -75522,10 +75522,10 @@
         <v>2555</v>
       </c>
       <c r="P685" t="s">
-        <v>2075</v>
+        <v>2084</v>
       </c>
       <c r="Q685">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="686" spans="14:17" x14ac:dyDescent="0.45">
@@ -75536,10 +75536,10 @@
         <v>2556</v>
       </c>
       <c r="P686" t="s">
-        <v>2086</v>
+        <v>2058</v>
       </c>
       <c r="Q686">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="687" spans="14:17" x14ac:dyDescent="0.45">
@@ -75550,10 +75550,10 @@
         <v>2557</v>
       </c>
       <c r="P687" t="s">
-        <v>2069</v>
+        <v>2078</v>
       </c>
       <c r="Q687">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="688" spans="14:17" x14ac:dyDescent="0.45">
@@ -75564,10 +75564,10 @@
         <v>2558</v>
       </c>
       <c r="P688" t="s">
-        <v>2089</v>
+        <v>2071</v>
       </c>
       <c r="Q688">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="689" spans="14:17" x14ac:dyDescent="0.45">
@@ -75578,10 +75578,10 @@
         <v>2559</v>
       </c>
       <c r="P689" t="s">
-        <v>2075</v>
+        <v>2065</v>
       </c>
       <c r="Q689">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="690" spans="14:17" x14ac:dyDescent="0.45">
@@ -75592,10 +75592,10 @@
         <v>2560</v>
       </c>
       <c r="P690" t="s">
-        <v>2077</v>
+        <v>2060</v>
       </c>
       <c r="Q690">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="691" spans="14:17" x14ac:dyDescent="0.45">
@@ -75606,7 +75606,7 @@
         <v>2561</v>
       </c>
       <c r="P691" t="s">
-        <v>2081</v>
+        <v>2055</v>
       </c>
       <c r="Q691">
         <v>0.85</v>
@@ -75620,7 +75620,7 @@
         <v>2562</v>
       </c>
       <c r="P692" t="s">
-        <v>2058</v>
+        <v>2102</v>
       </c>
       <c r="Q692">
         <v>0.85</v>
@@ -75634,7 +75634,7 @@
         <v>2563</v>
       </c>
       <c r="P693" t="s">
-        <v>2096</v>
+        <v>2051</v>
       </c>
       <c r="Q693">
         <v>0.85</v>
@@ -75648,7 +75648,7 @@
         <v>2564</v>
       </c>
       <c r="P694" t="s">
-        <v>2100</v>
+        <v>2087</v>
       </c>
       <c r="Q694">
         <v>0.85</v>
@@ -75676,7 +75676,7 @@
         <v>2566</v>
       </c>
       <c r="P696" t="s">
-        <v>2087</v>
+        <v>2051</v>
       </c>
       <c r="Q696">
         <v>0.85</v>
@@ -75690,7 +75690,7 @@
         <v>2567</v>
       </c>
       <c r="P697" t="s">
-        <v>2060</v>
+        <v>2094</v>
       </c>
       <c r="Q697">
         <v>0.85</v>
@@ -75704,7 +75704,7 @@
         <v>2568</v>
       </c>
       <c r="P698" t="s">
-        <v>2095</v>
+        <v>2104</v>
       </c>
       <c r="Q698">
         <v>0.85</v>
@@ -75718,10 +75718,10 @@
         <v>2569</v>
       </c>
       <c r="P699" t="s">
-        <v>2089</v>
+        <v>2094</v>
       </c>
       <c r="Q699">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="700" spans="14:17" x14ac:dyDescent="0.45">
@@ -75732,7 +75732,7 @@
         <v>2570</v>
       </c>
       <c r="P700" t="s">
-        <v>2097</v>
+        <v>2081</v>
       </c>
       <c r="Q700">
         <v>0.85</v>
@@ -75746,7 +75746,7 @@
         <v>2571</v>
       </c>
       <c r="P701" t="s">
-        <v>2065</v>
+        <v>2051</v>
       </c>
       <c r="Q701">
         <v>0.85</v>
@@ -75760,7 +75760,7 @@
         <v>2572</v>
       </c>
       <c r="P702" t="s">
-        <v>2052</v>
+        <v>2096</v>
       </c>
       <c r="Q702">
         <v>0.85</v>
@@ -75774,7 +75774,7 @@
         <v>2573</v>
       </c>
       <c r="P703" t="s">
-        <v>2051</v>
+        <v>2103</v>
       </c>
       <c r="Q703">
         <v>0.85</v>
@@ -75788,7 +75788,7 @@
         <v>2574</v>
       </c>
       <c r="P704" t="s">
-        <v>2103</v>
+        <v>2099</v>
       </c>
       <c r="Q704">
         <v>0.85</v>
@@ -75802,7 +75802,7 @@
         <v>2575</v>
       </c>
       <c r="P705" t="s">
-        <v>2101</v>
+        <v>2083</v>
       </c>
       <c r="Q705">
         <v>0.85</v>
@@ -75816,7 +75816,7 @@
         <v>2576</v>
       </c>
       <c r="P706" t="s">
-        <v>2070</v>
+        <v>2067</v>
       </c>
       <c r="Q706">
         <v>0.85</v>
@@ -75830,7 +75830,7 @@
         <v>2577</v>
       </c>
       <c r="P707" t="s">
-        <v>2073</v>
+        <v>2093</v>
       </c>
       <c r="Q707">
         <v>0.85</v>
@@ -75844,7 +75844,7 @@
         <v>2578</v>
       </c>
       <c r="P708" t="s">
-        <v>2095</v>
+        <v>2082</v>
       </c>
       <c r="Q708">
         <v>0.85</v>
@@ -75858,7 +75858,7 @@
         <v>2579</v>
       </c>
       <c r="P709" t="s">
-        <v>2079</v>
+        <v>2068</v>
       </c>
       <c r="Q709">
         <v>0.85</v>
@@ -75872,7 +75872,7 @@
         <v>2580</v>
       </c>
       <c r="P710" t="s">
-        <v>2088</v>
+        <v>2081</v>
       </c>
       <c r="Q710">
         <v>0.85</v>
@@ -75886,7 +75886,7 @@
         <v>2581</v>
       </c>
       <c r="P711" t="s">
-        <v>2106</v>
+        <v>2089</v>
       </c>
       <c r="Q711">
         <v>0.85</v>
@@ -75900,7 +75900,7 @@
         <v>2582</v>
       </c>
       <c r="P712" t="s">
-        <v>2090</v>
+        <v>2104</v>
       </c>
       <c r="Q712">
         <v>0.85</v>
@@ -75914,7 +75914,7 @@
         <v>2583</v>
       </c>
       <c r="P713" t="s">
-        <v>2051</v>
+        <v>2097</v>
       </c>
       <c r="Q713">
         <v>0.85</v>
@@ -75928,10 +75928,10 @@
         <v>2584</v>
       </c>
       <c r="P714" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
       <c r="Q714">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="715" spans="14:17" x14ac:dyDescent="0.45">
@@ -75942,7 +75942,7 @@
         <v>2585</v>
       </c>
       <c r="P715" t="s">
-        <v>2103</v>
+        <v>2095</v>
       </c>
       <c r="Q715">
         <v>0.85</v>
@@ -75956,7 +75956,7 @@
         <v>2586</v>
       </c>
       <c r="P716" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="Q716">
         <v>0.85</v>
@@ -75970,7 +75970,7 @@
         <v>2587</v>
       </c>
       <c r="P717" t="s">
-        <v>2089</v>
+        <v>2053</v>
       </c>
       <c r="Q717">
         <v>0.85</v>
@@ -75984,7 +75984,7 @@
         <v>2588</v>
       </c>
       <c r="P718" t="s">
-        <v>2055</v>
+        <v>2076</v>
       </c>
       <c r="Q718">
         <v>0.85</v>
@@ -75998,7 +75998,7 @@
         <v>2589</v>
       </c>
       <c r="P719" t="s">
-        <v>2086</v>
+        <v>2098</v>
       </c>
       <c r="Q719">
         <v>0.85</v>
@@ -76012,7 +76012,7 @@
         <v>2590</v>
       </c>
       <c r="P720" t="s">
-        <v>2098</v>
+        <v>2088</v>
       </c>
       <c r="Q720">
         <v>0.85</v>
@@ -76026,7 +76026,7 @@
         <v>2591</v>
       </c>
       <c r="P721" t="s">
-        <v>2058</v>
+        <v>2103</v>
       </c>
       <c r="Q721">
         <v>0.85</v>
@@ -76040,7 +76040,7 @@
         <v>2592</v>
       </c>
       <c r="P722" t="s">
-        <v>2088</v>
+        <v>2081</v>
       </c>
       <c r="Q722">
         <v>0.85</v>
@@ -76054,7 +76054,7 @@
         <v>2593</v>
       </c>
       <c r="P723" t="s">
-        <v>2106</v>
+        <v>2056</v>
       </c>
       <c r="Q723">
         <v>0.85</v>
@@ -76068,7 +76068,7 @@
         <v>2594</v>
       </c>
       <c r="P724" t="s">
-        <v>2101</v>
+        <v>2080</v>
       </c>
       <c r="Q724">
         <v>0.85</v>
@@ -76082,10 +76082,10 @@
         <v>2595</v>
       </c>
       <c r="P725" t="s">
-        <v>2075</v>
+        <v>2051</v>
       </c>
       <c r="Q725">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="726" spans="14:17" x14ac:dyDescent="0.45">
@@ -76096,10 +76096,10 @@
         <v>2596</v>
       </c>
       <c r="P726" t="s">
-        <v>2077</v>
+        <v>2104</v>
       </c>
       <c r="Q726">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="727" spans="14:17" x14ac:dyDescent="0.45">
@@ -76110,7 +76110,7 @@
         <v>2597</v>
       </c>
       <c r="P727" t="s">
-        <v>2055</v>
+        <v>2103</v>
       </c>
       <c r="Q727">
         <v>0.85</v>
@@ -76124,7 +76124,7 @@
         <v>2598</v>
       </c>
       <c r="P728" t="s">
-        <v>2055</v>
+        <v>2090</v>
       </c>
       <c r="Q728">
         <v>0.85</v>
@@ -76138,7 +76138,7 @@
         <v>2599</v>
       </c>
       <c r="P729" t="s">
-        <v>2109</v>
+        <v>2058</v>
       </c>
       <c r="Q729">
         <v>0.85</v>
@@ -76152,7 +76152,7 @@
         <v>2600</v>
       </c>
       <c r="P730" t="s">
-        <v>2107</v>
+        <v>2096</v>
       </c>
       <c r="Q730">
         <v>0.85</v>
@@ -76166,7 +76166,7 @@
         <v>2601</v>
       </c>
       <c r="P731" t="s">
-        <v>2068</v>
+        <v>2062</v>
       </c>
       <c r="Q731">
         <v>0.85</v>
@@ -76180,7 +76180,7 @@
         <v>2602</v>
       </c>
       <c r="P732" t="s">
-        <v>2071</v>
+        <v>2055</v>
       </c>
       <c r="Q732">
         <v>0.85</v>
@@ -76194,7 +76194,7 @@
         <v>2603</v>
       </c>
       <c r="P733" t="s">
-        <v>2083</v>
+        <v>2097</v>
       </c>
       <c r="Q733">
         <v>0.85</v>
@@ -76208,7 +76208,7 @@
         <v>2604</v>
       </c>
       <c r="P734" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="Q734">
         <v>0.85</v>
@@ -76222,7 +76222,7 @@
         <v>2605</v>
       </c>
       <c r="P735" t="s">
-        <v>2104</v>
+        <v>2077</v>
       </c>
       <c r="Q735">
         <v>0.85</v>
@@ -76236,7 +76236,7 @@
         <v>2606</v>
       </c>
       <c r="P736" t="s">
-        <v>2086</v>
+        <v>2075</v>
       </c>
       <c r="Q736">
         <v>0.85</v>
@@ -76250,7 +76250,7 @@
         <v>2607</v>
       </c>
       <c r="P737" t="s">
-        <v>2064</v>
+        <v>2101</v>
       </c>
       <c r="Q737">
         <v>0.85</v>
@@ -76264,7 +76264,7 @@
         <v>2608</v>
       </c>
       <c r="P738" t="s">
-        <v>2084</v>
+        <v>2077</v>
       </c>
       <c r="Q738">
         <v>0.85</v>
@@ -76278,7 +76278,7 @@
         <v>2609</v>
       </c>
       <c r="P739" t="s">
-        <v>2096</v>
+        <v>2104</v>
       </c>
       <c r="Q739">
         <v>0.85</v>
@@ -76292,7 +76292,7 @@
         <v>2610</v>
       </c>
       <c r="P740" t="s">
-        <v>2058</v>
+        <v>2089</v>
       </c>
       <c r="Q740">
         <v>0.85</v>
@@ -76306,7 +76306,7 @@
         <v>2611</v>
       </c>
       <c r="P741" t="s">
-        <v>2062</v>
+        <v>2108</v>
       </c>
       <c r="Q741">
         <v>0.85</v>
@@ -76320,7 +76320,7 @@
         <v>2612</v>
       </c>
       <c r="P742" t="s">
-        <v>2055</v>
+        <v>2076</v>
       </c>
       <c r="Q742">
         <v>0.85</v>
@@ -76334,7 +76334,7 @@
         <v>2613</v>
       </c>
       <c r="P743" t="s">
-        <v>2097</v>
+        <v>2084</v>
       </c>
       <c r="Q743">
         <v>0.85</v>
@@ -76348,7 +76348,7 @@
         <v>2614</v>
       </c>
       <c r="P744" t="s">
-        <v>2076</v>
+        <v>2052</v>
       </c>
       <c r="Q744">
         <v>0.85</v>
@@ -76362,7 +76362,7 @@
         <v>2615</v>
       </c>
       <c r="P745" t="s">
-        <v>2058</v>
+        <v>2093</v>
       </c>
       <c r="Q745">
         <v>0.85</v>
@@ -76376,7 +76376,7 @@
         <v>2616</v>
       </c>
       <c r="P746" t="s">
-        <v>2101</v>
+        <v>2074</v>
       </c>
       <c r="Q746">
         <v>0.85</v>
@@ -76390,7 +76390,7 @@
         <v>2617</v>
       </c>
       <c r="P747" t="s">
-        <v>2076</v>
+        <v>2103</v>
       </c>
       <c r="Q747">
         <v>0.85</v>
@@ -76418,7 +76418,7 @@
         <v>2619</v>
       </c>
       <c r="P749" t="s">
-        <v>2108</v>
+        <v>2058</v>
       </c>
       <c r="Q749">
         <v>0.85</v>
@@ -76432,7 +76432,7 @@
         <v>2620</v>
       </c>
       <c r="P750" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="Q750">
         <v>0.85</v>
@@ -76446,7 +76446,7 @@
         <v>2621</v>
       </c>
       <c r="P751" t="s">
-        <v>2052</v>
+        <v>2098</v>
       </c>
       <c r="Q751">
         <v>0.85</v>
@@ -76460,7 +76460,7 @@
         <v>2622</v>
       </c>
       <c r="P752" t="s">
-        <v>2093</v>
+        <v>2055</v>
       </c>
       <c r="Q752">
         <v>0.85</v>
@@ -76474,7 +76474,7 @@
         <v>2623</v>
       </c>
       <c r="P753" t="s">
-        <v>2074</v>
+        <v>2088</v>
       </c>
       <c r="Q753">
         <v>0.85</v>
@@ -76488,7 +76488,7 @@
         <v>2624</v>
       </c>
       <c r="P754" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="Q754">
         <v>0.85</v>
@@ -76502,10 +76502,10 @@
         <v>2625</v>
       </c>
       <c r="P755" t="s">
-        <v>2104</v>
+        <v>2055</v>
       </c>
       <c r="Q755">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="756" spans="14:17" x14ac:dyDescent="0.45">
@@ -76516,10 +76516,10 @@
         <v>2626</v>
       </c>
       <c r="P756" t="s">
-        <v>2051</v>
+        <v>2055</v>
       </c>
       <c r="Q756">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="757" spans="14:17" x14ac:dyDescent="0.45">
@@ -76530,7 +76530,7 @@
         <v>2627</v>
       </c>
       <c r="P757" t="s">
-        <v>2082</v>
+        <v>2109</v>
       </c>
       <c r="Q757">
         <v>0.85</v>
@@ -76544,7 +76544,7 @@
         <v>2628</v>
       </c>
       <c r="P758" t="s">
-        <v>2060</v>
+        <v>2107</v>
       </c>
       <c r="Q758">
         <v>0.85</v>
@@ -76558,7 +76558,7 @@
         <v>2629</v>
       </c>
       <c r="P759" t="s">
-        <v>2106</v>
+        <v>2071</v>
       </c>
       <c r="Q759">
         <v>0.85</v>
@@ -76572,7 +76572,7 @@
         <v>2630</v>
       </c>
       <c r="P760" t="s">
-        <v>2071</v>
+        <v>2083</v>
       </c>
       <c r="Q760">
         <v>0.85</v>
@@ -76586,7 +76586,7 @@
         <v>2631</v>
       </c>
       <c r="P761" t="s">
-        <v>2069</v>
+        <v>2086</v>
       </c>
       <c r="Q761">
         <v>0.85</v>
@@ -76600,7 +76600,7 @@
         <v>2632</v>
       </c>
       <c r="P762" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="Q762">
         <v>0.85</v>
@@ -76614,7 +76614,7 @@
         <v>2633</v>
       </c>
       <c r="P763" t="s">
-        <v>2106</v>
+        <v>2064</v>
       </c>
       <c r="Q763">
         <v>0.85</v>
@@ -76628,7 +76628,7 @@
         <v>2634</v>
       </c>
       <c r="P764" t="s">
-        <v>2080</v>
+        <v>2058</v>
       </c>
       <c r="Q764">
         <v>0.85</v>
@@ -76642,7 +76642,7 @@
         <v>2635</v>
       </c>
       <c r="P765" t="s">
-        <v>2061</v>
+        <v>2101</v>
       </c>
       <c r="Q765">
         <v>0.85</v>
@@ -76656,7 +76656,7 @@
         <v>2636</v>
       </c>
       <c r="P766" t="s">
-        <v>2076</v>
+        <v>2089</v>
       </c>
       <c r="Q766">
         <v>0.85</v>
@@ -76670,10 +76670,10 @@
         <v>2637</v>
       </c>
       <c r="P767" t="s">
-        <v>2083</v>
+        <v>2071</v>
       </c>
       <c r="Q767">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="768" spans="14:17" x14ac:dyDescent="0.45">
@@ -76684,10 +76684,10 @@
         <v>2638</v>
       </c>
       <c r="P768" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
       <c r="Q768">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="769" spans="14:17" x14ac:dyDescent="0.45">
@@ -76698,10 +76698,10 @@
         <v>2639</v>
       </c>
       <c r="P769" t="s">
-        <v>2084</v>
+        <v>2052</v>
       </c>
       <c r="Q769">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="770" spans="14:17" x14ac:dyDescent="0.45">
@@ -76712,10 +76712,10 @@
         <v>2640</v>
       </c>
       <c r="P770" t="s">
-        <v>2089</v>
+        <v>2106</v>
       </c>
       <c r="Q770">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="771" spans="14:17" x14ac:dyDescent="0.45">
@@ -76726,10 +76726,10 @@
         <v>2641</v>
       </c>
       <c r="P771" t="s">
-        <v>2105</v>
+        <v>2065</v>
       </c>
       <c r="Q771">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="772" spans="14:17" x14ac:dyDescent="0.45">
@@ -76740,7 +76740,7 @@
         <v>2642</v>
       </c>
       <c r="P772" t="s">
-        <v>2075</v>
+        <v>2093</v>
       </c>
       <c r="Q772">
         <v>0.85</v>
@@ -76754,7 +76754,7 @@
         <v>2643</v>
       </c>
       <c r="P773" t="s">
-        <v>2076</v>
+        <v>2065</v>
       </c>
       <c r="Q773">
         <v>0.85</v>
@@ -76768,7 +76768,7 @@
         <v>2644</v>
       </c>
       <c r="P774" t="s">
-        <v>2071</v>
+        <v>2084</v>
       </c>
       <c r="Q774">
         <v>0.85</v>
@@ -76782,7 +76782,7 @@
         <v>2645</v>
       </c>
       <c r="P775" t="s">
-        <v>2053</v>
+        <v>2103</v>
       </c>
       <c r="Q775">
         <v>0.85</v>
@@ -76796,7 +76796,7 @@
         <v>2646</v>
       </c>
       <c r="P776" t="s">
-        <v>2055</v>
+        <v>2083</v>
       </c>
       <c r="Q776">
         <v>0.85</v>
@@ -76810,7 +76810,7 @@
         <v>2647</v>
       </c>
       <c r="P777" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="Q777">
         <v>0.85</v>
@@ -76824,7 +76824,7 @@
         <v>2648</v>
       </c>
       <c r="P778" t="s">
-        <v>2093</v>
+        <v>2102</v>
       </c>
       <c r="Q778">
         <v>0.85</v>
@@ -76838,7 +76838,7 @@
         <v>2649</v>
       </c>
       <c r="P779" t="s">
-        <v>2060</v>
+        <v>2106</v>
       </c>
       <c r="Q779">
         <v>0.85</v>
@@ -76852,7 +76852,7 @@
         <v>2650</v>
       </c>
       <c r="P780" t="s">
-        <v>2083</v>
+        <v>2106</v>
       </c>
       <c r="Q780">
         <v>0.85</v>
@@ -76866,7 +76866,7 @@
         <v>2651</v>
       </c>
       <c r="P781" t="s">
-        <v>2093</v>
+        <v>2071</v>
       </c>
       <c r="Q781">
         <v>0.85</v>
@@ -76880,7 +76880,7 @@
         <v>2652</v>
       </c>
       <c r="P782" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="Q782">
         <v>0.85</v>
@@ -76894,7 +76894,7 @@
         <v>2653</v>
       </c>
       <c r="P783" t="s">
-        <v>2098</v>
+        <v>2065</v>
       </c>
       <c r="Q783">
         <v>0.85</v>
@@ -76908,7 +76908,7 @@
         <v>2654</v>
       </c>
       <c r="P784" t="s">
-        <v>2071</v>
+        <v>2077</v>
       </c>
       <c r="Q784">
         <v>0.85</v>
@@ -76922,7 +76922,7 @@
         <v>2655</v>
       </c>
       <c r="P785" t="s">
-        <v>2098</v>
+        <v>2093</v>
       </c>
       <c r="Q785">
         <v>0.85</v>
@@ -76936,10 +76936,10 @@
         <v>2656</v>
       </c>
       <c r="P786" t="s">
-        <v>2053</v>
+        <v>2063</v>
       </c>
       <c r="Q786">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="787" spans="14:17" x14ac:dyDescent="0.45">
@@ -76950,10 +76950,10 @@
         <v>2657</v>
       </c>
       <c r="P787" t="s">
-        <v>2051</v>
+        <v>2083</v>
       </c>
       <c r="Q787">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="788" spans="14:17" x14ac:dyDescent="0.45">
@@ -76964,10 +76964,10 @@
         <v>2658</v>
       </c>
       <c r="P788" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
       <c r="Q788">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="789" spans="14:17" x14ac:dyDescent="0.45">
@@ -76978,7 +76978,7 @@
         <v>2659</v>
       </c>
       <c r="P789" t="s">
-        <v>2065</v>
+        <v>2058</v>
       </c>
       <c r="Q789">
         <v>0.85</v>
@@ -76992,7 +76992,7 @@
         <v>2660</v>
       </c>
       <c r="P790" t="s">
-        <v>2060</v>
+        <v>2067</v>
       </c>
       <c r="Q790">
         <v>0.85</v>
@@ -77006,7 +77006,7 @@
         <v>2661</v>
       </c>
       <c r="P791" t="s">
-        <v>2106</v>
+        <v>2078</v>
       </c>
       <c r="Q791">
         <v>0.85</v>
@@ -77020,7 +77020,7 @@
         <v>2662</v>
       </c>
       <c r="P792" t="s">
-        <v>2060</v>
+        <v>2106</v>
       </c>
       <c r="Q792">
         <v>0.85</v>
@@ -77034,7 +77034,7 @@
         <v>2663</v>
       </c>
       <c r="P793" t="s">
-        <v>2081</v>
+        <v>2106</v>
       </c>
       <c r="Q793">
         <v>0.85</v>
@@ -77048,7 +77048,7 @@
         <v>2664</v>
       </c>
       <c r="P794" t="s">
-        <v>2076</v>
+        <v>2101</v>
       </c>
       <c r="Q794">
         <v>0.85</v>
@@ -77062,7 +77062,7 @@
         <v>2665</v>
       </c>
       <c r="P795" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="Q795">
         <v>0.85</v>
@@ -77076,7 +77076,7 @@
         <v>2666</v>
       </c>
       <c r="P796" t="s">
-        <v>2055</v>
+        <v>2101</v>
       </c>
       <c r="Q796">
         <v>0.85</v>
@@ -77090,7 +77090,7 @@
         <v>2667</v>
       </c>
       <c r="P797" t="s">
-        <v>2086</v>
+        <v>2098</v>
       </c>
       <c r="Q797">
         <v>0.85</v>
@@ -77104,7 +77104,7 @@
         <v>2668</v>
       </c>
       <c r="P798" t="s">
-        <v>2101</v>
+        <v>2051</v>
       </c>
       <c r="Q798">
         <v>0.85</v>
@@ -77118,7 +77118,7 @@
         <v>2669</v>
       </c>
       <c r="P799" t="s">
-        <v>2060</v>
+        <v>2081</v>
       </c>
       <c r="Q799">
         <v>0.85</v>
@@ -77132,7 +77132,7 @@
         <v>2670</v>
       </c>
       <c r="P800" t="s">
-        <v>2081</v>
+        <v>2098</v>
       </c>
       <c r="Q800">
         <v>0.85</v>
@@ -77146,7 +77146,7 @@
         <v>2671</v>
       </c>
       <c r="P801" t="s">
-        <v>2062</v>
+        <v>2055</v>
       </c>
       <c r="Q801">
         <v>0.85</v>
@@ -77160,7 +77160,7 @@
         <v>2672</v>
       </c>
       <c r="P802" t="s">
-        <v>2076</v>
+        <v>2096</v>
       </c>
       <c r="Q802">
         <v>0.85</v>
@@ -77174,7 +77174,7 @@
         <v>2673</v>
       </c>
       <c r="P803" t="s">
-        <v>2087</v>
+        <v>2096</v>
       </c>
       <c r="Q803">
         <v>0.85</v>
@@ -77188,7 +77188,7 @@
         <v>2674</v>
       </c>
       <c r="P804" t="s">
-        <v>2086</v>
+        <v>2071</v>
       </c>
       <c r="Q804">
         <v>0.85</v>
@@ -77216,7 +77216,7 @@
         <v>2676</v>
       </c>
       <c r="P806" t="s">
-        <v>2081</v>
+        <v>2105</v>
       </c>
       <c r="Q806">
         <v>0.85</v>
@@ -77230,7 +77230,7 @@
         <v>2677</v>
       </c>
       <c r="P807" t="s">
-        <v>2089</v>
+        <v>2051</v>
       </c>
       <c r="Q807">
         <v>0.85</v>
@@ -77244,7 +77244,7 @@
         <v>2678</v>
       </c>
       <c r="P808" t="s">
-        <v>2069</v>
+        <v>2058</v>
       </c>
       <c r="Q808">
         <v>0.85</v>
@@ -77258,7 +77258,7 @@
         <v>2679</v>
       </c>
       <c r="P809" t="s">
-        <v>2109</v>
+        <v>2097</v>
       </c>
       <c r="Q809">
         <v>0.85</v>
@@ -77272,7 +77272,7 @@
         <v>2680</v>
       </c>
       <c r="P810" t="s">
-        <v>2106</v>
+        <v>2077</v>
       </c>
       <c r="Q810">
         <v>0.85</v>
@@ -77286,7 +77286,7 @@
         <v>2681</v>
       </c>
       <c r="P811" t="s">
-        <v>2073</v>
+        <v>2109</v>
       </c>
       <c r="Q811">
         <v>0.85</v>
@@ -77300,7 +77300,7 @@
         <v>2682</v>
       </c>
       <c r="P812" t="s">
-        <v>2075</v>
+        <v>2103</v>
       </c>
       <c r="Q812">
         <v>0.85</v>
@@ -77314,7 +77314,7 @@
         <v>2683</v>
       </c>
       <c r="P813" t="s">
-        <v>2055</v>
+        <v>2098</v>
       </c>
       <c r="Q813">
         <v>0.85</v>
@@ -77328,10 +77328,10 @@
         <v>2684</v>
       </c>
       <c r="P814" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="Q814">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="815" spans="14:17" x14ac:dyDescent="0.45">
@@ -77342,7 +77342,7 @@
         <v>2685</v>
       </c>
       <c r="P815" t="s">
-        <v>2060</v>
+        <v>2075</v>
       </c>
       <c r="Q815">
         <v>0.85</v>
@@ -77356,7 +77356,7 @@
         <v>2686</v>
       </c>
       <c r="P816" t="s">
-        <v>2060</v>
+        <v>2073</v>
       </c>
       <c r="Q816">
         <v>0.85</v>
@@ -77370,7 +77370,7 @@
         <v>2687</v>
       </c>
       <c r="P817" t="s">
-        <v>2051</v>
+        <v>2108</v>
       </c>
       <c r="Q817">
         <v>0.85</v>
@@ -77384,7 +77384,7 @@
         <v>2688</v>
       </c>
       <c r="P818" t="s">
-        <v>2063</v>
+        <v>2083</v>
       </c>
       <c r="Q818">
         <v>0.85</v>
@@ -77412,7 +77412,7 @@
         <v>2690</v>
       </c>
       <c r="P820" t="s">
-        <v>2102</v>
+        <v>2087</v>
       </c>
       <c r="Q820">
         <v>0.85</v>
@@ -77426,7 +77426,7 @@
         <v>2691</v>
       </c>
       <c r="P821" t="s">
-        <v>2056</v>
+        <v>2107</v>
       </c>
       <c r="Q821">
         <v>0.85</v>
@@ -77440,7 +77440,7 @@
         <v>2692</v>
       </c>
       <c r="P822" t="s">
-        <v>2075</v>
+        <v>2055</v>
       </c>
       <c r="Q822">
         <v>0.85</v>
@@ -77454,7 +77454,7 @@
         <v>2693</v>
       </c>
       <c r="P823" t="s">
-        <v>2107</v>
+        <v>2087</v>
       </c>
       <c r="Q823">
         <v>0.85</v>
@@ -77468,10 +77468,10 @@
         <v>2694</v>
       </c>
       <c r="P824" t="s">
-        <v>2082</v>
+        <v>2104</v>
       </c>
       <c r="Q824">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="825" spans="14:17" x14ac:dyDescent="0.45">
@@ -77482,10 +77482,10 @@
         <v>2695</v>
       </c>
       <c r="P825" t="s">
-        <v>2058</v>
+        <v>2076</v>
       </c>
       <c r="Q825">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="826" spans="14:17" x14ac:dyDescent="0.45">
@@ -77496,7 +77496,7 @@
         <v>2696</v>
       </c>
       <c r="P826" t="s">
-        <v>2095</v>
+        <v>2086</v>
       </c>
       <c r="Q826">
         <v>0.85</v>
@@ -77510,7 +77510,7 @@
         <v>2697</v>
       </c>
       <c r="P827" t="s">
-        <v>2062</v>
+        <v>2106</v>
       </c>
       <c r="Q827">
         <v>0.85</v>
@@ -77524,7 +77524,7 @@
         <v>2698</v>
       </c>
       <c r="P828" t="s">
-        <v>2108</v>
+        <v>2051</v>
       </c>
       <c r="Q828">
         <v>0.85</v>
@@ -77538,7 +77538,7 @@
         <v>2699</v>
       </c>
       <c r="P829" t="s">
-        <v>2088</v>
+        <v>2051</v>
       </c>
       <c r="Q829">
         <v>0.85</v>
@@ -77552,7 +77552,7 @@
         <v>2700</v>
       </c>
       <c r="P830" t="s">
-        <v>2053</v>
+        <v>2108</v>
       </c>
       <c r="Q830">
         <v>0.85</v>
@@ -77566,7 +77566,7 @@
         <v>2701</v>
       </c>
       <c r="P831" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="Q831">
         <v>0.85</v>
@@ -77580,7 +77580,7 @@
         <v>2702</v>
       </c>
       <c r="P832" t="s">
-        <v>2096</v>
+        <v>2058</v>
       </c>
       <c r="Q832">
         <v>0.85</v>
@@ -77594,7 +77594,7 @@
         <v>2703</v>
       </c>
       <c r="P833" t="s">
-        <v>2071</v>
+        <v>2094</v>
       </c>
       <c r="Q833">
         <v>0.85</v>
@@ -77608,7 +77608,7 @@
         <v>2704</v>
       </c>
       <c r="P834" t="s">
-        <v>2057</v>
+        <v>2076</v>
       </c>
       <c r="Q834">
         <v>0.85</v>
@@ -77622,7 +77622,7 @@
         <v>2705</v>
       </c>
       <c r="P835" t="s">
-        <v>2078</v>
+        <v>2093</v>
       </c>
       <c r="Q835">
         <v>0.85</v>
@@ -77636,7 +77636,7 @@
         <v>2706</v>
       </c>
       <c r="P836" t="s">
-        <v>2076</v>
+        <v>2086</v>
       </c>
       <c r="Q836">
         <v>0.85</v>
@@ -77664,7 +77664,7 @@
         <v>2708</v>
       </c>
       <c r="P838" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="Q838">
         <v>0.85</v>
@@ -77678,7 +77678,7 @@
         <v>2709</v>
       </c>
       <c r="P839" t="s">
-        <v>2080</v>
+        <v>2102</v>
       </c>
       <c r="Q839">
         <v>0.85</v>
@@ -77692,7 +77692,7 @@
         <v>2710</v>
       </c>
       <c r="P840" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="Q840">
         <v>0.85</v>
@@ -77706,7 +77706,7 @@
         <v>2711</v>
       </c>
       <c r="P841" t="s">
-        <v>2063</v>
+        <v>2070</v>
       </c>
       <c r="Q841">
         <v>0.85</v>
@@ -77720,7 +77720,7 @@
         <v>2712</v>
       </c>
       <c r="P842" t="s">
-        <v>2071</v>
+        <v>2083</v>
       </c>
       <c r="Q842">
         <v>0.85</v>
@@ -77734,7 +77734,7 @@
         <v>2713</v>
       </c>
       <c r="P843" t="s">
-        <v>2088</v>
+        <v>2103</v>
       </c>
       <c r="Q843">
         <v>0.85</v>
@@ -77748,7 +77748,7 @@
         <v>2714</v>
       </c>
       <c r="P844" t="s">
-        <v>2078</v>
+        <v>2094</v>
       </c>
       <c r="Q844">
         <v>0.85</v>
@@ -77762,7 +77762,7 @@
         <v>2715</v>
       </c>
       <c r="P845" t="s">
-        <v>2065</v>
+        <v>2102</v>
       </c>
       <c r="Q845">
         <v>0.85</v>
@@ -77776,7 +77776,7 @@
         <v>2716</v>
       </c>
       <c r="P846" t="s">
-        <v>2089</v>
+        <v>2076</v>
       </c>
       <c r="Q846">
         <v>0.85</v>
@@ -77790,7 +77790,7 @@
         <v>2717</v>
       </c>
       <c r="P847" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="Q847">
         <v>0.85</v>
@@ -77804,7 +77804,7 @@
         <v>2718</v>
       </c>
       <c r="P848" t="s">
-        <v>2081</v>
+        <v>2100</v>
       </c>
       <c r="Q848">
         <v>0.85</v>
@@ -77818,7 +77818,7 @@
         <v>2719</v>
       </c>
       <c r="P849" t="s">
-        <v>2052</v>
+        <v>2060</v>
       </c>
       <c r="Q849">
         <v>0.85</v>
@@ -77832,7 +77832,7 @@
         <v>2720</v>
       </c>
       <c r="P850" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="Q850">
         <v>0.85</v>
@@ -77846,7 +77846,7 @@
         <v>2721</v>
       </c>
       <c r="P851" t="s">
-        <v>2102</v>
+        <v>2089</v>
       </c>
       <c r="Q851">
         <v>0.85</v>
@@ -77860,7 +77860,7 @@
         <v>2722</v>
       </c>
       <c r="P852" t="s">
-        <v>2089</v>
+        <v>2103</v>
       </c>
       <c r="Q852">
         <v>0.85</v>
@@ -77874,7 +77874,7 @@
         <v>2723</v>
       </c>
       <c r="P853" t="s">
-        <v>2089</v>
+        <v>2051</v>
       </c>
       <c r="Q853">
         <v>0.85</v>
@@ -77888,7 +77888,7 @@
         <v>2724</v>
       </c>
       <c r="P854" t="s">
-        <v>2059</v>
+        <v>2103</v>
       </c>
       <c r="Q854">
         <v>0.85</v>
@@ -77902,10 +77902,10 @@
         <v>2725</v>
       </c>
       <c r="P855" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="Q855">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -77914,7 +77914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB9DA03-E9EF-4269-911E-7B634A675105}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8DFCE33-5410-4EFE-A034-211587D5F4D3}">
   <dimension ref="A1:I287"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD0EFE1-7790-4DF9-BE23-6865B8072516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E83CB0-83AB-4713-8D35-57F590C085C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emissions" sheetId="5" r:id="rId1"/>
@@ -6409,1852 +6409,1852 @@
     <t>co2_Anqing_CHN</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_Shaoguan_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104365-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115523_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Shaoguan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Tongling_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115454_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105105_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107982_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103003_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Anqing_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101467_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Beichengqu_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Fuzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Hangzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111650_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115437_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115489_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Changzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115373_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000109191_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115490_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103478_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104066_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107983_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115297_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yangjiang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Rizhao_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Wuan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105137_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114266_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114532_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Zouping_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shaoguan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Liuzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CHN45p9N129p3E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109190_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115851_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115811_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104105_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CHN45p9N129p3E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yingchuan_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109118_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102034-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yicheng_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109859_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Luohe_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yakeshi_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yangzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103166_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000191-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000103395_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106819_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101757_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106502_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109010-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Fuzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103385_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Wulan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106459_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Ningde_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000100712_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102943_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Jingling_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Hejin_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109218_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114302_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Anshun_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CCS_Hangzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Shahezhai_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yiyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115477_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Nanjing_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115817_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115841_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Putian_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Tongling_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000103364_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103153_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114365_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Hejin_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101368_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CHN44p7N89p1E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115390_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101367_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115348_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Tongshan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115448_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101789_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104520_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Nantong_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000107469_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115313_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104073-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110695_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Nanjing_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Xiaoyi_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111005_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110262-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104169_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yuanquan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103784-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yingchuan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Linyi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000108246_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_CCS_G100001000353-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101468_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114703_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Wulan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Changzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103293_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000109862_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109861_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shijiazhuang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104418_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107477-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_CCS_G100001000354-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Wuhan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yicheng_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000104640_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000111314_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000104144_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Tangshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Xiaoyi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102033-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Luohe_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Anshun_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Liaoyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115716_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115844_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115391_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115559_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000102229_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Mianyang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Fangchenggang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103151_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Shaoguan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103384_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yangjiang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000112939_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Fuzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yangzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115474_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Sizhan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103167_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Changzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tianjin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Hangzhou_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110112-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yiyang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104503_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104076-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Xiaoxita_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Chongqing_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102813_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Jingling_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Wulan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Hohhot_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Tangshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115372_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110694_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_ZhongdongShequ_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111817_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Liaoyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115825-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CHN44p7N89p1E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115495_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115952_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Fangchenggang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115826-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000113225_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Beichengqu_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103882_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CHN45p9N129p3E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yanggezhuang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Qabqa_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115813_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115476_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103394_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106354_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Beichengqu_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Wuan_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114702_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Zouping_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115347_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115731_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101756_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111453_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Qabqa_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110114-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115450_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111006_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Rizhao_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104519_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115447_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111602-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yangzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000279_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Ningde_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_CCS_G100001000355-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Wuhan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Zouping_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103867_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114710_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Xiaoyi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105096_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106309_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101768_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114746_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Xiaoxita_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110134_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115400_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yuanquan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Shanghai_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115880_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yingchuan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Fangchenggang_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110113-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000109192_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Putian_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tongshan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Rizhao_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115560_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115521_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Hohhot_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Changzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104367-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103479_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Beichengqu_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Anshun_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CHN44p7N89p1E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yicheng_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109117_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Luohe_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CHN44p2N116p5E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yanggezhuang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000108347_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111200_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114202_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103152_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000104143_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115653_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111818_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000100234_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000103363_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111479_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109207_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103868_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Anshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Chongqing_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101335_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109656-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000111313_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Jingling_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Hohhot_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101919_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109208_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Sanhe_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104684_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001004192_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114200-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000100235_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000280_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115370-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Liuzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yingchuan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115850_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111569_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000108245_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Sizhan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Anqing_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000108892_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shahezhai_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CHN44p2N116p5E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111756-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104366-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Shanghai_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Nantong_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103459_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111142_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115382-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yakeshi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Hohhot_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Tongshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Sanhe_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111201_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yangzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102942_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103449-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Sizhan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115452_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115845_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101729_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102872_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Shijiazhuang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yuanquan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104682_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shanghai_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Nantong_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Tianjin_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Luohe_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Xiaoyi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115449_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CHN44p2N116p5E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CHN44p7N89p1E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000113342_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115371-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Tongshan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yakeshi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106501_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104622-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114267_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114364_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115654_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shanghai_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106355_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111298_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Putian_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yiyang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105104_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111299_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104504_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106820_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Anshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yangjiang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tianjin_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Wuhan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102041_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111568_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115878_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_ZhongdongShequ_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104074-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Linyi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Qabqa_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103450-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Chongqing_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115814_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110263_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110115-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yuanquan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Luohe_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Nantong_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111663_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Jingling_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Shijiazhuang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Hejin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109027_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115953_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Anshun_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114835_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Harbin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104623_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CHN44p4N121p8E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000101734_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000100894_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Fangchenggang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000112940_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CCS_Hangzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104486-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000108348_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115842-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103458_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Changzhou_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Luohe_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104104_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109189_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114199-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115475_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000104235_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_CCS_G100001000352-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104368-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Fangchenggang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yingchuan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000236_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115438_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CCS_Hangzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CHN44p4N121p8E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Ningde_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Sanhe_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115346-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Putian_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yiyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115453_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Anshun_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114040_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105138-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109205_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yingchuan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Putian_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115494_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Wuan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104428-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106310_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109028_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yangjiang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Liuzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_CHN44p7N89p1E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Jinbi_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115312_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Hangzhou_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106460_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000100893_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115931_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Shanghai_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Manlin_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Nanjing_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000100711_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Shaoguan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000107468_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105306_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105160_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102102_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104065_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Putian_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000101769_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111465-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104064-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115334_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104621-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111664_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109009-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115496_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CCS_Hangzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000110133_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115815_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Fuzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106643_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105065_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000237_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CHN44p2N116p5E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yangjiang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Nanjing_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115517_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114747_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Harbin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Hejin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111649_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Sizhan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Hohhot_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106226_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115932_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115810_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111454_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Wulan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Kuqa_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Anshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Mianyang_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Changzhou_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Zouping_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yangjiang_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Chongqing_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yiyang_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115524_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CHN44p4N121p8E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Shanghai_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000113343_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103471_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000190-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115656_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105064_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Rizhao_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103783-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105159_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yuanquan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115838_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Liaoyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102929_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shahezhai_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Ningde_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Luohe_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Kuqa_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000108893_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115451_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104417_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Xiaoxita_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Yiyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yanggezhuang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Shaoguan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Tianjin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103150_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105097_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103004_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106227_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yingchuan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Sanhe_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Jingling_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shanghai_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yangzhou_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103294_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Nanjing_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101790_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102944_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104429-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115345-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114802_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000101735_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111994_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115493_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000104639_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102101_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Yangzhou_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000109029_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tongling_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115816_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115879_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111466-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102871_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Xichang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Sizhan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CCS_G100000109030_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103393_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102811_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115715_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103611_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Qabqa_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tongshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103612_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104716_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000105307_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Wuan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000106644_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102042_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102812_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Mianyang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Manlin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103392_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114201_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shaoguan_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yangjiang_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shaoguan_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shijiazhuang_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Tongshan_CHN_ge400mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Chongqing_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115296_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Chongqing_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Mianyang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115839_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102930_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Hejin_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103362_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111755-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001000347_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Yangjiang_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Xiaoyi_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Chongqing_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115459_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104683_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109860_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000114533_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Rizhao_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115640_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109655-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Zouping_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Tongshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000102228_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102157_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103881_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114039_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101336_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115641_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104485-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Nantong_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104717_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115812_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102941_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114834_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115458_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_CHN44p2N116p5E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115532_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Changzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Xiaoxita_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111995_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114301_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111478_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Nantong_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Fangchenggang_CHN_ge400mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CHN44p7N89p1E_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Liuzhou_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tongling_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115401_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104685_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115383-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111603-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115520_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109217_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104063-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115732_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102810_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103463_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115642_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Shanghai_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Tongling_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_Hohhot_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115639_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000111143_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102817-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104624_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115843-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Fangchenggang_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Nanjing_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_CHN44p4N121p8E_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115655_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_ZhongdongShequ_CHN_ge300mw_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100001004194_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115840_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000101728_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000103414_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000102816-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114709_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_Tangshan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000109206_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000104075-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_ultra-supercritical_G100000115335_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000107476-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000115531_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_Sizhan_CHN_ge300mw-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_ultra-supercritical_G100000114803_ccs-rf</t>
+    <t>ep_coal_usc_G100000111200_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106820_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115335_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yiyang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103166_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102930_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105097_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000108892_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Liuzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Anshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Shaoguan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103478_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114710_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111143_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109207_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104076-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tongshan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yanggezhuang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115655_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115811_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Hejin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Qabqa_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115653_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000111313_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000102228_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115931_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Manlin_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111603-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114532_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Tongshan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Wulan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Changzhou_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Chongqing_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000191-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115879_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105138-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Fangchenggang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103384_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Liuzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111756-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115560_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103385_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Kuqa_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Rizhao_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103393_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104105_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115814_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Qabqa_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Hejin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Fuzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115639_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101728_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Hohhot_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000104143_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115312_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Sanhe_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yingchuan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Sizhan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Chongqing_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105065_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Anshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tongling_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CHN45p9N129p3E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shaoguan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yuanquan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Tongshan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Fuzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Changzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115656_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000113343_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102041_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115475_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115812_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Hangzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Chongqing_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105159_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Rizhao_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115932_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104624_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115817_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115559_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114200-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Nantong_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Chongqing_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102157_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115524_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111995_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shahezhai_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111006_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000100893_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106310_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CHN44p2N116p5E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Linyi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115843-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CHN44p4N121p8E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103881_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Changzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000108348_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Xichang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104065_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Zouping_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115477_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115474_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Sanhe_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Anshun_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Putian_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Xiaoyi_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Anqing_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115451_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000102229_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Fangchenggang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111201_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Anshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103394_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102941_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Tongling_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115878_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114302_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Hohhot_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115842-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111994_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109118_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105137_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Nantong_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110695_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tongling_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yangjiang_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Zouping_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103153_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Shaoguan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109117_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000108347_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000101734_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CHN44p2N116p5E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Zouping_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115731_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105160_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115348_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000100711_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110133_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115334_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104063-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CHN44p7N89p1E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103784-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105064_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Jingling_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yuanquan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000104144_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102102_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000107469_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104366-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103450-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yangjiang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yangzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Fangchenggang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CHN44p4N121p8E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115476_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000103363_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103362_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109206_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000100234_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115297_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tangshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Mianyang_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Shanghai_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Liuzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000109029_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000101735_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Shaoguan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104418_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111664_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115815_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115816_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115641_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111298_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115716_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Wuhan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Changzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Hejin_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Chongqing_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111454_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115531_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103392_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114803_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Shijiazhuang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Liaoyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Wulan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111569_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103783-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103293_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Beichengqu_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102810_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Tongling_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Anqing_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101336_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_ZhongdongShequ_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Shanghai_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111649_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105307_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111817_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CHN44p2N116p5E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Jingling_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Xiaoyi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Liuzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114703_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115715_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102811_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shijiazhuang_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Sanhe_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114202_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101367_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yakeshi_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yanggezhuang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CCS_Hangzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yangzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Liaoyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000237_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Xiaoyi_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000113342_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104485-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Jinbi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106460_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yuanquan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115640_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yangzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Xiaoxita_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115438_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103004_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Wuhan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115489_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101919_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115850_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Xiaoyi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000104640_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yangzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000280_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104622-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101335_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yicheng_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CHN44p4N121p8E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Luohe_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110115-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110112-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103459_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Ningde_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104520_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111602-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115493_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yicheng_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104682_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Nanjing_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115953_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000109192_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115372_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102944_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shanghai_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Hohhot_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Nanjing_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CHN44p2N116p5E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Qabqa_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_CCS_G100001000355-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110114-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Hejin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000236_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115453_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103449-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109027_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Putian_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CHN44p7N89p1E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Sizhan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104683_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115521_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115437_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109861_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Nanjing_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114039_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Sizhan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yangjiang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Hohhot_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yangjiang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114267_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Kuqa_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103458_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Ningde_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tianjin_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101468_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102872_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Anshun_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Ningde_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Tangshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yingchuan_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115371-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Chongqing_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114364_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101790_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111465-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000100235_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yingchuan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000109862_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115520_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Ningde_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CHN44p7N89p1E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000347_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111005_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115459_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Wuhan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yuanquan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Rizhao_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103151_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106227_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111755-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115490_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115844_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Wulan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111568_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109205_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107476-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115454_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Wuan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Rizhao_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110113-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Tongshan_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yiyang_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Wuan_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103471_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CCS_Hangzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yangzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115458_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103612_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000104235_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yangjiang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104623_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104365-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000100894_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103463_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103867_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Sizhan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yingchuan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115382-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111299_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Nanjing_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111479_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103150_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Wuan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Nanjing_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000107468_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115532_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104716_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Putian_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104066_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yakeshi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Tongshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115346-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115732_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Putian_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115851_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115373_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CHN45p9N129p3E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000112939_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115523_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shanghai_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104074-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109860_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101756_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103003_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106355_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115400_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106644_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115495_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000109191_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114365_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115496_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tongshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001004192_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000108893_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104073-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000112940_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105104_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115813_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Wuan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111453_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111650_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Tangshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115390_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106643_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103611_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115296_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000113225_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Beichengqu_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shaoguan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110134_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114201_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103152_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Shanghai_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Fangchenggang_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114746_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115383-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Jingling_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shaoguan_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yingchuan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Luohe_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101757_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000101769_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yiyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106459_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yangjiang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107477-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104685_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Shanghai_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105105_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Putian_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101368_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102042_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106502_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Fangchenggang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109208_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114747_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106819_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109859_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Anshun_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104169_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102813_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109009-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000100712_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000103364_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102101_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Wulan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Xiaoxita_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Hejin_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106226_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CCS_Hangzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CHN44p7N89p1E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Luohe_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000104639_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103167_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000111314_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CHN44p7N89p1E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102034-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Nantong_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111142_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102812_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115654_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Beichengqu_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Hohhot_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114040_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103414_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Luohe_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109190_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104621-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Tianjin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115952_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Shahezhai_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_ZhongdongShequ_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_ZhongdongShequ_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109656-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109655-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Luohe_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115347_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109218_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111478_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Hohhot_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Xiaoxita_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Xiaoxita_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104064-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Liaoyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Zouping_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000109030_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101789_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110263_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yingchuan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115839_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104075-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107983_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000103395_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Anshun_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105096_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shanghai_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115642_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Nantong_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CHN44p4N121p8E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Hangzhou_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Fangchenggang_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102943_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115494_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Hangzhou_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Tianjin_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Luohe_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yangzhou_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102033-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110262-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115448_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000190-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110694_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Tongshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102816-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101729_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114802_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102817-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yiyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114533_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102929_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104417_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115313_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Zouping_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Mianyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yiyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104429-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111818_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115345-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115452_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109217_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103882_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Rizhao_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115370-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115880_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CCS_Hangzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Harbin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104428-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Chongqing_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115845_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104368-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104367-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Changzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107982_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Mianyang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yingchuan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yangjiang_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000279_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114301_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shanghai_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102942_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yicheng_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Fuzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yiyang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Anshun_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114266_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115447_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Sizhan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Luohe_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Sanhe_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shijiazhuang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_CCS_G100001000352-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104486-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111663_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114702_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115401_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Jingling_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115825-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115449_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Sizhan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yuanquan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CHN44p2N116p5E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Nanjing_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Shaoguan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Tongling_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Putian_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Manlin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Jingling_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CHN45p9N129p3E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000108246_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101467_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106354_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shaoguan_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109010-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Mianyang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109028_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105306_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115826-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106501_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104684_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104717_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Shijiazhuang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103294_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115450_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Linyi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_CCS_G100001000354-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114834_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Qabqa_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Harbin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yanggezhuang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101768_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104503_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115841_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tianjin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104104_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114199-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115840_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Fangchenggang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103868_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Nantong_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114835_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Changzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Xiaoyi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102871_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_CCS_G100001000353-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CHN44p7N89p1E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109189_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115517_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115838_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115391_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103479_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yangjiang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001004194_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yakeshi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115810_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shahezhai_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104519_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Fuzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111466-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106309_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104504_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114709_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000108245_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Beichengqu_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Nantong_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Changzhou_CHN_400_rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -10585,7 +10585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1982A0FD-01A1-404E-8A17-7B542CBBFA37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E96716-1A88-449D-8592-BEF3264F4FE9}">
   <dimension ref="B2:AG1714"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51938,7 +51938,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A068989-CF01-4D98-876F-C3FD232FEFF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F89DD4-0CBE-4220-8164-461D7ACD2F97}">
   <dimension ref="B9:L24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -64859,7 +64859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A267F55-58AF-4472-96A7-3A26CC4BCC06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A590469-6A10-4FEB-88F9-92128A1F835E}">
   <dimension ref="B2:Q855"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -69292,10 +69292,10 @@
         <v>2110</v>
       </c>
       <c r="P240" t="s">
-        <v>2089</v>
+        <v>2083</v>
       </c>
       <c r="Q240">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="241" spans="14:17" x14ac:dyDescent="0.45">
@@ -69320,7 +69320,7 @@
         <v>2112</v>
       </c>
       <c r="P242" t="s">
-        <v>2055</v>
+        <v>2089</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -69334,7 +69334,7 @@
         <v>2113</v>
       </c>
       <c r="P243" t="s">
-        <v>2089</v>
+        <v>2060</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -69348,7 +69348,7 @@
         <v>2114</v>
       </c>
       <c r="P244" t="s">
-        <v>2108</v>
+        <v>2077</v>
       </c>
       <c r="Q244">
         <v>0.85</v>
@@ -69362,7 +69362,7 @@
         <v>2115</v>
       </c>
       <c r="P245" t="s">
-        <v>2071</v>
+        <v>2083</v>
       </c>
       <c r="Q245">
         <v>0.85</v>
@@ -69404,7 +69404,7 @@
         <v>2118</v>
       </c>
       <c r="P248" t="s">
-        <v>2088</v>
+        <v>2073</v>
       </c>
       <c r="Q248">
         <v>0.85</v>
@@ -69418,7 +69418,7 @@
         <v>2119</v>
       </c>
       <c r="P249" t="s">
-        <v>2109</v>
+        <v>2054</v>
       </c>
       <c r="Q249">
         <v>0.85</v>
@@ -69432,7 +69432,7 @@
         <v>2120</v>
       </c>
       <c r="P250" t="s">
-        <v>2095</v>
+        <v>2089</v>
       </c>
       <c r="Q250">
         <v>0.85</v>
@@ -69446,7 +69446,7 @@
         <v>2121</v>
       </c>
       <c r="P251" t="s">
-        <v>2087</v>
+        <v>2103</v>
       </c>
       <c r="Q251">
         <v>0.85</v>
@@ -69460,7 +69460,7 @@
         <v>2122</v>
       </c>
       <c r="P252" t="s">
-        <v>2083</v>
+        <v>2089</v>
       </c>
       <c r="Q252">
         <v>0.85</v>
@@ -69474,7 +69474,7 @@
         <v>2123</v>
       </c>
       <c r="P253" t="s">
-        <v>2063</v>
+        <v>2094</v>
       </c>
       <c r="Q253">
         <v>0.85</v>
@@ -69488,7 +69488,7 @@
         <v>2124</v>
       </c>
       <c r="P254" t="s">
-        <v>2051</v>
+        <v>2080</v>
       </c>
       <c r="Q254">
         <v>0.85</v>
@@ -69502,7 +69502,7 @@
         <v>2125</v>
       </c>
       <c r="P255" t="s">
-        <v>2051</v>
+        <v>2095</v>
       </c>
       <c r="Q255">
         <v>0.85</v>
@@ -69516,7 +69516,7 @@
         <v>2126</v>
       </c>
       <c r="P256" t="s">
-        <v>2082</v>
+        <v>2106</v>
       </c>
       <c r="Q256">
         <v>0.85</v>
@@ -69530,7 +69530,7 @@
         <v>2127</v>
       </c>
       <c r="P257" t="s">
-        <v>2058</v>
+        <v>2095</v>
       </c>
       <c r="Q257">
         <v>0.85</v>
@@ -69544,7 +69544,7 @@
         <v>2128</v>
       </c>
       <c r="P258" t="s">
-        <v>2103</v>
+        <v>2094</v>
       </c>
       <c r="Q258">
         <v>0.85</v>
@@ -69572,7 +69572,7 @@
         <v>2130</v>
       </c>
       <c r="P260" t="s">
-        <v>2082</v>
+        <v>2101</v>
       </c>
       <c r="Q260">
         <v>0.85</v>
@@ -69586,7 +69586,7 @@
         <v>2131</v>
       </c>
       <c r="P261" t="s">
-        <v>2103</v>
+        <v>2088</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -69600,7 +69600,7 @@
         <v>2132</v>
       </c>
       <c r="P262" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
       <c r="Q262">
         <v>0.85</v>
@@ -69614,7 +69614,7 @@
         <v>2133</v>
       </c>
       <c r="P263" t="s">
-        <v>2081</v>
+        <v>2104</v>
       </c>
       <c r="Q263">
         <v>0.85</v>
@@ -69628,7 +69628,7 @@
         <v>2134</v>
       </c>
       <c r="P264" t="s">
-        <v>2093</v>
+        <v>2106</v>
       </c>
       <c r="Q264">
         <v>0.85</v>
@@ -69642,7 +69642,7 @@
         <v>2135</v>
       </c>
       <c r="P265" t="s">
-        <v>2071</v>
+        <v>2065</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -69656,7 +69656,7 @@
         <v>2136</v>
       </c>
       <c r="P266" t="s">
-        <v>2094</v>
+        <v>2064</v>
       </c>
       <c r="Q266">
         <v>0.85</v>
@@ -69684,7 +69684,7 @@
         <v>2138</v>
       </c>
       <c r="P268" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="Q268">
         <v>0.85</v>
@@ -69698,7 +69698,7 @@
         <v>2139</v>
       </c>
       <c r="P269" t="s">
-        <v>2060</v>
+        <v>2106</v>
       </c>
       <c r="Q269">
         <v>0.85</v>
@@ -69712,7 +69712,7 @@
         <v>2140</v>
       </c>
       <c r="P270" t="s">
-        <v>2083</v>
+        <v>2069</v>
       </c>
       <c r="Q270">
         <v>0.85</v>
@@ -69726,10 +69726,10 @@
         <v>2141</v>
       </c>
       <c r="P271" t="s">
-        <v>2078</v>
+        <v>2058</v>
       </c>
       <c r="Q271">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="272" spans="14:17" x14ac:dyDescent="0.45">
@@ -69740,10 +69740,10 @@
         <v>2142</v>
       </c>
       <c r="P272" t="s">
-        <v>2089</v>
+        <v>2065</v>
       </c>
       <c r="Q272">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="273" spans="14:17" x14ac:dyDescent="0.45">
@@ -69754,7 +69754,7 @@
         <v>2143</v>
       </c>
       <c r="P273" t="s">
-        <v>2073</v>
+        <v>2051</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -69768,7 +69768,7 @@
         <v>2144</v>
       </c>
       <c r="P274" t="s">
-        <v>2079</v>
+        <v>2084</v>
       </c>
       <c r="Q274">
         <v>0.85</v>
@@ -69782,7 +69782,7 @@
         <v>2145</v>
       </c>
       <c r="P275" t="s">
-        <v>2065</v>
+        <v>2081</v>
       </c>
       <c r="Q275">
         <v>0.85</v>
@@ -69796,7 +69796,7 @@
         <v>2146</v>
       </c>
       <c r="P276" t="s">
-        <v>2094</v>
+        <v>2077</v>
       </c>
       <c r="Q276">
         <v>0.85</v>
@@ -69810,7 +69810,7 @@
         <v>2147</v>
       </c>
       <c r="P277" t="s">
-        <v>2065</v>
+        <v>2103</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -69824,7 +69824,7 @@
         <v>2148</v>
       </c>
       <c r="P278" t="s">
-        <v>2060</v>
+        <v>2073</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -69838,7 +69838,7 @@
         <v>2149</v>
       </c>
       <c r="P279" t="s">
-        <v>2079</v>
+        <v>2106</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -69852,10 +69852,10 @@
         <v>2150</v>
       </c>
       <c r="P280" t="s">
-        <v>2081</v>
+        <v>2101</v>
       </c>
       <c r="Q280">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="281" spans="14:17" x14ac:dyDescent="0.45">
@@ -69880,7 +69880,7 @@
         <v>2152</v>
       </c>
       <c r="P282" t="s">
-        <v>2095</v>
+        <v>2068</v>
       </c>
       <c r="Q282">
         <v>0.85</v>
@@ -69894,7 +69894,7 @@
         <v>2153</v>
       </c>
       <c r="P283" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="Q283">
         <v>0.85</v>
@@ -69908,7 +69908,7 @@
         <v>2154</v>
       </c>
       <c r="P284" t="s">
-        <v>2063</v>
+        <v>2058</v>
       </c>
       <c r="Q284">
         <v>0.85</v>
@@ -69922,7 +69922,7 @@
         <v>2155</v>
       </c>
       <c r="P285" t="s">
-        <v>2082</v>
+        <v>2060</v>
       </c>
       <c r="Q285">
         <v>0.85</v>
@@ -69936,7 +69936,7 @@
         <v>2156</v>
       </c>
       <c r="P286" t="s">
-        <v>2061</v>
+        <v>2088</v>
       </c>
       <c r="Q286">
         <v>0.85</v>
@@ -69950,7 +69950,7 @@
         <v>2157</v>
       </c>
       <c r="P287" t="s">
-        <v>2104</v>
+        <v>2088</v>
       </c>
       <c r="Q287">
         <v>0.85</v>
@@ -69964,7 +69964,7 @@
         <v>2158</v>
       </c>
       <c r="P288" t="s">
-        <v>2077</v>
+        <v>2101</v>
       </c>
       <c r="Q288">
         <v>0.85</v>
@@ -69978,7 +69978,7 @@
         <v>2159</v>
       </c>
       <c r="P289" t="s">
-        <v>2051</v>
+        <v>2083</v>
       </c>
       <c r="Q289">
         <v>0.85</v>
@@ -70006,7 +70006,7 @@
         <v>2161</v>
       </c>
       <c r="P291" t="s">
-        <v>2076</v>
+        <v>2094</v>
       </c>
       <c r="Q291">
         <v>0.85</v>
@@ -70020,7 +70020,7 @@
         <v>2162</v>
       </c>
       <c r="P292" t="s">
-        <v>2106</v>
+        <v>2086</v>
       </c>
       <c r="Q292">
         <v>0.85</v>
@@ -70034,7 +70034,7 @@
         <v>2163</v>
       </c>
       <c r="P293" t="s">
-        <v>2093</v>
+        <v>2051</v>
       </c>
       <c r="Q293">
         <v>0.85</v>
@@ -70048,7 +70048,7 @@
         <v>2164</v>
       </c>
       <c r="P294" t="s">
-        <v>2051</v>
+        <v>2109</v>
       </c>
       <c r="Q294">
         <v>0.85</v>
@@ -70062,7 +70062,7 @@
         <v>2165</v>
       </c>
       <c r="P295" t="s">
-        <v>2083</v>
+        <v>2056</v>
       </c>
       <c r="Q295">
         <v>0.85</v>
@@ -70076,7 +70076,7 @@
         <v>2166</v>
       </c>
       <c r="P296" t="s">
-        <v>2103</v>
+        <v>2081</v>
       </c>
       <c r="Q296">
         <v>0.85</v>
@@ -70090,7 +70090,7 @@
         <v>2167</v>
       </c>
       <c r="P297" t="s">
-        <v>2069</v>
+        <v>2103</v>
       </c>
       <c r="Q297">
         <v>0.85</v>
@@ -70104,7 +70104,7 @@
         <v>2168</v>
       </c>
       <c r="P298" t="s">
-        <v>2089</v>
+        <v>2065</v>
       </c>
       <c r="Q298">
         <v>0.85</v>
@@ -70118,7 +70118,7 @@
         <v>2169</v>
       </c>
       <c r="P299" t="s">
-        <v>2093</v>
+        <v>2104</v>
       </c>
       <c r="Q299">
         <v>0.85</v>
@@ -70132,7 +70132,7 @@
         <v>2170</v>
       </c>
       <c r="P300" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="Q300">
         <v>0.85</v>
@@ -70146,7 +70146,7 @@
         <v>2171</v>
       </c>
       <c r="P301" t="s">
-        <v>2096</v>
+        <v>2108</v>
       </c>
       <c r="Q301">
         <v>0.85</v>
@@ -70160,7 +70160,7 @@
         <v>2172</v>
       </c>
       <c r="P302" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="Q302">
         <v>0.85</v>
@@ -70174,7 +70174,7 @@
         <v>2173</v>
       </c>
       <c r="P303" t="s">
-        <v>2101</v>
+        <v>2089</v>
       </c>
       <c r="Q303">
         <v>0.85</v>
@@ -70188,7 +70188,7 @@
         <v>2174</v>
       </c>
       <c r="P304" t="s">
-        <v>2087</v>
+        <v>2096</v>
       </c>
       <c r="Q304">
         <v>0.85</v>
@@ -70202,7 +70202,7 @@
         <v>2175</v>
       </c>
       <c r="P305" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
       <c r="Q305">
         <v>0.85</v>
@@ -70216,7 +70216,7 @@
         <v>2176</v>
       </c>
       <c r="P306" t="s">
-        <v>2059</v>
+        <v>2083</v>
       </c>
       <c r="Q306">
         <v>0.85</v>
@@ -70230,7 +70230,7 @@
         <v>2177</v>
       </c>
       <c r="P307" t="s">
-        <v>2063</v>
+        <v>2058</v>
       </c>
       <c r="Q307">
         <v>0.85</v>
@@ -70244,7 +70244,7 @@
         <v>2178</v>
       </c>
       <c r="P308" t="s">
-        <v>2067</v>
+        <v>2094</v>
       </c>
       <c r="Q308">
         <v>0.85</v>
@@ -70258,7 +70258,7 @@
         <v>2179</v>
       </c>
       <c r="P309" t="s">
-        <v>2060</v>
+        <v>2087</v>
       </c>
       <c r="Q309">
         <v>0.85</v>
@@ -70272,7 +70272,7 @@
         <v>2180</v>
       </c>
       <c r="P310" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="Q310">
         <v>0.85</v>
@@ -70286,10 +70286,10 @@
         <v>2181</v>
       </c>
       <c r="P311" t="s">
-        <v>2090</v>
+        <v>2106</v>
       </c>
       <c r="Q311">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="312" spans="14:17" x14ac:dyDescent="0.45">
@@ -70300,7 +70300,7 @@
         <v>2182</v>
       </c>
       <c r="P312" t="s">
-        <v>2076</v>
+        <v>2096</v>
       </c>
       <c r="Q312">
         <v>0.85</v>
@@ -70314,7 +70314,7 @@
         <v>2183</v>
       </c>
       <c r="P313" t="s">
-        <v>2103</v>
+        <v>2063</v>
       </c>
       <c r="Q313">
         <v>0.85</v>
@@ -70328,7 +70328,7 @@
         <v>2184</v>
       </c>
       <c r="P314" t="s">
-        <v>2076</v>
+        <v>2065</v>
       </c>
       <c r="Q314">
         <v>0.85</v>
@@ -70342,7 +70342,7 @@
         <v>2185</v>
       </c>
       <c r="P315" t="s">
-        <v>2108</v>
+        <v>2051</v>
       </c>
       <c r="Q315">
         <v>0.85</v>
@@ -70356,10 +70356,10 @@
         <v>2186</v>
       </c>
       <c r="P316" t="s">
-        <v>2060</v>
+        <v>2094</v>
       </c>
       <c r="Q316">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="317" spans="14:17" x14ac:dyDescent="0.45">
@@ -70370,7 +70370,7 @@
         <v>2187</v>
       </c>
       <c r="P317" t="s">
-        <v>2089</v>
+        <v>2065</v>
       </c>
       <c r="Q317">
         <v>0.85</v>
@@ -70384,7 +70384,7 @@
         <v>2188</v>
       </c>
       <c r="P318" t="s">
-        <v>2083</v>
+        <v>2093</v>
       </c>
       <c r="Q318">
         <v>0.85</v>
@@ -70398,7 +70398,7 @@
         <v>2189</v>
       </c>
       <c r="P319" t="s">
-        <v>2101</v>
+        <v>2076</v>
       </c>
       <c r="Q319">
         <v>0.85</v>
@@ -70412,7 +70412,7 @@
         <v>2190</v>
       </c>
       <c r="P320" t="s">
-        <v>2076</v>
+        <v>2101</v>
       </c>
       <c r="Q320">
         <v>0.85</v>
@@ -70426,7 +70426,7 @@
         <v>2191</v>
       </c>
       <c r="P321" t="s">
-        <v>2075</v>
+        <v>2060</v>
       </c>
       <c r="Q321">
         <v>0.85</v>
@@ -70440,10 +70440,10 @@
         <v>2192</v>
       </c>
       <c r="P322" t="s">
-        <v>2051</v>
+        <v>2098</v>
       </c>
       <c r="Q322">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="323" spans="14:17" x14ac:dyDescent="0.45">
@@ -70454,10 +70454,10 @@
         <v>2193</v>
       </c>
       <c r="P323" t="s">
-        <v>2076</v>
+        <v>2065</v>
       </c>
       <c r="Q323">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="324" spans="14:17" x14ac:dyDescent="0.45">
@@ -70468,7 +70468,7 @@
         <v>2194</v>
       </c>
       <c r="P324" t="s">
-        <v>2055</v>
+        <v>2101</v>
       </c>
       <c r="Q324">
         <v>0.85</v>
@@ -70482,7 +70482,7 @@
         <v>2195</v>
       </c>
       <c r="P325" t="s">
-        <v>2106</v>
+        <v>2055</v>
       </c>
       <c r="Q325">
         <v>0.85</v>
@@ -70496,7 +70496,7 @@
         <v>2196</v>
       </c>
       <c r="P326" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="Q326">
         <v>0.85</v>
@@ -70510,7 +70510,7 @@
         <v>2197</v>
       </c>
       <c r="P327" t="s">
-        <v>2058</v>
+        <v>2067</v>
       </c>
       <c r="Q327">
         <v>0.85</v>
@@ -70524,7 +70524,7 @@
         <v>2198</v>
       </c>
       <c r="P328" t="s">
-        <v>2103</v>
+        <v>2075</v>
       </c>
       <c r="Q328">
         <v>0.85</v>
@@ -70538,7 +70538,7 @@
         <v>2199</v>
       </c>
       <c r="P329" t="s">
-        <v>2098</v>
+        <v>2078</v>
       </c>
       <c r="Q329">
         <v>0.85</v>
@@ -70552,7 +70552,7 @@
         <v>2200</v>
       </c>
       <c r="P330" t="s">
-        <v>2063</v>
+        <v>2069</v>
       </c>
       <c r="Q330">
         <v>0.85</v>
@@ -70566,7 +70566,7 @@
         <v>2201</v>
       </c>
       <c r="P331" t="s">
-        <v>2109</v>
+        <v>2105</v>
       </c>
       <c r="Q331">
         <v>0.85</v>
@@ -70580,7 +70580,7 @@
         <v>2202</v>
       </c>
       <c r="P332" t="s">
-        <v>2095</v>
+        <v>2062</v>
       </c>
       <c r="Q332">
         <v>0.85</v>
@@ -70594,7 +70594,7 @@
         <v>2203</v>
       </c>
       <c r="P333" t="s">
-        <v>2051</v>
+        <v>2086</v>
       </c>
       <c r="Q333">
         <v>0.85</v>
@@ -70608,7 +70608,7 @@
         <v>2204</v>
       </c>
       <c r="P334" t="s">
-        <v>2090</v>
+        <v>2102</v>
       </c>
       <c r="Q334">
         <v>0.85</v>
@@ -70622,7 +70622,7 @@
         <v>2205</v>
       </c>
       <c r="P335" t="s">
-        <v>2092</v>
+        <v>2073</v>
       </c>
       <c r="Q335">
         <v>0.85</v>
@@ -70636,7 +70636,7 @@
         <v>2206</v>
       </c>
       <c r="P336" t="s">
-        <v>2075</v>
+        <v>2058</v>
       </c>
       <c r="Q336">
         <v>0.85</v>
@@ -70650,7 +70650,7 @@
         <v>2207</v>
       </c>
       <c r="P337" t="s">
-        <v>2108</v>
+        <v>2089</v>
       </c>
       <c r="Q337">
         <v>0.85</v>
@@ -70664,7 +70664,7 @@
         <v>2208</v>
       </c>
       <c r="P338" t="s">
-        <v>2108</v>
+        <v>2074</v>
       </c>
       <c r="Q338">
         <v>0.85</v>
@@ -70678,7 +70678,7 @@
         <v>2209</v>
       </c>
       <c r="P339" t="s">
-        <v>2096</v>
+        <v>2104</v>
       </c>
       <c r="Q339">
         <v>0.85</v>
@@ -70692,7 +70692,7 @@
         <v>2210</v>
       </c>
       <c r="P340" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="Q340">
         <v>0.85</v>
@@ -70720,7 +70720,7 @@
         <v>2212</v>
       </c>
       <c r="P342" t="s">
-        <v>2062</v>
+        <v>2106</v>
       </c>
       <c r="Q342">
         <v>0.85</v>
@@ -70734,7 +70734,7 @@
         <v>2213</v>
       </c>
       <c r="P343" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="Q343">
         <v>0.85</v>
@@ -70748,7 +70748,7 @@
         <v>2214</v>
       </c>
       <c r="P344" t="s">
-        <v>2086</v>
+        <v>2059</v>
       </c>
       <c r="Q344">
         <v>0.85</v>
@@ -70762,7 +70762,7 @@
         <v>2215</v>
       </c>
       <c r="P345" t="s">
-        <v>2095</v>
+        <v>2076</v>
       </c>
       <c r="Q345">
         <v>0.85</v>
@@ -70776,7 +70776,7 @@
         <v>2216</v>
       </c>
       <c r="P346" t="s">
-        <v>2106</v>
+        <v>2092</v>
       </c>
       <c r="Q346">
         <v>0.85</v>
@@ -70790,7 +70790,7 @@
         <v>2217</v>
       </c>
       <c r="P347" t="s">
-        <v>2069</v>
+        <v>2109</v>
       </c>
       <c r="Q347">
         <v>0.85</v>
@@ -70804,7 +70804,7 @@
         <v>2218</v>
       </c>
       <c r="P348" t="s">
-        <v>2058</v>
+        <v>2089</v>
       </c>
       <c r="Q348">
         <v>0.85</v>
@@ -70818,7 +70818,7 @@
         <v>2219</v>
       </c>
       <c r="P349" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="Q349">
         <v>0.85</v>
@@ -70832,7 +70832,7 @@
         <v>2220</v>
       </c>
       <c r="P350" t="s">
-        <v>2063</v>
+        <v>2077</v>
       </c>
       <c r="Q350">
         <v>0.85</v>
@@ -70846,7 +70846,7 @@
         <v>2221</v>
       </c>
       <c r="P351" t="s">
-        <v>2063</v>
+        <v>2083</v>
       </c>
       <c r="Q351">
         <v>0.85</v>
@@ -70860,7 +70860,7 @@
         <v>2222</v>
       </c>
       <c r="P352" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="Q352">
         <v>0.85</v>
@@ -70874,7 +70874,7 @@
         <v>2223</v>
       </c>
       <c r="P353" t="s">
-        <v>2104</v>
+        <v>2058</v>
       </c>
       <c r="Q353">
         <v>0.85</v>
@@ -70888,7 +70888,7 @@
         <v>2224</v>
       </c>
       <c r="P354" t="s">
-        <v>2103</v>
+        <v>2096</v>
       </c>
       <c r="Q354">
         <v>0.85</v>
@@ -70902,7 +70902,7 @@
         <v>2225</v>
       </c>
       <c r="P355" t="s">
-        <v>2086</v>
+        <v>2108</v>
       </c>
       <c r="Q355">
         <v>0.85</v>
@@ -70916,7 +70916,7 @@
         <v>2226</v>
       </c>
       <c r="P356" t="s">
-        <v>2055</v>
+        <v>2084</v>
       </c>
       <c r="Q356">
         <v>0.85</v>
@@ -70930,7 +70930,7 @@
         <v>2227</v>
       </c>
       <c r="P357" t="s">
-        <v>2091</v>
+        <v>2109</v>
       </c>
       <c r="Q357">
         <v>0.85</v>
@@ -70944,7 +70944,7 @@
         <v>2228</v>
       </c>
       <c r="P358" t="s">
-        <v>2101</v>
+        <v>2086</v>
       </c>
       <c r="Q358">
         <v>0.85</v>
@@ -70958,7 +70958,7 @@
         <v>2229</v>
       </c>
       <c r="P359" t="s">
-        <v>2104</v>
+        <v>2086</v>
       </c>
       <c r="Q359">
         <v>0.85</v>
@@ -70972,7 +70972,7 @@
         <v>2230</v>
       </c>
       <c r="P360" t="s">
-        <v>2051</v>
+        <v>2077</v>
       </c>
       <c r="Q360">
         <v>0.85</v>
@@ -70986,7 +70986,7 @@
         <v>2231</v>
       </c>
       <c r="P361" t="s">
-        <v>2100</v>
+        <v>2103</v>
       </c>
       <c r="Q361">
         <v>0.85</v>
@@ -71000,7 +71000,7 @@
         <v>2232</v>
       </c>
       <c r="P362" t="s">
-        <v>2092</v>
+        <v>2081</v>
       </c>
       <c r="Q362">
         <v>0.85</v>
@@ -71014,7 +71014,7 @@
         <v>2233</v>
       </c>
       <c r="P363" t="s">
-        <v>2095</v>
+        <v>2098</v>
       </c>
       <c r="Q363">
         <v>0.85</v>
@@ -71028,7 +71028,7 @@
         <v>2234</v>
       </c>
       <c r="P364" t="s">
-        <v>2082</v>
+        <v>2051</v>
       </c>
       <c r="Q364">
         <v>0.85</v>
@@ -71042,7 +71042,7 @@
         <v>2235</v>
       </c>
       <c r="P365" t="s">
-        <v>2059</v>
+        <v>2108</v>
       </c>
       <c r="Q365">
         <v>0.85</v>
@@ -71056,10 +71056,10 @@
         <v>2236</v>
       </c>
       <c r="P366" t="s">
-        <v>2099</v>
+        <v>2071</v>
       </c>
       <c r="Q366">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="367" spans="14:17" x14ac:dyDescent="0.45">
@@ -71070,10 +71070,10 @@
         <v>2237</v>
       </c>
       <c r="P367" t="s">
-        <v>2098</v>
+        <v>2078</v>
       </c>
       <c r="Q367">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="368" spans="14:17" x14ac:dyDescent="0.45">
@@ -71084,7 +71084,7 @@
         <v>2238</v>
       </c>
       <c r="P368" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="Q368">
         <v>0.85</v>
@@ -71098,7 +71098,7 @@
         <v>2239</v>
       </c>
       <c r="P369" t="s">
-        <v>2051</v>
+        <v>2089</v>
       </c>
       <c r="Q369">
         <v>0.85</v>
@@ -71112,7 +71112,7 @@
         <v>2240</v>
       </c>
       <c r="P370" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="Q370">
         <v>0.85</v>
@@ -71126,7 +71126,7 @@
         <v>2241</v>
       </c>
       <c r="P371" t="s">
-        <v>2106</v>
+        <v>2089</v>
       </c>
       <c r="Q371">
         <v>0.85</v>
@@ -71140,7 +71140,7 @@
         <v>2242</v>
       </c>
       <c r="P372" t="s">
-        <v>2084</v>
+        <v>2076</v>
       </c>
       <c r="Q372">
         <v>0.85</v>
@@ -71154,7 +71154,7 @@
         <v>2243</v>
       </c>
       <c r="P373" t="s">
-        <v>2077</v>
+        <v>2105</v>
       </c>
       <c r="Q373">
         <v>0.85</v>
@@ -71168,7 +71168,7 @@
         <v>2244</v>
       </c>
       <c r="P374" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="Q374">
         <v>0.85</v>
@@ -71182,7 +71182,7 @@
         <v>2245</v>
       </c>
       <c r="P375" t="s">
-        <v>2089</v>
+        <v>2076</v>
       </c>
       <c r="Q375">
         <v>0.85</v>
@@ -71196,7 +71196,7 @@
         <v>2246</v>
       </c>
       <c r="P376" t="s">
-        <v>2103</v>
+        <v>2051</v>
       </c>
       <c r="Q376">
         <v>0.85</v>
@@ -71210,7 +71210,7 @@
         <v>2247</v>
       </c>
       <c r="P377" t="s">
-        <v>2071</v>
+        <v>2055</v>
       </c>
       <c r="Q377">
         <v>0.85</v>
@@ -71224,7 +71224,7 @@
         <v>2248</v>
       </c>
       <c r="P378" t="s">
-        <v>2095</v>
+        <v>2051</v>
       </c>
       <c r="Q378">
         <v>0.85</v>
@@ -71238,7 +71238,7 @@
         <v>2249</v>
       </c>
       <c r="P379" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="Q379">
         <v>0.85</v>
@@ -71252,7 +71252,7 @@
         <v>2250</v>
       </c>
       <c r="P380" t="s">
-        <v>2104</v>
+        <v>2089</v>
       </c>
       <c r="Q380">
         <v>0.85</v>
@@ -71266,7 +71266,7 @@
         <v>2251</v>
       </c>
       <c r="P381" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="Q381">
         <v>0.85</v>
@@ -71280,7 +71280,7 @@
         <v>2252</v>
       </c>
       <c r="P382" t="s">
-        <v>2103</v>
+        <v>2075</v>
       </c>
       <c r="Q382">
         <v>0.85</v>
@@ -71294,7 +71294,7 @@
         <v>2253</v>
       </c>
       <c r="P383" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="Q383">
         <v>0.85</v>
@@ -71308,7 +71308,7 @@
         <v>2254</v>
       </c>
       <c r="P384" t="s">
-        <v>2058</v>
+        <v>2104</v>
       </c>
       <c r="Q384">
         <v>0.85</v>
@@ -71322,7 +71322,7 @@
         <v>2255</v>
       </c>
       <c r="P385" t="s">
-        <v>2053</v>
+        <v>2080</v>
       </c>
       <c r="Q385">
         <v>0.85</v>
@@ -71336,10 +71336,10 @@
         <v>2256</v>
       </c>
       <c r="P386" t="s">
-        <v>2063</v>
+        <v>2096</v>
       </c>
       <c r="Q386">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="387" spans="14:17" x14ac:dyDescent="0.45">
@@ -71350,7 +71350,7 @@
         <v>2257</v>
       </c>
       <c r="P387" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="Q387">
         <v>0.85</v>
@@ -71364,7 +71364,7 @@
         <v>2258</v>
       </c>
       <c r="P388" t="s">
-        <v>2060</v>
+        <v>2077</v>
       </c>
       <c r="Q388">
         <v>0.85</v>
@@ -71378,7 +71378,7 @@
         <v>2259</v>
       </c>
       <c r="P389" t="s">
-        <v>2089</v>
+        <v>2063</v>
       </c>
       <c r="Q389">
         <v>0.85</v>
@@ -71392,7 +71392,7 @@
         <v>2260</v>
       </c>
       <c r="P390" t="s">
-        <v>2095</v>
+        <v>2076</v>
       </c>
       <c r="Q390">
         <v>0.85</v>
@@ -71406,7 +71406,7 @@
         <v>2261</v>
       </c>
       <c r="P391" t="s">
-        <v>2097</v>
+        <v>2078</v>
       </c>
       <c r="Q391">
         <v>0.85</v>
@@ -71420,7 +71420,7 @@
         <v>2262</v>
       </c>
       <c r="P392" t="s">
-        <v>2065</v>
+        <v>2071</v>
       </c>
       <c r="Q392">
         <v>0.85</v>
@@ -71434,7 +71434,7 @@
         <v>2263</v>
       </c>
       <c r="P393" t="s">
-        <v>2086</v>
+        <v>2104</v>
       </c>
       <c r="Q393">
         <v>0.85</v>
@@ -71448,7 +71448,7 @@
         <v>2264</v>
       </c>
       <c r="P394" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
       <c r="Q394">
         <v>0.85</v>
@@ -71462,7 +71462,7 @@
         <v>2265</v>
       </c>
       <c r="P395" t="s">
-        <v>2069</v>
+        <v>2102</v>
       </c>
       <c r="Q395">
         <v>0.85</v>
@@ -71476,7 +71476,7 @@
         <v>2266</v>
       </c>
       <c r="P396" t="s">
-        <v>2086</v>
+        <v>2081</v>
       </c>
       <c r="Q396">
         <v>0.85</v>
@@ -71490,7 +71490,7 @@
         <v>2267</v>
       </c>
       <c r="P397" t="s">
-        <v>2100</v>
+        <v>2060</v>
       </c>
       <c r="Q397">
         <v>0.85</v>
@@ -71504,7 +71504,7 @@
         <v>2268</v>
       </c>
       <c r="P398" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="Q398">
         <v>0.85</v>
@@ -71518,7 +71518,7 @@
         <v>2269</v>
       </c>
       <c r="P399" t="s">
-        <v>2051</v>
+        <v>2060</v>
       </c>
       <c r="Q399">
         <v>0.85</v>
@@ -71532,7 +71532,7 @@
         <v>2270</v>
       </c>
       <c r="P400" t="s">
-        <v>2070</v>
+        <v>2109</v>
       </c>
       <c r="Q400">
         <v>0.85</v>
@@ -71546,7 +71546,7 @@
         <v>2271</v>
       </c>
       <c r="P401" t="s">
-        <v>2106</v>
+        <v>2093</v>
       </c>
       <c r="Q401">
         <v>0.85</v>
@@ -71560,7 +71560,7 @@
         <v>2272</v>
       </c>
       <c r="P402" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="Q402">
         <v>0.85</v>
@@ -71574,10 +71574,10 @@
         <v>2273</v>
       </c>
       <c r="P403" t="s">
-        <v>2056</v>
+        <v>2084</v>
       </c>
       <c r="Q403">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="404" spans="14:17" x14ac:dyDescent="0.45">
@@ -71588,7 +71588,7 @@
         <v>2274</v>
       </c>
       <c r="P404" t="s">
-        <v>2075</v>
+        <v>2051</v>
       </c>
       <c r="Q404">
         <v>0.85</v>
@@ -71602,7 +71602,7 @@
         <v>2275</v>
       </c>
       <c r="P405" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="Q405">
         <v>0.85</v>
@@ -71630,7 +71630,7 @@
         <v>2277</v>
       </c>
       <c r="P407" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="Q407">
         <v>0.85</v>
@@ -71644,7 +71644,7 @@
         <v>2278</v>
       </c>
       <c r="P408" t="s">
-        <v>2056</v>
+        <v>2089</v>
       </c>
       <c r="Q408">
         <v>0.85</v>
@@ -71658,7 +71658,7 @@
         <v>2279</v>
       </c>
       <c r="P409" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="Q409">
         <v>0.85</v>
@@ -71672,7 +71672,7 @@
         <v>2280</v>
       </c>
       <c r="P410" t="s">
-        <v>2087</v>
+        <v>2093</v>
       </c>
       <c r="Q410">
         <v>0.85</v>
@@ -71686,7 +71686,7 @@
         <v>2281</v>
       </c>
       <c r="P411" t="s">
-        <v>2073</v>
+        <v>2088</v>
       </c>
       <c r="Q411">
         <v>0.85</v>
@@ -71700,7 +71700,7 @@
         <v>2282</v>
       </c>
       <c r="P412" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
       <c r="Q412">
         <v>0.85</v>
@@ -71714,7 +71714,7 @@
         <v>2283</v>
       </c>
       <c r="P413" t="s">
-        <v>2095</v>
+        <v>2051</v>
       </c>
       <c r="Q413">
         <v>0.85</v>
@@ -71728,7 +71728,7 @@
         <v>2284</v>
       </c>
       <c r="P414" t="s">
-        <v>2088</v>
+        <v>2071</v>
       </c>
       <c r="Q414">
         <v>0.85</v>
@@ -71742,7 +71742,7 @@
         <v>2285</v>
       </c>
       <c r="P415" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="Q415">
         <v>0.85</v>
@@ -71756,7 +71756,7 @@
         <v>2286</v>
       </c>
       <c r="P416" t="s">
-        <v>2081</v>
+        <v>2055</v>
       </c>
       <c r="Q416">
         <v>0.85</v>
@@ -71784,7 +71784,7 @@
         <v>2288</v>
       </c>
       <c r="P418" t="s">
-        <v>2106</v>
+        <v>2101</v>
       </c>
       <c r="Q418">
         <v>0.85</v>
@@ -71798,7 +71798,7 @@
         <v>2289</v>
       </c>
       <c r="P419" t="s">
-        <v>2087</v>
+        <v>2065</v>
       </c>
       <c r="Q419">
         <v>0.85</v>
@@ -71812,10 +71812,10 @@
         <v>2290</v>
       </c>
       <c r="P420" t="s">
-        <v>2107</v>
+        <v>2103</v>
       </c>
       <c r="Q420">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="421" spans="14:17" x14ac:dyDescent="0.45">
@@ -71826,7 +71826,7 @@
         <v>2291</v>
       </c>
       <c r="P421" t="s">
-        <v>2106</v>
+        <v>2051</v>
       </c>
       <c r="Q421">
         <v>0.85</v>
@@ -71840,7 +71840,7 @@
         <v>2292</v>
       </c>
       <c r="P422" t="s">
-        <v>2078</v>
+        <v>2058</v>
       </c>
       <c r="Q422">
         <v>0.85</v>
@@ -71854,7 +71854,7 @@
         <v>2293</v>
       </c>
       <c r="P423" t="s">
-        <v>2055</v>
+        <v>2097</v>
       </c>
       <c r="Q423">
         <v>0.85</v>
@@ -71868,7 +71868,7 @@
         <v>2294</v>
       </c>
       <c r="P424" t="s">
-        <v>2076</v>
+        <v>2052</v>
       </c>
       <c r="Q424">
         <v>0.85</v>
@@ -71882,7 +71882,7 @@
         <v>2295</v>
       </c>
       <c r="P425" t="s">
-        <v>2106</v>
+        <v>2099</v>
       </c>
       <c r="Q425">
         <v>0.85</v>
@@ -71896,7 +71896,7 @@
         <v>2296</v>
       </c>
       <c r="P426" t="s">
-        <v>2103</v>
+        <v>2069</v>
       </c>
       <c r="Q426">
         <v>0.85</v>
@@ -71910,7 +71910,7 @@
         <v>2297</v>
       </c>
       <c r="P427" t="s">
-        <v>2088</v>
+        <v>2098</v>
       </c>
       <c r="Q427">
         <v>0.85</v>
@@ -71924,7 +71924,7 @@
         <v>2298</v>
       </c>
       <c r="P428" t="s">
-        <v>2053</v>
+        <v>2081</v>
       </c>
       <c r="Q428">
         <v>0.85</v>
@@ -71938,7 +71938,7 @@
         <v>2299</v>
       </c>
       <c r="P429" t="s">
-        <v>2089</v>
+        <v>2103</v>
       </c>
       <c r="Q429">
         <v>0.85</v>
@@ -71952,7 +71952,7 @@
         <v>2300</v>
       </c>
       <c r="P430" t="s">
-        <v>2075</v>
+        <v>2087</v>
       </c>
       <c r="Q430">
         <v>0.85</v>
@@ -71966,7 +71966,7 @@
         <v>2301</v>
       </c>
       <c r="P431" t="s">
-        <v>2094</v>
+        <v>2086</v>
       </c>
       <c r="Q431">
         <v>0.85</v>
@@ -71980,7 +71980,7 @@
         <v>2302</v>
       </c>
       <c r="P432" t="s">
-        <v>2103</v>
+        <v>2108</v>
       </c>
       <c r="Q432">
         <v>0.85</v>
@@ -71994,7 +71994,7 @@
         <v>2303</v>
       </c>
       <c r="P433" t="s">
-        <v>2076</v>
+        <v>2109</v>
       </c>
       <c r="Q433">
         <v>0.85</v>
@@ -72008,7 +72008,7 @@
         <v>2304</v>
       </c>
       <c r="P434" t="s">
-        <v>2107</v>
+        <v>2098</v>
       </c>
       <c r="Q434">
         <v>0.85</v>
@@ -72022,7 +72022,7 @@
         <v>2305</v>
       </c>
       <c r="P435" t="s">
-        <v>2104</v>
+        <v>2070</v>
       </c>
       <c r="Q435">
         <v>0.85</v>
@@ -72036,7 +72036,7 @@
         <v>2306</v>
       </c>
       <c r="P436" t="s">
-        <v>2088</v>
+        <v>2051</v>
       </c>
       <c r="Q436">
         <v>0.85</v>
@@ -72050,7 +72050,7 @@
         <v>2307</v>
       </c>
       <c r="P437" t="s">
-        <v>2093</v>
+        <v>2051</v>
       </c>
       <c r="Q437">
         <v>0.85</v>
@@ -72064,7 +72064,7 @@
         <v>2308</v>
       </c>
       <c r="P438" t="s">
-        <v>2086</v>
+        <v>2109</v>
       </c>
       <c r="Q438">
         <v>0.85</v>
@@ -72078,7 +72078,7 @@
         <v>2309</v>
       </c>
       <c r="P439" t="s">
-        <v>2055</v>
+        <v>2106</v>
       </c>
       <c r="Q439">
         <v>0.85</v>
@@ -72092,7 +72092,7 @@
         <v>2310</v>
       </c>
       <c r="P440" t="s">
-        <v>2078</v>
+        <v>2105</v>
       </c>
       <c r="Q440">
         <v>0.85</v>
@@ -72106,7 +72106,7 @@
         <v>2311</v>
       </c>
       <c r="P441" t="s">
-        <v>2089</v>
+        <v>2080</v>
       </c>
       <c r="Q441">
         <v>0.85</v>
@@ -72120,7 +72120,7 @@
         <v>2312</v>
       </c>
       <c r="P442" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="Q442">
         <v>0.85</v>
@@ -72134,7 +72134,7 @@
         <v>2313</v>
       </c>
       <c r="P443" t="s">
-        <v>2092</v>
+        <v>2073</v>
       </c>
       <c r="Q443">
         <v>0.85</v>
@@ -72148,7 +72148,7 @@
         <v>2314</v>
       </c>
       <c r="P444" t="s">
-        <v>2098</v>
+        <v>2106</v>
       </c>
       <c r="Q444">
         <v>0.85</v>
@@ -72162,7 +72162,7 @@
         <v>2315</v>
       </c>
       <c r="P445" t="s">
-        <v>2069</v>
+        <v>2098</v>
       </c>
       <c r="Q445">
         <v>0.85</v>
@@ -72176,7 +72176,7 @@
         <v>2316</v>
       </c>
       <c r="P446" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
       <c r="Q446">
         <v>0.85</v>
@@ -72190,10 +72190,10 @@
         <v>2317</v>
       </c>
       <c r="P447" t="s">
-        <v>2076</v>
+        <v>2052</v>
       </c>
       <c r="Q447">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="448" spans="14:17" x14ac:dyDescent="0.45">
@@ -72204,10 +72204,10 @@
         <v>2318</v>
       </c>
       <c r="P448" t="s">
-        <v>2097</v>
+        <v>2056</v>
       </c>
       <c r="Q448">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="449" spans="14:17" x14ac:dyDescent="0.45">
@@ -72218,7 +72218,7 @@
         <v>2319</v>
       </c>
       <c r="P449" t="s">
-        <v>2084</v>
+        <v>2101</v>
       </c>
       <c r="Q449">
         <v>0.85</v>
@@ -72232,7 +72232,7 @@
         <v>2320</v>
       </c>
       <c r="P450" t="s">
-        <v>2083</v>
+        <v>2076</v>
       </c>
       <c r="Q450">
         <v>0.85</v>
@@ -72246,7 +72246,7 @@
         <v>2321</v>
       </c>
       <c r="P451" t="s">
-        <v>2096</v>
+        <v>2061</v>
       </c>
       <c r="Q451">
         <v>0.85</v>
@@ -72260,7 +72260,7 @@
         <v>2322</v>
       </c>
       <c r="P452" t="s">
-        <v>2051</v>
+        <v>2095</v>
       </c>
       <c r="Q452">
         <v>0.85</v>
@@ -72274,7 +72274,7 @@
         <v>2323</v>
       </c>
       <c r="P453" t="s">
-        <v>2051</v>
+        <v>2063</v>
       </c>
       <c r="Q453">
         <v>0.85</v>
@@ -72288,7 +72288,7 @@
         <v>2324</v>
       </c>
       <c r="P454" t="s">
-        <v>2081</v>
+        <v>2104</v>
       </c>
       <c r="Q454">
         <v>0.85</v>
@@ -72302,10 +72302,10 @@
         <v>2325</v>
       </c>
       <c r="P455" t="s">
-        <v>2077</v>
+        <v>2099</v>
       </c>
       <c r="Q455">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="456" spans="14:17" x14ac:dyDescent="0.45">
@@ -72316,7 +72316,7 @@
         <v>2326</v>
       </c>
       <c r="P456" t="s">
-        <v>2053</v>
+        <v>2060</v>
       </c>
       <c r="Q456">
         <v>0.85</v>
@@ -72330,7 +72330,7 @@
         <v>2327</v>
       </c>
       <c r="P457" t="s">
-        <v>2065</v>
+        <v>2092</v>
       </c>
       <c r="Q457">
         <v>0.85</v>
@@ -72344,7 +72344,7 @@
         <v>2328</v>
       </c>
       <c r="P458" t="s">
-        <v>2076</v>
+        <v>2087</v>
       </c>
       <c r="Q458">
         <v>0.85</v>
@@ -72358,7 +72358,7 @@
         <v>2329</v>
       </c>
       <c r="P459" t="s">
-        <v>2106</v>
+        <v>2081</v>
       </c>
       <c r="Q459">
         <v>0.85</v>
@@ -72372,7 +72372,7 @@
         <v>2330</v>
       </c>
       <c r="P460" t="s">
-        <v>2094</v>
+        <v>2072</v>
       </c>
       <c r="Q460">
         <v>0.85</v>
@@ -72386,7 +72386,7 @@
         <v>2331</v>
       </c>
       <c r="P461" t="s">
-        <v>2101</v>
+        <v>2089</v>
       </c>
       <c r="Q461">
         <v>0.85</v>
@@ -72400,7 +72400,7 @@
         <v>2332</v>
       </c>
       <c r="P462" t="s">
-        <v>2055</v>
+        <v>2096</v>
       </c>
       <c r="Q462">
         <v>0.85</v>
@@ -72414,7 +72414,7 @@
         <v>2333</v>
       </c>
       <c r="P463" t="s">
-        <v>2086</v>
+        <v>2058</v>
       </c>
       <c r="Q463">
         <v>0.85</v>
@@ -72428,7 +72428,7 @@
         <v>2334</v>
       </c>
       <c r="P464" t="s">
-        <v>2058</v>
+        <v>2104</v>
       </c>
       <c r="Q464">
         <v>0.85</v>
@@ -72442,7 +72442,7 @@
         <v>2335</v>
       </c>
       <c r="P465" t="s">
-        <v>2076</v>
+        <v>2097</v>
       </c>
       <c r="Q465">
         <v>0.85</v>
@@ -72456,7 +72456,7 @@
         <v>2336</v>
       </c>
       <c r="P466" t="s">
-        <v>2103</v>
+        <v>2051</v>
       </c>
       <c r="Q466">
         <v>0.85</v>
@@ -72470,7 +72470,7 @@
         <v>2337</v>
       </c>
       <c r="P467" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="Q467">
         <v>0.85</v>
@@ -72484,7 +72484,7 @@
         <v>2338</v>
       </c>
       <c r="P468" t="s">
-        <v>2059</v>
+        <v>2055</v>
       </c>
       <c r="Q468">
         <v>0.85</v>
@@ -72498,7 +72498,7 @@
         <v>2339</v>
       </c>
       <c r="P469" t="s">
-        <v>2075</v>
+        <v>2082</v>
       </c>
       <c r="Q469">
         <v>0.85</v>
@@ -72512,10 +72512,10 @@
         <v>2340</v>
       </c>
       <c r="P470" t="s">
-        <v>2091</v>
+        <v>2086</v>
       </c>
       <c r="Q470">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="471" spans="14:17" x14ac:dyDescent="0.45">
@@ -72526,7 +72526,7 @@
         <v>2341</v>
       </c>
       <c r="P471" t="s">
-        <v>2103</v>
+        <v>2094</v>
       </c>
       <c r="Q471">
         <v>0.85</v>
@@ -72540,7 +72540,7 @@
         <v>2342</v>
       </c>
       <c r="P472" t="s">
-        <v>2082</v>
+        <v>2092</v>
       </c>
       <c r="Q472">
         <v>0.85</v>
@@ -72554,7 +72554,7 @@
         <v>2343</v>
       </c>
       <c r="P473" t="s">
-        <v>2105</v>
+        <v>2101</v>
       </c>
       <c r="Q473">
         <v>0.85</v>
@@ -72568,7 +72568,7 @@
         <v>2344</v>
       </c>
       <c r="P474" t="s">
-        <v>2095</v>
+        <v>2104</v>
       </c>
       <c r="Q474">
         <v>0.85</v>
@@ -72582,7 +72582,7 @@
         <v>2345</v>
       </c>
       <c r="P475" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="Q475">
         <v>0.85</v>
@@ -72596,7 +72596,7 @@
         <v>2346</v>
       </c>
       <c r="P476" t="s">
-        <v>2083</v>
+        <v>2093</v>
       </c>
       <c r="Q476">
         <v>0.85</v>
@@ -72610,7 +72610,7 @@
         <v>2347</v>
       </c>
       <c r="P477" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
       <c r="Q477">
         <v>0.85</v>
@@ -72624,7 +72624,7 @@
         <v>2348</v>
       </c>
       <c r="P478" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="Q478">
         <v>0.85</v>
@@ -72638,7 +72638,7 @@
         <v>2349</v>
       </c>
       <c r="P479" t="s">
-        <v>2051</v>
+        <v>2102</v>
       </c>
       <c r="Q479">
         <v>0.85</v>
@@ -72652,7 +72652,7 @@
         <v>2350</v>
       </c>
       <c r="P480" t="s">
-        <v>2098</v>
+        <v>2082</v>
       </c>
       <c r="Q480">
         <v>0.85</v>
@@ -72666,7 +72666,7 @@
         <v>2351</v>
       </c>
       <c r="P481" t="s">
-        <v>2106</v>
+        <v>2053</v>
       </c>
       <c r="Q481">
         <v>0.85</v>
@@ -72680,7 +72680,7 @@
         <v>2352</v>
       </c>
       <c r="P482" t="s">
-        <v>2109</v>
+        <v>2053</v>
       </c>
       <c r="Q482">
         <v>0.85</v>
@@ -72694,7 +72694,7 @@
         <v>2353</v>
       </c>
       <c r="P483" t="s">
-        <v>2060</v>
+        <v>2071</v>
       </c>
       <c r="Q483">
         <v>0.85</v>
@@ -72708,7 +72708,7 @@
         <v>2354</v>
       </c>
       <c r="P484" t="s">
-        <v>2103</v>
+        <v>2093</v>
       </c>
       <c r="Q484">
         <v>0.85</v>
@@ -72722,7 +72722,7 @@
         <v>2355</v>
       </c>
       <c r="P485" t="s">
-        <v>2080</v>
+        <v>2103</v>
       </c>
       <c r="Q485">
         <v>0.85</v>
@@ -72736,7 +72736,7 @@
         <v>2356</v>
       </c>
       <c r="P486" t="s">
-        <v>2089</v>
+        <v>2107</v>
       </c>
       <c r="Q486">
         <v>0.85</v>
@@ -72750,7 +72750,7 @@
         <v>2357</v>
       </c>
       <c r="P487" t="s">
-        <v>2054</v>
+        <v>2075</v>
       </c>
       <c r="Q487">
         <v>0.85</v>
@@ -72764,10 +72764,10 @@
         <v>2358</v>
       </c>
       <c r="P488" t="s">
-        <v>2065</v>
+        <v>2091</v>
       </c>
       <c r="Q488">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="489" spans="14:17" x14ac:dyDescent="0.45">
@@ -72778,7 +72778,7 @@
         <v>2359</v>
       </c>
       <c r="P489" t="s">
-        <v>2098</v>
+        <v>2093</v>
       </c>
       <c r="Q489">
         <v>0.85</v>
@@ -72792,10 +72792,10 @@
         <v>2360</v>
       </c>
       <c r="P490" t="s">
-        <v>2067</v>
+        <v>2090</v>
       </c>
       <c r="Q490">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="491" spans="14:17" x14ac:dyDescent="0.45">
@@ -72806,7 +72806,7 @@
         <v>2361</v>
       </c>
       <c r="P491" t="s">
-        <v>2104</v>
+        <v>2089</v>
       </c>
       <c r="Q491">
         <v>0.85</v>
@@ -72820,7 +72820,7 @@
         <v>2362</v>
       </c>
       <c r="P492" t="s">
-        <v>2080</v>
+        <v>2065</v>
       </c>
       <c r="Q492">
         <v>0.85</v>
@@ -72834,7 +72834,7 @@
         <v>2363</v>
       </c>
       <c r="P493" t="s">
-        <v>2086</v>
+        <v>2103</v>
       </c>
       <c r="Q493">
         <v>0.85</v>
@@ -72848,7 +72848,7 @@
         <v>2364</v>
       </c>
       <c r="P494" t="s">
-        <v>2086</v>
+        <v>2096</v>
       </c>
       <c r="Q494">
         <v>0.85</v>
@@ -72862,7 +72862,7 @@
         <v>2365</v>
       </c>
       <c r="P495" t="s">
-        <v>2080</v>
+        <v>2051</v>
       </c>
       <c r="Q495">
         <v>0.85</v>
@@ -72876,10 +72876,10 @@
         <v>2366</v>
       </c>
       <c r="P496" t="s">
-        <v>2056</v>
+        <v>2086</v>
       </c>
       <c r="Q496">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="497" spans="14:17" x14ac:dyDescent="0.45">
@@ -72890,7 +72890,7 @@
         <v>2367</v>
       </c>
       <c r="P497" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="Q497">
         <v>0.85</v>
@@ -72904,7 +72904,7 @@
         <v>2368</v>
       </c>
       <c r="P498" t="s">
-        <v>2083</v>
+        <v>2105</v>
       </c>
       <c r="Q498">
         <v>0.85</v>
@@ -72918,7 +72918,7 @@
         <v>2369</v>
       </c>
       <c r="P499" t="s">
-        <v>2060</v>
+        <v>2088</v>
       </c>
       <c r="Q499">
         <v>0.85</v>
@@ -72932,7 +72932,7 @@
         <v>2370</v>
       </c>
       <c r="P500" t="s">
-        <v>2109</v>
+        <v>2086</v>
       </c>
       <c r="Q500">
         <v>0.85</v>
@@ -72946,7 +72946,7 @@
         <v>2371</v>
       </c>
       <c r="P501" t="s">
-        <v>2088</v>
+        <v>2053</v>
       </c>
       <c r="Q501">
         <v>0.85</v>
@@ -72960,7 +72960,7 @@
         <v>2372</v>
       </c>
       <c r="P502" t="s">
-        <v>2069</v>
+        <v>2101</v>
       </c>
       <c r="Q502">
         <v>0.85</v>
@@ -72974,7 +72974,7 @@
         <v>2373</v>
       </c>
       <c r="P503" t="s">
-        <v>2073</v>
+        <v>2060</v>
       </c>
       <c r="Q503">
         <v>0.85</v>
@@ -72988,7 +72988,7 @@
         <v>2374</v>
       </c>
       <c r="P504" t="s">
-        <v>2081</v>
+        <v>2071</v>
       </c>
       <c r="Q504">
         <v>0.85</v>
@@ -73002,7 +73002,7 @@
         <v>2375</v>
       </c>
       <c r="P505" t="s">
-        <v>2094</v>
+        <v>2078</v>
       </c>
       <c r="Q505">
         <v>0.85</v>
@@ -73016,7 +73016,7 @@
         <v>2376</v>
       </c>
       <c r="P506" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
       <c r="Q506">
         <v>0.85</v>
@@ -73030,7 +73030,7 @@
         <v>2377</v>
       </c>
       <c r="P507" t="s">
-        <v>2055</v>
+        <v>2076</v>
       </c>
       <c r="Q507">
         <v>0.85</v>
@@ -73044,7 +73044,7 @@
         <v>2378</v>
       </c>
       <c r="P508" t="s">
-        <v>2103</v>
+        <v>2075</v>
       </c>
       <c r="Q508">
         <v>0.85</v>
@@ -73058,7 +73058,7 @@
         <v>2379</v>
       </c>
       <c r="P509" t="s">
-        <v>2109</v>
+        <v>2103</v>
       </c>
       <c r="Q509">
         <v>0.85</v>
@@ -73072,7 +73072,7 @@
         <v>2380</v>
       </c>
       <c r="P510" t="s">
-        <v>2081</v>
+        <v>2093</v>
       </c>
       <c r="Q510">
         <v>0.85</v>
@@ -73086,7 +73086,7 @@
         <v>2381</v>
       </c>
       <c r="P511" t="s">
-        <v>2067</v>
+        <v>2055</v>
       </c>
       <c r="Q511">
         <v>0.85</v>
@@ -73100,7 +73100,7 @@
         <v>2382</v>
       </c>
       <c r="P512" t="s">
-        <v>2105</v>
+        <v>2051</v>
       </c>
       <c r="Q512">
         <v>0.85</v>
@@ -73114,7 +73114,7 @@
         <v>2383</v>
       </c>
       <c r="P513" t="s">
-        <v>2106</v>
+        <v>2063</v>
       </c>
       <c r="Q513">
         <v>0.85</v>
@@ -73128,7 +73128,7 @@
         <v>2384</v>
       </c>
       <c r="P514" t="s">
-        <v>2076</v>
+        <v>2090</v>
       </c>
       <c r="Q514">
         <v>0.85</v>
@@ -73142,7 +73142,7 @@
         <v>2385</v>
       </c>
       <c r="P515" t="s">
-        <v>2051</v>
+        <v>2101</v>
       </c>
       <c r="Q515">
         <v>0.85</v>
@@ -73156,7 +73156,7 @@
         <v>2386</v>
       </c>
       <c r="P516" t="s">
-        <v>2098</v>
+        <v>2103</v>
       </c>
       <c r="Q516">
         <v>0.85</v>
@@ -73184,7 +73184,7 @@
         <v>2388</v>
       </c>
       <c r="P518" t="s">
-        <v>2094</v>
+        <v>2086</v>
       </c>
       <c r="Q518">
         <v>0.85</v>
@@ -73198,7 +73198,7 @@
         <v>2389</v>
       </c>
       <c r="P519" t="s">
-        <v>2087</v>
+        <v>2071</v>
       </c>
       <c r="Q519">
         <v>0.85</v>
@@ -73212,7 +73212,7 @@
         <v>2390</v>
       </c>
       <c r="P520" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="Q520">
         <v>0.85</v>
@@ -73226,7 +73226,7 @@
         <v>2391</v>
       </c>
       <c r="P521" t="s">
-        <v>2086</v>
+        <v>2068</v>
       </c>
       <c r="Q521">
         <v>0.85</v>
@@ -73240,7 +73240,7 @@
         <v>2392</v>
       </c>
       <c r="P522" t="s">
-        <v>2106</v>
+        <v>2071</v>
       </c>
       <c r="Q522">
         <v>0.85</v>
@@ -73254,7 +73254,7 @@
         <v>2393</v>
       </c>
       <c r="P523" t="s">
-        <v>2056</v>
+        <v>2093</v>
       </c>
       <c r="Q523">
         <v>0.85</v>
@@ -73268,7 +73268,7 @@
         <v>2394</v>
       </c>
       <c r="P524" t="s">
-        <v>2083</v>
+        <v>2053</v>
       </c>
       <c r="Q524">
         <v>0.85</v>
@@ -73282,7 +73282,7 @@
         <v>2395</v>
       </c>
       <c r="P525" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
       <c r="Q525">
         <v>0.85</v>
@@ -73296,7 +73296,7 @@
         <v>2396</v>
       </c>
       <c r="P526" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
       <c r="Q526">
         <v>0.85</v>
@@ -73310,7 +73310,7 @@
         <v>2397</v>
       </c>
       <c r="P527" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="Q527">
         <v>0.85</v>
@@ -73324,7 +73324,7 @@
         <v>2398</v>
       </c>
       <c r="P528" t="s">
-        <v>2103</v>
+        <v>2093</v>
       </c>
       <c r="Q528">
         <v>0.85</v>
@@ -73338,7 +73338,7 @@
         <v>2399</v>
       </c>
       <c r="P529" t="s">
-        <v>2089</v>
+        <v>2100</v>
       </c>
       <c r="Q529">
         <v>0.85</v>
@@ -73352,10 +73352,10 @@
         <v>2400</v>
       </c>
       <c r="P530" t="s">
-        <v>2086</v>
+        <v>2081</v>
       </c>
       <c r="Q530">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="531" spans="14:17" x14ac:dyDescent="0.45">
@@ -73366,7 +73366,7 @@
         <v>2401</v>
       </c>
       <c r="P531" t="s">
-        <v>2094</v>
+        <v>2069</v>
       </c>
       <c r="Q531">
         <v>0.85</v>
@@ -73380,7 +73380,7 @@
         <v>2402</v>
       </c>
       <c r="P532" t="s">
-        <v>2093</v>
+        <v>2065</v>
       </c>
       <c r="Q532">
         <v>0.85</v>
@@ -73394,7 +73394,7 @@
         <v>2403</v>
       </c>
       <c r="P533" t="s">
-        <v>2052</v>
+        <v>2083</v>
       </c>
       <c r="Q533">
         <v>0.85</v>
@@ -73408,7 +73408,7 @@
         <v>2404</v>
       </c>
       <c r="P534" t="s">
-        <v>2096</v>
+        <v>2058</v>
       </c>
       <c r="Q534">
         <v>0.85</v>
@@ -73422,7 +73422,7 @@
         <v>2405</v>
       </c>
       <c r="P535" t="s">
-        <v>2093</v>
+        <v>2052</v>
       </c>
       <c r="Q535">
         <v>0.85</v>
@@ -73436,10 +73436,10 @@
         <v>2406</v>
       </c>
       <c r="P536" t="s">
-        <v>2051</v>
+        <v>2109</v>
       </c>
       <c r="Q536">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="537" spans="14:17" x14ac:dyDescent="0.45">
@@ -73450,10 +73450,10 @@
         <v>2407</v>
       </c>
       <c r="P537" t="s">
-        <v>2098</v>
+        <v>2081</v>
       </c>
       <c r="Q537">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="538" spans="14:17" x14ac:dyDescent="0.45">
@@ -73464,10 +73464,10 @@
         <v>2408</v>
       </c>
       <c r="P538" t="s">
-        <v>2053</v>
+        <v>2063</v>
       </c>
       <c r="Q538">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="539" spans="14:17" x14ac:dyDescent="0.45">
@@ -73478,7 +73478,7 @@
         <v>2409</v>
       </c>
       <c r="P539" t="s">
-        <v>2082</v>
+        <v>2055</v>
       </c>
       <c r="Q539">
         <v>0.85</v>
@@ -73492,7 +73492,7 @@
         <v>2410</v>
       </c>
       <c r="P540" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="Q540">
         <v>0.85</v>
@@ -73506,7 +73506,7 @@
         <v>2411</v>
       </c>
       <c r="P541" t="s">
-        <v>2089</v>
+        <v>2075</v>
       </c>
       <c r="Q541">
         <v>0.85</v>
@@ -73520,7 +73520,7 @@
         <v>2412</v>
       </c>
       <c r="P542" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="Q542">
         <v>0.85</v>
@@ -73548,7 +73548,7 @@
         <v>2414</v>
       </c>
       <c r="P544" t="s">
-        <v>2087</v>
+        <v>2077</v>
       </c>
       <c r="Q544">
         <v>0.85</v>
@@ -73562,7 +73562,7 @@
         <v>2415</v>
       </c>
       <c r="P545" t="s">
-        <v>2069</v>
+        <v>2055</v>
       </c>
       <c r="Q545">
         <v>0.85</v>
@@ -73576,7 +73576,7 @@
         <v>2416</v>
       </c>
       <c r="P546" t="s">
-        <v>2106</v>
+        <v>2096</v>
       </c>
       <c r="Q546">
         <v>0.85</v>
@@ -73590,7 +73590,7 @@
         <v>2417</v>
       </c>
       <c r="P547" t="s">
-        <v>2061</v>
+        <v>2094</v>
       </c>
       <c r="Q547">
         <v>0.85</v>
@@ -73604,7 +73604,7 @@
         <v>2418</v>
       </c>
       <c r="P548" t="s">
-        <v>2093</v>
+        <v>2076</v>
       </c>
       <c r="Q548">
         <v>0.85</v>
@@ -73618,7 +73618,7 @@
         <v>2419</v>
       </c>
       <c r="P549" t="s">
-        <v>2093</v>
+        <v>2103</v>
       </c>
       <c r="Q549">
         <v>0.85</v>
@@ -73632,7 +73632,7 @@
         <v>2420</v>
       </c>
       <c r="P550" t="s">
-        <v>2060</v>
+        <v>2106</v>
       </c>
       <c r="Q550">
         <v>0.85</v>
@@ -73646,7 +73646,7 @@
         <v>2421</v>
       </c>
       <c r="P551" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="Q551">
         <v>0.85</v>
@@ -73660,7 +73660,7 @@
         <v>2422</v>
       </c>
       <c r="P552" t="s">
-        <v>2098</v>
+        <v>2086</v>
       </c>
       <c r="Q552">
         <v>0.85</v>
@@ -73674,7 +73674,7 @@
         <v>2423</v>
       </c>
       <c r="P553" t="s">
-        <v>2051</v>
+        <v>2069</v>
       </c>
       <c r="Q553">
         <v>0.85</v>
@@ -73688,7 +73688,7 @@
         <v>2424</v>
       </c>
       <c r="P554" t="s">
-        <v>2106</v>
+        <v>2098</v>
       </c>
       <c r="Q554">
         <v>0.85</v>
@@ -73702,7 +73702,7 @@
         <v>2425</v>
       </c>
       <c r="P555" t="s">
-        <v>2071</v>
+        <v>2060</v>
       </c>
       <c r="Q555">
         <v>0.85</v>
@@ -73716,7 +73716,7 @@
         <v>2426</v>
       </c>
       <c r="P556" t="s">
-        <v>2076</v>
+        <v>2103</v>
       </c>
       <c r="Q556">
         <v>0.85</v>
@@ -73730,7 +73730,7 @@
         <v>2427</v>
       </c>
       <c r="P557" t="s">
-        <v>2060</v>
+        <v>2071</v>
       </c>
       <c r="Q557">
         <v>0.85</v>
@@ -73744,7 +73744,7 @@
         <v>2428</v>
       </c>
       <c r="P558" t="s">
-        <v>2098</v>
+        <v>2107</v>
       </c>
       <c r="Q558">
         <v>0.85</v>
@@ -73758,7 +73758,7 @@
         <v>2429</v>
       </c>
       <c r="P559" t="s">
-        <v>2071</v>
+        <v>2094</v>
       </c>
       <c r="Q559">
         <v>0.85</v>
@@ -73772,7 +73772,7 @@
         <v>2430</v>
       </c>
       <c r="P560" t="s">
-        <v>2089</v>
+        <v>2053</v>
       </c>
       <c r="Q560">
         <v>0.85</v>
@@ -73786,10 +73786,10 @@
         <v>2431</v>
       </c>
       <c r="P561" t="s">
-        <v>2076</v>
+        <v>2106</v>
       </c>
       <c r="Q561">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="562" spans="14:17" x14ac:dyDescent="0.45">
@@ -73800,10 +73800,10 @@
         <v>2432</v>
       </c>
       <c r="P562" t="s">
-        <v>2054</v>
+        <v>2060</v>
       </c>
       <c r="Q562">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="563" spans="14:17" x14ac:dyDescent="0.45">
@@ -73814,10 +73814,10 @@
         <v>2433</v>
       </c>
       <c r="P563" t="s">
-        <v>2071</v>
+        <v>2107</v>
       </c>
       <c r="Q563">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="564" spans="14:17" x14ac:dyDescent="0.45">
@@ -73828,7 +73828,7 @@
         <v>2434</v>
       </c>
       <c r="P564" t="s">
-        <v>2053</v>
+        <v>2106</v>
       </c>
       <c r="Q564">
         <v>0.85</v>
@@ -73842,7 +73842,7 @@
         <v>2435</v>
       </c>
       <c r="P565" t="s">
-        <v>2055</v>
+        <v>2063</v>
       </c>
       <c r="Q565">
         <v>0.85</v>
@@ -73856,7 +73856,7 @@
         <v>2436</v>
       </c>
       <c r="P566" t="s">
-        <v>2083</v>
+        <v>2104</v>
       </c>
       <c r="Q566">
         <v>0.85</v>
@@ -73870,7 +73870,7 @@
         <v>2437</v>
       </c>
       <c r="P567" t="s">
-        <v>2098</v>
+        <v>2077</v>
       </c>
       <c r="Q567">
         <v>0.85</v>
@@ -73884,7 +73884,7 @@
         <v>2438</v>
       </c>
       <c r="P568" t="s">
-        <v>2084</v>
+        <v>2055</v>
       </c>
       <c r="Q568">
         <v>0.85</v>
@@ -73898,7 +73898,7 @@
         <v>2439</v>
       </c>
       <c r="P569" t="s">
-        <v>2070</v>
+        <v>2106</v>
       </c>
       <c r="Q569">
         <v>0.85</v>
@@ -73912,7 +73912,7 @@
         <v>2440</v>
       </c>
       <c r="P570" t="s">
-        <v>2095</v>
+        <v>2071</v>
       </c>
       <c r="Q570">
         <v>0.85</v>
@@ -73926,7 +73926,7 @@
         <v>2441</v>
       </c>
       <c r="P571" t="s">
-        <v>2062</v>
+        <v>2093</v>
       </c>
       <c r="Q571">
         <v>0.85</v>
@@ -73940,7 +73940,7 @@
         <v>2442</v>
       </c>
       <c r="P572" t="s">
-        <v>2088</v>
+        <v>2076</v>
       </c>
       <c r="Q572">
         <v>0.85</v>
@@ -73968,7 +73968,7 @@
         <v>2444</v>
       </c>
       <c r="P574" t="s">
-        <v>2065</v>
+        <v>2106</v>
       </c>
       <c r="Q574">
         <v>0.85</v>
@@ -73982,7 +73982,7 @@
         <v>2445</v>
       </c>
       <c r="P575" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="Q575">
         <v>0.85</v>
@@ -73996,7 +73996,7 @@
         <v>2446</v>
       </c>
       <c r="P576" t="s">
-        <v>2108</v>
+        <v>2103</v>
       </c>
       <c r="Q576">
         <v>0.85</v>
@@ -74010,7 +74010,7 @@
         <v>2447</v>
       </c>
       <c r="P577" t="s">
-        <v>2053</v>
+        <v>2081</v>
       </c>
       <c r="Q577">
         <v>0.85</v>
@@ -74024,7 +74024,7 @@
         <v>2448</v>
       </c>
       <c r="P578" t="s">
-        <v>2096</v>
+        <v>2087</v>
       </c>
       <c r="Q578">
         <v>0.85</v>
@@ -74038,7 +74038,7 @@
         <v>2449</v>
       </c>
       <c r="P579" t="s">
-        <v>2082</v>
+        <v>2071</v>
       </c>
       <c r="Q579">
         <v>0.85</v>
@@ -74052,10 +74052,10 @@
         <v>2450</v>
       </c>
       <c r="P580" t="s">
-        <v>2098</v>
+        <v>2090</v>
       </c>
       <c r="Q580">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="581" spans="14:17" x14ac:dyDescent="0.45">
@@ -74066,7 +74066,7 @@
         <v>2451</v>
       </c>
       <c r="P581" t="s">
-        <v>2093</v>
+        <v>2103</v>
       </c>
       <c r="Q581">
         <v>0.85</v>
@@ -74080,7 +74080,7 @@
         <v>2452</v>
       </c>
       <c r="P582" t="s">
-        <v>2080</v>
+        <v>2076</v>
       </c>
       <c r="Q582">
         <v>0.85</v>
@@ -74094,7 +74094,7 @@
         <v>2453</v>
       </c>
       <c r="P583" t="s">
-        <v>2052</v>
+        <v>2107</v>
       </c>
       <c r="Q583">
         <v>0.85</v>
@@ -74108,7 +74108,7 @@
         <v>2454</v>
       </c>
       <c r="P584" t="s">
-        <v>2101</v>
+        <v>2090</v>
       </c>
       <c r="Q584">
         <v>0.85</v>
@@ -74122,7 +74122,7 @@
         <v>2455</v>
       </c>
       <c r="P585" t="s">
-        <v>2089</v>
+        <v>2063</v>
       </c>
       <c r="Q585">
         <v>0.85</v>
@@ -74136,7 +74136,7 @@
         <v>2456</v>
       </c>
       <c r="P586" t="s">
-        <v>2089</v>
+        <v>2051</v>
       </c>
       <c r="Q586">
         <v>0.85</v>
@@ -74150,7 +74150,7 @@
         <v>2457</v>
       </c>
       <c r="P587" t="s">
-        <v>2059</v>
+        <v>2055</v>
       </c>
       <c r="Q587">
         <v>0.85</v>
@@ -74164,7 +74164,7 @@
         <v>2458</v>
       </c>
       <c r="P588" t="s">
-        <v>2071</v>
+        <v>2076</v>
       </c>
       <c r="Q588">
         <v>0.85</v>
@@ -74178,7 +74178,7 @@
         <v>2459</v>
       </c>
       <c r="P589" t="s">
-        <v>2057</v>
+        <v>2104</v>
       </c>
       <c r="Q589">
         <v>0.85</v>
@@ -74192,7 +74192,7 @@
         <v>2460</v>
       </c>
       <c r="P590" t="s">
-        <v>2093</v>
+        <v>2061</v>
       </c>
       <c r="Q590">
         <v>0.85</v>
@@ -74206,7 +74206,7 @@
         <v>2461</v>
       </c>
       <c r="P591" t="s">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="Q591">
         <v>0.85</v>
@@ -74220,7 +74220,7 @@
         <v>2462</v>
       </c>
       <c r="P592" t="s">
-        <v>2076</v>
+        <v>2055</v>
       </c>
       <c r="Q592">
         <v>0.85</v>
@@ -74234,7 +74234,7 @@
         <v>2463</v>
       </c>
       <c r="P593" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="Q593">
         <v>0.85</v>
@@ -74248,7 +74248,7 @@
         <v>2464</v>
       </c>
       <c r="P594" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="Q594">
         <v>0.85</v>
@@ -74262,7 +74262,7 @@
         <v>2465</v>
       </c>
       <c r="P595" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="Q595">
         <v>0.85</v>
@@ -74276,7 +74276,7 @@
         <v>2466</v>
       </c>
       <c r="P596" t="s">
-        <v>2063</v>
+        <v>2103</v>
       </c>
       <c r="Q596">
         <v>0.85</v>
@@ -74290,7 +74290,7 @@
         <v>2467</v>
       </c>
       <c r="P597" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="Q597">
         <v>0.85</v>
@@ -74304,7 +74304,7 @@
         <v>2468</v>
       </c>
       <c r="P598" t="s">
-        <v>2089</v>
+        <v>2095</v>
       </c>
       <c r="Q598">
         <v>0.85</v>
@@ -74318,7 +74318,7 @@
         <v>2469</v>
       </c>
       <c r="P599" t="s">
-        <v>2086</v>
+        <v>2055</v>
       </c>
       <c r="Q599">
         <v>0.85</v>
@@ -74332,10 +74332,10 @@
         <v>2470</v>
       </c>
       <c r="P600" t="s">
-        <v>2071</v>
+        <v>2051</v>
       </c>
       <c r="Q600">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="601" spans="14:17" x14ac:dyDescent="0.45">
@@ -74346,10 +74346,10 @@
         <v>2471</v>
       </c>
       <c r="P601" t="s">
-        <v>2058</v>
+        <v>2095</v>
       </c>
       <c r="Q601">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="602" spans="14:17" x14ac:dyDescent="0.45">
@@ -74360,10 +74360,10 @@
         <v>2472</v>
       </c>
       <c r="P602" t="s">
-        <v>2082</v>
+        <v>2063</v>
       </c>
       <c r="Q602">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="603" spans="14:17" x14ac:dyDescent="0.45">
@@ -74374,7 +74374,7 @@
         <v>2473</v>
       </c>
       <c r="P603" t="s">
-        <v>2060</v>
+        <v>2106</v>
       </c>
       <c r="Q603">
         <v>0.85</v>
@@ -74388,7 +74388,7 @@
         <v>2474</v>
       </c>
       <c r="P604" t="s">
-        <v>2065</v>
+        <v>2088</v>
       </c>
       <c r="Q604">
         <v>0.85</v>
@@ -74402,7 +74402,7 @@
         <v>2475</v>
       </c>
       <c r="P605" t="s">
-        <v>2060</v>
+        <v>2106</v>
       </c>
       <c r="Q605">
         <v>0.85</v>
@@ -74416,7 +74416,7 @@
         <v>2476</v>
       </c>
       <c r="P606" t="s">
-        <v>2106</v>
+        <v>2083</v>
       </c>
       <c r="Q606">
         <v>0.85</v>
@@ -74430,7 +74430,7 @@
         <v>2477</v>
       </c>
       <c r="P607" t="s">
-        <v>2106</v>
+        <v>2071</v>
       </c>
       <c r="Q607">
         <v>0.85</v>
@@ -74444,7 +74444,7 @@
         <v>2478</v>
       </c>
       <c r="P608" t="s">
-        <v>2086</v>
+        <v>2075</v>
       </c>
       <c r="Q608">
         <v>0.85</v>
@@ -74458,7 +74458,7 @@
         <v>2479</v>
       </c>
       <c r="P609" t="s">
-        <v>2076</v>
+        <v>2065</v>
       </c>
       <c r="Q609">
         <v>0.85</v>
@@ -74472,7 +74472,7 @@
         <v>2480</v>
       </c>
       <c r="P610" t="s">
-        <v>2077</v>
+        <v>2083</v>
       </c>
       <c r="Q610">
         <v>0.85</v>
@@ -74486,7 +74486,7 @@
         <v>2481</v>
       </c>
       <c r="P611" t="s">
-        <v>2081</v>
+        <v>2075</v>
       </c>
       <c r="Q611">
         <v>0.85</v>
@@ -74500,7 +74500,7 @@
         <v>2482</v>
       </c>
       <c r="P612" t="s">
-        <v>2060</v>
+        <v>2106</v>
       </c>
       <c r="Q612">
         <v>0.85</v>
@@ -74514,7 +74514,7 @@
         <v>2483</v>
       </c>
       <c r="P613" t="s">
-        <v>2051</v>
+        <v>2083</v>
       </c>
       <c r="Q613">
         <v>0.85</v>
@@ -74528,7 +74528,7 @@
         <v>2484</v>
       </c>
       <c r="P614" t="s">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="Q614">
         <v>0.85</v>
@@ -74542,7 +74542,7 @@
         <v>2485</v>
       </c>
       <c r="P615" t="s">
-        <v>2102</v>
+        <v>2095</v>
       </c>
       <c r="Q615">
         <v>0.85</v>
@@ -74556,7 +74556,7 @@
         <v>2486</v>
       </c>
       <c r="P616" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="Q616">
         <v>0.85</v>
@@ -74570,7 +74570,7 @@
         <v>2487</v>
       </c>
       <c r="P617" t="s">
-        <v>2056</v>
+        <v>2098</v>
       </c>
       <c r="Q617">
         <v>0.85</v>
@@ -74584,7 +74584,7 @@
         <v>2488</v>
       </c>
       <c r="P618" t="s">
-        <v>2055</v>
+        <v>2096</v>
       </c>
       <c r="Q618">
         <v>0.85</v>
@@ -74598,7 +74598,7 @@
         <v>2489</v>
       </c>
       <c r="P619" t="s">
-        <v>2076</v>
+        <v>2107</v>
       </c>
       <c r="Q619">
         <v>0.85</v>
@@ -74612,7 +74612,7 @@
         <v>2490</v>
       </c>
       <c r="P620" t="s">
-        <v>2060</v>
+        <v>2103</v>
       </c>
       <c r="Q620">
         <v>0.85</v>
@@ -74626,7 +74626,7 @@
         <v>2491</v>
       </c>
       <c r="P621" t="s">
-        <v>2071</v>
+        <v>2051</v>
       </c>
       <c r="Q621">
         <v>0.85</v>
@@ -74640,7 +74640,7 @@
         <v>2492</v>
       </c>
       <c r="P622" t="s">
-        <v>2059</v>
+        <v>2100</v>
       </c>
       <c r="Q622">
         <v>0.85</v>
@@ -74654,7 +74654,7 @@
         <v>2493</v>
       </c>
       <c r="P623" t="s">
-        <v>2101</v>
+        <v>2051</v>
       </c>
       <c r="Q623">
         <v>0.85</v>
@@ -74668,7 +74668,7 @@
         <v>2494</v>
       </c>
       <c r="P624" t="s">
-        <v>2081</v>
+        <v>2071</v>
       </c>
       <c r="Q624">
         <v>0.85</v>
@@ -74682,7 +74682,7 @@
         <v>2495</v>
       </c>
       <c r="P625" t="s">
-        <v>2060</v>
+        <v>2055</v>
       </c>
       <c r="Q625">
         <v>0.85</v>
@@ -74696,7 +74696,7 @@
         <v>2496</v>
       </c>
       <c r="P626" t="s">
-        <v>2081</v>
+        <v>2093</v>
       </c>
       <c r="Q626">
         <v>0.85</v>
@@ -74710,7 +74710,7 @@
         <v>2497</v>
       </c>
       <c r="P627" t="s">
-        <v>2076</v>
+        <v>2106</v>
       </c>
       <c r="Q627">
         <v>0.85</v>
@@ -74724,7 +74724,7 @@
         <v>2498</v>
       </c>
       <c r="P628" t="s">
-        <v>2075</v>
+        <v>2087</v>
       </c>
       <c r="Q628">
         <v>0.85</v>
@@ -74738,7 +74738,7 @@
         <v>2499</v>
       </c>
       <c r="P629" t="s">
-        <v>2107</v>
+        <v>2089</v>
       </c>
       <c r="Q629">
         <v>0.85</v>
@@ -74752,7 +74752,7 @@
         <v>2500</v>
       </c>
       <c r="P630" t="s">
-        <v>2062</v>
+        <v>2084</v>
       </c>
       <c r="Q630">
         <v>0.85</v>
@@ -74766,7 +74766,7 @@
         <v>2501</v>
       </c>
       <c r="P631" t="s">
-        <v>2069</v>
+        <v>2101</v>
       </c>
       <c r="Q631">
         <v>0.85</v>
@@ -74794,7 +74794,7 @@
         <v>2503</v>
       </c>
       <c r="P633" t="s">
-        <v>2071</v>
+        <v>2051</v>
       </c>
       <c r="Q633">
         <v>0.85</v>
@@ -74808,10 +74808,10 @@
         <v>2504</v>
       </c>
       <c r="P634" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="Q634">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="635" spans="14:17" x14ac:dyDescent="0.45">
@@ -74822,7 +74822,7 @@
         <v>2505</v>
       </c>
       <c r="P635" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="Q635">
         <v>0.85</v>
@@ -74836,7 +74836,7 @@
         <v>2506</v>
       </c>
       <c r="P636" t="s">
-        <v>2072</v>
+        <v>2087</v>
       </c>
       <c r="Q636">
         <v>0.85</v>
@@ -74850,7 +74850,7 @@
         <v>2507</v>
       </c>
       <c r="P637" t="s">
-        <v>2109</v>
+        <v>2080</v>
       </c>
       <c r="Q637">
         <v>0.85</v>
@@ -74864,7 +74864,7 @@
         <v>2508</v>
       </c>
       <c r="P638" t="s">
-        <v>2063</v>
+        <v>2089</v>
       </c>
       <c r="Q638">
         <v>0.95</v>
@@ -74878,7 +74878,7 @@
         <v>2509</v>
       </c>
       <c r="P639" t="s">
-        <v>2089</v>
+        <v>2081</v>
       </c>
       <c r="Q639">
         <v>0.85</v>
@@ -74892,7 +74892,7 @@
         <v>2510</v>
       </c>
       <c r="P640" t="s">
-        <v>2078</v>
+        <v>2082</v>
       </c>
       <c r="Q640">
         <v>0.85</v>
@@ -74906,7 +74906,7 @@
         <v>2511</v>
       </c>
       <c r="P641" t="s">
-        <v>2065</v>
+        <v>2106</v>
       </c>
       <c r="Q641">
         <v>0.85</v>
@@ -74920,7 +74920,7 @@
         <v>2512</v>
       </c>
       <c r="P642" t="s">
-        <v>2051</v>
+        <v>2083</v>
       </c>
       <c r="Q642">
         <v>0.85</v>
@@ -74934,7 +74934,7 @@
         <v>2513</v>
       </c>
       <c r="P643" t="s">
-        <v>2064</v>
+        <v>2060</v>
       </c>
       <c r="Q643">
         <v>0.85</v>
@@ -74948,7 +74948,7 @@
         <v>2514</v>
       </c>
       <c r="P644" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="Q644">
         <v>0.85</v>
@@ -74962,7 +74962,7 @@
         <v>2515</v>
       </c>
       <c r="P645" t="s">
-        <v>2051</v>
+        <v>2071</v>
       </c>
       <c r="Q645">
         <v>0.85</v>
@@ -74976,7 +74976,7 @@
         <v>2516</v>
       </c>
       <c r="P646" t="s">
-        <v>2089</v>
+        <v>2103</v>
       </c>
       <c r="Q646">
         <v>0.85</v>
@@ -74990,7 +74990,7 @@
         <v>2517</v>
       </c>
       <c r="P647" t="s">
-        <v>2063</v>
+        <v>2093</v>
       </c>
       <c r="Q647">
         <v>0.85</v>
@@ -75004,7 +75004,7 @@
         <v>2518</v>
       </c>
       <c r="P648" t="s">
-        <v>2109</v>
+        <v>2051</v>
       </c>
       <c r="Q648">
         <v>0.85</v>
@@ -75018,7 +75018,7 @@
         <v>2519</v>
       </c>
       <c r="P649" t="s">
-        <v>2051</v>
+        <v>2098</v>
       </c>
       <c r="Q649">
         <v>0.85</v>
@@ -75032,7 +75032,7 @@
         <v>2520</v>
       </c>
       <c r="P650" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="Q650">
         <v>0.85</v>
@@ -75046,7 +75046,7 @@
         <v>2521</v>
       </c>
       <c r="P651" t="s">
-        <v>2104</v>
+        <v>2076</v>
       </c>
       <c r="Q651">
         <v>0.85</v>
@@ -75060,7 +75060,7 @@
         <v>2522</v>
       </c>
       <c r="P652" t="s">
-        <v>2076</v>
+        <v>2083</v>
       </c>
       <c r="Q652">
         <v>0.85</v>
@@ -75074,7 +75074,7 @@
         <v>2523</v>
       </c>
       <c r="P653" t="s">
-        <v>2083</v>
+        <v>2093</v>
       </c>
       <c r="Q653">
         <v>0.85</v>
@@ -75088,7 +75088,7 @@
         <v>2524</v>
       </c>
       <c r="P654" t="s">
-        <v>2052</v>
+        <v>2077</v>
       </c>
       <c r="Q654">
         <v>0.85</v>
@@ -75102,7 +75102,7 @@
         <v>2525</v>
       </c>
       <c r="P655" t="s">
-        <v>2104</v>
+        <v>2080</v>
       </c>
       <c r="Q655">
         <v>0.85</v>
@@ -75116,7 +75116,7 @@
         <v>2526</v>
       </c>
       <c r="P656" t="s">
-        <v>2089</v>
+        <v>2076</v>
       </c>
       <c r="Q656">
         <v>0.85</v>
@@ -75130,7 +75130,7 @@
         <v>2527</v>
       </c>
       <c r="P657" t="s">
-        <v>2093</v>
+        <v>2076</v>
       </c>
       <c r="Q657">
         <v>0.85</v>
@@ -75144,7 +75144,7 @@
         <v>2528</v>
       </c>
       <c r="P658" t="s">
-        <v>2093</v>
+        <v>2063</v>
       </c>
       <c r="Q658">
         <v>0.85</v>
@@ -75158,7 +75158,7 @@
         <v>2529</v>
       </c>
       <c r="P659" t="s">
-        <v>2051</v>
+        <v>2059</v>
       </c>
       <c r="Q659">
         <v>0.85</v>
@@ -75172,7 +75172,7 @@
         <v>2530</v>
       </c>
       <c r="P660" t="s">
-        <v>2075</v>
+        <v>2108</v>
       </c>
       <c r="Q660">
         <v>0.85</v>
@@ -75186,7 +75186,7 @@
         <v>2531</v>
       </c>
       <c r="P661" t="s">
-        <v>2063</v>
+        <v>2086</v>
       </c>
       <c r="Q661">
         <v>0.85</v>
@@ -75200,7 +75200,7 @@
         <v>2532</v>
       </c>
       <c r="P662" t="s">
-        <v>2084</v>
+        <v>2051</v>
       </c>
       <c r="Q662">
         <v>0.85</v>
@@ -75214,7 +75214,7 @@
         <v>2533</v>
       </c>
       <c r="P663" t="s">
-        <v>2088</v>
+        <v>2051</v>
       </c>
       <c r="Q663">
         <v>0.85</v>
@@ -75228,7 +75228,7 @@
         <v>2534</v>
       </c>
       <c r="P664" t="s">
-        <v>2083</v>
+        <v>2060</v>
       </c>
       <c r="Q664">
         <v>0.85</v>
@@ -75242,7 +75242,7 @@
         <v>2535</v>
       </c>
       <c r="P665" t="s">
-        <v>2071</v>
+        <v>2077</v>
       </c>
       <c r="Q665">
         <v>0.85</v>
@@ -75256,7 +75256,7 @@
         <v>2536</v>
       </c>
       <c r="P666" t="s">
-        <v>2104</v>
+        <v>2069</v>
       </c>
       <c r="Q666">
         <v>0.85</v>
@@ -75270,7 +75270,7 @@
         <v>2537</v>
       </c>
       <c r="P667" t="s">
-        <v>2060</v>
+        <v>2097</v>
       </c>
       <c r="Q667">
         <v>0.85</v>
@@ -75284,7 +75284,7 @@
         <v>2538</v>
       </c>
       <c r="P668" t="s">
-        <v>2105</v>
+        <v>2101</v>
       </c>
       <c r="Q668">
         <v>0.85</v>
@@ -75298,7 +75298,7 @@
         <v>2539</v>
       </c>
       <c r="P669" t="s">
-        <v>2071</v>
+        <v>2103</v>
       </c>
       <c r="Q669">
         <v>0.85</v>
@@ -75312,7 +75312,7 @@
         <v>2540</v>
       </c>
       <c r="P670" t="s">
-        <v>2090</v>
+        <v>2063</v>
       </c>
       <c r="Q670">
         <v>0.85</v>
@@ -75326,7 +75326,7 @@
         <v>2541</v>
       </c>
       <c r="P671" t="s">
-        <v>2106</v>
+        <v>2075</v>
       </c>
       <c r="Q671">
         <v>0.85</v>
@@ -75340,7 +75340,7 @@
         <v>2542</v>
       </c>
       <c r="P672" t="s">
-        <v>2076</v>
+        <v>2082</v>
       </c>
       <c r="Q672">
         <v>0.85</v>
@@ -75354,7 +75354,7 @@
         <v>2543</v>
       </c>
       <c r="P673" t="s">
-        <v>2057</v>
+        <v>2101</v>
       </c>
       <c r="Q673">
         <v>0.85</v>
@@ -75368,7 +75368,7 @@
         <v>2544</v>
       </c>
       <c r="P674" t="s">
-        <v>2101</v>
+        <v>2077</v>
       </c>
       <c r="Q674">
         <v>0.85</v>
@@ -75382,7 +75382,7 @@
         <v>2545</v>
       </c>
       <c r="P675" t="s">
-        <v>2051</v>
+        <v>2104</v>
       </c>
       <c r="Q675">
         <v>0.85</v>
@@ -75396,7 +75396,7 @@
         <v>2546</v>
       </c>
       <c r="P676" t="s">
-        <v>2103</v>
+        <v>2075</v>
       </c>
       <c r="Q676">
         <v>0.85</v>
@@ -75410,7 +75410,7 @@
         <v>2547</v>
       </c>
       <c r="P677" t="s">
-        <v>2086</v>
+        <v>2095</v>
       </c>
       <c r="Q677">
         <v>0.85</v>
@@ -75424,7 +75424,7 @@
         <v>2548</v>
       </c>
       <c r="P678" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="Q678">
         <v>0.85</v>
@@ -75438,7 +75438,7 @@
         <v>2549</v>
       </c>
       <c r="P679" t="s">
-        <v>2065</v>
+        <v>2094</v>
       </c>
       <c r="Q679">
         <v>0.85</v>
@@ -75452,7 +75452,7 @@
         <v>2550</v>
       </c>
       <c r="P680" t="s">
-        <v>2065</v>
+        <v>2086</v>
       </c>
       <c r="Q680">
         <v>0.85</v>
@@ -75466,7 +75466,7 @@
         <v>2551</v>
       </c>
       <c r="P681" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="Q681">
         <v>0.85</v>
@@ -75480,7 +75480,7 @@
         <v>2552</v>
       </c>
       <c r="P682" t="s">
-        <v>2069</v>
+        <v>2087</v>
       </c>
       <c r="Q682">
         <v>0.85</v>
@@ -75494,7 +75494,7 @@
         <v>2553</v>
       </c>
       <c r="P683" t="s">
-        <v>2068</v>
+        <v>2086</v>
       </c>
       <c r="Q683">
         <v>0.85</v>
@@ -75508,7 +75508,7 @@
         <v>2554</v>
       </c>
       <c r="P684" t="s">
-        <v>2054</v>
+        <v>2101</v>
       </c>
       <c r="Q684">
         <v>0.85</v>
@@ -75522,10 +75522,10 @@
         <v>2555</v>
       </c>
       <c r="P685" t="s">
-        <v>2084</v>
+        <v>2102</v>
       </c>
       <c r="Q685">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="686" spans="14:17" x14ac:dyDescent="0.45">
@@ -75536,10 +75536,10 @@
         <v>2556</v>
       </c>
       <c r="P686" t="s">
-        <v>2058</v>
+        <v>2082</v>
       </c>
       <c r="Q686">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="687" spans="14:17" x14ac:dyDescent="0.45">
@@ -75550,10 +75550,10 @@
         <v>2557</v>
       </c>
       <c r="P687" t="s">
-        <v>2078</v>
+        <v>2065</v>
       </c>
       <c r="Q687">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="688" spans="14:17" x14ac:dyDescent="0.45">
@@ -75564,10 +75564,10 @@
         <v>2558</v>
       </c>
       <c r="P688" t="s">
-        <v>2071</v>
+        <v>2093</v>
       </c>
       <c r="Q688">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="689" spans="14:17" x14ac:dyDescent="0.45">
@@ -75578,10 +75578,10 @@
         <v>2559</v>
       </c>
       <c r="P689" t="s">
-        <v>2065</v>
+        <v>2053</v>
       </c>
       <c r="Q689">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="690" spans="14:17" x14ac:dyDescent="0.45">
@@ -75592,10 +75592,10 @@
         <v>2560</v>
       </c>
       <c r="P690" t="s">
-        <v>2060</v>
+        <v>2089</v>
       </c>
       <c r="Q690">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="691" spans="14:17" x14ac:dyDescent="0.45">
@@ -75606,7 +75606,7 @@
         <v>2561</v>
       </c>
       <c r="P691" t="s">
-        <v>2055</v>
+        <v>2067</v>
       </c>
       <c r="Q691">
         <v>0.85</v>
@@ -75620,7 +75620,7 @@
         <v>2562</v>
       </c>
       <c r="P692" t="s">
-        <v>2102</v>
+        <v>2070</v>
       </c>
       <c r="Q692">
         <v>0.85</v>
@@ -75634,7 +75634,7 @@
         <v>2563</v>
       </c>
       <c r="P693" t="s">
-        <v>2051</v>
+        <v>2070</v>
       </c>
       <c r="Q693">
         <v>0.85</v>
@@ -75648,7 +75648,7 @@
         <v>2564</v>
       </c>
       <c r="P694" t="s">
-        <v>2087</v>
+        <v>2067</v>
       </c>
       <c r="Q694">
         <v>0.85</v>
@@ -75662,7 +75662,7 @@
         <v>2565</v>
       </c>
       <c r="P695" t="s">
-        <v>2106</v>
+        <v>2067</v>
       </c>
       <c r="Q695">
         <v>0.85</v>
@@ -75676,7 +75676,7 @@
         <v>2566</v>
       </c>
       <c r="P696" t="s">
-        <v>2051</v>
+        <v>2082</v>
       </c>
       <c r="Q696">
         <v>0.85</v>
@@ -75690,7 +75690,7 @@
         <v>2567</v>
       </c>
       <c r="P697" t="s">
-        <v>2094</v>
+        <v>2055</v>
       </c>
       <c r="Q697">
         <v>0.85</v>
@@ -75704,7 +75704,7 @@
         <v>2568</v>
       </c>
       <c r="P698" t="s">
-        <v>2104</v>
+        <v>2087</v>
       </c>
       <c r="Q698">
         <v>0.85</v>
@@ -75718,10 +75718,10 @@
         <v>2569</v>
       </c>
       <c r="P699" t="s">
-        <v>2094</v>
+        <v>2103</v>
       </c>
       <c r="Q699">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="700" spans="14:17" x14ac:dyDescent="0.45">
@@ -75732,7 +75732,7 @@
         <v>2570</v>
       </c>
       <c r="P700" t="s">
-        <v>2081</v>
+        <v>2086</v>
       </c>
       <c r="Q700">
         <v>0.85</v>
@@ -75746,7 +75746,7 @@
         <v>2571</v>
       </c>
       <c r="P701" t="s">
-        <v>2051</v>
+        <v>2097</v>
       </c>
       <c r="Q701">
         <v>0.85</v>
@@ -75760,7 +75760,7 @@
         <v>2572</v>
       </c>
       <c r="P702" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="Q702">
         <v>0.85</v>
@@ -75774,7 +75774,7 @@
         <v>2573</v>
       </c>
       <c r="P703" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="Q703">
         <v>0.85</v>
@@ -75802,7 +75802,7 @@
         <v>2575</v>
       </c>
       <c r="P705" t="s">
-        <v>2083</v>
+        <v>2078</v>
       </c>
       <c r="Q705">
         <v>0.85</v>
@@ -75816,7 +75816,7 @@
         <v>2576</v>
       </c>
       <c r="P706" t="s">
-        <v>2067</v>
+        <v>2089</v>
       </c>
       <c r="Q706">
         <v>0.85</v>
@@ -75830,7 +75830,7 @@
         <v>2577</v>
       </c>
       <c r="P707" t="s">
-        <v>2093</v>
+        <v>2058</v>
       </c>
       <c r="Q707">
         <v>0.85</v>
@@ -75844,7 +75844,7 @@
         <v>2578</v>
       </c>
       <c r="P708" t="s">
-        <v>2082</v>
+        <v>2108</v>
       </c>
       <c r="Q708">
         <v>0.85</v>
@@ -75858,7 +75858,7 @@
         <v>2579</v>
       </c>
       <c r="P709" t="s">
-        <v>2068</v>
+        <v>2081</v>
       </c>
       <c r="Q709">
         <v>0.85</v>
@@ -75872,7 +75872,7 @@
         <v>2580</v>
       </c>
       <c r="P710" t="s">
-        <v>2081</v>
+        <v>2103</v>
       </c>
       <c r="Q710">
         <v>0.85</v>
@@ -75886,7 +75886,7 @@
         <v>2581</v>
       </c>
       <c r="P711" t="s">
-        <v>2089</v>
+        <v>2095</v>
       </c>
       <c r="Q711">
         <v>0.85</v>
@@ -75900,7 +75900,7 @@
         <v>2582</v>
       </c>
       <c r="P712" t="s">
-        <v>2104</v>
+        <v>2081</v>
       </c>
       <c r="Q712">
         <v>0.85</v>
@@ -75914,7 +75914,7 @@
         <v>2583</v>
       </c>
       <c r="P713" t="s">
-        <v>2097</v>
+        <v>2058</v>
       </c>
       <c r="Q713">
         <v>0.85</v>
@@ -75928,7 +75928,7 @@
         <v>2584</v>
       </c>
       <c r="P714" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="Q714">
         <v>0.85</v>
@@ -75942,7 +75942,7 @@
         <v>2585</v>
       </c>
       <c r="P715" t="s">
-        <v>2095</v>
+        <v>2098</v>
       </c>
       <c r="Q715">
         <v>0.85</v>
@@ -75956,7 +75956,7 @@
         <v>2586</v>
       </c>
       <c r="P716" t="s">
-        <v>2089</v>
+        <v>2051</v>
       </c>
       <c r="Q716">
         <v>0.85</v>
@@ -75970,7 +75970,7 @@
         <v>2587</v>
       </c>
       <c r="P717" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="Q717">
         <v>0.85</v>
@@ -75984,7 +75984,7 @@
         <v>2588</v>
       </c>
       <c r="P718" t="s">
-        <v>2076</v>
+        <v>2098</v>
       </c>
       <c r="Q718">
         <v>0.85</v>
@@ -75998,7 +75998,7 @@
         <v>2589</v>
       </c>
       <c r="P719" t="s">
-        <v>2098</v>
+        <v>2102</v>
       </c>
       <c r="Q719">
         <v>0.85</v>
@@ -76012,10 +76012,10 @@
         <v>2590</v>
       </c>
       <c r="P720" t="s">
-        <v>2088</v>
+        <v>2063</v>
       </c>
       <c r="Q720">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="721" spans="14:17" x14ac:dyDescent="0.45">
@@ -76026,10 +76026,10 @@
         <v>2591</v>
       </c>
       <c r="P721" t="s">
-        <v>2103</v>
+        <v>2077</v>
       </c>
       <c r="Q721">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="722" spans="14:17" x14ac:dyDescent="0.45">
@@ -76040,7 +76040,7 @@
         <v>2592</v>
       </c>
       <c r="P722" t="s">
-        <v>2081</v>
+        <v>2096</v>
       </c>
       <c r="Q722">
         <v>0.85</v>
@@ -76054,7 +76054,7 @@
         <v>2593</v>
       </c>
       <c r="P723" t="s">
-        <v>2056</v>
+        <v>2075</v>
       </c>
       <c r="Q723">
         <v>0.85</v>
@@ -76068,10 +76068,10 @@
         <v>2594</v>
       </c>
       <c r="P724" t="s">
-        <v>2080</v>
+        <v>2063</v>
       </c>
       <c r="Q724">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="725" spans="14:17" x14ac:dyDescent="0.45">
@@ -76082,7 +76082,7 @@
         <v>2595</v>
       </c>
       <c r="P725" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="Q725">
         <v>0.95</v>
@@ -76096,7 +76096,7 @@
         <v>2596</v>
       </c>
       <c r="P726" t="s">
-        <v>2104</v>
+        <v>2082</v>
       </c>
       <c r="Q726">
         <v>0.95</v>
@@ -76110,10 +76110,10 @@
         <v>2597</v>
       </c>
       <c r="P727" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="Q727">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="728" spans="14:17" x14ac:dyDescent="0.45">
@@ -76124,7 +76124,7 @@
         <v>2598</v>
       </c>
       <c r="P728" t="s">
-        <v>2090</v>
+        <v>2095</v>
       </c>
       <c r="Q728">
         <v>0.85</v>
@@ -76138,7 +76138,7 @@
         <v>2599</v>
       </c>
       <c r="P729" t="s">
-        <v>2058</v>
+        <v>2108</v>
       </c>
       <c r="Q729">
         <v>0.85</v>
@@ -76152,7 +76152,7 @@
         <v>2600</v>
       </c>
       <c r="P730" t="s">
-        <v>2096</v>
+        <v>2076</v>
       </c>
       <c r="Q730">
         <v>0.85</v>
@@ -76166,7 +76166,7 @@
         <v>2601</v>
       </c>
       <c r="P731" t="s">
-        <v>2062</v>
+        <v>2051</v>
       </c>
       <c r="Q731">
         <v>0.85</v>
@@ -76180,7 +76180,7 @@
         <v>2602</v>
       </c>
       <c r="P732" t="s">
-        <v>2055</v>
+        <v>2051</v>
       </c>
       <c r="Q732">
         <v>0.85</v>
@@ -76194,7 +76194,7 @@
         <v>2603</v>
       </c>
       <c r="P733" t="s">
-        <v>2097</v>
+        <v>2106</v>
       </c>
       <c r="Q733">
         <v>0.85</v>
@@ -76222,7 +76222,7 @@
         <v>2605</v>
       </c>
       <c r="P735" t="s">
-        <v>2077</v>
+        <v>2094</v>
       </c>
       <c r="Q735">
         <v>0.85</v>
@@ -76236,7 +76236,7 @@
         <v>2606</v>
       </c>
       <c r="P736" t="s">
-        <v>2075</v>
+        <v>2097</v>
       </c>
       <c r="Q736">
         <v>0.85</v>
@@ -76250,7 +76250,7 @@
         <v>2607</v>
       </c>
       <c r="P737" t="s">
-        <v>2101</v>
+        <v>2076</v>
       </c>
       <c r="Q737">
         <v>0.85</v>
@@ -76264,7 +76264,7 @@
         <v>2608</v>
       </c>
       <c r="P738" t="s">
-        <v>2077</v>
+        <v>2060</v>
       </c>
       <c r="Q738">
         <v>0.85</v>
@@ -76278,7 +76278,7 @@
         <v>2609</v>
       </c>
       <c r="P739" t="s">
-        <v>2104</v>
+        <v>2083</v>
       </c>
       <c r="Q739">
         <v>0.85</v>
@@ -76292,7 +76292,7 @@
         <v>2610</v>
       </c>
       <c r="P740" t="s">
-        <v>2089</v>
+        <v>2083</v>
       </c>
       <c r="Q740">
         <v>0.85</v>
@@ -76306,7 +76306,7 @@
         <v>2611</v>
       </c>
       <c r="P741" t="s">
-        <v>2108</v>
+        <v>2104</v>
       </c>
       <c r="Q741">
         <v>0.85</v>
@@ -76320,7 +76320,7 @@
         <v>2612</v>
       </c>
       <c r="P742" t="s">
-        <v>2076</v>
+        <v>2109</v>
       </c>
       <c r="Q742">
         <v>0.85</v>
@@ -76334,7 +76334,7 @@
         <v>2613</v>
       </c>
       <c r="P743" t="s">
-        <v>2084</v>
+        <v>2078</v>
       </c>
       <c r="Q743">
         <v>0.85</v>
@@ -76348,7 +76348,7 @@
         <v>2614</v>
       </c>
       <c r="P744" t="s">
-        <v>2052</v>
+        <v>2084</v>
       </c>
       <c r="Q744">
         <v>0.85</v>
@@ -76362,7 +76362,7 @@
         <v>2615</v>
       </c>
       <c r="P745" t="s">
-        <v>2093</v>
+        <v>2060</v>
       </c>
       <c r="Q745">
         <v>0.85</v>
@@ -76376,7 +76376,7 @@
         <v>2616</v>
       </c>
       <c r="P746" t="s">
-        <v>2074</v>
+        <v>2062</v>
       </c>
       <c r="Q746">
         <v>0.85</v>
@@ -76390,7 +76390,7 @@
         <v>2617</v>
       </c>
       <c r="P747" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="Q747">
         <v>0.85</v>
@@ -76404,7 +76404,7 @@
         <v>2618</v>
       </c>
       <c r="P748" t="s">
-        <v>2089</v>
+        <v>2055</v>
       </c>
       <c r="Q748">
         <v>0.85</v>
@@ -76418,7 +76418,7 @@
         <v>2619</v>
       </c>
       <c r="P749" t="s">
-        <v>2058</v>
+        <v>2089</v>
       </c>
       <c r="Q749">
         <v>0.85</v>
@@ -76432,7 +76432,7 @@
         <v>2620</v>
       </c>
       <c r="P750" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="Q750">
         <v>0.85</v>
@@ -76446,7 +76446,7 @@
         <v>2621</v>
       </c>
       <c r="P751" t="s">
-        <v>2098</v>
+        <v>2073</v>
       </c>
       <c r="Q751">
         <v>0.85</v>
@@ -76460,7 +76460,7 @@
         <v>2622</v>
       </c>
       <c r="P752" t="s">
-        <v>2055</v>
+        <v>2094</v>
       </c>
       <c r="Q752">
         <v>0.85</v>
@@ -76474,7 +76474,7 @@
         <v>2623</v>
       </c>
       <c r="P753" t="s">
-        <v>2088</v>
+        <v>2069</v>
       </c>
       <c r="Q753">
         <v>0.85</v>
@@ -76488,7 +76488,7 @@
         <v>2624</v>
       </c>
       <c r="P754" t="s">
-        <v>2106</v>
+        <v>2051</v>
       </c>
       <c r="Q754">
         <v>0.85</v>
@@ -76502,7 +76502,7 @@
         <v>2625</v>
       </c>
       <c r="P755" t="s">
-        <v>2055</v>
+        <v>2063</v>
       </c>
       <c r="Q755">
         <v>0.85</v>
@@ -76516,7 +76516,7 @@
         <v>2626</v>
       </c>
       <c r="P756" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="Q756">
         <v>0.85</v>
@@ -76530,7 +76530,7 @@
         <v>2627</v>
       </c>
       <c r="P757" t="s">
-        <v>2109</v>
+        <v>2062</v>
       </c>
       <c r="Q757">
         <v>0.85</v>
@@ -76544,7 +76544,7 @@
         <v>2628</v>
       </c>
       <c r="P758" t="s">
-        <v>2107</v>
+        <v>2065</v>
       </c>
       <c r="Q758">
         <v>0.85</v>
@@ -76558,7 +76558,7 @@
         <v>2629</v>
       </c>
       <c r="P759" t="s">
-        <v>2071</v>
+        <v>2086</v>
       </c>
       <c r="Q759">
         <v>0.85</v>
@@ -76572,7 +76572,7 @@
         <v>2630</v>
       </c>
       <c r="P760" t="s">
-        <v>2083</v>
+        <v>2076</v>
       </c>
       <c r="Q760">
         <v>0.85</v>
@@ -76586,7 +76586,7 @@
         <v>2631</v>
       </c>
       <c r="P761" t="s">
-        <v>2086</v>
+        <v>2076</v>
       </c>
       <c r="Q761">
         <v>0.85</v>
@@ -76600,7 +76600,7 @@
         <v>2632</v>
       </c>
       <c r="P762" t="s">
-        <v>2084</v>
+        <v>2058</v>
       </c>
       <c r="Q762">
         <v>0.85</v>
@@ -76614,7 +76614,7 @@
         <v>2633</v>
       </c>
       <c r="P763" t="s">
-        <v>2064</v>
+        <v>2081</v>
       </c>
       <c r="Q763">
         <v>0.85</v>
@@ -76628,7 +76628,7 @@
         <v>2634</v>
       </c>
       <c r="P764" t="s">
-        <v>2058</v>
+        <v>2084</v>
       </c>
       <c r="Q764">
         <v>0.85</v>
@@ -76642,7 +76642,7 @@
         <v>2635</v>
       </c>
       <c r="P765" t="s">
-        <v>2101</v>
+        <v>2081</v>
       </c>
       <c r="Q765">
         <v>0.85</v>
@@ -76656,10 +76656,10 @@
         <v>2636</v>
       </c>
       <c r="P766" t="s">
-        <v>2089</v>
+        <v>2071</v>
       </c>
       <c r="Q766">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="767" spans="14:17" x14ac:dyDescent="0.45">
@@ -76670,10 +76670,10 @@
         <v>2637</v>
       </c>
       <c r="P767" t="s">
-        <v>2071</v>
+        <v>2088</v>
       </c>
       <c r="Q767">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="768" spans="14:17" x14ac:dyDescent="0.45">
@@ -76684,10 +76684,10 @@
         <v>2638</v>
       </c>
       <c r="P768" t="s">
-        <v>2089</v>
+        <v>2109</v>
       </c>
       <c r="Q768">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="769" spans="14:17" x14ac:dyDescent="0.45">
@@ -76698,7 +76698,7 @@
         <v>2639</v>
       </c>
       <c r="P769" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="Q769">
         <v>0.95</v>
@@ -76712,10 +76712,10 @@
         <v>2640</v>
       </c>
       <c r="P770" t="s">
-        <v>2106</v>
+        <v>2096</v>
       </c>
       <c r="Q770">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="771" spans="14:17" x14ac:dyDescent="0.45">
@@ -76726,10 +76726,10 @@
         <v>2641</v>
       </c>
       <c r="P771" t="s">
-        <v>2065</v>
+        <v>2091</v>
       </c>
       <c r="Q771">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="772" spans="14:17" x14ac:dyDescent="0.45">
@@ -76740,7 +76740,7 @@
         <v>2642</v>
       </c>
       <c r="P772" t="s">
-        <v>2093</v>
+        <v>2083</v>
       </c>
       <c r="Q772">
         <v>0.85</v>
@@ -76754,7 +76754,7 @@
         <v>2643</v>
       </c>
       <c r="P773" t="s">
-        <v>2065</v>
+        <v>2060</v>
       </c>
       <c r="Q773">
         <v>0.85</v>
@@ -76768,7 +76768,7 @@
         <v>2644</v>
       </c>
       <c r="P774" t="s">
-        <v>2084</v>
+        <v>2059</v>
       </c>
       <c r="Q774">
         <v>0.85</v>
@@ -76782,7 +76782,7 @@
         <v>2645</v>
       </c>
       <c r="P775" t="s">
-        <v>2103</v>
+        <v>2060</v>
       </c>
       <c r="Q775">
         <v>0.85</v>
@@ -76796,7 +76796,7 @@
         <v>2646</v>
       </c>
       <c r="P776" t="s">
-        <v>2083</v>
+        <v>2076</v>
       </c>
       <c r="Q776">
         <v>0.85</v>
@@ -76810,7 +76810,7 @@
         <v>2647</v>
       </c>
       <c r="P777" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="Q777">
         <v>0.85</v>
@@ -76824,7 +76824,7 @@
         <v>2648</v>
       </c>
       <c r="P778" t="s">
-        <v>2102</v>
+        <v>2082</v>
       </c>
       <c r="Q778">
         <v>0.85</v>
@@ -76838,7 +76838,7 @@
         <v>2649</v>
       </c>
       <c r="P779" t="s">
-        <v>2106</v>
+        <v>2056</v>
       </c>
       <c r="Q779">
         <v>0.85</v>
@@ -76852,7 +76852,7 @@
         <v>2650</v>
       </c>
       <c r="P780" t="s">
-        <v>2106</v>
+        <v>2052</v>
       </c>
       <c r="Q780">
         <v>0.85</v>
@@ -76866,7 +76866,7 @@
         <v>2651</v>
       </c>
       <c r="P781" t="s">
-        <v>2071</v>
+        <v>2086</v>
       </c>
       <c r="Q781">
         <v>0.85</v>
@@ -76880,7 +76880,7 @@
         <v>2652</v>
       </c>
       <c r="P782" t="s">
-        <v>2092</v>
+        <v>2081</v>
       </c>
       <c r="Q782">
         <v>0.85</v>
@@ -76894,7 +76894,7 @@
         <v>2653</v>
       </c>
       <c r="P783" t="s">
-        <v>2065</v>
+        <v>2093</v>
       </c>
       <c r="Q783">
         <v>0.85</v>
@@ -76908,7 +76908,7 @@
         <v>2654</v>
       </c>
       <c r="P784" t="s">
-        <v>2077</v>
+        <v>2106</v>
       </c>
       <c r="Q784">
         <v>0.85</v>
@@ -76922,7 +76922,7 @@
         <v>2655</v>
       </c>
       <c r="P785" t="s">
-        <v>2093</v>
+        <v>2083</v>
       </c>
       <c r="Q785">
         <v>0.85</v>
@@ -76936,7 +76936,7 @@
         <v>2656</v>
       </c>
       <c r="P786" t="s">
-        <v>2063</v>
+        <v>2080</v>
       </c>
       <c r="Q786">
         <v>0.85</v>
@@ -76950,7 +76950,7 @@
         <v>2657</v>
       </c>
       <c r="P787" t="s">
-        <v>2083</v>
+        <v>2056</v>
       </c>
       <c r="Q787">
         <v>0.85</v>
@@ -76964,7 +76964,7 @@
         <v>2658</v>
       </c>
       <c r="P788" t="s">
-        <v>2094</v>
+        <v>2089</v>
       </c>
       <c r="Q788">
         <v>0.85</v>
@@ -76978,7 +76978,7 @@
         <v>2659</v>
       </c>
       <c r="P789" t="s">
-        <v>2058</v>
+        <v>2103</v>
       </c>
       <c r="Q789">
         <v>0.85</v>
@@ -76992,7 +76992,7 @@
         <v>2660</v>
       </c>
       <c r="P790" t="s">
-        <v>2067</v>
+        <v>2096</v>
       </c>
       <c r="Q790">
         <v>0.85</v>
@@ -77006,7 +77006,7 @@
         <v>2661</v>
       </c>
       <c r="P791" t="s">
-        <v>2078</v>
+        <v>2105</v>
       </c>
       <c r="Q791">
         <v>0.85</v>
@@ -77020,7 +77020,7 @@
         <v>2662</v>
       </c>
       <c r="P792" t="s">
-        <v>2106</v>
+        <v>2090</v>
       </c>
       <c r="Q792">
         <v>0.85</v>
@@ -77034,7 +77034,7 @@
         <v>2663</v>
       </c>
       <c r="P793" t="s">
-        <v>2106</v>
+        <v>2089</v>
       </c>
       <c r="Q793">
         <v>0.85</v>
@@ -77048,7 +77048,7 @@
         <v>2664</v>
       </c>
       <c r="P794" t="s">
-        <v>2101</v>
+        <v>2108</v>
       </c>
       <c r="Q794">
         <v>0.85</v>
@@ -77062,7 +77062,7 @@
         <v>2665</v>
       </c>
       <c r="P795" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="Q795">
         <v>0.85</v>
@@ -77076,7 +77076,7 @@
         <v>2666</v>
       </c>
       <c r="P796" t="s">
-        <v>2101</v>
+        <v>2064</v>
       </c>
       <c r="Q796">
         <v>0.85</v>
@@ -77090,7 +77090,7 @@
         <v>2667</v>
       </c>
       <c r="P797" t="s">
-        <v>2098</v>
+        <v>2080</v>
       </c>
       <c r="Q797">
         <v>0.85</v>
@@ -77104,7 +77104,7 @@
         <v>2668</v>
       </c>
       <c r="P798" t="s">
-        <v>2051</v>
+        <v>2079</v>
       </c>
       <c r="Q798">
         <v>0.85</v>
@@ -77118,7 +77118,7 @@
         <v>2669</v>
       </c>
       <c r="P799" t="s">
-        <v>2081</v>
+        <v>2055</v>
       </c>
       <c r="Q799">
         <v>0.85</v>
@@ -77132,7 +77132,7 @@
         <v>2670</v>
       </c>
       <c r="P800" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
       <c r="Q800">
         <v>0.85</v>
@@ -77146,7 +77146,7 @@
         <v>2671</v>
       </c>
       <c r="P801" t="s">
-        <v>2055</v>
+        <v>2106</v>
       </c>
       <c r="Q801">
         <v>0.85</v>
@@ -77160,10 +77160,10 @@
         <v>2672</v>
       </c>
       <c r="P802" t="s">
-        <v>2096</v>
+        <v>2089</v>
       </c>
       <c r="Q802">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="803" spans="14:17" x14ac:dyDescent="0.45">
@@ -77174,7 +77174,7 @@
         <v>2673</v>
       </c>
       <c r="P803" t="s">
-        <v>2096</v>
+        <v>2051</v>
       </c>
       <c r="Q803">
         <v>0.85</v>
@@ -77188,7 +77188,7 @@
         <v>2674</v>
       </c>
       <c r="P804" t="s">
-        <v>2071</v>
+        <v>2084</v>
       </c>
       <c r="Q804">
         <v>0.85</v>
@@ -77202,7 +77202,7 @@
         <v>2675</v>
       </c>
       <c r="P805" t="s">
-        <v>2077</v>
+        <v>2089</v>
       </c>
       <c r="Q805">
         <v>0.85</v>
@@ -77216,7 +77216,7 @@
         <v>2676</v>
       </c>
       <c r="P806" t="s">
-        <v>2105</v>
+        <v>2109</v>
       </c>
       <c r="Q806">
         <v>0.85</v>
@@ -77230,7 +77230,7 @@
         <v>2677</v>
       </c>
       <c r="P807" t="s">
-        <v>2051</v>
+        <v>2056</v>
       </c>
       <c r="Q807">
         <v>0.85</v>
@@ -77244,7 +77244,7 @@
         <v>2678</v>
       </c>
       <c r="P808" t="s">
-        <v>2058</v>
+        <v>2093</v>
       </c>
       <c r="Q808">
         <v>0.85</v>
@@ -77258,7 +77258,7 @@
         <v>2679</v>
       </c>
       <c r="P809" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
       <c r="Q809">
         <v>0.85</v>
@@ -77272,7 +77272,7 @@
         <v>2680</v>
       </c>
       <c r="P810" t="s">
-        <v>2077</v>
+        <v>2055</v>
       </c>
       <c r="Q810">
         <v>0.85</v>
@@ -77286,7 +77286,7 @@
         <v>2681</v>
       </c>
       <c r="P811" t="s">
-        <v>2109</v>
+        <v>2052</v>
       </c>
       <c r="Q811">
         <v>0.85</v>
@@ -77314,7 +77314,7 @@
         <v>2683</v>
       </c>
       <c r="P813" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
       <c r="Q813">
         <v>0.85</v>
@@ -77328,10 +77328,10 @@
         <v>2684</v>
       </c>
       <c r="P814" t="s">
-        <v>2077</v>
+        <v>2062</v>
       </c>
       <c r="Q814">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="815" spans="14:17" x14ac:dyDescent="0.45">
@@ -77342,7 +77342,7 @@
         <v>2685</v>
       </c>
       <c r="P815" t="s">
-        <v>2075</v>
+        <v>2086</v>
       </c>
       <c r="Q815">
         <v>0.85</v>
@@ -77356,7 +77356,7 @@
         <v>2686</v>
       </c>
       <c r="P816" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="Q816">
         <v>0.85</v>
@@ -77370,7 +77370,7 @@
         <v>2687</v>
       </c>
       <c r="P817" t="s">
-        <v>2108</v>
+        <v>2088</v>
       </c>
       <c r="Q817">
         <v>0.85</v>
@@ -77384,7 +77384,7 @@
         <v>2688</v>
       </c>
       <c r="P818" t="s">
-        <v>2083</v>
+        <v>2057</v>
       </c>
       <c r="Q818">
         <v>0.85</v>
@@ -77398,7 +77398,7 @@
         <v>2689</v>
       </c>
       <c r="P819" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="Q819">
         <v>0.85</v>
@@ -77412,7 +77412,7 @@
         <v>2690</v>
       </c>
       <c r="P820" t="s">
-        <v>2087</v>
+        <v>2083</v>
       </c>
       <c r="Q820">
         <v>0.85</v>
@@ -77426,7 +77426,7 @@
         <v>2691</v>
       </c>
       <c r="P821" t="s">
-        <v>2107</v>
+        <v>2089</v>
       </c>
       <c r="Q821">
         <v>0.85</v>
@@ -77440,7 +77440,7 @@
         <v>2692</v>
       </c>
       <c r="P822" t="s">
-        <v>2055</v>
+        <v>2103</v>
       </c>
       <c r="Q822">
         <v>0.85</v>
@@ -77454,7 +77454,7 @@
         <v>2693</v>
       </c>
       <c r="P823" t="s">
-        <v>2087</v>
+        <v>2053</v>
       </c>
       <c r="Q823">
         <v>0.85</v>
@@ -77468,7 +77468,7 @@
         <v>2694</v>
       </c>
       <c r="P824" t="s">
-        <v>2104</v>
+        <v>2060</v>
       </c>
       <c r="Q824">
         <v>0.85</v>
@@ -77482,7 +77482,7 @@
         <v>2695</v>
       </c>
       <c r="P825" t="s">
-        <v>2076</v>
+        <v>2060</v>
       </c>
       <c r="Q825">
         <v>0.85</v>
@@ -77496,7 +77496,7 @@
         <v>2696</v>
       </c>
       <c r="P826" t="s">
-        <v>2086</v>
+        <v>2103</v>
       </c>
       <c r="Q826">
         <v>0.85</v>
@@ -77510,7 +77510,7 @@
         <v>2697</v>
       </c>
       <c r="P827" t="s">
-        <v>2106</v>
+        <v>2077</v>
       </c>
       <c r="Q827">
         <v>0.85</v>
@@ -77524,7 +77524,7 @@
         <v>2698</v>
       </c>
       <c r="P828" t="s">
-        <v>2051</v>
+        <v>2089</v>
       </c>
       <c r="Q828">
         <v>0.85</v>
@@ -77538,7 +77538,7 @@
         <v>2699</v>
       </c>
       <c r="P829" t="s">
-        <v>2051</v>
+        <v>2098</v>
       </c>
       <c r="Q829">
         <v>0.85</v>
@@ -77552,7 +77552,7 @@
         <v>2700</v>
       </c>
       <c r="P830" t="s">
-        <v>2108</v>
+        <v>2071</v>
       </c>
       <c r="Q830">
         <v>0.85</v>
@@ -77566,7 +77566,7 @@
         <v>2701</v>
       </c>
       <c r="P831" t="s">
-        <v>2086</v>
+        <v>2058</v>
       </c>
       <c r="Q831">
         <v>0.85</v>
@@ -77580,7 +77580,7 @@
         <v>2702</v>
       </c>
       <c r="P832" t="s">
-        <v>2058</v>
+        <v>2092</v>
       </c>
       <c r="Q832">
         <v>0.85</v>
@@ -77594,7 +77594,7 @@
         <v>2703</v>
       </c>
       <c r="P833" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="Q833">
         <v>0.85</v>
@@ -77608,7 +77608,7 @@
         <v>2704</v>
       </c>
       <c r="P834" t="s">
-        <v>2076</v>
+        <v>2086</v>
       </c>
       <c r="Q834">
         <v>0.85</v>
@@ -77622,7 +77622,7 @@
         <v>2705</v>
       </c>
       <c r="P835" t="s">
-        <v>2093</v>
+        <v>2075</v>
       </c>
       <c r="Q835">
         <v>0.85</v>
@@ -77636,7 +77636,7 @@
         <v>2706</v>
       </c>
       <c r="P836" t="s">
-        <v>2086</v>
+        <v>2065</v>
       </c>
       <c r="Q836">
         <v>0.85</v>
@@ -77650,7 +77650,7 @@
         <v>2707</v>
       </c>
       <c r="P837" t="s">
-        <v>2077</v>
+        <v>2106</v>
       </c>
       <c r="Q837">
         <v>0.85</v>
@@ -77664,7 +77664,7 @@
         <v>2708</v>
       </c>
       <c r="P838" t="s">
-        <v>2090</v>
+        <v>2103</v>
       </c>
       <c r="Q838">
         <v>0.85</v>
@@ -77678,7 +77678,7 @@
         <v>2709</v>
       </c>
       <c r="P839" t="s">
-        <v>2102</v>
+        <v>2051</v>
       </c>
       <c r="Q839">
         <v>0.85</v>
@@ -77692,7 +77692,7 @@
         <v>2710</v>
       </c>
       <c r="P840" t="s">
-        <v>2094</v>
+        <v>2103</v>
       </c>
       <c r="Q840">
         <v>0.85</v>
@@ -77706,7 +77706,7 @@
         <v>2711</v>
       </c>
       <c r="P841" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="Q841">
         <v>0.85</v>
@@ -77734,7 +77734,7 @@
         <v>2713</v>
       </c>
       <c r="P843" t="s">
-        <v>2103</v>
+        <v>2061</v>
       </c>
       <c r="Q843">
         <v>0.85</v>
@@ -77748,7 +77748,7 @@
         <v>2714</v>
       </c>
       <c r="P844" t="s">
-        <v>2094</v>
+        <v>2065</v>
       </c>
       <c r="Q844">
         <v>0.85</v>
@@ -77762,7 +77762,7 @@
         <v>2715</v>
       </c>
       <c r="P845" t="s">
-        <v>2102</v>
+        <v>2067</v>
       </c>
       <c r="Q845">
         <v>0.85</v>
@@ -77776,7 +77776,7 @@
         <v>2716</v>
       </c>
       <c r="P846" t="s">
-        <v>2076</v>
+        <v>2103</v>
       </c>
       <c r="Q846">
         <v>0.85</v>
@@ -77790,7 +77790,7 @@
         <v>2717</v>
       </c>
       <c r="P847" t="s">
-        <v>2089</v>
+        <v>2083</v>
       </c>
       <c r="Q847">
         <v>0.85</v>
@@ -77804,7 +77804,7 @@
         <v>2718</v>
       </c>
       <c r="P848" t="s">
-        <v>2100</v>
+        <v>2052</v>
       </c>
       <c r="Q848">
         <v>0.85</v>
@@ -77818,7 +77818,7 @@
         <v>2719</v>
       </c>
       <c r="P849" t="s">
-        <v>2060</v>
+        <v>2069</v>
       </c>
       <c r="Q849">
         <v>0.85</v>
@@ -77832,7 +77832,7 @@
         <v>2720</v>
       </c>
       <c r="P850" t="s">
-        <v>2095</v>
+        <v>2089</v>
       </c>
       <c r="Q850">
         <v>0.85</v>
@@ -77860,7 +77860,7 @@
         <v>2722</v>
       </c>
       <c r="P852" t="s">
-        <v>2103</v>
+        <v>2055</v>
       </c>
       <c r="Q852">
         <v>0.85</v>
@@ -77874,7 +77874,7 @@
         <v>2723</v>
       </c>
       <c r="P853" t="s">
-        <v>2051</v>
+        <v>2087</v>
       </c>
       <c r="Q853">
         <v>0.85</v>
@@ -77888,10 +77888,10 @@
         <v>2724</v>
       </c>
       <c r="P854" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="Q854">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="855" spans="14:17" x14ac:dyDescent="0.45">
@@ -77902,10 +77902,10 @@
         <v>2725</v>
       </c>
       <c r="P855" t="s">
-        <v>2097</v>
+        <v>2058</v>
       </c>
       <c r="Q855">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -77914,7 +77914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8DFCE33-5410-4EFE-A034-211587D5F4D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAA8DE9-CF18-433E-95A3-47C8BAE197CF}">
   <dimension ref="A1:I287"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E83CB0-83AB-4713-8D35-57F590C085C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F494576D-CE23-4183-A2F8-80A87FEEA8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6409,6 +6409,1224 @@
     <t>co2_Anqing_CHN</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_Yangzhou_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yangjiang_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103882_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Rizhao_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102816-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101729_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114802_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104368-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115845_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104367-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Changzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115448_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102033-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110262-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115370-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102817-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yiyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000190-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110694_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Tongshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104429-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111818_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109217_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115452_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115345-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115880_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CCS_Hangzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Harbin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107982_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Mianyang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104428-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Chongqing_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Wuan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yiyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Mianyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114533_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102929_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115313_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104417_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Zouping_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000279_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114301_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Chongqing_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111201_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111006_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000100893_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106310_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CHN44p2N116p5E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Linyi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yingchuan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115843-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CHN44p4N121p8E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114302_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115878_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CHN44p7N89p1E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102157_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shanghai_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103881_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Changzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yangjiang_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Zouping_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115524_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111995_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shahezhai_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115477_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115474_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Sanhe_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Anshun_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Putian_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Anqing_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Xiaoyi_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000102229_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115451_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Fangchenggang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115842-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111994_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109118_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105137_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Nantong_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yingchuan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103394_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102941_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Tongling_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104065_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Zouping_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000108348_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Xichang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110695_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tongling_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shijiazhuang_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111569_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103783-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103293_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Beichengqu_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115815_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115816_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115641_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111649_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111817_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105307_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Jingling_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Xiaoyi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Liuzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000101735_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Shaoguan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000109029_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104418_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102810_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Tongling_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111298_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Sanhe_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111664_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111454_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115531_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114803_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103392_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Shijiazhuang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Liaoyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Wulan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Anqing_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115715_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102811_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114703_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101336_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_ZhongdongShequ_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Shanghai_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CHN44p4N121p8E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Changzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Hejin_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115716_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Wuhan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shijiazhuang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114202_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101367_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yakeshi_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Mianyang_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yangzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Fangchenggang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109117_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000108347_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000101734_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Hohhot_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Zouping_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115731_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115348_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000100711_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105160_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115297_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CHN44p4N121p8E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110133_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115334_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103153_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Shaoguan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102102_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000104144_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yanggezhuang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000107469_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103450-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104366-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115476_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000103363_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103362_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Xiaoyi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tangshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000100234_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109206_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103784-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105064_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Jingling_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yuanquan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104063-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CHN44p7N89p1E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Jingling_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Shanghai_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Liuzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Nanjing_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101919_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115489_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000237_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Xiaoyi_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104485-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000113342_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110115-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110112-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103459_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Ningde_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yanggezhuang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115850_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106460_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yuanquan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yicheng_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CCS_Hangzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yangzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Liaoyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Xiaoxita_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115438_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103004_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Wuhan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000104640_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yangzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115493_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104520_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111602-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000280_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104622-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101335_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Anshun_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yicheng_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Luohe_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115640_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yangzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104682_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115841_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tianjin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109028_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105306_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115826-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109010-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Mianyang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104104_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114199-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115840_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Fangchenggang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104717_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106501_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104684_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Shijiazhuang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Tianjin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_CCS_G100001000354-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114834_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Qabqa_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104503_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101768_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103868_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Nantong_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Changzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114835_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115450_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Hejin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Linyi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103294_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102871_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yiyang_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Tongshan_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115844_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115490_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111755-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111465-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000100235_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CHN44p2N116p5E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000109862_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115520_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Ningde_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Rizhao_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111568_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109205_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CHN44p7N89p1E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Wuan_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114364_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101790_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yuanquan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103151_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106227_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107476-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110113-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115454_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115459_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Wuhan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000347_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111005_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103471_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CCS_Hangzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yangzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Fangchenggang_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115296_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115400_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Rizhao_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106644_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000109191_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115496_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115495_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114365_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114201_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110134_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Luohe_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106355_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001004192_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000108893_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shaoguan_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Tangshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115390_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103611_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106643_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000113225_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Beichengqu_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103152_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shaoguan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111453_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111650_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105104_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104073-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000112940_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115813_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Wuan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115383-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114746_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shanghai_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104716_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115532_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Putian_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104365-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000100894_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103463_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103867_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Sizhan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Jinbi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115851_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115373_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CHN44p2N116p5E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CHN45p9N129p3E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115458_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000104235_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103612_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yangjiang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Anshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Xiaoyi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104623_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111479_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103150_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Nanjing_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000107468_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104066_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yakeshi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Tongshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000112939_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115523_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115732_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115346-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Putian_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Nanjing_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115382-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111299_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104074-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101756_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103003_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109860_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Nantong_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Rizhao_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yingchuan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103385_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Kuqa_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115656_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115812_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102041_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115475_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000113343_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Hohhot_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Hangzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Chongqing_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103384_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Liuzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Chongqing_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103393_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104105_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111756-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115560_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115639_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101728_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Harbin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Xiaoxita_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115312_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000104143_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Sanhe_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105065_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Anshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CHN45p9N129p3E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tongling_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yuanquan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105159_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CHN44p7N89p1E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Fuzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Tongshan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Changzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Fuzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115814_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Shahezhai_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Qabqa_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115932_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114200-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115817_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104624_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115559_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Changzhou_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yangjiang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Sizhan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103166_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102930_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105097_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000102228_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115931_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115653_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000108892_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Liuzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Anshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Shaoguan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Chongqing_CHN_400_rf</t>
+  </si>
+  <si>
     <t>ep_coal_usc_G100000111200_rf</t>
   </si>
   <si>
@@ -6418,1843 +7636,625 @@
     <t>ep_c_coal_usc_G100000115335_rf</t>
   </si>
   <si>
+    <t>ep_coal_usc_G100000109207_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104076-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tongshan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Rizhao_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yanggezhuang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115655_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115811_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Hejin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Qabqa_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111603-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Manlin_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114532_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Tongshan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Wulan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000111313_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Shaoguan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111143_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114710_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103478_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000191-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115879_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105138-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Beichengqu_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Fangchenggang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Hangzhou_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Tianjin_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Hangzhou_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Liaoyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114040_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103414_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Luohe_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CHN44p7N89p1E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115642_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Nantong_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102812_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111142_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115654_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101789_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000109030_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110263_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yingchuan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109190_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104621-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Fangchenggang_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Luohe_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Beichengqu_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111478_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115347_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109218_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Hohhot_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Wuan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Xiaoxita_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104064-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104075-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115839_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107983_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000103395_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Anshun_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CHN44p4N121p8E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105096_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shanghai_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109656-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109655-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Luohe_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115952_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_ZhongdongShequ_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_ZhongdongShequ_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102943_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115494_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Nantong_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109189_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115517_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115838_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104504_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111466-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115391_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103479_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yangjiang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Changzhou_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_CCS_G100001000353-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104519_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Fuzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114709_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Shanghai_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106309_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115810_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shahezhai_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001004194_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yakeshi_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000108245_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shanghai_CHN_400_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115401_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000111663_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114702_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Wulan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Zouping_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Jingling_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yiyang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Fuzhou_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Anshun_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CHN45p9N129p3E_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102942_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yicheng_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115825-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114266_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115447_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Sizhan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Luohe_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Shaoguan_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CHN44p7N89p1E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_CCS_G100001000352-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Hohhot_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104486-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115449_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Sizhan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yuanquan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Shaoguan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000108246_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101467_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106354_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_CHN44p2N116p5E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Nanjing_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Tongling_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Putian_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Manlin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Jingling_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Sanhe_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114267_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Kuqa_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110114-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_CCS_G100001000355-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Hejin_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100001000236_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103449-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109027_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115453_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Putian_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tongshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Sizhan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Tangshan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115953_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102944_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000109192_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115372_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Hohhot_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103458_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Ningde_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Tianjin_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104683_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000115437_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109861_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115521_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Nanjing_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_Yingchuan_CHN_400-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Nanjing_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Qabqa_CHN_300_rf</t>
+  </si>
+  <si>
     <t>ep_coal_sc_Yiyang_CHN_300_rf</t>
   </si>
   <si>
-    <t>ep_coal_usc_G100000103166_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102930_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000105097_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000108892_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Liuzhou_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Anshan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Shaoguan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103478_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000114710_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111143_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109207_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104076-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Tongshan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Yanggezhuang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115655_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115811_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Hejin_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Qabqa_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115653_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000111313_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000102228_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115931_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Manlin_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111603-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000114532_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Tongshan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Wulan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Changzhou_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Chongqing_CHN_400_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100001000191-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115879_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000105138-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Fangchenggang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103384_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Liuzhou_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111756-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115560_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103385_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Kuqa_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Rizhao_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103393_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104105_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115814_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Qabqa_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Hejin_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Fuzhou_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115639_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101728_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Hohhot_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000104143_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115312_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Sanhe_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Yingchuan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Sizhan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Chongqing_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000105065_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Anshan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Tongling_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_CHN45p9N129p3E_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Shaoguan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Yuanquan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Tongshan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Fuzhou_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Changzhou_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115656_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000113343_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102041_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115475_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115812_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Hangzhou_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Chongqing_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000105159_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Rizhao_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115932_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104624_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115817_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115559_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000114200-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Nantong_CHN_400_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Chongqing_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102157_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115524_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111995_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Shahezhai_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111006_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000100893_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106310_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CHN44p2N116p5E_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Linyi_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115843-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CHN44p4N121p8E_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103881_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Changzhou_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000108348_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Xichang_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104065_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Zouping_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115477_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115474_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Sanhe_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Anshun_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Putian_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Xiaoyi_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Anqing_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115451_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000102229_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Fangchenggang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111201_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Anshan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103394_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102941_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Tongling_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115878_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000114302_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Hohhot_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115842-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111994_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109118_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000105137_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Nantong_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110695_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Tongling_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yangjiang_CHN_400_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Zouping_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103153_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Shaoguan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109117_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000108347_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000101734_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_CHN44p2N116p5E_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Zouping_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115731_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000105160_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115348_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000100711_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110133_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115334_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104063-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CHN44p7N89p1E_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103784-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000105064_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Jingling_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Yuanquan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000104144_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102102_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CCS_G100000107469_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104366-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103450-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Yangjiang_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Yangzhou_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Fangchenggang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CHN44p4N121p8E_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115476_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000103363_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103362_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109206_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000100234_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115297_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Tangshan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Mianyang_CHN_400_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Shanghai_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Liuzhou_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CCS_G100000109029_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000101735_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Shaoguan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104418_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111664_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115815_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115816_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115641_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111298_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115716_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Wuhan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Changzhou_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Hejin_CHN_300_rf</t>
+    <t>ep_coal_usc_CHN44p2N116p5E_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yangjiang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Hohhot_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101468_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102872_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Ningde_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000114039_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Yangjiang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Sizhan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000115371-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Chongqing_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109859_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106819_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000114747_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Anshun_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106459_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yangjiang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107477-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104685_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Shanghai_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106226_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_CCS_Hangzhou_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Yingchuan_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_Luohe_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000104169_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109009-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102813_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000105105_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yingchuan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101757_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000101769_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Yiyang_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102042_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000106502_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Fangchenggang_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000109208_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000102101_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000100712_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000103364_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Wulan_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_Xiaoxita_CHN_300-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_CCS_G100000104639_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000103167_rf</t>
+  </si>
+  <si>
+    <t>ep_c_coal_usc_G100000111314_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_Hejin_CHN_300_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000101368_rf</t>
   </si>
   <si>
     <t>ep_coal_st_Chongqing_CHN_300-CHP_rf</t>
   </si>
   <si>
-    <t>ep_coal_usc_G100000111454_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115531_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103392_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000114803_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Shijiazhuang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Liaoyang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Wulan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111569_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103783-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103293_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Beichengqu_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102810_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Tongling_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Anqing_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101336_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_ZhongdongShequ_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Shanghai_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111649_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000105307_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111817_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_CHN44p2N116p5E_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Jingling_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Xiaoyi_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Liuzhou_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000114703_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115715_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102811_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shijiazhuang_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Sanhe_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000114202_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101367_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Yakeshi_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Yanggezhuang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_CCS_Hangzhou_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Yangzhou_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Liaoyang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100001000237_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Xiaoyi_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000113342_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104485-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Jinbi_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106460_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Yuanquan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115640_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Yangzhou_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Xiaoxita_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115438_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103004_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Wuhan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115489_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101919_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115850_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Xiaoyi_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CCS_G100000104640_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Yangzhou_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100001000280_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104622-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101335_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Yicheng_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_CHN44p4N121p8E_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Luohe_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110115-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110112-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103459_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Ningde_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104520_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111602-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115493_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yicheng_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104682_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Nanjing_CHN_400_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115953_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000109192_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115372_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102944_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Shanghai_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Hohhot_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Nanjing_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CHN44p2N116p5E_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Qabqa_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_CCS_G100001000355-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110114-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Hejin_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100001000236_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115453_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103449-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109027_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Putian_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_CHN44p7N89p1E_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Sizhan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104683_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115521_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115437_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109861_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Nanjing_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000114039_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Sizhan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Yangjiang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Hohhot_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Yangjiang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000114267_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Kuqa_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103458_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Ningde_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Tianjin_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101468_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102872_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Anshun_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Ningde_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Tangshan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yingchuan_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115371-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Chongqing_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000114364_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101790_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111465-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000100235_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Yingchuan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000109862_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115520_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Ningde_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_CHN44p7N89p1E_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100001000347_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111005_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115459_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Wuhan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Yuanquan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Rizhao_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103151_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106227_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111755-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115490_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115844_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Wulan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111568_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109205_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107476-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115454_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Wuan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Rizhao_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110113-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Tongshan_CHN_400_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yiyang_CHN_400_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Wuan_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103471_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_CCS_Hangzhou_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Yangzhou_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115458_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103612_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000104235_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Yangjiang_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104623_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104365-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000100894_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103463_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103867_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Sizhan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Yingchuan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115382-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111299_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Nanjing_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111479_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103150_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Wuan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Nanjing_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CCS_G100000107468_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115532_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104716_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Putian_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104066_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Yakeshi_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Tongshan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115346-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115732_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Putian_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115851_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115373_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_CHN45p9N129p3E_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000112939_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115523_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shanghai_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104074-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109860_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101756_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103003_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106355_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115400_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106644_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115495_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000109191_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000114365_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115496_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Tongshan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100001004192_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000108893_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104073-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000112940_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000105104_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115813_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Wuan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111453_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111650_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Tangshan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115390_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106643_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103611_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115296_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000113225_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Beichengqu_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Shaoguan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110134_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000114201_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103152_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Shanghai_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Fangchenggang_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000114746_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115383-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Jingling_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shaoguan_CHN_400_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Yingchuan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Luohe_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101757_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000101769_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Yiyang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106459_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Yangjiang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107477-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104685_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Shanghai_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000105105_rf</t>
-  </si>
-  <si>
     <t>ep_coal_st_Putian_CHN_300_rf</t>
   </si>
   <si>
-    <t>ep_coal_usc_G100000101368_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102042_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106502_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Fangchenggang_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109208_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000114747_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106819_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109859_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Anshun_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104169_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102813_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109009-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000100712_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000103364_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102101_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Wulan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Xiaoxita_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Hejin_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106226_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_CCS_Hangzhou_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_CHN44p7N89p1E_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Luohe_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CCS_G100000104639_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103167_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000111314_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_CHN44p7N89p1E_CHN_300-CHP_rf</t>
-  </si>
-  <si>
     <t>ep_coal_usc_G100000102034-CHP_rf</t>
   </si>
   <si>
     <t>ep_coal_sc_Nantong_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111142_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102812_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115654_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Beichengqu_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Hohhot_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000114040_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103414_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Luohe_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109190_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104621-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Tianjin_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115952_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Shahezhai_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_ZhongdongShequ_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_ZhongdongShequ_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109656-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109655-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Luohe_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115347_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109218_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111478_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Hohhot_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Xiaoxita_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Xiaoxita_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104064-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Liaoyang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Zouping_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CCS_G100000109030_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101789_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110263_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Yingchuan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115839_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104075-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107983_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CCS_G100000103395_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Anshun_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000105096_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Shanghai_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115642_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Nantong_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_CHN44p4N121p8E_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Hangzhou_CHN_400_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Fangchenggang_CHN_400_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102943_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115494_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Hangzhou_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Tianjin_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Luohe_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yangzhou_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102033-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110262-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115448_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100001000190-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110694_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Tongshan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102816-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101729_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000114802_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102817-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Yiyang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000114533_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102929_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104417_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115313_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Zouping_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Mianyang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Yiyang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104429-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111818_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115345-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115452_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109217_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103882_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Rizhao_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115370-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115880_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_CCS_Hangzhou_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Harbin_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104428-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Chongqing_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115845_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104368-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104367-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Changzhou_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107982_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Mianyang_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Yingchuan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Yangjiang_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100001000279_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000114301_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shanghai_CHN_400_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102942_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Yicheng_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Fuzhou_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Yiyang_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Anshun_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000114266_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115447_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Sizhan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Luohe_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Sanhe_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Shijiazhuang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_CCS_G100001000352-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104486-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111663_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000114702_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115401_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Jingling_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115825-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115449_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Sizhan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Yuanquan_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_CHN44p2N116p5E_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Nanjing_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Shaoguan_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Tongling_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Putian_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Manlin_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Jingling_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_CHN45p9N129p3E_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000108246_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101467_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106354_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Shaoguan_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109010-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Mianyang_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109028_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000105306_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115826-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106501_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104684_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104717_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Shijiazhuang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103294_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115450_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Linyi_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_CCS_G100001000354-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000114834_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Qabqa_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Harbin_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Yanggezhuang_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000101768_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104503_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115841_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Tianjin_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104104_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000114199-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115840_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_Fangchenggang_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103868_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Nantong_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000114835_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Changzhou_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Xiaoyi_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000102871_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_CCS_G100001000353-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_CHN44p7N89p1E_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000109189_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115517_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115838_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000115391_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000103479_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Yangjiang_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100001004194_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Yakeshi_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_coal_usc_G100000115810_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Shahezhai_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104519_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_Fuzhou_CHN_300_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000111466-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000106309_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000104504_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000114709_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000108245_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_Beichengqu_CHN_300-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Nantong_CHN_400-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_Changzhou_CHN_400_rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -10585,7 +10585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E96716-1A88-449D-8592-BEF3264F4FE9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95BDA2D6-4075-47FE-A5E3-6257FD03FA93}">
   <dimension ref="B2:AG1714"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51938,7 +51938,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F89DD4-0CBE-4220-8164-461D7ACD2F97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B33615-F5D3-4448-8DB9-E1F4E3C91E6D}">
   <dimension ref="B9:L24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -64859,7 +64859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A590469-6A10-4FEB-88F9-92128A1F835E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD515016-8DA9-4588-BF3B-492B8B2287B6}">
   <dimension ref="B2:Q855"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -69292,10 +69292,10 @@
         <v>2110</v>
       </c>
       <c r="P240" t="s">
-        <v>2083</v>
+        <v>2104</v>
       </c>
       <c r="Q240">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="241" spans="14:17" x14ac:dyDescent="0.45">
@@ -69306,10 +69306,10 @@
         <v>2111</v>
       </c>
       <c r="P241" t="s">
-        <v>2076</v>
+        <v>2071</v>
       </c>
       <c r="Q241">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="242" spans="14:17" x14ac:dyDescent="0.45">
@@ -69320,7 +69320,7 @@
         <v>2112</v>
       </c>
       <c r="P242" t="s">
-        <v>2089</v>
+        <v>2073</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -69334,7 +69334,7 @@
         <v>2113</v>
       </c>
       <c r="P243" t="s">
-        <v>2060</v>
+        <v>2094</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -69348,7 +69348,7 @@
         <v>2114</v>
       </c>
       <c r="P244" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="Q244">
         <v>0.85</v>
@@ -69362,7 +69362,7 @@
         <v>2115</v>
       </c>
       <c r="P245" t="s">
-        <v>2083</v>
+        <v>2094</v>
       </c>
       <c r="Q245">
         <v>0.85</v>
@@ -69376,7 +69376,7 @@
         <v>2116</v>
       </c>
       <c r="P246" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="Q246">
         <v>0.85</v>
@@ -69390,7 +69390,7 @@
         <v>2117</v>
       </c>
       <c r="P247" t="s">
-        <v>2081</v>
+        <v>2076</v>
       </c>
       <c r="Q247">
         <v>0.85</v>
@@ -69404,7 +69404,7 @@
         <v>2118</v>
       </c>
       <c r="P248" t="s">
-        <v>2073</v>
+        <v>2086</v>
       </c>
       <c r="Q248">
         <v>0.85</v>
@@ -69418,7 +69418,7 @@
         <v>2119</v>
       </c>
       <c r="P249" t="s">
-        <v>2054</v>
+        <v>2076</v>
       </c>
       <c r="Q249">
         <v>0.85</v>
@@ -69432,7 +69432,7 @@
         <v>2120</v>
       </c>
       <c r="P250" t="s">
-        <v>2089</v>
+        <v>2058</v>
       </c>
       <c r="Q250">
         <v>0.85</v>
@@ -69446,7 +69446,7 @@
         <v>2121</v>
       </c>
       <c r="P251" t="s">
-        <v>2103</v>
+        <v>2076</v>
       </c>
       <c r="Q251">
         <v>0.85</v>
@@ -69460,7 +69460,7 @@
         <v>2122</v>
       </c>
       <c r="P252" t="s">
-        <v>2089</v>
+        <v>2095</v>
       </c>
       <c r="Q252">
         <v>0.85</v>
@@ -69474,7 +69474,7 @@
         <v>2123</v>
       </c>
       <c r="P253" t="s">
-        <v>2094</v>
+        <v>2108</v>
       </c>
       <c r="Q253">
         <v>0.85</v>
@@ -69488,7 +69488,7 @@
         <v>2124</v>
       </c>
       <c r="P254" t="s">
-        <v>2080</v>
+        <v>2069</v>
       </c>
       <c r="Q254">
         <v>0.85</v>
@@ -69502,7 +69502,7 @@
         <v>2125</v>
       </c>
       <c r="P255" t="s">
-        <v>2095</v>
+        <v>2076</v>
       </c>
       <c r="Q255">
         <v>0.85</v>
@@ -69516,7 +69516,7 @@
         <v>2126</v>
       </c>
       <c r="P256" t="s">
-        <v>2106</v>
+        <v>2060</v>
       </c>
       <c r="Q256">
         <v>0.85</v>
@@ -69530,7 +69530,7 @@
         <v>2127</v>
       </c>
       <c r="P257" t="s">
-        <v>2095</v>
+        <v>2051</v>
       </c>
       <c r="Q257">
         <v>0.85</v>
@@ -69544,7 +69544,7 @@
         <v>2128</v>
       </c>
       <c r="P258" t="s">
-        <v>2094</v>
+        <v>2051</v>
       </c>
       <c r="Q258">
         <v>0.85</v>
@@ -69558,7 +69558,7 @@
         <v>2129</v>
       </c>
       <c r="P259" t="s">
-        <v>2065</v>
+        <v>2106</v>
       </c>
       <c r="Q259">
         <v>0.85</v>
@@ -69572,7 +69572,7 @@
         <v>2130</v>
       </c>
       <c r="P260" t="s">
-        <v>2101</v>
+        <v>2062</v>
       </c>
       <c r="Q260">
         <v>0.85</v>
@@ -69586,7 +69586,7 @@
         <v>2131</v>
       </c>
       <c r="P261" t="s">
-        <v>2088</v>
+        <v>2106</v>
       </c>
       <c r="Q261">
         <v>0.85</v>
@@ -69600,7 +69600,7 @@
         <v>2132</v>
       </c>
       <c r="P262" t="s">
-        <v>2098</v>
+        <v>2087</v>
       </c>
       <c r="Q262">
         <v>0.85</v>
@@ -69614,7 +69614,7 @@
         <v>2133</v>
       </c>
       <c r="P263" t="s">
-        <v>2104</v>
+        <v>2089</v>
       </c>
       <c r="Q263">
         <v>0.85</v>
@@ -69628,7 +69628,7 @@
         <v>2134</v>
       </c>
       <c r="P264" t="s">
-        <v>2106</v>
+        <v>2055</v>
       </c>
       <c r="Q264">
         <v>0.85</v>
@@ -69642,7 +69642,7 @@
         <v>2135</v>
       </c>
       <c r="P265" t="s">
-        <v>2065</v>
+        <v>2051</v>
       </c>
       <c r="Q265">
         <v>0.85</v>
@@ -69656,7 +69656,7 @@
         <v>2136</v>
       </c>
       <c r="P266" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="Q266">
         <v>0.85</v>
@@ -69670,7 +69670,7 @@
         <v>2137</v>
       </c>
       <c r="P267" t="s">
-        <v>2107</v>
+        <v>2057</v>
       </c>
       <c r="Q267">
         <v>0.85</v>
@@ -69684,7 +69684,7 @@
         <v>2138</v>
       </c>
       <c r="P268" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="Q268">
         <v>0.85</v>
@@ -69698,7 +69698,7 @@
         <v>2139</v>
       </c>
       <c r="P269" t="s">
-        <v>2106</v>
+        <v>2084</v>
       </c>
       <c r="Q269">
         <v>0.85</v>
@@ -69712,7 +69712,7 @@
         <v>2140</v>
       </c>
       <c r="P270" t="s">
-        <v>2069</v>
+        <v>2062</v>
       </c>
       <c r="Q270">
         <v>0.85</v>
@@ -69726,10 +69726,10 @@
         <v>2141</v>
       </c>
       <c r="P271" t="s">
-        <v>2058</v>
+        <v>2065</v>
       </c>
       <c r="Q271">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="272" spans="14:17" x14ac:dyDescent="0.45">
@@ -69740,10 +69740,10 @@
         <v>2142</v>
       </c>
       <c r="P272" t="s">
-        <v>2065</v>
+        <v>2107</v>
       </c>
       <c r="Q272">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="273" spans="14:17" x14ac:dyDescent="0.45">
@@ -69754,7 +69754,7 @@
         <v>2143</v>
       </c>
       <c r="P273" t="s">
-        <v>2051</v>
+        <v>2060</v>
       </c>
       <c r="Q273">
         <v>0.85</v>
@@ -69782,7 +69782,7 @@
         <v>2145</v>
       </c>
       <c r="P275" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="Q275">
         <v>0.85</v>
@@ -69796,7 +69796,7 @@
         <v>2146</v>
       </c>
       <c r="P276" t="s">
-        <v>2077</v>
+        <v>2083</v>
       </c>
       <c r="Q276">
         <v>0.85</v>
@@ -69810,7 +69810,7 @@
         <v>2147</v>
       </c>
       <c r="P277" t="s">
-        <v>2103</v>
+        <v>2109</v>
       </c>
       <c r="Q277">
         <v>0.85</v>
@@ -69824,7 +69824,7 @@
         <v>2148</v>
       </c>
       <c r="P278" t="s">
-        <v>2073</v>
+        <v>2104</v>
       </c>
       <c r="Q278">
         <v>0.85</v>
@@ -69838,7 +69838,7 @@
         <v>2149</v>
       </c>
       <c r="P279" t="s">
-        <v>2106</v>
+        <v>2078</v>
       </c>
       <c r="Q279">
         <v>0.85</v>
@@ -69852,7 +69852,7 @@
         <v>2150</v>
       </c>
       <c r="P280" t="s">
-        <v>2101</v>
+        <v>2088</v>
       </c>
       <c r="Q280">
         <v>0.85</v>
@@ -69866,7 +69866,7 @@
         <v>2151</v>
       </c>
       <c r="P281" t="s">
-        <v>2103</v>
+        <v>2109</v>
       </c>
       <c r="Q281">
         <v>0.85</v>
@@ -69880,10 +69880,10 @@
         <v>2152</v>
       </c>
       <c r="P282" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
       <c r="Q282">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="283" spans="14:17" x14ac:dyDescent="0.45">
@@ -69894,7 +69894,7 @@
         <v>2153</v>
       </c>
       <c r="P283" t="s">
-        <v>2094</v>
+        <v>2083</v>
       </c>
       <c r="Q283">
         <v>0.85</v>
@@ -69908,7 +69908,7 @@
         <v>2154</v>
       </c>
       <c r="P284" t="s">
-        <v>2058</v>
+        <v>2075</v>
       </c>
       <c r="Q284">
         <v>0.85</v>
@@ -69922,7 +69922,7 @@
         <v>2155</v>
       </c>
       <c r="P285" t="s">
-        <v>2060</v>
+        <v>2078</v>
       </c>
       <c r="Q285">
         <v>0.85</v>
@@ -69936,7 +69936,7 @@
         <v>2156</v>
       </c>
       <c r="P286" t="s">
-        <v>2088</v>
+        <v>2069</v>
       </c>
       <c r="Q286">
         <v>0.85</v>
@@ -69950,7 +69950,7 @@
         <v>2157</v>
       </c>
       <c r="P287" t="s">
-        <v>2088</v>
+        <v>2105</v>
       </c>
       <c r="Q287">
         <v>0.85</v>
@@ -69964,7 +69964,7 @@
         <v>2158</v>
       </c>
       <c r="P288" t="s">
-        <v>2101</v>
+        <v>2062</v>
       </c>
       <c r="Q288">
         <v>0.85</v>
@@ -69978,7 +69978,7 @@
         <v>2159</v>
       </c>
       <c r="P289" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="Q289">
         <v>0.85</v>
@@ -69992,7 +69992,7 @@
         <v>2160</v>
       </c>
       <c r="P290" t="s">
-        <v>2058</v>
+        <v>2086</v>
       </c>
       <c r="Q290">
         <v>0.85</v>
@@ -70006,7 +70006,7 @@
         <v>2161</v>
       </c>
       <c r="P291" t="s">
-        <v>2094</v>
+        <v>2102</v>
       </c>
       <c r="Q291">
         <v>0.85</v>
@@ -70020,7 +70020,7 @@
         <v>2162</v>
       </c>
       <c r="P292" t="s">
-        <v>2086</v>
+        <v>2109</v>
       </c>
       <c r="Q292">
         <v>0.85</v>
@@ -70034,7 +70034,7 @@
         <v>2163</v>
       </c>
       <c r="P293" t="s">
-        <v>2051</v>
+        <v>2084</v>
       </c>
       <c r="Q293">
         <v>0.85</v>
@@ -70048,7 +70048,7 @@
         <v>2164</v>
       </c>
       <c r="P294" t="s">
-        <v>2109</v>
+        <v>2075</v>
       </c>
       <c r="Q294">
         <v>0.85</v>
@@ -70062,7 +70062,7 @@
         <v>2165</v>
       </c>
       <c r="P295" t="s">
-        <v>2056</v>
+        <v>2101</v>
       </c>
       <c r="Q295">
         <v>0.85</v>
@@ -70076,7 +70076,7 @@
         <v>2166</v>
       </c>
       <c r="P296" t="s">
-        <v>2081</v>
+        <v>2051</v>
       </c>
       <c r="Q296">
         <v>0.85</v>
@@ -70090,7 +70090,7 @@
         <v>2167</v>
       </c>
       <c r="P297" t="s">
-        <v>2103</v>
+        <v>2073</v>
       </c>
       <c r="Q297">
         <v>0.85</v>
@@ -70104,7 +70104,7 @@
         <v>2168</v>
       </c>
       <c r="P298" t="s">
-        <v>2065</v>
+        <v>2058</v>
       </c>
       <c r="Q298">
         <v>0.85</v>
@@ -70118,10 +70118,10 @@
         <v>2169</v>
       </c>
       <c r="P299" t="s">
-        <v>2104</v>
+        <v>2071</v>
       </c>
       <c r="Q299">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="300" spans="14:17" x14ac:dyDescent="0.45">
@@ -70132,10 +70132,10 @@
         <v>2170</v>
       </c>
       <c r="P300" t="s">
-        <v>2054</v>
+        <v>2078</v>
       </c>
       <c r="Q300">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="301" spans="14:17" x14ac:dyDescent="0.45">
@@ -70146,7 +70146,7 @@
         <v>2171</v>
       </c>
       <c r="P301" t="s">
-        <v>2108</v>
+        <v>2055</v>
       </c>
       <c r="Q301">
         <v>0.85</v>
@@ -70160,7 +70160,7 @@
         <v>2172</v>
       </c>
       <c r="P302" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="Q302">
         <v>0.85</v>
@@ -70174,7 +70174,7 @@
         <v>2173</v>
       </c>
       <c r="P303" t="s">
-        <v>2089</v>
+        <v>2067</v>
       </c>
       <c r="Q303">
         <v>0.85</v>
@@ -70188,7 +70188,7 @@
         <v>2174</v>
       </c>
       <c r="P304" t="s">
-        <v>2096</v>
+        <v>2081</v>
       </c>
       <c r="Q304">
         <v>0.85</v>
@@ -70216,7 +70216,7 @@
         <v>2176</v>
       </c>
       <c r="P306" t="s">
-        <v>2083</v>
+        <v>2056</v>
       </c>
       <c r="Q306">
         <v>0.85</v>
@@ -70230,7 +70230,7 @@
         <v>2177</v>
       </c>
       <c r="P307" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="Q307">
         <v>0.85</v>
@@ -70244,7 +70244,7 @@
         <v>2178</v>
       </c>
       <c r="P308" t="s">
-        <v>2094</v>
+        <v>2076</v>
       </c>
       <c r="Q308">
         <v>0.85</v>
@@ -70258,7 +70258,7 @@
         <v>2179</v>
       </c>
       <c r="P309" t="s">
-        <v>2087</v>
+        <v>2109</v>
       </c>
       <c r="Q309">
         <v>0.85</v>
@@ -70272,7 +70272,7 @@
         <v>2180</v>
       </c>
       <c r="P310" t="s">
-        <v>2083</v>
+        <v>2092</v>
       </c>
       <c r="Q310">
         <v>0.85</v>
@@ -70300,7 +70300,7 @@
         <v>2182</v>
       </c>
       <c r="P312" t="s">
-        <v>2096</v>
+        <v>2089</v>
       </c>
       <c r="Q312">
         <v>0.85</v>
@@ -70314,7 +70314,7 @@
         <v>2183</v>
       </c>
       <c r="P313" t="s">
-        <v>2063</v>
+        <v>2077</v>
       </c>
       <c r="Q313">
         <v>0.85</v>
@@ -70328,7 +70328,7 @@
         <v>2184</v>
       </c>
       <c r="P314" t="s">
-        <v>2065</v>
+        <v>2086</v>
       </c>
       <c r="Q314">
         <v>0.85</v>
@@ -70342,7 +70342,7 @@
         <v>2185</v>
       </c>
       <c r="P315" t="s">
-        <v>2051</v>
+        <v>2077</v>
       </c>
       <c r="Q315">
         <v>0.85</v>
@@ -70356,10 +70356,10 @@
         <v>2186</v>
       </c>
       <c r="P316" t="s">
-        <v>2094</v>
+        <v>2103</v>
       </c>
       <c r="Q316">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="317" spans="14:17" x14ac:dyDescent="0.45">
@@ -70370,7 +70370,7 @@
         <v>2187</v>
       </c>
       <c r="P317" t="s">
-        <v>2065</v>
+        <v>2081</v>
       </c>
       <c r="Q317">
         <v>0.85</v>
@@ -70384,7 +70384,7 @@
         <v>2188</v>
       </c>
       <c r="P318" t="s">
-        <v>2093</v>
+        <v>2098</v>
       </c>
       <c r="Q318">
         <v>0.85</v>
@@ -70398,7 +70398,7 @@
         <v>2189</v>
       </c>
       <c r="P319" t="s">
-        <v>2076</v>
+        <v>2081</v>
       </c>
       <c r="Q319">
         <v>0.85</v>
@@ -70412,7 +70412,7 @@
         <v>2190</v>
       </c>
       <c r="P320" t="s">
-        <v>2101</v>
+        <v>2058</v>
       </c>
       <c r="Q320">
         <v>0.85</v>
@@ -70426,7 +70426,7 @@
         <v>2191</v>
       </c>
       <c r="P321" t="s">
-        <v>2060</v>
+        <v>2096</v>
       </c>
       <c r="Q321">
         <v>0.85</v>
@@ -70440,10 +70440,10 @@
         <v>2192</v>
       </c>
       <c r="P322" t="s">
-        <v>2098</v>
+        <v>2108</v>
       </c>
       <c r="Q322">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="323" spans="14:17" x14ac:dyDescent="0.45">
@@ -70454,10 +70454,10 @@
         <v>2193</v>
       </c>
       <c r="P323" t="s">
-        <v>2065</v>
+        <v>2104</v>
       </c>
       <c r="Q323">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="324" spans="14:17" x14ac:dyDescent="0.45">
@@ -70468,7 +70468,7 @@
         <v>2194</v>
       </c>
       <c r="P324" t="s">
-        <v>2101</v>
+        <v>2078</v>
       </c>
       <c r="Q324">
         <v>0.85</v>
@@ -70482,7 +70482,7 @@
         <v>2195</v>
       </c>
       <c r="P325" t="s">
-        <v>2055</v>
+        <v>2089</v>
       </c>
       <c r="Q325">
         <v>0.85</v>
@@ -70496,7 +70496,7 @@
         <v>2196</v>
       </c>
       <c r="P326" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
       <c r="Q326">
         <v>0.85</v>
@@ -70510,7 +70510,7 @@
         <v>2197</v>
       </c>
       <c r="P327" t="s">
-        <v>2067</v>
+        <v>2051</v>
       </c>
       <c r="Q327">
         <v>0.85</v>
@@ -70524,7 +70524,7 @@
         <v>2198</v>
       </c>
       <c r="P328" t="s">
-        <v>2075</v>
+        <v>2108</v>
       </c>
       <c r="Q328">
         <v>0.85</v>
@@ -70538,10 +70538,10 @@
         <v>2199</v>
       </c>
       <c r="P329" t="s">
-        <v>2078</v>
+        <v>2052</v>
       </c>
       <c r="Q329">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="330" spans="14:17" x14ac:dyDescent="0.45">
@@ -70552,7 +70552,7 @@
         <v>2200</v>
       </c>
       <c r="P330" t="s">
-        <v>2069</v>
+        <v>2098</v>
       </c>
       <c r="Q330">
         <v>0.85</v>
@@ -70566,7 +70566,7 @@
         <v>2201</v>
       </c>
       <c r="P331" t="s">
-        <v>2105</v>
+        <v>2081</v>
       </c>
       <c r="Q331">
         <v>0.85</v>
@@ -70580,7 +70580,7 @@
         <v>2202</v>
       </c>
       <c r="P332" t="s">
-        <v>2062</v>
+        <v>2103</v>
       </c>
       <c r="Q332">
         <v>0.85</v>
@@ -70594,7 +70594,7 @@
         <v>2203</v>
       </c>
       <c r="P333" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="Q333">
         <v>0.85</v>
@@ -70608,7 +70608,7 @@
         <v>2204</v>
       </c>
       <c r="P334" t="s">
-        <v>2102</v>
+        <v>2088</v>
       </c>
       <c r="Q334">
         <v>0.85</v>
@@ -70622,7 +70622,7 @@
         <v>2205</v>
       </c>
       <c r="P335" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="Q335">
         <v>0.85</v>
@@ -70636,7 +70636,7 @@
         <v>2206</v>
       </c>
       <c r="P336" t="s">
-        <v>2058</v>
+        <v>2051</v>
       </c>
       <c r="Q336">
         <v>0.85</v>
@@ -70650,7 +70650,7 @@
         <v>2207</v>
       </c>
       <c r="P337" t="s">
-        <v>2089</v>
+        <v>2051</v>
       </c>
       <c r="Q337">
         <v>0.85</v>
@@ -70664,7 +70664,7 @@
         <v>2208</v>
       </c>
       <c r="P338" t="s">
-        <v>2074</v>
+        <v>2106</v>
       </c>
       <c r="Q338">
         <v>0.85</v>
@@ -70678,7 +70678,7 @@
         <v>2209</v>
       </c>
       <c r="P339" t="s">
-        <v>2104</v>
+        <v>2109</v>
       </c>
       <c r="Q339">
         <v>0.85</v>
@@ -70692,7 +70692,7 @@
         <v>2210</v>
       </c>
       <c r="P340" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="Q340">
         <v>0.85</v>
@@ -70706,7 +70706,7 @@
         <v>2211</v>
       </c>
       <c r="P341" t="s">
-        <v>2081</v>
+        <v>2092</v>
       </c>
       <c r="Q341">
         <v>0.85</v>
@@ -70720,7 +70720,7 @@
         <v>2212</v>
       </c>
       <c r="P342" t="s">
-        <v>2106</v>
+        <v>2073</v>
       </c>
       <c r="Q342">
         <v>0.85</v>
@@ -70734,7 +70734,7 @@
         <v>2213</v>
       </c>
       <c r="P343" t="s">
-        <v>2056</v>
+        <v>2076</v>
       </c>
       <c r="Q343">
         <v>0.85</v>
@@ -70748,7 +70748,7 @@
         <v>2214</v>
       </c>
       <c r="P344" t="s">
-        <v>2059</v>
+        <v>2089</v>
       </c>
       <c r="Q344">
         <v>0.85</v>
@@ -70762,7 +70762,7 @@
         <v>2215</v>
       </c>
       <c r="P345" t="s">
-        <v>2076</v>
+        <v>2089</v>
       </c>
       <c r="Q345">
         <v>0.85</v>
@@ -70776,7 +70776,7 @@
         <v>2216</v>
       </c>
       <c r="P346" t="s">
-        <v>2092</v>
+        <v>2104</v>
       </c>
       <c r="Q346">
         <v>0.85</v>
@@ -70790,7 +70790,7 @@
         <v>2217</v>
       </c>
       <c r="P347" t="s">
-        <v>2109</v>
+        <v>2086</v>
       </c>
       <c r="Q347">
         <v>0.85</v>
@@ -70804,7 +70804,7 @@
         <v>2218</v>
       </c>
       <c r="P348" t="s">
-        <v>2089</v>
+        <v>2108</v>
       </c>
       <c r="Q348">
         <v>0.85</v>
@@ -70818,7 +70818,7 @@
         <v>2219</v>
       </c>
       <c r="P349" t="s">
-        <v>2106</v>
+        <v>2071</v>
       </c>
       <c r="Q349">
         <v>0.85</v>
@@ -70832,10 +70832,10 @@
         <v>2220</v>
       </c>
       <c r="P350" t="s">
-        <v>2077</v>
+        <v>2056</v>
       </c>
       <c r="Q350">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="351" spans="14:17" x14ac:dyDescent="0.45">
@@ -70846,7 +70846,7 @@
         <v>2221</v>
       </c>
       <c r="P351" t="s">
-        <v>2083</v>
+        <v>2093</v>
       </c>
       <c r="Q351">
         <v>0.85</v>
@@ -70860,7 +70860,7 @@
         <v>2222</v>
       </c>
       <c r="P352" t="s">
-        <v>2054</v>
+        <v>2103</v>
       </c>
       <c r="Q352">
         <v>0.85</v>
@@ -70874,7 +70874,7 @@
         <v>2223</v>
       </c>
       <c r="P353" t="s">
-        <v>2058</v>
+        <v>2051</v>
       </c>
       <c r="Q353">
         <v>0.85</v>
@@ -70888,7 +70888,7 @@
         <v>2224</v>
       </c>
       <c r="P354" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="Q354">
         <v>0.85</v>
@@ -70902,7 +70902,7 @@
         <v>2225</v>
       </c>
       <c r="P355" t="s">
-        <v>2108</v>
+        <v>2058</v>
       </c>
       <c r="Q355">
         <v>0.85</v>
@@ -70916,7 +70916,7 @@
         <v>2226</v>
       </c>
       <c r="P356" t="s">
-        <v>2084</v>
+        <v>2052</v>
       </c>
       <c r="Q356">
         <v>0.85</v>
@@ -70930,7 +70930,7 @@
         <v>2227</v>
       </c>
       <c r="P357" t="s">
-        <v>2109</v>
+        <v>2099</v>
       </c>
       <c r="Q357">
         <v>0.85</v>
@@ -70944,7 +70944,7 @@
         <v>2228</v>
       </c>
       <c r="P358" t="s">
-        <v>2086</v>
+        <v>2069</v>
       </c>
       <c r="Q358">
         <v>0.85</v>
@@ -70958,7 +70958,7 @@
         <v>2229</v>
       </c>
       <c r="P359" t="s">
-        <v>2086</v>
+        <v>2109</v>
       </c>
       <c r="Q359">
         <v>0.85</v>
@@ -70972,7 +70972,7 @@
         <v>2230</v>
       </c>
       <c r="P360" t="s">
-        <v>2077</v>
+        <v>2098</v>
       </c>
       <c r="Q360">
         <v>0.85</v>
@@ -70986,7 +70986,7 @@
         <v>2231</v>
       </c>
       <c r="P361" t="s">
-        <v>2103</v>
+        <v>2086</v>
       </c>
       <c r="Q361">
         <v>0.85</v>
@@ -71000,7 +71000,7 @@
         <v>2232</v>
       </c>
       <c r="P362" t="s">
-        <v>2081</v>
+        <v>2106</v>
       </c>
       <c r="Q362">
         <v>0.85</v>
@@ -71028,7 +71028,7 @@
         <v>2234</v>
       </c>
       <c r="P364" t="s">
-        <v>2051</v>
+        <v>2070</v>
       </c>
       <c r="Q364">
         <v>0.85</v>
@@ -71042,7 +71042,7 @@
         <v>2235</v>
       </c>
       <c r="P365" t="s">
-        <v>2108</v>
+        <v>2051</v>
       </c>
       <c r="Q365">
         <v>0.85</v>
@@ -71056,10 +71056,10 @@
         <v>2236</v>
       </c>
       <c r="P366" t="s">
-        <v>2071</v>
+        <v>2102</v>
       </c>
       <c r="Q366">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="367" spans="14:17" x14ac:dyDescent="0.45">
@@ -71070,10 +71070,10 @@
         <v>2237</v>
       </c>
       <c r="P367" t="s">
-        <v>2078</v>
+        <v>2058</v>
       </c>
       <c r="Q367">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="368" spans="14:17" x14ac:dyDescent="0.45">
@@ -71084,7 +71084,7 @@
         <v>2238</v>
       </c>
       <c r="P368" t="s">
-        <v>2089</v>
+        <v>2101</v>
       </c>
       <c r="Q368">
         <v>0.85</v>
@@ -71098,7 +71098,7 @@
         <v>2239</v>
       </c>
       <c r="P369" t="s">
-        <v>2089</v>
+        <v>2098</v>
       </c>
       <c r="Q369">
         <v>0.85</v>
@@ -71112,7 +71112,7 @@
         <v>2240</v>
       </c>
       <c r="P370" t="s">
-        <v>2103</v>
+        <v>2055</v>
       </c>
       <c r="Q370">
         <v>0.85</v>
@@ -71126,7 +71126,7 @@
         <v>2241</v>
       </c>
       <c r="P371" t="s">
-        <v>2089</v>
+        <v>2052</v>
       </c>
       <c r="Q371">
         <v>0.85</v>
@@ -71140,7 +71140,7 @@
         <v>2242</v>
       </c>
       <c r="P372" t="s">
-        <v>2076</v>
+        <v>2101</v>
       </c>
       <c r="Q372">
         <v>0.85</v>
@@ -71154,7 +71154,7 @@
         <v>2243</v>
       </c>
       <c r="P373" t="s">
-        <v>2105</v>
+        <v>2076</v>
       </c>
       <c r="Q373">
         <v>0.85</v>
@@ -71168,7 +71168,7 @@
         <v>2244</v>
       </c>
       <c r="P374" t="s">
-        <v>2078</v>
+        <v>2061</v>
       </c>
       <c r="Q374">
         <v>0.85</v>
@@ -71182,10 +71182,10 @@
         <v>2245</v>
       </c>
       <c r="P375" t="s">
-        <v>2076</v>
+        <v>2084</v>
       </c>
       <c r="Q375">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="376" spans="14:17" x14ac:dyDescent="0.45">
@@ -71196,7 +71196,7 @@
         <v>2246</v>
       </c>
       <c r="P376" t="s">
-        <v>2051</v>
+        <v>2104</v>
       </c>
       <c r="Q376">
         <v>0.85</v>
@@ -71210,7 +71210,7 @@
         <v>2247</v>
       </c>
       <c r="P377" t="s">
-        <v>2055</v>
+        <v>2077</v>
       </c>
       <c r="Q377">
         <v>0.85</v>
@@ -71224,7 +71224,7 @@
         <v>2248</v>
       </c>
       <c r="P378" t="s">
-        <v>2051</v>
+        <v>2103</v>
       </c>
       <c r="Q378">
         <v>0.85</v>
@@ -71238,7 +71238,7 @@
         <v>2249</v>
       </c>
       <c r="P379" t="s">
-        <v>2084</v>
+        <v>2089</v>
       </c>
       <c r="Q379">
         <v>0.85</v>
@@ -71252,7 +71252,7 @@
         <v>2250</v>
       </c>
       <c r="P380" t="s">
-        <v>2089</v>
+        <v>2076</v>
       </c>
       <c r="Q380">
         <v>0.85</v>
@@ -71266,7 +71266,7 @@
         <v>2251</v>
       </c>
       <c r="P381" t="s">
-        <v>2104</v>
+        <v>2086</v>
       </c>
       <c r="Q381">
         <v>0.85</v>
@@ -71280,7 +71280,7 @@
         <v>2252</v>
       </c>
       <c r="P382" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="Q382">
         <v>0.85</v>
@@ -71294,7 +71294,7 @@
         <v>2253</v>
       </c>
       <c r="P383" t="s">
-        <v>2081</v>
+        <v>2076</v>
       </c>
       <c r="Q383">
         <v>0.85</v>
@@ -71308,7 +71308,7 @@
         <v>2254</v>
       </c>
       <c r="P384" t="s">
-        <v>2104</v>
+        <v>2055</v>
       </c>
       <c r="Q384">
         <v>0.85</v>
@@ -71322,7 +71322,7 @@
         <v>2255</v>
       </c>
       <c r="P385" t="s">
-        <v>2080</v>
+        <v>2051</v>
       </c>
       <c r="Q385">
         <v>0.85</v>
@@ -71336,7 +71336,7 @@
         <v>2256</v>
       </c>
       <c r="P386" t="s">
-        <v>2096</v>
+        <v>2051</v>
       </c>
       <c r="Q386">
         <v>0.85</v>
@@ -71350,7 +71350,7 @@
         <v>2257</v>
       </c>
       <c r="P387" t="s">
-        <v>2051</v>
+        <v>2093</v>
       </c>
       <c r="Q387">
         <v>0.85</v>
@@ -71364,7 +71364,7 @@
         <v>2258</v>
       </c>
       <c r="P388" t="s">
-        <v>2077</v>
+        <v>2102</v>
       </c>
       <c r="Q388">
         <v>0.85</v>
@@ -71378,7 +71378,7 @@
         <v>2259</v>
       </c>
       <c r="P389" t="s">
-        <v>2063</v>
+        <v>2084</v>
       </c>
       <c r="Q389">
         <v>0.85</v>
@@ -71392,7 +71392,7 @@
         <v>2260</v>
       </c>
       <c r="P390" t="s">
-        <v>2076</v>
+        <v>2089</v>
       </c>
       <c r="Q390">
         <v>0.85</v>
@@ -71406,7 +71406,7 @@
         <v>2261</v>
       </c>
       <c r="P391" t="s">
-        <v>2078</v>
+        <v>2089</v>
       </c>
       <c r="Q391">
         <v>0.85</v>
@@ -71420,7 +71420,7 @@
         <v>2262</v>
       </c>
       <c r="P392" t="s">
-        <v>2071</v>
+        <v>2089</v>
       </c>
       <c r="Q392">
         <v>0.85</v>
@@ -71434,7 +71434,7 @@
         <v>2263</v>
       </c>
       <c r="P393" t="s">
-        <v>2104</v>
+        <v>2077</v>
       </c>
       <c r="Q393">
         <v>0.85</v>
@@ -71448,7 +71448,7 @@
         <v>2264</v>
       </c>
       <c r="P394" t="s">
-        <v>2077</v>
+        <v>2051</v>
       </c>
       <c r="Q394">
         <v>0.85</v>
@@ -71462,7 +71462,7 @@
         <v>2265</v>
       </c>
       <c r="P395" t="s">
-        <v>2102</v>
+        <v>2095</v>
       </c>
       <c r="Q395">
         <v>0.85</v>
@@ -71476,7 +71476,7 @@
         <v>2266</v>
       </c>
       <c r="P396" t="s">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="Q396">
         <v>0.85</v>
@@ -71490,7 +71490,7 @@
         <v>2267</v>
       </c>
       <c r="P397" t="s">
-        <v>2060</v>
+        <v>2078</v>
       </c>
       <c r="Q397">
         <v>0.85</v>
@@ -71504,7 +71504,7 @@
         <v>2268</v>
       </c>
       <c r="P398" t="s">
-        <v>2102</v>
+        <v>2076</v>
       </c>
       <c r="Q398">
         <v>0.85</v>
@@ -71518,7 +71518,7 @@
         <v>2269</v>
       </c>
       <c r="P399" t="s">
-        <v>2060</v>
+        <v>2081</v>
       </c>
       <c r="Q399">
         <v>0.85</v>
@@ -71532,7 +71532,7 @@
         <v>2270</v>
       </c>
       <c r="P400" t="s">
-        <v>2109</v>
+        <v>2060</v>
       </c>
       <c r="Q400">
         <v>0.85</v>
@@ -71546,7 +71546,7 @@
         <v>2271</v>
       </c>
       <c r="P401" t="s">
-        <v>2093</v>
+        <v>2102</v>
       </c>
       <c r="Q401">
         <v>0.85</v>
@@ -71560,7 +71560,7 @@
         <v>2272</v>
       </c>
       <c r="P402" t="s">
-        <v>2100</v>
+        <v>2092</v>
       </c>
       <c r="Q402">
         <v>0.85</v>
@@ -71574,10 +71574,10 @@
         <v>2273</v>
       </c>
       <c r="P403" t="s">
-        <v>2084</v>
+        <v>2100</v>
       </c>
       <c r="Q403">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="404" spans="14:17" x14ac:dyDescent="0.45">
@@ -71588,7 +71588,7 @@
         <v>2274</v>
       </c>
       <c r="P404" t="s">
-        <v>2051</v>
+        <v>2109</v>
       </c>
       <c r="Q404">
         <v>0.85</v>
@@ -71602,7 +71602,7 @@
         <v>2275</v>
       </c>
       <c r="P405" t="s">
-        <v>2073</v>
+        <v>2060</v>
       </c>
       <c r="Q405">
         <v>0.85</v>
@@ -71616,7 +71616,7 @@
         <v>2276</v>
       </c>
       <c r="P406" t="s">
-        <v>2089</v>
+        <v>2081</v>
       </c>
       <c r="Q406">
         <v>0.85</v>
@@ -71630,7 +71630,7 @@
         <v>2277</v>
       </c>
       <c r="P407" t="s">
-        <v>2076</v>
+        <v>2104</v>
       </c>
       <c r="Q407">
         <v>0.85</v>
@@ -71644,7 +71644,7 @@
         <v>2278</v>
       </c>
       <c r="P408" t="s">
-        <v>2089</v>
+        <v>2080</v>
       </c>
       <c r="Q408">
         <v>0.85</v>
@@ -71658,7 +71658,7 @@
         <v>2279</v>
       </c>
       <c r="P409" t="s">
-        <v>2104</v>
+        <v>2096</v>
       </c>
       <c r="Q409">
         <v>0.85</v>
@@ -71672,7 +71672,7 @@
         <v>2280</v>
       </c>
       <c r="P410" t="s">
-        <v>2093</v>
+        <v>2104</v>
       </c>
       <c r="Q410">
         <v>0.85</v>
@@ -71686,7 +71686,7 @@
         <v>2281</v>
       </c>
       <c r="P411" t="s">
-        <v>2088</v>
+        <v>2075</v>
       </c>
       <c r="Q411">
         <v>0.85</v>
@@ -71700,7 +71700,7 @@
         <v>2282</v>
       </c>
       <c r="P412" t="s">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="Q412">
         <v>0.85</v>
@@ -71728,7 +71728,7 @@
         <v>2284</v>
       </c>
       <c r="P414" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="Q414">
         <v>0.85</v>
@@ -71742,10 +71742,10 @@
         <v>2285</v>
       </c>
       <c r="P415" t="s">
-        <v>2098</v>
+        <v>2090</v>
       </c>
       <c r="Q415">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="416" spans="14:17" x14ac:dyDescent="0.45">
@@ -71756,7 +71756,7 @@
         <v>2286</v>
       </c>
       <c r="P416" t="s">
-        <v>2055</v>
+        <v>2086</v>
       </c>
       <c r="Q416">
         <v>0.85</v>
@@ -71770,7 +71770,7 @@
         <v>2287</v>
       </c>
       <c r="P417" t="s">
-        <v>2058</v>
+        <v>2082</v>
       </c>
       <c r="Q417">
         <v>0.85</v>
@@ -71784,7 +71784,7 @@
         <v>2288</v>
       </c>
       <c r="P418" t="s">
-        <v>2101</v>
+        <v>2060</v>
       </c>
       <c r="Q418">
         <v>0.85</v>
@@ -71798,7 +71798,7 @@
         <v>2289</v>
       </c>
       <c r="P419" t="s">
-        <v>2065</v>
+        <v>2092</v>
       </c>
       <c r="Q419">
         <v>0.85</v>
@@ -71812,7 +71812,7 @@
         <v>2290</v>
       </c>
       <c r="P420" t="s">
-        <v>2103</v>
+        <v>2081</v>
       </c>
       <c r="Q420">
         <v>0.85</v>
@@ -71826,7 +71826,7 @@
         <v>2291</v>
       </c>
       <c r="P421" t="s">
-        <v>2051</v>
+        <v>2087</v>
       </c>
       <c r="Q421">
         <v>0.85</v>
@@ -71840,7 +71840,7 @@
         <v>2292</v>
       </c>
       <c r="P422" t="s">
-        <v>2058</v>
+        <v>2053</v>
       </c>
       <c r="Q422">
         <v>0.85</v>
@@ -71854,7 +71854,7 @@
         <v>2293</v>
       </c>
       <c r="P423" t="s">
-        <v>2097</v>
+        <v>2053</v>
       </c>
       <c r="Q423">
         <v>0.85</v>
@@ -71868,7 +71868,7 @@
         <v>2294</v>
       </c>
       <c r="P424" t="s">
-        <v>2052</v>
+        <v>2071</v>
       </c>
       <c r="Q424">
         <v>0.85</v>
@@ -71882,7 +71882,7 @@
         <v>2295</v>
       </c>
       <c r="P425" t="s">
-        <v>2099</v>
+        <v>2093</v>
       </c>
       <c r="Q425">
         <v>0.85</v>
@@ -71896,7 +71896,7 @@
         <v>2296</v>
       </c>
       <c r="P426" t="s">
-        <v>2069</v>
+        <v>2095</v>
       </c>
       <c r="Q426">
         <v>0.85</v>
@@ -71910,7 +71910,7 @@
         <v>2297</v>
       </c>
       <c r="P427" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
       <c r="Q427">
         <v>0.85</v>
@@ -71924,7 +71924,7 @@
         <v>2298</v>
       </c>
       <c r="P428" t="s">
-        <v>2081</v>
+        <v>2089</v>
       </c>
       <c r="Q428">
         <v>0.85</v>
@@ -71938,7 +71938,7 @@
         <v>2299</v>
       </c>
       <c r="P429" t="s">
-        <v>2103</v>
+        <v>2096</v>
       </c>
       <c r="Q429">
         <v>0.85</v>
@@ -71952,10 +71952,10 @@
         <v>2300</v>
       </c>
       <c r="P430" t="s">
-        <v>2087</v>
+        <v>2091</v>
       </c>
       <c r="Q430">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="431" spans="14:17" x14ac:dyDescent="0.45">
@@ -71966,7 +71966,7 @@
         <v>2301</v>
       </c>
       <c r="P431" t="s">
-        <v>2086</v>
+        <v>2063</v>
       </c>
       <c r="Q431">
         <v>0.85</v>
@@ -71980,7 +71980,7 @@
         <v>2302</v>
       </c>
       <c r="P432" t="s">
-        <v>2108</v>
+        <v>2104</v>
       </c>
       <c r="Q432">
         <v>0.85</v>
@@ -71994,7 +71994,7 @@
         <v>2303</v>
       </c>
       <c r="P433" t="s">
-        <v>2109</v>
+        <v>2099</v>
       </c>
       <c r="Q433">
         <v>0.85</v>
@@ -72008,7 +72008,7 @@
         <v>2304</v>
       </c>
       <c r="P434" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="Q434">
         <v>0.85</v>
@@ -72022,7 +72022,7 @@
         <v>2305</v>
       </c>
       <c r="P435" t="s">
-        <v>2070</v>
+        <v>2051</v>
       </c>
       <c r="Q435">
         <v>0.85</v>
@@ -72036,7 +72036,7 @@
         <v>2306</v>
       </c>
       <c r="P436" t="s">
-        <v>2051</v>
+        <v>2088</v>
       </c>
       <c r="Q436">
         <v>0.85</v>
@@ -72050,7 +72050,7 @@
         <v>2307</v>
       </c>
       <c r="P437" t="s">
-        <v>2051</v>
+        <v>2055</v>
       </c>
       <c r="Q437">
         <v>0.85</v>
@@ -72064,7 +72064,7 @@
         <v>2308</v>
       </c>
       <c r="P438" t="s">
-        <v>2109</v>
+        <v>2101</v>
       </c>
       <c r="Q438">
         <v>0.85</v>
@@ -72078,7 +72078,7 @@
         <v>2309</v>
       </c>
       <c r="P439" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="Q439">
         <v>0.85</v>
@@ -72092,7 +72092,7 @@
         <v>2310</v>
       </c>
       <c r="P440" t="s">
-        <v>2105</v>
+        <v>2075</v>
       </c>
       <c r="Q440">
         <v>0.85</v>
@@ -72106,7 +72106,7 @@
         <v>2311</v>
       </c>
       <c r="P441" t="s">
-        <v>2080</v>
+        <v>2103</v>
       </c>
       <c r="Q441">
         <v>0.85</v>
@@ -72120,7 +72120,7 @@
         <v>2312</v>
       </c>
       <c r="P442" t="s">
-        <v>2092</v>
+        <v>2107</v>
       </c>
       <c r="Q442">
         <v>0.85</v>
@@ -72134,7 +72134,7 @@
         <v>2313</v>
       </c>
       <c r="P443" t="s">
-        <v>2073</v>
+        <v>2088</v>
       </c>
       <c r="Q443">
         <v>0.85</v>
@@ -72148,7 +72148,7 @@
         <v>2314</v>
       </c>
       <c r="P444" t="s">
-        <v>2106</v>
+        <v>2093</v>
       </c>
       <c r="Q444">
         <v>0.85</v>
@@ -72176,7 +72176,7 @@
         <v>2316</v>
       </c>
       <c r="P446" t="s">
-        <v>2086</v>
+        <v>2059</v>
       </c>
       <c r="Q446">
         <v>0.85</v>
@@ -72190,10 +72190,10 @@
         <v>2317</v>
       </c>
       <c r="P447" t="s">
-        <v>2052</v>
+        <v>2091</v>
       </c>
       <c r="Q447">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="448" spans="14:17" x14ac:dyDescent="0.45">
@@ -72204,10 +72204,10 @@
         <v>2318</v>
       </c>
       <c r="P448" t="s">
-        <v>2056</v>
+        <v>2082</v>
       </c>
       <c r="Q448">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="449" spans="14:17" x14ac:dyDescent="0.45">
@@ -72218,7 +72218,7 @@
         <v>2319</v>
       </c>
       <c r="P449" t="s">
-        <v>2101</v>
+        <v>2058</v>
       </c>
       <c r="Q449">
         <v>0.85</v>
@@ -72232,7 +72232,7 @@
         <v>2320</v>
       </c>
       <c r="P450" t="s">
-        <v>2076</v>
+        <v>2104</v>
       </c>
       <c r="Q450">
         <v>0.85</v>
@@ -72246,7 +72246,7 @@
         <v>2321</v>
       </c>
       <c r="P451" t="s">
-        <v>2061</v>
+        <v>2093</v>
       </c>
       <c r="Q451">
         <v>0.85</v>
@@ -72260,7 +72260,7 @@
         <v>2322</v>
       </c>
       <c r="P452" t="s">
-        <v>2095</v>
+        <v>2103</v>
       </c>
       <c r="Q452">
         <v>0.85</v>
@@ -72274,7 +72274,7 @@
         <v>2323</v>
       </c>
       <c r="P453" t="s">
-        <v>2063</v>
+        <v>2053</v>
       </c>
       <c r="Q453">
         <v>0.85</v>
@@ -72288,7 +72288,7 @@
         <v>2324</v>
       </c>
       <c r="P454" t="s">
-        <v>2104</v>
+        <v>2089</v>
       </c>
       <c r="Q454">
         <v>0.85</v>
@@ -72302,7 +72302,7 @@
         <v>2325</v>
       </c>
       <c r="P455" t="s">
-        <v>2099</v>
+        <v>2109</v>
       </c>
       <c r="Q455">
         <v>0.85</v>
@@ -72316,7 +72316,7 @@
         <v>2326</v>
       </c>
       <c r="P456" t="s">
-        <v>2060</v>
+        <v>2056</v>
       </c>
       <c r="Q456">
         <v>0.85</v>
@@ -72330,7 +72330,7 @@
         <v>2327</v>
       </c>
       <c r="P457" t="s">
-        <v>2092</v>
+        <v>2051</v>
       </c>
       <c r="Q457">
         <v>0.85</v>
@@ -72344,7 +72344,7 @@
         <v>2328</v>
       </c>
       <c r="P458" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="Q458">
         <v>0.85</v>
@@ -72358,7 +72358,7 @@
         <v>2329</v>
       </c>
       <c r="P459" t="s">
-        <v>2081</v>
+        <v>2060</v>
       </c>
       <c r="Q459">
         <v>0.85</v>
@@ -72372,7 +72372,7 @@
         <v>2330</v>
       </c>
       <c r="P460" t="s">
-        <v>2072</v>
+        <v>2060</v>
       </c>
       <c r="Q460">
         <v>0.85</v>
@@ -72386,7 +72386,7 @@
         <v>2331</v>
       </c>
       <c r="P461" t="s">
-        <v>2089</v>
+        <v>2103</v>
       </c>
       <c r="Q461">
         <v>0.85</v>
@@ -72400,7 +72400,7 @@
         <v>2332</v>
       </c>
       <c r="P462" t="s">
-        <v>2096</v>
+        <v>2077</v>
       </c>
       <c r="Q462">
         <v>0.85</v>
@@ -72414,7 +72414,7 @@
         <v>2333</v>
       </c>
       <c r="P463" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
       <c r="Q463">
         <v>0.85</v>
@@ -72428,7 +72428,7 @@
         <v>2334</v>
       </c>
       <c r="P464" t="s">
-        <v>2104</v>
+        <v>2093</v>
       </c>
       <c r="Q464">
         <v>0.85</v>
@@ -72442,7 +72442,7 @@
         <v>2335</v>
       </c>
       <c r="P465" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
       <c r="Q465">
         <v>0.85</v>
@@ -72456,7 +72456,7 @@
         <v>2336</v>
       </c>
       <c r="P466" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="Q466">
         <v>0.85</v>
@@ -72470,7 +72470,7 @@
         <v>2337</v>
       </c>
       <c r="P467" t="s">
-        <v>2088</v>
+        <v>2053</v>
       </c>
       <c r="Q467">
         <v>0.85</v>
@@ -72484,7 +72484,7 @@
         <v>2338</v>
       </c>
       <c r="P468" t="s">
-        <v>2055</v>
+        <v>2086</v>
       </c>
       <c r="Q468">
         <v>0.85</v>
@@ -72498,7 +72498,7 @@
         <v>2339</v>
       </c>
       <c r="P469" t="s">
-        <v>2082</v>
+        <v>2071</v>
       </c>
       <c r="Q469">
         <v>0.85</v>
@@ -72512,7 +72512,7 @@
         <v>2340</v>
       </c>
       <c r="P470" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="Q470">
         <v>0.85</v>
@@ -72526,7 +72526,7 @@
         <v>2341</v>
       </c>
       <c r="P471" t="s">
-        <v>2094</v>
+        <v>2089</v>
       </c>
       <c r="Q471">
         <v>0.85</v>
@@ -72540,7 +72540,7 @@
         <v>2342</v>
       </c>
       <c r="P472" t="s">
-        <v>2092</v>
+        <v>2083</v>
       </c>
       <c r="Q472">
         <v>0.85</v>
@@ -72554,7 +72554,7 @@
         <v>2343</v>
       </c>
       <c r="P473" t="s">
-        <v>2101</v>
+        <v>2089</v>
       </c>
       <c r="Q473">
         <v>0.85</v>
@@ -72568,7 +72568,7 @@
         <v>2344</v>
       </c>
       <c r="P474" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
       <c r="Q474">
         <v>0.85</v>
@@ -72582,7 +72582,7 @@
         <v>2345</v>
       </c>
       <c r="P475" t="s">
-        <v>2088</v>
+        <v>2058</v>
       </c>
       <c r="Q475">
         <v>0.85</v>
@@ -72596,7 +72596,7 @@
         <v>2346</v>
       </c>
       <c r="P476" t="s">
-        <v>2093</v>
+        <v>2071</v>
       </c>
       <c r="Q476">
         <v>0.85</v>
@@ -72610,7 +72610,7 @@
         <v>2347</v>
       </c>
       <c r="P477" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
       <c r="Q477">
         <v>0.85</v>
@@ -72624,7 +72624,7 @@
         <v>2348</v>
       </c>
       <c r="P478" t="s">
-        <v>2091</v>
+        <v>2101</v>
       </c>
       <c r="Q478">
         <v>0.85</v>
@@ -72638,7 +72638,7 @@
         <v>2349</v>
       </c>
       <c r="P479" t="s">
-        <v>2102</v>
+        <v>2062</v>
       </c>
       <c r="Q479">
         <v>0.85</v>
@@ -72652,7 +72652,7 @@
         <v>2350</v>
       </c>
       <c r="P480" t="s">
-        <v>2082</v>
+        <v>2103</v>
       </c>
       <c r="Q480">
         <v>0.85</v>
@@ -72666,7 +72666,7 @@
         <v>2351</v>
       </c>
       <c r="P481" t="s">
-        <v>2053</v>
+        <v>2093</v>
       </c>
       <c r="Q481">
         <v>0.85</v>
@@ -72680,10 +72680,10 @@
         <v>2352</v>
       </c>
       <c r="P482" t="s">
-        <v>2053</v>
+        <v>2060</v>
       </c>
       <c r="Q482">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="483" spans="14:17" x14ac:dyDescent="0.45">
@@ -72694,10 +72694,10 @@
         <v>2353</v>
       </c>
       <c r="P483" t="s">
-        <v>2071</v>
+        <v>2106</v>
       </c>
       <c r="Q483">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="484" spans="14:17" x14ac:dyDescent="0.45">
@@ -72708,7 +72708,7 @@
         <v>2354</v>
       </c>
       <c r="P484" t="s">
-        <v>2093</v>
+        <v>2086</v>
       </c>
       <c r="Q484">
         <v>0.85</v>
@@ -72722,7 +72722,7 @@
         <v>2355</v>
       </c>
       <c r="P485" t="s">
-        <v>2103</v>
+        <v>2082</v>
       </c>
       <c r="Q485">
         <v>0.85</v>
@@ -72736,7 +72736,7 @@
         <v>2356</v>
       </c>
       <c r="P486" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="Q486">
         <v>0.85</v>
@@ -72750,7 +72750,7 @@
         <v>2357</v>
       </c>
       <c r="P487" t="s">
-        <v>2075</v>
+        <v>2052</v>
       </c>
       <c r="Q487">
         <v>0.85</v>
@@ -72764,10 +72764,10 @@
         <v>2358</v>
       </c>
       <c r="P488" t="s">
-        <v>2091</v>
+        <v>2109</v>
       </c>
       <c r="Q488">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="489" spans="14:17" x14ac:dyDescent="0.45">
@@ -72778,7 +72778,7 @@
         <v>2359</v>
       </c>
       <c r="P489" t="s">
-        <v>2093</v>
+        <v>2105</v>
       </c>
       <c r="Q489">
         <v>0.85</v>
@@ -72792,10 +72792,10 @@
         <v>2360</v>
       </c>
       <c r="P490" t="s">
-        <v>2090</v>
+        <v>2063</v>
       </c>
       <c r="Q490">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="491" spans="14:17" x14ac:dyDescent="0.45">
@@ -72806,7 +72806,7 @@
         <v>2361</v>
       </c>
       <c r="P491" t="s">
-        <v>2089</v>
+        <v>2055</v>
       </c>
       <c r="Q491">
         <v>0.85</v>
@@ -72820,7 +72820,7 @@
         <v>2362</v>
       </c>
       <c r="P492" t="s">
-        <v>2065</v>
+        <v>2093</v>
       </c>
       <c r="Q492">
         <v>0.85</v>
@@ -72834,7 +72834,7 @@
         <v>2363</v>
       </c>
       <c r="P493" t="s">
-        <v>2103</v>
+        <v>2094</v>
       </c>
       <c r="Q493">
         <v>0.85</v>
@@ -72848,7 +72848,7 @@
         <v>2364</v>
       </c>
       <c r="P494" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="Q494">
         <v>0.85</v>
@@ -72862,7 +72862,7 @@
         <v>2365</v>
       </c>
       <c r="P495" t="s">
-        <v>2051</v>
+        <v>2060</v>
       </c>
       <c r="Q495">
         <v>0.85</v>
@@ -72876,7 +72876,7 @@
         <v>2366</v>
       </c>
       <c r="P496" t="s">
-        <v>2086</v>
+        <v>2075</v>
       </c>
       <c r="Q496">
         <v>0.85</v>
@@ -72890,10 +72890,10 @@
         <v>2367</v>
       </c>
       <c r="P497" t="s">
-        <v>2090</v>
+        <v>2107</v>
       </c>
       <c r="Q497">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="498" spans="14:17" x14ac:dyDescent="0.45">
@@ -72904,7 +72904,7 @@
         <v>2368</v>
       </c>
       <c r="P498" t="s">
-        <v>2105</v>
+        <v>2083</v>
       </c>
       <c r="Q498">
         <v>0.85</v>
@@ -72918,7 +72918,7 @@
         <v>2369</v>
       </c>
       <c r="P499" t="s">
-        <v>2088</v>
+        <v>2058</v>
       </c>
       <c r="Q499">
         <v>0.85</v>
@@ -72932,7 +72932,7 @@
         <v>2370</v>
       </c>
       <c r="P500" t="s">
-        <v>2086</v>
+        <v>2096</v>
       </c>
       <c r="Q500">
         <v>0.85</v>
@@ -72946,7 +72946,7 @@
         <v>2371</v>
       </c>
       <c r="P501" t="s">
-        <v>2053</v>
+        <v>2076</v>
       </c>
       <c r="Q501">
         <v>0.85</v>
@@ -72960,7 +72960,7 @@
         <v>2372</v>
       </c>
       <c r="P502" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="Q502">
         <v>0.85</v>
@@ -72974,7 +72974,7 @@
         <v>2373</v>
       </c>
       <c r="P503" t="s">
-        <v>2060</v>
+        <v>2103</v>
       </c>
       <c r="Q503">
         <v>0.85</v>
@@ -72988,7 +72988,7 @@
         <v>2374</v>
       </c>
       <c r="P504" t="s">
-        <v>2071</v>
+        <v>2053</v>
       </c>
       <c r="Q504">
         <v>0.85</v>
@@ -73002,7 +73002,7 @@
         <v>2375</v>
       </c>
       <c r="P505" t="s">
-        <v>2078</v>
+        <v>2071</v>
       </c>
       <c r="Q505">
         <v>0.85</v>
@@ -73016,7 +73016,7 @@
         <v>2376</v>
       </c>
       <c r="P506" t="s">
-        <v>2089</v>
+        <v>2077</v>
       </c>
       <c r="Q506">
         <v>0.85</v>
@@ -73030,7 +73030,7 @@
         <v>2377</v>
       </c>
       <c r="P507" t="s">
-        <v>2076</v>
+        <v>2055</v>
       </c>
       <c r="Q507">
         <v>0.85</v>
@@ -73044,7 +73044,7 @@
         <v>2378</v>
       </c>
       <c r="P508" t="s">
-        <v>2075</v>
+        <v>2106</v>
       </c>
       <c r="Q508">
         <v>0.85</v>
@@ -73058,7 +73058,7 @@
         <v>2379</v>
       </c>
       <c r="P509" t="s">
-        <v>2103</v>
+        <v>2075</v>
       </c>
       <c r="Q509">
         <v>0.85</v>
@@ -73072,7 +73072,7 @@
         <v>2380</v>
       </c>
       <c r="P510" t="s">
-        <v>2093</v>
+        <v>2106</v>
       </c>
       <c r="Q510">
         <v>0.85</v>
@@ -73086,7 +73086,7 @@
         <v>2381</v>
       </c>
       <c r="P511" t="s">
-        <v>2055</v>
+        <v>2063</v>
       </c>
       <c r="Q511">
         <v>0.85</v>
@@ -73100,7 +73100,7 @@
         <v>2382</v>
       </c>
       <c r="P512" t="s">
-        <v>2051</v>
+        <v>2104</v>
       </c>
       <c r="Q512">
         <v>0.85</v>
@@ -73114,10 +73114,10 @@
         <v>2383</v>
       </c>
       <c r="P513" t="s">
-        <v>2063</v>
+        <v>2077</v>
       </c>
       <c r="Q513">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="514" spans="14:17" x14ac:dyDescent="0.45">
@@ -73128,7 +73128,7 @@
         <v>2384</v>
       </c>
       <c r="P514" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="Q514">
         <v>0.85</v>
@@ -73142,7 +73142,7 @@
         <v>2385</v>
       </c>
       <c r="P515" t="s">
-        <v>2101</v>
+        <v>2083</v>
       </c>
       <c r="Q515">
         <v>0.85</v>
@@ -73156,7 +73156,7 @@
         <v>2386</v>
       </c>
       <c r="P516" t="s">
-        <v>2103</v>
+        <v>2094</v>
       </c>
       <c r="Q516">
         <v>0.85</v>
@@ -73184,7 +73184,7 @@
         <v>2388</v>
       </c>
       <c r="P518" t="s">
-        <v>2086</v>
+        <v>2065</v>
       </c>
       <c r="Q518">
         <v>0.85</v>
@@ -73198,7 +73198,7 @@
         <v>2389</v>
       </c>
       <c r="P519" t="s">
-        <v>2071</v>
+        <v>2075</v>
       </c>
       <c r="Q519">
         <v>0.85</v>
@@ -73212,7 +73212,7 @@
         <v>2390</v>
       </c>
       <c r="P520" t="s">
-        <v>2060</v>
+        <v>2075</v>
       </c>
       <c r="Q520">
         <v>0.85</v>
@@ -73226,7 +73226,7 @@
         <v>2391</v>
       </c>
       <c r="P521" t="s">
-        <v>2068</v>
+        <v>2083</v>
       </c>
       <c r="Q521">
         <v>0.85</v>
@@ -73240,7 +73240,7 @@
         <v>2392</v>
       </c>
       <c r="P522" t="s">
-        <v>2071</v>
+        <v>2101</v>
       </c>
       <c r="Q522">
         <v>0.85</v>
@@ -73254,7 +73254,7 @@
         <v>2393</v>
       </c>
       <c r="P523" t="s">
-        <v>2093</v>
+        <v>2084</v>
       </c>
       <c r="Q523">
         <v>0.85</v>
@@ -73268,7 +73268,7 @@
         <v>2394</v>
       </c>
       <c r="P524" t="s">
-        <v>2053</v>
+        <v>2082</v>
       </c>
       <c r="Q524">
         <v>0.85</v>
@@ -73282,7 +73282,7 @@
         <v>2395</v>
       </c>
       <c r="P525" t="s">
-        <v>2095</v>
+        <v>2106</v>
       </c>
       <c r="Q525">
         <v>0.85</v>
@@ -73296,7 +73296,7 @@
         <v>2396</v>
       </c>
       <c r="P526" t="s">
-        <v>2093</v>
+        <v>2083</v>
       </c>
       <c r="Q526">
         <v>0.85</v>
@@ -73310,7 +73310,7 @@
         <v>2397</v>
       </c>
       <c r="P527" t="s">
-        <v>2059</v>
+        <v>2081</v>
       </c>
       <c r="Q527">
         <v>0.85</v>
@@ -73324,10 +73324,10 @@
         <v>2398</v>
       </c>
       <c r="P528" t="s">
-        <v>2093</v>
+        <v>2089</v>
       </c>
       <c r="Q528">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="529" spans="14:17" x14ac:dyDescent="0.45">
@@ -73352,10 +73352,10 @@
         <v>2400</v>
       </c>
       <c r="P530" t="s">
-        <v>2081</v>
+        <v>2051</v>
       </c>
       <c r="Q530">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="531" spans="14:17" x14ac:dyDescent="0.45">
@@ -73366,7 +73366,7 @@
         <v>2401</v>
       </c>
       <c r="P531" t="s">
-        <v>2069</v>
+        <v>2055</v>
       </c>
       <c r="Q531">
         <v>0.85</v>
@@ -73380,7 +73380,7 @@
         <v>2402</v>
       </c>
       <c r="P532" t="s">
-        <v>2065</v>
+        <v>2071</v>
       </c>
       <c r="Q532">
         <v>0.85</v>
@@ -73394,7 +73394,7 @@
         <v>2403</v>
       </c>
       <c r="P533" t="s">
-        <v>2083</v>
+        <v>2106</v>
       </c>
       <c r="Q533">
         <v>0.85</v>
@@ -73408,7 +73408,7 @@
         <v>2404</v>
       </c>
       <c r="P534" t="s">
-        <v>2058</v>
+        <v>2087</v>
       </c>
       <c r="Q534">
         <v>0.85</v>
@@ -73422,7 +73422,7 @@
         <v>2405</v>
       </c>
       <c r="P535" t="s">
-        <v>2052</v>
+        <v>2089</v>
       </c>
       <c r="Q535">
         <v>0.85</v>
@@ -73436,7 +73436,7 @@
         <v>2406</v>
       </c>
       <c r="P536" t="s">
-        <v>2109</v>
+        <v>2089</v>
       </c>
       <c r="Q536">
         <v>0.85</v>
@@ -73450,7 +73450,7 @@
         <v>2407</v>
       </c>
       <c r="P537" t="s">
-        <v>2081</v>
+        <v>2103</v>
       </c>
       <c r="Q537">
         <v>0.85</v>
@@ -73464,7 +73464,7 @@
         <v>2408</v>
       </c>
       <c r="P538" t="s">
-        <v>2063</v>
+        <v>2051</v>
       </c>
       <c r="Q538">
         <v>0.85</v>
@@ -73478,7 +73478,7 @@
         <v>2409</v>
       </c>
       <c r="P539" t="s">
-        <v>2055</v>
+        <v>2098</v>
       </c>
       <c r="Q539">
         <v>0.85</v>
@@ -73492,7 +73492,7 @@
         <v>2410</v>
       </c>
       <c r="P540" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="Q540">
         <v>0.85</v>
@@ -73506,7 +73506,7 @@
         <v>2411</v>
       </c>
       <c r="P541" t="s">
-        <v>2075</v>
+        <v>2095</v>
       </c>
       <c r="Q541">
         <v>0.85</v>
@@ -73520,7 +73520,7 @@
         <v>2412</v>
       </c>
       <c r="P542" t="s">
-        <v>2106</v>
+        <v>2096</v>
       </c>
       <c r="Q542">
         <v>0.85</v>
@@ -73534,7 +73534,7 @@
         <v>2413</v>
       </c>
       <c r="P543" t="s">
-        <v>2075</v>
+        <v>2107</v>
       </c>
       <c r="Q543">
         <v>0.85</v>
@@ -73548,7 +73548,7 @@
         <v>2414</v>
       </c>
       <c r="P544" t="s">
-        <v>2077</v>
+        <v>2087</v>
       </c>
       <c r="Q544">
         <v>0.85</v>
@@ -73562,7 +73562,7 @@
         <v>2415</v>
       </c>
       <c r="P545" t="s">
-        <v>2055</v>
+        <v>2076</v>
       </c>
       <c r="Q545">
         <v>0.85</v>
@@ -73576,10 +73576,10 @@
         <v>2416</v>
       </c>
       <c r="P546" t="s">
-        <v>2096</v>
+        <v>2051</v>
       </c>
       <c r="Q546">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="547" spans="14:17" x14ac:dyDescent="0.45">
@@ -73590,7 +73590,7 @@
         <v>2417</v>
       </c>
       <c r="P547" t="s">
-        <v>2094</v>
+        <v>2055</v>
       </c>
       <c r="Q547">
         <v>0.85</v>
@@ -73604,7 +73604,7 @@
         <v>2418</v>
       </c>
       <c r="P548" t="s">
-        <v>2076</v>
+        <v>2051</v>
       </c>
       <c r="Q548">
         <v>0.85</v>
@@ -73618,7 +73618,7 @@
         <v>2419</v>
       </c>
       <c r="P549" t="s">
-        <v>2103</v>
+        <v>2076</v>
       </c>
       <c r="Q549">
         <v>0.85</v>
@@ -73632,7 +73632,7 @@
         <v>2420</v>
       </c>
       <c r="P550" t="s">
-        <v>2106</v>
+        <v>2076</v>
       </c>
       <c r="Q550">
         <v>0.85</v>
@@ -73646,7 +73646,7 @@
         <v>2421</v>
       </c>
       <c r="P551" t="s">
-        <v>2082</v>
+        <v>2078</v>
       </c>
       <c r="Q551">
         <v>0.85</v>
@@ -73660,7 +73660,7 @@
         <v>2422</v>
       </c>
       <c r="P552" t="s">
-        <v>2086</v>
+        <v>2106</v>
       </c>
       <c r="Q552">
         <v>0.85</v>
@@ -73674,7 +73674,7 @@
         <v>2423</v>
       </c>
       <c r="P553" t="s">
-        <v>2069</v>
+        <v>2089</v>
       </c>
       <c r="Q553">
         <v>0.85</v>
@@ -73688,7 +73688,7 @@
         <v>2424</v>
       </c>
       <c r="P554" t="s">
-        <v>2098</v>
+        <v>2103</v>
       </c>
       <c r="Q554">
         <v>0.85</v>
@@ -73702,7 +73702,7 @@
         <v>2425</v>
       </c>
       <c r="P555" t="s">
-        <v>2060</v>
+        <v>2072</v>
       </c>
       <c r="Q555">
         <v>0.85</v>
@@ -73716,7 +73716,7 @@
         <v>2426</v>
       </c>
       <c r="P556" t="s">
-        <v>2103</v>
+        <v>2094</v>
       </c>
       <c r="Q556">
         <v>0.85</v>
@@ -73730,7 +73730,7 @@
         <v>2427</v>
       </c>
       <c r="P557" t="s">
-        <v>2071</v>
+        <v>2103</v>
       </c>
       <c r="Q557">
         <v>0.85</v>
@@ -73744,7 +73744,7 @@
         <v>2428</v>
       </c>
       <c r="P558" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="Q558">
         <v>0.85</v>
@@ -73758,7 +73758,7 @@
         <v>2429</v>
       </c>
       <c r="P559" t="s">
-        <v>2094</v>
+        <v>2079</v>
       </c>
       <c r="Q559">
         <v>0.85</v>
@@ -73772,7 +73772,7 @@
         <v>2430</v>
       </c>
       <c r="P560" t="s">
-        <v>2053</v>
+        <v>2077</v>
       </c>
       <c r="Q560">
         <v>0.85</v>
@@ -73789,7 +73789,7 @@
         <v>2106</v>
       </c>
       <c r="Q561">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="562" spans="14:17" x14ac:dyDescent="0.45">
@@ -73800,10 +73800,10 @@
         <v>2432</v>
       </c>
       <c r="P562" t="s">
-        <v>2060</v>
+        <v>2055</v>
       </c>
       <c r="Q562">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="563" spans="14:17" x14ac:dyDescent="0.45">
@@ -73814,10 +73814,10 @@
         <v>2433</v>
       </c>
       <c r="P563" t="s">
-        <v>2107</v>
+        <v>2071</v>
       </c>
       <c r="Q563">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="564" spans="14:17" x14ac:dyDescent="0.45">
@@ -73828,7 +73828,7 @@
         <v>2434</v>
       </c>
       <c r="P564" t="s">
-        <v>2106</v>
+        <v>2054</v>
       </c>
       <c r="Q564">
         <v>0.85</v>
@@ -73842,7 +73842,7 @@
         <v>2435</v>
       </c>
       <c r="P565" t="s">
-        <v>2063</v>
+        <v>2092</v>
       </c>
       <c r="Q565">
         <v>0.85</v>
@@ -73856,7 +73856,7 @@
         <v>2436</v>
       </c>
       <c r="P566" t="s">
-        <v>2104</v>
+        <v>2093</v>
       </c>
       <c r="Q566">
         <v>0.85</v>
@@ -73870,7 +73870,7 @@
         <v>2437</v>
       </c>
       <c r="P567" t="s">
-        <v>2077</v>
+        <v>2103</v>
       </c>
       <c r="Q567">
         <v>0.85</v>
@@ -73884,7 +73884,7 @@
         <v>2438</v>
       </c>
       <c r="P568" t="s">
-        <v>2055</v>
+        <v>2076</v>
       </c>
       <c r="Q568">
         <v>0.85</v>
@@ -73898,7 +73898,7 @@
         <v>2439</v>
       </c>
       <c r="P569" t="s">
-        <v>2106</v>
+        <v>2090</v>
       </c>
       <c r="Q569">
         <v>0.85</v>
@@ -73912,7 +73912,7 @@
         <v>2440</v>
       </c>
       <c r="P570" t="s">
-        <v>2071</v>
+        <v>2063</v>
       </c>
       <c r="Q570">
         <v>0.85</v>
@@ -73926,7 +73926,7 @@
         <v>2441</v>
       </c>
       <c r="P571" t="s">
-        <v>2093</v>
+        <v>2104</v>
       </c>
       <c r="Q571">
         <v>0.85</v>
@@ -73940,7 +73940,7 @@
         <v>2442</v>
       </c>
       <c r="P572" t="s">
-        <v>2076</v>
+        <v>2061</v>
       </c>
       <c r="Q572">
         <v>0.85</v>
@@ -73954,7 +73954,7 @@
         <v>2443</v>
       </c>
       <c r="P573" t="s">
-        <v>2078</v>
+        <v>2106</v>
       </c>
       <c r="Q573">
         <v>0.85</v>
@@ -73968,7 +73968,7 @@
         <v>2444</v>
       </c>
       <c r="P574" t="s">
-        <v>2106</v>
+        <v>2095</v>
       </c>
       <c r="Q574">
         <v>0.85</v>
@@ -73982,7 +73982,7 @@
         <v>2445</v>
       </c>
       <c r="P575" t="s">
-        <v>2089</v>
+        <v>2055</v>
       </c>
       <c r="Q575">
         <v>0.85</v>
@@ -73996,7 +73996,7 @@
         <v>2446</v>
       </c>
       <c r="P576" t="s">
-        <v>2103</v>
+        <v>2076</v>
       </c>
       <c r="Q576">
         <v>0.85</v>
@@ -74010,7 +74010,7 @@
         <v>2447</v>
       </c>
       <c r="P577" t="s">
-        <v>2081</v>
+        <v>2055</v>
       </c>
       <c r="Q577">
         <v>0.85</v>
@@ -74024,7 +74024,7 @@
         <v>2448</v>
       </c>
       <c r="P578" t="s">
-        <v>2087</v>
+        <v>2076</v>
       </c>
       <c r="Q578">
         <v>0.85</v>
@@ -74038,7 +74038,7 @@
         <v>2449</v>
       </c>
       <c r="P579" t="s">
-        <v>2071</v>
+        <v>2090</v>
       </c>
       <c r="Q579">
         <v>0.85</v>
@@ -74052,7 +74052,7 @@
         <v>2450</v>
       </c>
       <c r="P580" t="s">
-        <v>2090</v>
+        <v>2087</v>
       </c>
       <c r="Q580">
         <v>0.85</v>
@@ -74066,7 +74066,7 @@
         <v>2451</v>
       </c>
       <c r="P581" t="s">
-        <v>2103</v>
+        <v>2071</v>
       </c>
       <c r="Q581">
         <v>0.85</v>
@@ -74080,7 +74080,7 @@
         <v>2452</v>
       </c>
       <c r="P582" t="s">
-        <v>2076</v>
+        <v>2095</v>
       </c>
       <c r="Q582">
         <v>0.85</v>
@@ -74094,7 +74094,7 @@
         <v>2453</v>
       </c>
       <c r="P583" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="Q583">
         <v>0.85</v>
@@ -74108,7 +74108,7 @@
         <v>2454</v>
       </c>
       <c r="P584" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="Q584">
         <v>0.85</v>
@@ -74136,10 +74136,10 @@
         <v>2456</v>
       </c>
       <c r="P586" t="s">
-        <v>2051</v>
+        <v>2098</v>
       </c>
       <c r="Q586">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="587" spans="14:17" x14ac:dyDescent="0.45">
@@ -74150,10 +74150,10 @@
         <v>2457</v>
       </c>
       <c r="P587" t="s">
-        <v>2055</v>
+        <v>2094</v>
       </c>
       <c r="Q587">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="588" spans="14:17" x14ac:dyDescent="0.45">
@@ -74164,7 +74164,7 @@
         <v>2458</v>
       </c>
       <c r="P588" t="s">
-        <v>2076</v>
+        <v>2081</v>
       </c>
       <c r="Q588">
         <v>0.85</v>
@@ -74178,7 +74178,7 @@
         <v>2459</v>
       </c>
       <c r="P589" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="Q589">
         <v>0.85</v>
@@ -74192,7 +74192,7 @@
         <v>2460</v>
       </c>
       <c r="P590" t="s">
-        <v>2061</v>
+        <v>2068</v>
       </c>
       <c r="Q590">
         <v>0.85</v>
@@ -74206,7 +74206,7 @@
         <v>2461</v>
       </c>
       <c r="P591" t="s">
-        <v>2106</v>
+        <v>2094</v>
       </c>
       <c r="Q591">
         <v>0.85</v>
@@ -74220,7 +74220,7 @@
         <v>2462</v>
       </c>
       <c r="P592" t="s">
-        <v>2055</v>
+        <v>2096</v>
       </c>
       <c r="Q592">
         <v>0.85</v>
@@ -74234,7 +74234,7 @@
         <v>2463</v>
       </c>
       <c r="P593" t="s">
-        <v>2076</v>
+        <v>2083</v>
       </c>
       <c r="Q593">
         <v>0.85</v>
@@ -74248,7 +74248,7 @@
         <v>2464</v>
       </c>
       <c r="P594" t="s">
-        <v>2076</v>
+        <v>2106</v>
       </c>
       <c r="Q594">
         <v>0.85</v>
@@ -74262,7 +74262,7 @@
         <v>2465</v>
       </c>
       <c r="P595" t="s">
-        <v>2094</v>
+        <v>2087</v>
       </c>
       <c r="Q595">
         <v>0.85</v>
@@ -74276,7 +74276,7 @@
         <v>2466</v>
       </c>
       <c r="P596" t="s">
-        <v>2103</v>
+        <v>2086</v>
       </c>
       <c r="Q596">
         <v>0.85</v>
@@ -74290,7 +74290,7 @@
         <v>2467</v>
       </c>
       <c r="P597" t="s">
-        <v>2079</v>
+        <v>2063</v>
       </c>
       <c r="Q597">
         <v>0.85</v>
@@ -74304,7 +74304,7 @@
         <v>2468</v>
       </c>
       <c r="P598" t="s">
-        <v>2095</v>
+        <v>2065</v>
       </c>
       <c r="Q598">
         <v>0.85</v>
@@ -74318,7 +74318,7 @@
         <v>2469</v>
       </c>
       <c r="P599" t="s">
-        <v>2055</v>
+        <v>2103</v>
       </c>
       <c r="Q599">
         <v>0.85</v>
@@ -74332,10 +74332,10 @@
         <v>2470</v>
       </c>
       <c r="P600" t="s">
-        <v>2051</v>
+        <v>2073</v>
       </c>
       <c r="Q600">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="601" spans="14:17" x14ac:dyDescent="0.45">
@@ -74346,7 +74346,7 @@
         <v>2471</v>
       </c>
       <c r="P601" t="s">
-        <v>2095</v>
+        <v>2065</v>
       </c>
       <c r="Q601">
         <v>0.85</v>
@@ -74360,7 +74360,7 @@
         <v>2472</v>
       </c>
       <c r="P602" t="s">
-        <v>2063</v>
+        <v>2058</v>
       </c>
       <c r="Q602">
         <v>0.85</v>
@@ -74374,7 +74374,7 @@
         <v>2473</v>
       </c>
       <c r="P603" t="s">
-        <v>2106</v>
+        <v>2060</v>
       </c>
       <c r="Q603">
         <v>0.85</v>
@@ -74388,7 +74388,7 @@
         <v>2474</v>
       </c>
       <c r="P604" t="s">
-        <v>2088</v>
+        <v>2106</v>
       </c>
       <c r="Q604">
         <v>0.85</v>
@@ -74402,7 +74402,7 @@
         <v>2475</v>
       </c>
       <c r="P605" t="s">
-        <v>2106</v>
+        <v>2101</v>
       </c>
       <c r="Q605">
         <v>0.85</v>
@@ -74416,7 +74416,7 @@
         <v>2476</v>
       </c>
       <c r="P606" t="s">
-        <v>2083</v>
+        <v>2058</v>
       </c>
       <c r="Q606">
         <v>0.85</v>
@@ -74430,7 +74430,7 @@
         <v>2477</v>
       </c>
       <c r="P607" t="s">
-        <v>2071</v>
+        <v>2094</v>
       </c>
       <c r="Q607">
         <v>0.85</v>
@@ -74444,7 +74444,7 @@
         <v>2478</v>
       </c>
       <c r="P608" t="s">
-        <v>2075</v>
+        <v>2057</v>
       </c>
       <c r="Q608">
         <v>0.85</v>
@@ -74458,7 +74458,7 @@
         <v>2479</v>
       </c>
       <c r="P609" t="s">
-        <v>2065</v>
+        <v>2097</v>
       </c>
       <c r="Q609">
         <v>0.85</v>
@@ -74472,7 +74472,7 @@
         <v>2480</v>
       </c>
       <c r="P610" t="s">
-        <v>2083</v>
+        <v>2109</v>
       </c>
       <c r="Q610">
         <v>0.85</v>
@@ -74486,7 +74486,7 @@
         <v>2481</v>
       </c>
       <c r="P611" t="s">
-        <v>2075</v>
+        <v>2051</v>
       </c>
       <c r="Q611">
         <v>0.85</v>
@@ -74500,7 +74500,7 @@
         <v>2482</v>
       </c>
       <c r="P612" t="s">
-        <v>2106</v>
+        <v>2056</v>
       </c>
       <c r="Q612">
         <v>0.85</v>
@@ -74514,7 +74514,7 @@
         <v>2483</v>
       </c>
       <c r="P613" t="s">
-        <v>2083</v>
+        <v>2104</v>
       </c>
       <c r="Q613">
         <v>0.85</v>
@@ -74528,7 +74528,7 @@
         <v>2484</v>
       </c>
       <c r="P614" t="s">
-        <v>2081</v>
+        <v>2054</v>
       </c>
       <c r="Q614">
         <v>0.85</v>
@@ -74542,7 +74542,7 @@
         <v>2485</v>
       </c>
       <c r="P615" t="s">
-        <v>2095</v>
+        <v>2079</v>
       </c>
       <c r="Q615">
         <v>0.85</v>
@@ -74556,7 +74556,7 @@
         <v>2486</v>
       </c>
       <c r="P616" t="s">
-        <v>2095</v>
+        <v>2108</v>
       </c>
       <c r="Q616">
         <v>0.85</v>
@@ -74570,7 +74570,7 @@
         <v>2487</v>
       </c>
       <c r="P617" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="Q617">
         <v>0.85</v>
@@ -74584,7 +74584,7 @@
         <v>2488</v>
       </c>
       <c r="P618" t="s">
-        <v>2096</v>
+        <v>2051</v>
       </c>
       <c r="Q618">
         <v>0.85</v>
@@ -74598,7 +74598,7 @@
         <v>2489</v>
       </c>
       <c r="P619" t="s">
-        <v>2107</v>
+        <v>2075</v>
       </c>
       <c r="Q619">
         <v>0.85</v>
@@ -74612,7 +74612,7 @@
         <v>2490</v>
       </c>
       <c r="P620" t="s">
-        <v>2103</v>
+        <v>2083</v>
       </c>
       <c r="Q620">
         <v>0.85</v>
@@ -74626,7 +74626,7 @@
         <v>2491</v>
       </c>
       <c r="P621" t="s">
-        <v>2051</v>
+        <v>2106</v>
       </c>
       <c r="Q621">
         <v>0.85</v>
@@ -74640,7 +74640,7 @@
         <v>2492</v>
       </c>
       <c r="P622" t="s">
-        <v>2100</v>
+        <v>2058</v>
       </c>
       <c r="Q622">
         <v>0.85</v>
@@ -74654,7 +74654,7 @@
         <v>2493</v>
       </c>
       <c r="P623" t="s">
-        <v>2051</v>
+        <v>2083</v>
       </c>
       <c r="Q623">
         <v>0.85</v>
@@ -74668,7 +74668,7 @@
         <v>2494</v>
       </c>
       <c r="P624" t="s">
-        <v>2071</v>
+        <v>2088</v>
       </c>
       <c r="Q624">
         <v>0.85</v>
@@ -74682,7 +74682,7 @@
         <v>2495</v>
       </c>
       <c r="P625" t="s">
-        <v>2055</v>
+        <v>2067</v>
       </c>
       <c r="Q625">
         <v>0.85</v>
@@ -74696,7 +74696,7 @@
         <v>2496</v>
       </c>
       <c r="P626" t="s">
-        <v>2093</v>
+        <v>2088</v>
       </c>
       <c r="Q626">
         <v>0.85</v>
@@ -74710,7 +74710,7 @@
         <v>2497</v>
       </c>
       <c r="P627" t="s">
-        <v>2106</v>
+        <v>2065</v>
       </c>
       <c r="Q627">
         <v>0.85</v>
@@ -74724,7 +74724,7 @@
         <v>2498</v>
       </c>
       <c r="P628" t="s">
-        <v>2087</v>
+        <v>2060</v>
       </c>
       <c r="Q628">
         <v>0.85</v>
@@ -74738,7 +74738,7 @@
         <v>2499</v>
       </c>
       <c r="P629" t="s">
-        <v>2089</v>
+        <v>2076</v>
       </c>
       <c r="Q629">
         <v>0.85</v>
@@ -74752,7 +74752,7 @@
         <v>2500</v>
       </c>
       <c r="P630" t="s">
-        <v>2084</v>
+        <v>2093</v>
       </c>
       <c r="Q630">
         <v>0.85</v>
@@ -74780,10 +74780,10 @@
         <v>2502</v>
       </c>
       <c r="P632" t="s">
-        <v>2089</v>
+        <v>2058</v>
       </c>
       <c r="Q632">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="633" spans="14:17" x14ac:dyDescent="0.45">
@@ -74794,7 +74794,7 @@
         <v>2503</v>
       </c>
       <c r="P633" t="s">
-        <v>2051</v>
+        <v>2071</v>
       </c>
       <c r="Q633">
         <v>0.85</v>
@@ -74808,10 +74808,10 @@
         <v>2504</v>
       </c>
       <c r="P634" t="s">
-        <v>2077</v>
+        <v>2103</v>
       </c>
       <c r="Q634">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="635" spans="14:17" x14ac:dyDescent="0.45">
@@ -74822,7 +74822,7 @@
         <v>2505</v>
       </c>
       <c r="P635" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="Q635">
         <v>0.85</v>
@@ -74836,7 +74836,7 @@
         <v>2506</v>
       </c>
       <c r="P636" t="s">
-        <v>2087</v>
+        <v>2083</v>
       </c>
       <c r="Q636">
         <v>0.85</v>
@@ -74850,7 +74850,7 @@
         <v>2507</v>
       </c>
       <c r="P637" t="s">
-        <v>2080</v>
+        <v>2098</v>
       </c>
       <c r="Q637">
         <v>0.85</v>
@@ -74864,10 +74864,10 @@
         <v>2508</v>
       </c>
       <c r="P638" t="s">
-        <v>2089</v>
+        <v>2106</v>
       </c>
       <c r="Q638">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="639" spans="14:17" x14ac:dyDescent="0.45">
@@ -74878,7 +74878,7 @@
         <v>2509</v>
       </c>
       <c r="P639" t="s">
-        <v>2081</v>
+        <v>2065</v>
       </c>
       <c r="Q639">
         <v>0.85</v>
@@ -74892,7 +74892,7 @@
         <v>2510</v>
       </c>
       <c r="P640" t="s">
-        <v>2082</v>
+        <v>2098</v>
       </c>
       <c r="Q640">
         <v>0.85</v>
@@ -74906,7 +74906,7 @@
         <v>2511</v>
       </c>
       <c r="P641" t="s">
-        <v>2106</v>
+        <v>2081</v>
       </c>
       <c r="Q641">
         <v>0.85</v>
@@ -74920,7 +74920,7 @@
         <v>2512</v>
       </c>
       <c r="P642" t="s">
-        <v>2083</v>
+        <v>2073</v>
       </c>
       <c r="Q642">
         <v>0.85</v>
@@ -74934,7 +74934,7 @@
         <v>2513</v>
       </c>
       <c r="P643" t="s">
-        <v>2060</v>
+        <v>2054</v>
       </c>
       <c r="Q643">
         <v>0.85</v>
@@ -74962,10 +74962,10 @@
         <v>2515</v>
       </c>
       <c r="P645" t="s">
-        <v>2071</v>
+        <v>2065</v>
       </c>
       <c r="Q645">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="646" spans="14:17" x14ac:dyDescent="0.45">
@@ -74976,7 +74976,7 @@
         <v>2516</v>
       </c>
       <c r="P646" t="s">
-        <v>2103</v>
+        <v>2083</v>
       </c>
       <c r="Q646">
         <v>0.85</v>
@@ -74990,7 +74990,7 @@
         <v>2517</v>
       </c>
       <c r="P647" t="s">
-        <v>2093</v>
+        <v>2076</v>
       </c>
       <c r="Q647">
         <v>0.85</v>
@@ -75004,7 +75004,7 @@
         <v>2518</v>
       </c>
       <c r="P648" t="s">
-        <v>2051</v>
+        <v>2089</v>
       </c>
       <c r="Q648">
         <v>0.85</v>
@@ -75018,7 +75018,7 @@
         <v>2519</v>
       </c>
       <c r="P649" t="s">
-        <v>2098</v>
+        <v>2080</v>
       </c>
       <c r="Q649">
         <v>0.85</v>
@@ -75032,7 +75032,7 @@
         <v>2520</v>
       </c>
       <c r="P650" t="s">
-        <v>2076</v>
+        <v>2095</v>
       </c>
       <c r="Q650">
         <v>0.85</v>
@@ -75046,7 +75046,7 @@
         <v>2521</v>
       </c>
       <c r="P651" t="s">
-        <v>2076</v>
+        <v>2106</v>
       </c>
       <c r="Q651">
         <v>0.85</v>
@@ -75060,7 +75060,7 @@
         <v>2522</v>
       </c>
       <c r="P652" t="s">
-        <v>2083</v>
+        <v>2094</v>
       </c>
       <c r="Q652">
         <v>0.85</v>
@@ -75074,7 +75074,7 @@
         <v>2523</v>
       </c>
       <c r="P653" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="Q653">
         <v>0.85</v>
@@ -75088,7 +75088,7 @@
         <v>2524</v>
       </c>
       <c r="P654" t="s">
-        <v>2077</v>
+        <v>2094</v>
       </c>
       <c r="Q654">
         <v>0.85</v>
@@ -75102,7 +75102,7 @@
         <v>2525</v>
       </c>
       <c r="P655" t="s">
-        <v>2080</v>
+        <v>2065</v>
       </c>
       <c r="Q655">
         <v>0.85</v>
@@ -75116,7 +75116,7 @@
         <v>2526</v>
       </c>
       <c r="P656" t="s">
-        <v>2076</v>
+        <v>2101</v>
       </c>
       <c r="Q656">
         <v>0.85</v>
@@ -75130,7 +75130,7 @@
         <v>2527</v>
       </c>
       <c r="P657" t="s">
-        <v>2076</v>
+        <v>2088</v>
       </c>
       <c r="Q657">
         <v>0.85</v>
@@ -75144,7 +75144,7 @@
         <v>2528</v>
       </c>
       <c r="P658" t="s">
-        <v>2063</v>
+        <v>2107</v>
       </c>
       <c r="Q658">
         <v>0.85</v>
@@ -75158,7 +75158,7 @@
         <v>2529</v>
       </c>
       <c r="P659" t="s">
-        <v>2059</v>
+        <v>2064</v>
       </c>
       <c r="Q659">
         <v>0.85</v>
@@ -75172,7 +75172,7 @@
         <v>2530</v>
       </c>
       <c r="P660" t="s">
-        <v>2108</v>
+        <v>2083</v>
       </c>
       <c r="Q660">
         <v>0.85</v>
@@ -75186,7 +75186,7 @@
         <v>2531</v>
       </c>
       <c r="P661" t="s">
-        <v>2086</v>
+        <v>2106</v>
       </c>
       <c r="Q661">
         <v>0.85</v>
@@ -75200,7 +75200,7 @@
         <v>2532</v>
       </c>
       <c r="P662" t="s">
-        <v>2051</v>
+        <v>2069</v>
       </c>
       <c r="Q662">
         <v>0.85</v>
@@ -75214,7 +75214,7 @@
         <v>2533</v>
       </c>
       <c r="P663" t="s">
-        <v>2051</v>
+        <v>2104</v>
       </c>
       <c r="Q663">
         <v>0.85</v>
@@ -75228,7 +75228,7 @@
         <v>2534</v>
       </c>
       <c r="P664" t="s">
-        <v>2060</v>
+        <v>2089</v>
       </c>
       <c r="Q664">
         <v>0.85</v>
@@ -75242,7 +75242,7 @@
         <v>2535</v>
       </c>
       <c r="P665" t="s">
-        <v>2077</v>
+        <v>2094</v>
       </c>
       <c r="Q665">
         <v>0.85</v>
@@ -75256,7 +75256,7 @@
         <v>2536</v>
       </c>
       <c r="P666" t="s">
-        <v>2069</v>
+        <v>2089</v>
       </c>
       <c r="Q666">
         <v>0.85</v>
@@ -75270,7 +75270,7 @@
         <v>2537</v>
       </c>
       <c r="P667" t="s">
-        <v>2097</v>
+        <v>2103</v>
       </c>
       <c r="Q667">
         <v>0.85</v>
@@ -75284,7 +75284,7 @@
         <v>2538</v>
       </c>
       <c r="P668" t="s">
-        <v>2101</v>
+        <v>2051</v>
       </c>
       <c r="Q668">
         <v>0.85</v>
@@ -75298,7 +75298,7 @@
         <v>2539</v>
       </c>
       <c r="P669" t="s">
-        <v>2103</v>
+        <v>2084</v>
       </c>
       <c r="Q669">
         <v>0.85</v>
@@ -75312,7 +75312,7 @@
         <v>2540</v>
       </c>
       <c r="P670" t="s">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="Q670">
         <v>0.85</v>
@@ -75326,7 +75326,7 @@
         <v>2541</v>
       </c>
       <c r="P671" t="s">
-        <v>2075</v>
+        <v>2087</v>
       </c>
       <c r="Q671">
         <v>0.85</v>
@@ -75340,7 +75340,7 @@
         <v>2542</v>
       </c>
       <c r="P672" t="s">
-        <v>2082</v>
+        <v>2077</v>
       </c>
       <c r="Q672">
         <v>0.85</v>
@@ -75354,10 +75354,10 @@
         <v>2543</v>
       </c>
       <c r="P673" t="s">
-        <v>2101</v>
+        <v>2063</v>
       </c>
       <c r="Q673">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="674" spans="14:17" x14ac:dyDescent="0.45">
@@ -75368,10 +75368,10 @@
         <v>2544</v>
       </c>
       <c r="P674" t="s">
-        <v>2077</v>
+        <v>2053</v>
       </c>
       <c r="Q674">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="675" spans="14:17" x14ac:dyDescent="0.45">
@@ -75382,10 +75382,10 @@
         <v>2545</v>
       </c>
       <c r="P675" t="s">
-        <v>2104</v>
+        <v>2063</v>
       </c>
       <c r="Q675">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="676" spans="14:17" x14ac:dyDescent="0.45">
@@ -75396,7 +75396,7 @@
         <v>2546</v>
       </c>
       <c r="P676" t="s">
-        <v>2075</v>
+        <v>2099</v>
       </c>
       <c r="Q676">
         <v>0.85</v>
@@ -75410,7 +75410,7 @@
         <v>2547</v>
       </c>
       <c r="P677" t="s">
-        <v>2095</v>
+        <v>2101</v>
       </c>
       <c r="Q677">
         <v>0.85</v>
@@ -75424,7 +75424,7 @@
         <v>2548</v>
       </c>
       <c r="P678" t="s">
-        <v>2098</v>
+        <v>2102</v>
       </c>
       <c r="Q678">
         <v>0.85</v>
@@ -75438,7 +75438,7 @@
         <v>2549</v>
       </c>
       <c r="P679" t="s">
-        <v>2094</v>
+        <v>2082</v>
       </c>
       <c r="Q679">
         <v>0.85</v>
@@ -75452,7 +75452,7 @@
         <v>2550</v>
       </c>
       <c r="P680" t="s">
-        <v>2086</v>
+        <v>2075</v>
       </c>
       <c r="Q680">
         <v>0.85</v>
@@ -75466,7 +75466,7 @@
         <v>2551</v>
       </c>
       <c r="P681" t="s">
-        <v>2098</v>
+        <v>2051</v>
       </c>
       <c r="Q681">
         <v>0.85</v>
@@ -75480,7 +75480,7 @@
         <v>2552</v>
       </c>
       <c r="P682" t="s">
-        <v>2087</v>
+        <v>2098</v>
       </c>
       <c r="Q682">
         <v>0.85</v>
@@ -75508,7 +75508,7 @@
         <v>2554</v>
       </c>
       <c r="P684" t="s">
-        <v>2101</v>
+        <v>2094</v>
       </c>
       <c r="Q684">
         <v>0.85</v>
@@ -75522,7 +75522,7 @@
         <v>2555</v>
       </c>
       <c r="P685" t="s">
-        <v>2102</v>
+        <v>2098</v>
       </c>
       <c r="Q685">
         <v>0.85</v>
@@ -75536,7 +75536,7 @@
         <v>2556</v>
       </c>
       <c r="P686" t="s">
-        <v>2082</v>
+        <v>2058</v>
       </c>
       <c r="Q686">
         <v>0.85</v>
@@ -75550,7 +75550,7 @@
         <v>2557</v>
       </c>
       <c r="P687" t="s">
-        <v>2065</v>
+        <v>2089</v>
       </c>
       <c r="Q687">
         <v>0.85</v>
@@ -75564,7 +75564,7 @@
         <v>2558</v>
       </c>
       <c r="P688" t="s">
-        <v>2093</v>
+        <v>2108</v>
       </c>
       <c r="Q688">
         <v>0.85</v>
@@ -75578,7 +75578,7 @@
         <v>2559</v>
       </c>
       <c r="P689" t="s">
-        <v>2053</v>
+        <v>2081</v>
       </c>
       <c r="Q689">
         <v>0.85</v>
@@ -75592,7 +75592,7 @@
         <v>2560</v>
       </c>
       <c r="P690" t="s">
-        <v>2089</v>
+        <v>2065</v>
       </c>
       <c r="Q690">
         <v>0.85</v>
@@ -75606,7 +75606,7 @@
         <v>2561</v>
       </c>
       <c r="P691" t="s">
-        <v>2067</v>
+        <v>2093</v>
       </c>
       <c r="Q691">
         <v>0.85</v>
@@ -75620,10 +75620,10 @@
         <v>2562</v>
       </c>
       <c r="P692" t="s">
-        <v>2070</v>
+        <v>2077</v>
       </c>
       <c r="Q692">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="693" spans="14:17" x14ac:dyDescent="0.45">
@@ -75634,10 +75634,10 @@
         <v>2563</v>
       </c>
       <c r="P693" t="s">
-        <v>2070</v>
+        <v>2082</v>
       </c>
       <c r="Q693">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="694" spans="14:17" x14ac:dyDescent="0.45">
@@ -75648,7 +75648,7 @@
         <v>2564</v>
       </c>
       <c r="P694" t="s">
-        <v>2067</v>
+        <v>2087</v>
       </c>
       <c r="Q694">
         <v>0.85</v>
@@ -75662,7 +75662,7 @@
         <v>2565</v>
       </c>
       <c r="P695" t="s">
-        <v>2067</v>
+        <v>2103</v>
       </c>
       <c r="Q695">
         <v>0.85</v>
@@ -75676,7 +75676,7 @@
         <v>2566</v>
       </c>
       <c r="P696" t="s">
-        <v>2082</v>
+        <v>2055</v>
       </c>
       <c r="Q696">
         <v>0.85</v>
@@ -75690,7 +75690,7 @@
         <v>2567</v>
       </c>
       <c r="P697" t="s">
-        <v>2055</v>
+        <v>2087</v>
       </c>
       <c r="Q697">
         <v>0.85</v>
@@ -75704,7 +75704,7 @@
         <v>2568</v>
       </c>
       <c r="P698" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="Q698">
         <v>0.85</v>
@@ -75718,7 +75718,7 @@
         <v>2569</v>
       </c>
       <c r="P699" t="s">
-        <v>2103</v>
+        <v>2107</v>
       </c>
       <c r="Q699">
         <v>0.85</v>
@@ -75732,7 +75732,7 @@
         <v>2570</v>
       </c>
       <c r="P700" t="s">
-        <v>2086</v>
+        <v>2097</v>
       </c>
       <c r="Q700">
         <v>0.85</v>
@@ -75746,7 +75746,7 @@
         <v>2571</v>
       </c>
       <c r="P701" t="s">
-        <v>2097</v>
+        <v>2104</v>
       </c>
       <c r="Q701">
         <v>0.85</v>
@@ -75760,7 +75760,7 @@
         <v>2572</v>
       </c>
       <c r="P702" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="Q702">
         <v>0.85</v>
@@ -75774,7 +75774,7 @@
         <v>2573</v>
       </c>
       <c r="P703" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="Q703">
         <v>0.85</v>
@@ -75788,7 +75788,7 @@
         <v>2574</v>
       </c>
       <c r="P704" t="s">
-        <v>2099</v>
+        <v>2081</v>
       </c>
       <c r="Q704">
         <v>0.85</v>
@@ -75802,7 +75802,7 @@
         <v>2575</v>
       </c>
       <c r="P705" t="s">
-        <v>2078</v>
+        <v>2058</v>
       </c>
       <c r="Q705">
         <v>0.85</v>
@@ -75816,7 +75816,7 @@
         <v>2576</v>
       </c>
       <c r="P706" t="s">
-        <v>2089</v>
+        <v>2059</v>
       </c>
       <c r="Q706">
         <v>0.85</v>
@@ -75830,7 +75830,7 @@
         <v>2577</v>
       </c>
       <c r="P707" t="s">
-        <v>2058</v>
+        <v>2102</v>
       </c>
       <c r="Q707">
         <v>0.85</v>
@@ -75844,7 +75844,7 @@
         <v>2578</v>
       </c>
       <c r="P708" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
       <c r="Q708">
         <v>0.85</v>
@@ -75858,7 +75858,7 @@
         <v>2579</v>
       </c>
       <c r="P709" t="s">
-        <v>2081</v>
+        <v>2051</v>
       </c>
       <c r="Q709">
         <v>0.85</v>
@@ -75872,7 +75872,7 @@
         <v>2580</v>
       </c>
       <c r="P710" t="s">
-        <v>2103</v>
+        <v>2067</v>
       </c>
       <c r="Q710">
         <v>0.85</v>
@@ -75886,7 +75886,7 @@
         <v>2581</v>
       </c>
       <c r="P711" t="s">
-        <v>2095</v>
+        <v>2067</v>
       </c>
       <c r="Q711">
         <v>0.85</v>
@@ -75900,7 +75900,7 @@
         <v>2582</v>
       </c>
       <c r="P712" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="Q712">
         <v>0.85</v>
@@ -75914,7 +75914,7 @@
         <v>2583</v>
       </c>
       <c r="P713" t="s">
-        <v>2058</v>
+        <v>2089</v>
       </c>
       <c r="Q713">
         <v>0.85</v>
@@ -75928,7 +75928,7 @@
         <v>2584</v>
       </c>
       <c r="P714" t="s">
-        <v>2059</v>
+        <v>2070</v>
       </c>
       <c r="Q714">
         <v>0.85</v>
@@ -75942,7 +75942,7 @@
         <v>2585</v>
       </c>
       <c r="P715" t="s">
-        <v>2098</v>
+        <v>2070</v>
       </c>
       <c r="Q715">
         <v>0.85</v>
@@ -75956,7 +75956,7 @@
         <v>2586</v>
       </c>
       <c r="P716" t="s">
-        <v>2051</v>
+        <v>2096</v>
       </c>
       <c r="Q716">
         <v>0.85</v>
@@ -75970,7 +75970,7 @@
         <v>2587</v>
       </c>
       <c r="P717" t="s">
-        <v>2051</v>
+        <v>2075</v>
       </c>
       <c r="Q717">
         <v>0.85</v>
@@ -75987,7 +75987,7 @@
         <v>2098</v>
       </c>
       <c r="Q718">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="719" spans="14:17" x14ac:dyDescent="0.45">
@@ -75998,7 +75998,7 @@
         <v>2589</v>
       </c>
       <c r="P719" t="s">
-        <v>2102</v>
+        <v>2065</v>
       </c>
       <c r="Q719">
         <v>0.85</v>
@@ -76012,10 +76012,10 @@
         <v>2590</v>
       </c>
       <c r="P720" t="s">
-        <v>2063</v>
+        <v>2106</v>
       </c>
       <c r="Q720">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="721" spans="14:17" x14ac:dyDescent="0.45">
@@ -76026,10 +76026,10 @@
         <v>2591</v>
       </c>
       <c r="P721" t="s">
-        <v>2077</v>
+        <v>2103</v>
       </c>
       <c r="Q721">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="722" spans="14:17" x14ac:dyDescent="0.45">
@@ -76040,7 +76040,7 @@
         <v>2592</v>
       </c>
       <c r="P722" t="s">
-        <v>2096</v>
+        <v>2089</v>
       </c>
       <c r="Q722">
         <v>0.85</v>
@@ -76054,7 +76054,7 @@
         <v>2593</v>
       </c>
       <c r="P723" t="s">
-        <v>2075</v>
+        <v>2052</v>
       </c>
       <c r="Q723">
         <v>0.85</v>
@@ -76068,10 +76068,10 @@
         <v>2594</v>
       </c>
       <c r="P724" t="s">
-        <v>2063</v>
+        <v>2051</v>
       </c>
       <c r="Q724">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="725" spans="14:17" x14ac:dyDescent="0.45">
@@ -76082,10 +76082,10 @@
         <v>2595</v>
       </c>
       <c r="P725" t="s">
-        <v>2053</v>
+        <v>2103</v>
       </c>
       <c r="Q725">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="726" spans="14:17" x14ac:dyDescent="0.45">
@@ -76096,10 +76096,10 @@
         <v>2596</v>
       </c>
       <c r="P726" t="s">
-        <v>2082</v>
+        <v>2071</v>
       </c>
       <c r="Q726">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="727" spans="14:17" x14ac:dyDescent="0.45">
@@ -76110,7 +76110,7 @@
         <v>2597</v>
       </c>
       <c r="P727" t="s">
-        <v>2104</v>
+        <v>2058</v>
       </c>
       <c r="Q727">
         <v>0.95</v>
@@ -76124,7 +76124,7 @@
         <v>2598</v>
       </c>
       <c r="P728" t="s">
-        <v>2095</v>
+        <v>2086</v>
       </c>
       <c r="Q728">
         <v>0.85</v>
@@ -76138,7 +76138,7 @@
         <v>2599</v>
       </c>
       <c r="P729" t="s">
-        <v>2108</v>
+        <v>2103</v>
       </c>
       <c r="Q729">
         <v>0.85</v>
@@ -76152,7 +76152,7 @@
         <v>2600</v>
       </c>
       <c r="P730" t="s">
-        <v>2076</v>
+        <v>2083</v>
       </c>
       <c r="Q730">
         <v>0.85</v>
@@ -76166,7 +76166,7 @@
         <v>2601</v>
       </c>
       <c r="P731" t="s">
-        <v>2051</v>
+        <v>2089</v>
       </c>
       <c r="Q731">
         <v>0.85</v>
@@ -76194,7 +76194,7 @@
         <v>2603</v>
       </c>
       <c r="P733" t="s">
-        <v>2106</v>
+        <v>2069</v>
       </c>
       <c r="Q733">
         <v>0.85</v>
@@ -76208,7 +76208,7 @@
         <v>2604</v>
       </c>
       <c r="P734" t="s">
-        <v>2076</v>
+        <v>2065</v>
       </c>
       <c r="Q734">
         <v>0.85</v>
@@ -76222,7 +76222,7 @@
         <v>2605</v>
       </c>
       <c r="P735" t="s">
-        <v>2094</v>
+        <v>2067</v>
       </c>
       <c r="Q735">
         <v>0.85</v>
@@ -76236,7 +76236,7 @@
         <v>2606</v>
       </c>
       <c r="P736" t="s">
-        <v>2097</v>
+        <v>2083</v>
       </c>
       <c r="Q736">
         <v>0.85</v>
@@ -76250,7 +76250,7 @@
         <v>2607</v>
       </c>
       <c r="P737" t="s">
-        <v>2076</v>
+        <v>2061</v>
       </c>
       <c r="Q737">
         <v>0.85</v>
@@ -76264,7 +76264,7 @@
         <v>2608</v>
       </c>
       <c r="P738" t="s">
-        <v>2060</v>
+        <v>2055</v>
       </c>
       <c r="Q738">
         <v>0.85</v>
@@ -76278,10 +76278,10 @@
         <v>2609</v>
       </c>
       <c r="P739" t="s">
-        <v>2083</v>
+        <v>2051</v>
       </c>
       <c r="Q739">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="740" spans="14:17" x14ac:dyDescent="0.45">
@@ -76306,7 +76306,7 @@
         <v>2611</v>
       </c>
       <c r="P741" t="s">
-        <v>2104</v>
+        <v>2093</v>
       </c>
       <c r="Q741">
         <v>0.85</v>
@@ -76320,7 +76320,7 @@
         <v>2612</v>
       </c>
       <c r="P742" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
       <c r="Q742">
         <v>0.85</v>
@@ -76334,7 +76334,7 @@
         <v>2613</v>
       </c>
       <c r="P743" t="s">
-        <v>2078</v>
+        <v>2069</v>
       </c>
       <c r="Q743">
         <v>0.85</v>
@@ -76348,7 +76348,7 @@
         <v>2614</v>
       </c>
       <c r="P744" t="s">
-        <v>2084</v>
+        <v>2078</v>
       </c>
       <c r="Q744">
         <v>0.85</v>
@@ -76362,7 +76362,7 @@
         <v>2615</v>
       </c>
       <c r="P745" t="s">
-        <v>2060</v>
+        <v>2080</v>
       </c>
       <c r="Q745">
         <v>0.85</v>
@@ -76376,7 +76376,7 @@
         <v>2616</v>
       </c>
       <c r="P746" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="Q746">
         <v>0.85</v>
@@ -76390,7 +76390,7 @@
         <v>2617</v>
       </c>
       <c r="P747" t="s">
-        <v>2106</v>
+        <v>2083</v>
       </c>
       <c r="Q747">
         <v>0.85</v>
@@ -76404,7 +76404,7 @@
         <v>2618</v>
       </c>
       <c r="P748" t="s">
-        <v>2055</v>
+        <v>2059</v>
       </c>
       <c r="Q748">
         <v>0.85</v>
@@ -76418,7 +76418,7 @@
         <v>2619</v>
       </c>
       <c r="P749" t="s">
-        <v>2089</v>
+        <v>2079</v>
       </c>
       <c r="Q749">
         <v>0.85</v>
@@ -76432,7 +76432,7 @@
         <v>2620</v>
       </c>
       <c r="P750" t="s">
-        <v>2087</v>
+        <v>2096</v>
       </c>
       <c r="Q750">
         <v>0.85</v>
@@ -76446,7 +76446,7 @@
         <v>2621</v>
       </c>
       <c r="P751" t="s">
-        <v>2073</v>
+        <v>2091</v>
       </c>
       <c r="Q751">
         <v>0.85</v>
@@ -76460,7 +76460,7 @@
         <v>2622</v>
       </c>
       <c r="P752" t="s">
-        <v>2094</v>
+        <v>2056</v>
       </c>
       <c r="Q752">
         <v>0.85</v>
@@ -76474,7 +76474,7 @@
         <v>2623</v>
       </c>
       <c r="P753" t="s">
-        <v>2069</v>
+        <v>2060</v>
       </c>
       <c r="Q753">
         <v>0.85</v>
@@ -76488,7 +76488,7 @@
         <v>2624</v>
       </c>
       <c r="P754" t="s">
-        <v>2051</v>
+        <v>2076</v>
       </c>
       <c r="Q754">
         <v>0.85</v>
@@ -76502,7 +76502,7 @@
         <v>2625</v>
       </c>
       <c r="P755" t="s">
-        <v>2063</v>
+        <v>2103</v>
       </c>
       <c r="Q755">
         <v>0.85</v>
@@ -76516,7 +76516,7 @@
         <v>2626</v>
       </c>
       <c r="P756" t="s">
-        <v>2057</v>
+        <v>2082</v>
       </c>
       <c r="Q756">
         <v>0.85</v>
@@ -76530,10 +76530,10 @@
         <v>2627</v>
       </c>
       <c r="P757" t="s">
-        <v>2062</v>
+        <v>2089</v>
       </c>
       <c r="Q757">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="758" spans="14:17" x14ac:dyDescent="0.45">
@@ -76544,7 +76544,7 @@
         <v>2628</v>
       </c>
       <c r="P758" t="s">
-        <v>2065</v>
+        <v>2075</v>
       </c>
       <c r="Q758">
         <v>0.85</v>
@@ -76572,7 +76572,7 @@
         <v>2630</v>
       </c>
       <c r="P760" t="s">
-        <v>2076</v>
+        <v>2086</v>
       </c>
       <c r="Q760">
         <v>0.85</v>
@@ -76586,7 +76586,7 @@
         <v>2631</v>
       </c>
       <c r="P761" t="s">
-        <v>2076</v>
+        <v>2081</v>
       </c>
       <c r="Q761">
         <v>0.85</v>
@@ -76600,7 +76600,7 @@
         <v>2632</v>
       </c>
       <c r="P762" t="s">
-        <v>2058</v>
+        <v>2089</v>
       </c>
       <c r="Q762">
         <v>0.85</v>
@@ -76614,7 +76614,7 @@
         <v>2633</v>
       </c>
       <c r="P763" t="s">
-        <v>2081</v>
+        <v>2103</v>
       </c>
       <c r="Q763">
         <v>0.85</v>
@@ -76628,7 +76628,7 @@
         <v>2634</v>
       </c>
       <c r="P764" t="s">
-        <v>2084</v>
+        <v>2096</v>
       </c>
       <c r="Q764">
         <v>0.85</v>
@@ -76642,7 +76642,7 @@
         <v>2635</v>
       </c>
       <c r="P765" t="s">
-        <v>2081</v>
+        <v>2089</v>
       </c>
       <c r="Q765">
         <v>0.85</v>
@@ -76656,10 +76656,10 @@
         <v>2636</v>
       </c>
       <c r="P766" t="s">
-        <v>2071</v>
+        <v>2055</v>
       </c>
       <c r="Q766">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="767" spans="14:17" x14ac:dyDescent="0.45">
@@ -76670,7 +76670,7 @@
         <v>2637</v>
       </c>
       <c r="P767" t="s">
-        <v>2088</v>
+        <v>2095</v>
       </c>
       <c r="Q767">
         <v>0.85</v>
@@ -76684,7 +76684,7 @@
         <v>2638</v>
       </c>
       <c r="P768" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
       <c r="Q768">
         <v>0.85</v>
@@ -76698,10 +76698,10 @@
         <v>2639</v>
       </c>
       <c r="P769" t="s">
-        <v>2051</v>
+        <v>2105</v>
       </c>
       <c r="Q769">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="770" spans="14:17" x14ac:dyDescent="0.45">
@@ -76712,7 +76712,7 @@
         <v>2640</v>
       </c>
       <c r="P770" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
       <c r="Q770">
         <v>0.85</v>
@@ -76726,7 +76726,7 @@
         <v>2641</v>
       </c>
       <c r="P771" t="s">
-        <v>2091</v>
+        <v>2108</v>
       </c>
       <c r="Q771">
         <v>0.85</v>
@@ -76740,7 +76740,7 @@
         <v>2642</v>
       </c>
       <c r="P772" t="s">
-        <v>2083</v>
+        <v>2076</v>
       </c>
       <c r="Q772">
         <v>0.85</v>
@@ -76754,7 +76754,7 @@
         <v>2643</v>
       </c>
       <c r="P773" t="s">
-        <v>2060</v>
+        <v>2064</v>
       </c>
       <c r="Q773">
         <v>0.85</v>
@@ -76768,7 +76768,7 @@
         <v>2644</v>
       </c>
       <c r="P774" t="s">
-        <v>2059</v>
+        <v>2080</v>
       </c>
       <c r="Q774">
         <v>0.85</v>
@@ -76782,7 +76782,7 @@
         <v>2645</v>
       </c>
       <c r="P775" t="s">
-        <v>2060</v>
+        <v>2056</v>
       </c>
       <c r="Q775">
         <v>0.85</v>
@@ -76796,7 +76796,7 @@
         <v>2646</v>
       </c>
       <c r="P776" t="s">
-        <v>2076</v>
+        <v>2060</v>
       </c>
       <c r="Q776">
         <v>0.85</v>
@@ -76810,7 +76810,7 @@
         <v>2647</v>
       </c>
       <c r="P777" t="s">
-        <v>2103</v>
+        <v>2068</v>
       </c>
       <c r="Q777">
         <v>0.85</v>
@@ -76824,7 +76824,7 @@
         <v>2648</v>
       </c>
       <c r="P778" t="s">
-        <v>2082</v>
+        <v>2053</v>
       </c>
       <c r="Q778">
         <v>0.85</v>
@@ -76838,7 +76838,7 @@
         <v>2649</v>
       </c>
       <c r="P779" t="s">
-        <v>2056</v>
+        <v>2086</v>
       </c>
       <c r="Q779">
         <v>0.85</v>
@@ -76852,7 +76852,7 @@
         <v>2650</v>
       </c>
       <c r="P780" t="s">
-        <v>2052</v>
+        <v>2101</v>
       </c>
       <c r="Q780">
         <v>0.85</v>
@@ -76866,7 +76866,7 @@
         <v>2651</v>
       </c>
       <c r="P781" t="s">
-        <v>2086</v>
+        <v>2060</v>
       </c>
       <c r="Q781">
         <v>0.85</v>
@@ -76880,7 +76880,7 @@
         <v>2652</v>
       </c>
       <c r="P782" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="Q782">
         <v>0.85</v>
@@ -76894,7 +76894,7 @@
         <v>2653</v>
       </c>
       <c r="P783" t="s">
-        <v>2093</v>
+        <v>2089</v>
       </c>
       <c r="Q783">
         <v>0.85</v>
@@ -76908,7 +76908,7 @@
         <v>2654</v>
       </c>
       <c r="P784" t="s">
-        <v>2106</v>
+        <v>2071</v>
       </c>
       <c r="Q784">
         <v>0.85</v>
@@ -76922,7 +76922,7 @@
         <v>2655</v>
       </c>
       <c r="P785" t="s">
-        <v>2083</v>
+        <v>2076</v>
       </c>
       <c r="Q785">
         <v>0.85</v>
@@ -76936,7 +76936,7 @@
         <v>2656</v>
       </c>
       <c r="P786" t="s">
-        <v>2080</v>
+        <v>2106</v>
       </c>
       <c r="Q786">
         <v>0.85</v>
@@ -76950,7 +76950,7 @@
         <v>2657</v>
       </c>
       <c r="P787" t="s">
-        <v>2056</v>
+        <v>2103</v>
       </c>
       <c r="Q787">
         <v>0.85</v>
@@ -76964,7 +76964,7 @@
         <v>2658</v>
       </c>
       <c r="P788" t="s">
-        <v>2089</v>
+        <v>2100</v>
       </c>
       <c r="Q788">
         <v>0.85</v>
@@ -76978,7 +76978,7 @@
         <v>2659</v>
       </c>
       <c r="P789" t="s">
-        <v>2103</v>
+        <v>2089</v>
       </c>
       <c r="Q789">
         <v>0.85</v>
@@ -77006,7 +77006,7 @@
         <v>2661</v>
       </c>
       <c r="P791" t="s">
-        <v>2105</v>
+        <v>2065</v>
       </c>
       <c r="Q791">
         <v>0.85</v>
@@ -77020,7 +77020,7 @@
         <v>2662</v>
       </c>
       <c r="P792" t="s">
-        <v>2090</v>
+        <v>2103</v>
       </c>
       <c r="Q792">
         <v>0.85</v>
@@ -77034,7 +77034,7 @@
         <v>2663</v>
       </c>
       <c r="P793" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
       <c r="Q793">
         <v>0.85</v>
@@ -77048,7 +77048,7 @@
         <v>2664</v>
       </c>
       <c r="P794" t="s">
-        <v>2108</v>
+        <v>2071</v>
       </c>
       <c r="Q794">
         <v>0.85</v>
@@ -77062,7 +77062,7 @@
         <v>2665</v>
       </c>
       <c r="P795" t="s">
-        <v>2076</v>
+        <v>2093</v>
       </c>
       <c r="Q795">
         <v>0.85</v>
@@ -77076,7 +77076,7 @@
         <v>2666</v>
       </c>
       <c r="P796" t="s">
-        <v>2064</v>
+        <v>2053</v>
       </c>
       <c r="Q796">
         <v>0.85</v>
@@ -77090,7 +77090,7 @@
         <v>2667</v>
       </c>
       <c r="P797" t="s">
-        <v>2080</v>
+        <v>2093</v>
       </c>
       <c r="Q797">
         <v>0.85</v>
@@ -77104,7 +77104,7 @@
         <v>2668</v>
       </c>
       <c r="P798" t="s">
-        <v>2079</v>
+        <v>2051</v>
       </c>
       <c r="Q798">
         <v>0.85</v>
@@ -77118,7 +77118,7 @@
         <v>2669</v>
       </c>
       <c r="P799" t="s">
-        <v>2055</v>
+        <v>2063</v>
       </c>
       <c r="Q799">
         <v>0.85</v>
@@ -77132,7 +77132,7 @@
         <v>2670</v>
       </c>
       <c r="P800" t="s">
-        <v>2095</v>
+        <v>2055</v>
       </c>
       <c r="Q800">
         <v>0.85</v>
@@ -77146,7 +77146,7 @@
         <v>2671</v>
       </c>
       <c r="P801" t="s">
-        <v>2106</v>
+        <v>2090</v>
       </c>
       <c r="Q801">
         <v>0.85</v>
@@ -77160,7 +77160,7 @@
         <v>2672</v>
       </c>
       <c r="P802" t="s">
-        <v>2089</v>
+        <v>2081</v>
       </c>
       <c r="Q802">
         <v>0.95</v>
@@ -77174,7 +77174,7 @@
         <v>2673</v>
       </c>
       <c r="P803" t="s">
-        <v>2051</v>
+        <v>2090</v>
       </c>
       <c r="Q803">
         <v>0.85</v>
@@ -77188,7 +77188,7 @@
         <v>2674</v>
       </c>
       <c r="P804" t="s">
-        <v>2084</v>
+        <v>2088</v>
       </c>
       <c r="Q804">
         <v>0.85</v>
@@ -77202,7 +77202,7 @@
         <v>2675</v>
       </c>
       <c r="P805" t="s">
-        <v>2089</v>
+        <v>2060</v>
       </c>
       <c r="Q805">
         <v>0.85</v>
@@ -77216,7 +77216,7 @@
         <v>2676</v>
       </c>
       <c r="P806" t="s">
-        <v>2109</v>
+        <v>2105</v>
       </c>
       <c r="Q806">
         <v>0.85</v>
@@ -77230,7 +77230,7 @@
         <v>2677</v>
       </c>
       <c r="P807" t="s">
-        <v>2056</v>
+        <v>2071</v>
       </c>
       <c r="Q807">
         <v>0.85</v>
@@ -77244,7 +77244,7 @@
         <v>2678</v>
       </c>
       <c r="P808" t="s">
-        <v>2093</v>
+        <v>2086</v>
       </c>
       <c r="Q808">
         <v>0.85</v>
@@ -77258,7 +77258,7 @@
         <v>2679</v>
       </c>
       <c r="P809" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="Q809">
         <v>0.85</v>
@@ -77272,7 +77272,7 @@
         <v>2680</v>
       </c>
       <c r="P810" t="s">
-        <v>2055</v>
+        <v>2093</v>
       </c>
       <c r="Q810">
         <v>0.85</v>
@@ -77286,7 +77286,7 @@
         <v>2681</v>
       </c>
       <c r="P811" t="s">
-        <v>2052</v>
+        <v>2093</v>
       </c>
       <c r="Q811">
         <v>0.85</v>
@@ -77300,7 +77300,7 @@
         <v>2682</v>
       </c>
       <c r="P812" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="Q812">
         <v>0.85</v>
@@ -77314,7 +77314,7 @@
         <v>2683</v>
       </c>
       <c r="P813" t="s">
-        <v>2089</v>
+        <v>2071</v>
       </c>
       <c r="Q813">
         <v>0.85</v>
@@ -77328,7 +77328,7 @@
         <v>2684</v>
       </c>
       <c r="P814" t="s">
-        <v>2062</v>
+        <v>2103</v>
       </c>
       <c r="Q814">
         <v>0.85</v>
@@ -77342,7 +77342,7 @@
         <v>2685</v>
       </c>
       <c r="P815" t="s">
-        <v>2086</v>
+        <v>2069</v>
       </c>
       <c r="Q815">
         <v>0.85</v>
@@ -77356,7 +77356,7 @@
         <v>2686</v>
       </c>
       <c r="P816" t="s">
-        <v>2071</v>
+        <v>2065</v>
       </c>
       <c r="Q816">
         <v>0.85</v>
@@ -77370,7 +77370,7 @@
         <v>2687</v>
       </c>
       <c r="P817" t="s">
-        <v>2088</v>
+        <v>2063</v>
       </c>
       <c r="Q817">
         <v>0.85</v>
@@ -77384,7 +77384,7 @@
         <v>2688</v>
       </c>
       <c r="P818" t="s">
-        <v>2057</v>
+        <v>2076</v>
       </c>
       <c r="Q818">
         <v>0.85</v>
@@ -77398,7 +77398,7 @@
         <v>2689</v>
       </c>
       <c r="P819" t="s">
-        <v>2095</v>
+        <v>2076</v>
       </c>
       <c r="Q819">
         <v>0.85</v>
@@ -77412,7 +77412,7 @@
         <v>2690</v>
       </c>
       <c r="P820" t="s">
-        <v>2083</v>
+        <v>2059</v>
       </c>
       <c r="Q820">
         <v>0.85</v>
@@ -77440,7 +77440,7 @@
         <v>2692</v>
       </c>
       <c r="P822" t="s">
-        <v>2103</v>
+        <v>2071</v>
       </c>
       <c r="Q822">
         <v>0.85</v>
@@ -77454,7 +77454,7 @@
         <v>2693</v>
       </c>
       <c r="P823" t="s">
-        <v>2053</v>
+        <v>2103</v>
       </c>
       <c r="Q823">
         <v>0.85</v>
@@ -77468,7 +77468,7 @@
         <v>2694</v>
       </c>
       <c r="P824" t="s">
-        <v>2060</v>
+        <v>2093</v>
       </c>
       <c r="Q824">
         <v>0.85</v>
@@ -77482,7 +77482,7 @@
         <v>2695</v>
       </c>
       <c r="P825" t="s">
-        <v>2060</v>
+        <v>2051</v>
       </c>
       <c r="Q825">
         <v>0.85</v>
@@ -77510,7 +77510,7 @@
         <v>2697</v>
       </c>
       <c r="P827" t="s">
-        <v>2077</v>
+        <v>2063</v>
       </c>
       <c r="Q827">
         <v>0.85</v>
@@ -77524,7 +77524,7 @@
         <v>2698</v>
       </c>
       <c r="P828" t="s">
-        <v>2089</v>
+        <v>2081</v>
       </c>
       <c r="Q828">
         <v>0.85</v>
@@ -77538,7 +77538,7 @@
         <v>2699</v>
       </c>
       <c r="P829" t="s">
-        <v>2098</v>
+        <v>2082</v>
       </c>
       <c r="Q829">
         <v>0.85</v>
@@ -77552,7 +77552,7 @@
         <v>2700</v>
       </c>
       <c r="P830" t="s">
-        <v>2071</v>
+        <v>2108</v>
       </c>
       <c r="Q830">
         <v>0.85</v>
@@ -77566,7 +77566,7 @@
         <v>2701</v>
       </c>
       <c r="P831" t="s">
-        <v>2058</v>
+        <v>2051</v>
       </c>
       <c r="Q831">
         <v>0.85</v>
@@ -77580,7 +77580,7 @@
         <v>2702</v>
       </c>
       <c r="P832" t="s">
-        <v>2092</v>
+        <v>2086</v>
       </c>
       <c r="Q832">
         <v>0.85</v>
@@ -77594,7 +77594,7 @@
         <v>2703</v>
       </c>
       <c r="P833" t="s">
-        <v>2093</v>
+        <v>2098</v>
       </c>
       <c r="Q833">
         <v>0.85</v>
@@ -77608,7 +77608,7 @@
         <v>2704</v>
       </c>
       <c r="P834" t="s">
-        <v>2086</v>
+        <v>2081</v>
       </c>
       <c r="Q834">
         <v>0.85</v>
@@ -77622,7 +77622,7 @@
         <v>2705</v>
       </c>
       <c r="P835" t="s">
-        <v>2075</v>
+        <v>2106</v>
       </c>
       <c r="Q835">
         <v>0.85</v>
@@ -77636,7 +77636,7 @@
         <v>2706</v>
       </c>
       <c r="P836" t="s">
-        <v>2065</v>
+        <v>2083</v>
       </c>
       <c r="Q836">
         <v>0.85</v>
@@ -77650,7 +77650,7 @@
         <v>2707</v>
       </c>
       <c r="P837" t="s">
-        <v>2106</v>
+        <v>2060</v>
       </c>
       <c r="Q837">
         <v>0.85</v>
@@ -77664,7 +77664,7 @@
         <v>2708</v>
       </c>
       <c r="P838" t="s">
-        <v>2103</v>
+        <v>2083</v>
       </c>
       <c r="Q838">
         <v>0.85</v>
@@ -77678,7 +77678,7 @@
         <v>2709</v>
       </c>
       <c r="P839" t="s">
-        <v>2051</v>
+        <v>2093</v>
       </c>
       <c r="Q839">
         <v>0.85</v>
@@ -77692,7 +77692,7 @@
         <v>2710</v>
       </c>
       <c r="P840" t="s">
-        <v>2103</v>
+        <v>2077</v>
       </c>
       <c r="Q840">
         <v>0.85</v>
@@ -77706,7 +77706,7 @@
         <v>2711</v>
       </c>
       <c r="P841" t="s">
-        <v>2071</v>
+        <v>2080</v>
       </c>
       <c r="Q841">
         <v>0.85</v>
@@ -77720,7 +77720,7 @@
         <v>2712</v>
       </c>
       <c r="P842" t="s">
-        <v>2083</v>
+        <v>2077</v>
       </c>
       <c r="Q842">
         <v>0.85</v>
@@ -77734,7 +77734,7 @@
         <v>2713</v>
       </c>
       <c r="P843" t="s">
-        <v>2061</v>
+        <v>2051</v>
       </c>
       <c r="Q843">
         <v>0.85</v>
@@ -77748,7 +77748,7 @@
         <v>2714</v>
       </c>
       <c r="P844" t="s">
-        <v>2065</v>
+        <v>2060</v>
       </c>
       <c r="Q844">
         <v>0.85</v>
@@ -77762,7 +77762,7 @@
         <v>2715</v>
       </c>
       <c r="P845" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="Q845">
         <v>0.85</v>
@@ -77776,7 +77776,7 @@
         <v>2716</v>
       </c>
       <c r="P846" t="s">
-        <v>2103</v>
+        <v>2097</v>
       </c>
       <c r="Q846">
         <v>0.85</v>
@@ -77790,7 +77790,7 @@
         <v>2717</v>
       </c>
       <c r="P847" t="s">
-        <v>2083</v>
+        <v>2101</v>
       </c>
       <c r="Q847">
         <v>0.85</v>
@@ -77804,7 +77804,7 @@
         <v>2718</v>
       </c>
       <c r="P848" t="s">
-        <v>2052</v>
+        <v>2077</v>
       </c>
       <c r="Q848">
         <v>0.85</v>
@@ -77818,7 +77818,7 @@
         <v>2719</v>
       </c>
       <c r="P849" t="s">
-        <v>2069</v>
+        <v>2104</v>
       </c>
       <c r="Q849">
         <v>0.85</v>
@@ -77832,7 +77832,7 @@
         <v>2720</v>
       </c>
       <c r="P850" t="s">
-        <v>2089</v>
+        <v>2101</v>
       </c>
       <c r="Q850">
         <v>0.85</v>
@@ -77846,7 +77846,7 @@
         <v>2721</v>
       </c>
       <c r="P851" t="s">
-        <v>2089</v>
+        <v>2076</v>
       </c>
       <c r="Q851">
         <v>0.85</v>
@@ -77860,7 +77860,7 @@
         <v>2722</v>
       </c>
       <c r="P852" t="s">
-        <v>2055</v>
+        <v>2065</v>
       </c>
       <c r="Q852">
         <v>0.85</v>
@@ -77874,7 +77874,7 @@
         <v>2723</v>
       </c>
       <c r="P853" t="s">
-        <v>2087</v>
+        <v>2076</v>
       </c>
       <c r="Q853">
         <v>0.85</v>
@@ -77888,10 +77888,10 @@
         <v>2724</v>
       </c>
       <c r="P854" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
       <c r="Q854">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="855" spans="14:17" x14ac:dyDescent="0.45">
@@ -77902,10 +77902,10 @@
         <v>2725</v>
       </c>
       <c r="P855" t="s">
-        <v>2058</v>
+        <v>2098</v>
       </c>
       <c r="Q855">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -77914,7 +77914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAA8DE9-CF18-433E-95A3-47C8BAE197CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC3604C6-47F8-4514-9C4F-A6AA9728C6DF}">
   <dimension ref="A1:I287"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
